--- a/docs/CDOP_SCHEMA.xlsx
+++ b/docs/CDOP_SCHEMA.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rockmtnins-my.sharepoint.com/personal/sebastian_weeks_rmi_org/Documents/Documents/CDOP Resources/UseCase_Category CSVs_JSONs/Master Version/1_6_26/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rockmtnins-my.sharepoint.com/personal/sebastian_weeks_rmi_org/Documents/Documents/CDOP Resources/UseCase_Category CSVs_JSONs/Master Version/5_20_26/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="8_{B4C62B60-D2A0-4029-8754-A69B2B15C06E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6C95BECF-65D2-41F1-8BBB-2120DC4AE2DB}"/>
+  <xr:revisionPtr revIDLastSave="170" documentId="8_{836F5BCB-B55D-4CBC-976C-021D78BB22A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9C1D31AF-C3FE-4BD6-93C2-2DB20C3A4D82}"/>
   <bookViews>
-    <workbookView xWindow="-27780" yWindow="1035" windowWidth="26850" windowHeight="12255" activeTab="2" xr2:uid="{743398AF-A4FE-47C4-9368-972E95242EBF}"/>
+    <workbookView xWindow="10" yWindow="10" windowWidth="19180" windowHeight="11260" xr2:uid="{743398AF-A4FE-47C4-9368-972E95242EBF}"/>
   </bookViews>
   <sheets>
     <sheet name="Full List" sheetId="5" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3188" uniqueCount="321">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3184" uniqueCount="317">
   <si>
     <t>schema</t>
   </si>
@@ -991,18 +991,6 @@
   </si>
   <si>
     <t>Indicate the status of project issuance</t>
-  </si>
-  <si>
-    <t>LOCATION DETAILS</t>
-  </si>
-  <si>
-    <t>PROJECT APPROACH &amp; DETAILS</t>
-  </si>
-  <si>
-    <t>ISSUANCES</t>
-  </si>
-  <si>
-    <t>DISCLOSURES</t>
   </si>
 </sst>
 </file>
@@ -1037,6 +1025,7 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -1049,14 +1038,7 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="7" tint="-0.249977111117893"/>
-      <name val="Aptos Narrow"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
@@ -1065,8 +1047,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1089,12 +1077,6 @@
       <patternFill patternType="solid">
         <fgColor theme="0"/>
         <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.79998168889431442"/>
-        <bgColor theme="4" tint="0.79998168889431442"/>
       </patternFill>
     </fill>
   </fills>
@@ -1145,7 +1127,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1174,10 +1156,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -1513,7 +1496,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{752D3095-90A4-45FF-BD20-0492A3C6EFAC}">
-  <dimension ref="A1:L147"/>
+  <dimension ref="A1:L143"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="21.1796875" bestFit="1" customWidth="1"/>
@@ -1567,9 +1550,42 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="3" t="s">
-        <v>317</v>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I2" t="s">
+        <v>19</v>
+      </c>
+      <c r="J2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2" t="s">
+        <v>21</v>
+      </c>
+      <c r="L2" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
@@ -1580,13 +1596,13 @@
         <v>13</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3" t="s">
         <v>14</v>
       </c>
       <c r="E3" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="F3" t="s">
         <v>16</v>
@@ -1607,7 +1623,7 @@
         <v>21</v>
       </c>
       <c r="L3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
@@ -1618,22 +1634,22 @@
         <v>13</v>
       </c>
       <c r="C4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D4" t="s">
         <v>14</v>
       </c>
       <c r="E4" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F4" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="G4" t="s">
         <v>17</v>
       </c>
       <c r="H4" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="I4" t="s">
         <v>19</v>
@@ -1645,7 +1661,7 @@
         <v>21</v>
       </c>
       <c r="L4" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.35">
@@ -1656,22 +1672,22 @@
         <v>13</v>
       </c>
       <c r="C5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D5" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="E5" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="F5" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="G5" t="s">
         <v>17</v>
       </c>
       <c r="H5" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="I5" t="s">
         <v>19</v>
@@ -1683,7 +1699,7 @@
         <v>21</v>
       </c>
       <c r="L5" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
@@ -1694,13 +1710,13 @@
         <v>13</v>
       </c>
       <c r="C6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D6" t="s">
         <v>29</v>
       </c>
       <c r="E6" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="F6" t="s">
         <v>16</v>
@@ -1721,7 +1737,7 @@
         <v>21</v>
       </c>
       <c r="L6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
@@ -1732,22 +1748,22 @@
         <v>13</v>
       </c>
       <c r="C7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D7" t="s">
         <v>29</v>
       </c>
       <c r="E7" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F7" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="G7" t="s">
         <v>17</v>
       </c>
       <c r="H7" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="I7" t="s">
         <v>19</v>
@@ -1759,7 +1775,7 @@
         <v>21</v>
       </c>
       <c r="L7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.35">
@@ -1770,22 +1786,22 @@
         <v>13</v>
       </c>
       <c r="C8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D8" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E8" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="F8" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="G8" t="s">
         <v>17</v>
       </c>
       <c r="H8" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="I8" t="s">
         <v>19</v>
@@ -1797,7 +1813,7 @@
         <v>21</v>
       </c>
       <c r="L8" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.35">
@@ -1808,22 +1824,22 @@
         <v>13</v>
       </c>
       <c r="C9">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D9" t="s">
         <v>33</v>
       </c>
       <c r="E9" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="F9" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="G9" t="s">
         <v>17</v>
       </c>
       <c r="H9" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="I9" t="s">
         <v>19</v>
@@ -1835,7 +1851,7 @@
         <v>21</v>
       </c>
       <c r="L9" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.35">
@@ -1846,13 +1862,13 @@
         <v>13</v>
       </c>
       <c r="C10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D10" t="s">
         <v>33</v>
       </c>
       <c r="E10" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F10" t="s">
         <v>26</v>
@@ -1873,7 +1889,7 @@
         <v>21</v>
       </c>
       <c r="L10" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.35">
@@ -1884,22 +1900,22 @@
         <v>13</v>
       </c>
       <c r="C11">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D11" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E11" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="F11" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="G11" t="s">
         <v>17</v>
       </c>
       <c r="H11" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="I11" t="s">
         <v>19</v>
@@ -1911,7 +1927,7 @@
         <v>21</v>
       </c>
       <c r="L11" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.35">
@@ -1922,22 +1938,22 @@
         <v>13</v>
       </c>
       <c r="C12">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D12" t="s">
         <v>37</v>
       </c>
       <c r="E12" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="F12" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="G12" t="s">
         <v>17</v>
       </c>
       <c r="H12" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="I12" t="s">
         <v>19</v>
@@ -1949,7 +1965,7 @@
         <v>21</v>
       </c>
       <c r="L12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.35">
@@ -1960,13 +1976,13 @@
         <v>13</v>
       </c>
       <c r="C13">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D13" t="s">
         <v>37</v>
       </c>
       <c r="E13" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F13" t="s">
         <v>26</v>
@@ -1987,7 +2003,7 @@
         <v>21</v>
       </c>
       <c r="L13" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.35">
@@ -1998,34 +2014,34 @@
         <v>13</v>
       </c>
       <c r="C14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D14" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="E14" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="F14" t="s">
         <v>26</v>
       </c>
       <c r="G14" t="s">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="H14" t="s">
         <v>27</v>
       </c>
       <c r="I14" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="J14" t="s">
         <v>20</v>
       </c>
       <c r="K14" t="s">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="L14" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.35">
@@ -2036,10 +2052,10 @@
         <v>13</v>
       </c>
       <c r="C15">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D15" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="E15" t="s">
         <v>15</v>
@@ -2063,7 +2079,7 @@
         <v>44</v>
       </c>
       <c r="L15" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.35">
@@ -2074,13 +2090,13 @@
         <v>13</v>
       </c>
       <c r="C16">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D16" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E16" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="F16" t="s">
         <v>26</v>
@@ -2101,7 +2117,7 @@
         <v>44</v>
       </c>
       <c r="L16" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.35">
@@ -2112,10 +2128,10 @@
         <v>13</v>
       </c>
       <c r="C17">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D17" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="E17" t="s">
         <v>23</v>
@@ -2139,7 +2155,7 @@
         <v>44</v>
       </c>
       <c r="L17" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.35">
@@ -2150,13 +2166,13 @@
         <v>13</v>
       </c>
       <c r="C18">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D18" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E18" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F18" t="s">
         <v>26</v>
@@ -2177,7 +2193,7 @@
         <v>44</v>
       </c>
       <c r="L18" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.35">
@@ -2188,10 +2204,10 @@
         <v>13</v>
       </c>
       <c r="C19">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D19" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="E19" t="s">
         <v>25</v>
@@ -2215,7 +2231,7 @@
         <v>44</v>
       </c>
       <c r="L19" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.35">
@@ -2226,13 +2242,13 @@
         <v>13</v>
       </c>
       <c r="C20">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D20" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="E20" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="F20" t="s">
         <v>26</v>
@@ -2244,7 +2260,7 @@
         <v>27</v>
       </c>
       <c r="I20" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="J20" t="s">
         <v>20</v>
@@ -2253,7 +2269,7 @@
         <v>44</v>
       </c>
       <c r="L20" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.35">
@@ -2264,13 +2280,13 @@
         <v>13</v>
       </c>
       <c r="C21">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D21" t="s">
         <v>52</v>
       </c>
       <c r="E21" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="F21" t="s">
         <v>26</v>
@@ -2291,7 +2307,7 @@
         <v>44</v>
       </c>
       <c r="L21" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.35">
@@ -2302,13 +2318,13 @@
         <v>13</v>
       </c>
       <c r="C22">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D22" t="s">
         <v>52</v>
       </c>
       <c r="E22" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F22" t="s">
         <v>26</v>
@@ -2329,7 +2345,7 @@
         <v>44</v>
       </c>
       <c r="L22" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.35">
@@ -2340,25 +2356,25 @@
         <v>13</v>
       </c>
       <c r="C23">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D23" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="E23" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="F23" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="G23" t="s">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="H23" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="I23" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="J23" t="s">
         <v>20</v>
@@ -2367,7 +2383,7 @@
         <v>44</v>
       </c>
       <c r="L23" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.35">
@@ -2378,22 +2394,22 @@
         <v>13</v>
       </c>
       <c r="C24">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D24" t="s">
         <v>56</v>
       </c>
       <c r="E24" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="F24" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="G24" t="s">
         <v>17</v>
       </c>
       <c r="H24" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="I24" t="s">
         <v>43</v>
@@ -2405,7 +2421,7 @@
         <v>44</v>
       </c>
       <c r="L24" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.35">
@@ -2416,13 +2432,13 @@
         <v>13</v>
       </c>
       <c r="C25">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D25" t="s">
         <v>56</v>
       </c>
       <c r="E25" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F25" t="s">
         <v>26</v>
@@ -2443,7 +2459,7 @@
         <v>44</v>
       </c>
       <c r="L25" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.35">
@@ -2454,22 +2470,22 @@
         <v>13</v>
       </c>
       <c r="C26">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D26" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="E26" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="F26" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="G26" t="s">
         <v>17</v>
       </c>
       <c r="H26" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="I26" t="s">
         <v>43</v>
@@ -2481,7 +2497,7 @@
         <v>44</v>
       </c>
       <c r="L26" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.35">
@@ -2492,22 +2508,22 @@
         <v>13</v>
       </c>
       <c r="C27">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D27" t="s">
         <v>60</v>
       </c>
       <c r="E27" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="F27" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="G27" t="s">
         <v>17</v>
       </c>
       <c r="H27" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="I27" t="s">
         <v>43</v>
@@ -2519,7 +2535,7 @@
         <v>44</v>
       </c>
       <c r="L27" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.35">
@@ -2530,13 +2546,13 @@
         <v>13</v>
       </c>
       <c r="C28">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D28" t="s">
         <v>60</v>
       </c>
       <c r="E28" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F28" t="s">
         <v>26</v>
@@ -2557,7 +2573,7 @@
         <v>44</v>
       </c>
       <c r="L28" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.35">
@@ -2568,19 +2584,19 @@
         <v>13</v>
       </c>
       <c r="C29">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D29" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E29" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="F29" t="s">
         <v>26</v>
       </c>
       <c r="G29" t="s">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="H29" t="s">
         <v>27</v>
@@ -2595,7 +2611,7 @@
         <v>44</v>
       </c>
       <c r="L29" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.35">
@@ -2606,13 +2622,13 @@
         <v>13</v>
       </c>
       <c r="C30">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D30" t="s">
         <v>64</v>
       </c>
       <c r="E30" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="F30" t="s">
         <v>26</v>
@@ -2633,7 +2649,7 @@
         <v>44</v>
       </c>
       <c r="L30" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.35">
@@ -2644,13 +2660,13 @@
         <v>13</v>
       </c>
       <c r="C31">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D31" t="s">
         <v>64</v>
       </c>
       <c r="E31" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F31" t="s">
         <v>26</v>
@@ -2671,7 +2687,7 @@
         <v>44</v>
       </c>
       <c r="L31" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.35">
@@ -2682,13 +2698,13 @@
         <v>13</v>
       </c>
       <c r="C32">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D32" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="E32" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="F32" t="s">
         <v>26</v>
@@ -2709,7 +2725,7 @@
         <v>44</v>
       </c>
       <c r="L32" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.35">
@@ -2720,13 +2736,13 @@
         <v>13</v>
       </c>
       <c r="C33">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D33" t="s">
         <v>68</v>
       </c>
       <c r="E33" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="F33" t="s">
         <v>26</v>
@@ -2747,7 +2763,7 @@
         <v>44</v>
       </c>
       <c r="L33" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.35">
@@ -2758,13 +2774,13 @@
         <v>13</v>
       </c>
       <c r="C34">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D34" t="s">
         <v>68</v>
       </c>
       <c r="E34" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F34" t="s">
         <v>26</v>
@@ -2785,7 +2801,7 @@
         <v>44</v>
       </c>
       <c r="L34" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.35">
@@ -2796,22 +2812,22 @@
         <v>13</v>
       </c>
       <c r="C35">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D35" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="E35" t="s">
-        <v>25</v>
+        <v>73</v>
       </c>
       <c r="F35" t="s">
-        <v>26</v>
+        <v>74</v>
       </c>
       <c r="G35" t="s">
         <v>42</v>
       </c>
       <c r="H35" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="I35" t="s">
         <v>43</v>
@@ -2820,10 +2836,10 @@
         <v>20</v>
       </c>
       <c r="K35" t="s">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="L35" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.35">
@@ -2834,21 +2850,21 @@
         <v>13</v>
       </c>
       <c r="C36">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D36" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="E36" t="s">
         <v>73</v>
       </c>
-      <c r="F36" t="s">
+      <c r="F36" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="G36" t="s">
-        <v>42</v>
-      </c>
-      <c r="H36" t="s">
+      <c r="G36" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="H36" s="4" t="s">
         <v>18</v>
       </c>
       <c r="I36" t="s">
@@ -2861,7 +2877,7 @@
         <v>21</v>
       </c>
       <c r="L36" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.35">
@@ -2872,25 +2888,25 @@
         <v>13</v>
       </c>
       <c r="C37">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D37" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E37" t="s">
         <v>73</v>
       </c>
-      <c r="F37" s="4" t="s">
+      <c r="F37" t="s">
         <v>74</v>
       </c>
-      <c r="G37" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="H37" s="4" t="s">
+      <c r="G37" t="s">
+        <v>79</v>
+      </c>
+      <c r="H37" t="s">
         <v>18</v>
       </c>
       <c r="I37" t="s">
-        <v>43</v>
+        <v>80</v>
       </c>
       <c r="J37" t="s">
         <v>20</v>
@@ -2899,7 +2915,7 @@
         <v>21</v>
       </c>
       <c r="L37" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.35">
@@ -2910,34 +2926,34 @@
         <v>13</v>
       </c>
       <c r="C38">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D38" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="E38" t="s">
         <v>73</v>
       </c>
       <c r="F38" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="G38" t="s">
         <v>79</v>
       </c>
       <c r="H38" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="I38" t="s">
         <v>80</v>
       </c>
       <c r="J38" t="s">
-        <v>20</v>
+        <v>84</v>
       </c>
       <c r="K38" t="s">
         <v>21</v>
       </c>
       <c r="L38" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.35">
@@ -2948,22 +2964,22 @@
         <v>13</v>
       </c>
       <c r="C39">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D39" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="E39" t="s">
         <v>73</v>
       </c>
       <c r="F39" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="G39" t="s">
-        <v>79</v>
+        <v>17</v>
       </c>
       <c r="H39" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="I39" t="s">
         <v>80</v>
@@ -2975,7 +2991,7 @@
         <v>21</v>
       </c>
       <c r="L39" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.35">
@@ -2986,10 +3002,10 @@
         <v>13</v>
       </c>
       <c r="C40">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D40" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E40" t="s">
         <v>73</v>
@@ -2998,7 +3014,7 @@
         <v>74</v>
       </c>
       <c r="G40" t="s">
-        <v>17</v>
+        <v>79</v>
       </c>
       <c r="H40" t="s">
         <v>18</v>
@@ -3007,13 +3023,13 @@
         <v>80</v>
       </c>
       <c r="J40" t="s">
-        <v>84</v>
+        <v>20</v>
       </c>
       <c r="K40" t="s">
         <v>21</v>
       </c>
       <c r="L40" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.35">
@@ -3024,22 +3040,22 @@
         <v>13</v>
       </c>
       <c r="C41">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D41" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E41" t="s">
         <v>73</v>
       </c>
       <c r="F41" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="G41" t="s">
         <v>79</v>
       </c>
       <c r="H41" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="I41" t="s">
         <v>80</v>
@@ -3051,7 +3067,7 @@
         <v>21</v>
       </c>
       <c r="L41" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.35">
@@ -3062,10 +3078,10 @@
         <v>13</v>
       </c>
       <c r="C42">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D42" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E42" t="s">
         <v>73</v>
@@ -3089,7 +3105,7 @@
         <v>21</v>
       </c>
       <c r="L42" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.35">
@@ -3100,25 +3116,25 @@
         <v>13</v>
       </c>
       <c r="C43">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D43" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E43" t="s">
         <v>73</v>
       </c>
       <c r="F43" t="s">
-        <v>83</v>
+        <v>16</v>
       </c>
       <c r="G43" t="s">
-        <v>79</v>
-      </c>
-      <c r="H43" t="s">
+        <v>17</v>
+      </c>
+      <c r="H43" s="4" t="s">
         <v>27</v>
       </c>
       <c r="I43" t="s">
-        <v>80</v>
+        <v>19</v>
       </c>
       <c r="J43" t="s">
         <v>20</v>
@@ -3127,7 +3143,7 @@
         <v>21</v>
       </c>
       <c r="L43" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.35">
@@ -3138,16 +3154,16 @@
         <v>13</v>
       </c>
       <c r="C44">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D44" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E44" t="s">
         <v>73</v>
       </c>
-      <c r="F44" t="s">
-        <v>16</v>
+      <c r="F44" s="4" t="s">
+        <v>74</v>
       </c>
       <c r="G44" t="s">
         <v>17</v>
@@ -3165,7 +3181,7 @@
         <v>21</v>
       </c>
       <c r="L44" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.35">
@@ -3176,42 +3192,73 @@
         <v>13</v>
       </c>
       <c r="C45">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D45" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E45" t="s">
-        <v>73</v>
-      </c>
-      <c r="F45" s="4" t="s">
-        <v>74</v>
+        <v>99</v>
+      </c>
+      <c r="F45" t="s">
+        <v>26</v>
       </c>
       <c r="G45" t="s">
-        <v>17</v>
-      </c>
-      <c r="H45" s="4" t="s">
-        <v>27</v>
+        <v>100</v>
+      </c>
+      <c r="H45" t="s">
+        <v>101</v>
       </c>
       <c r="I45" t="s">
         <v>19</v>
       </c>
       <c r="J45" t="s">
-        <v>20</v>
+        <v>102</v>
       </c>
       <c r="K45" t="s">
-        <v>21</v>
+        <v>103</v>
       </c>
       <c r="L45" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A46" s="15" t="s">
-        <v>318</v>
-      </c>
-      <c r="F46" s="4"/>
-      <c r="H46" s="4"/>
+      <c r="A46" t="s">
+        <v>12</v>
+      </c>
+      <c r="B46" t="s">
+        <v>13</v>
+      </c>
+      <c r="C46">
+        <v>45</v>
+      </c>
+      <c r="D46" t="s">
+        <v>105</v>
+      </c>
+      <c r="E46" t="s">
+        <v>99</v>
+      </c>
+      <c r="F46" t="s">
+        <v>26</v>
+      </c>
+      <c r="G46" t="s">
+        <v>100</v>
+      </c>
+      <c r="H46" t="s">
+        <v>101</v>
+      </c>
+      <c r="I46" t="s">
+        <v>19</v>
+      </c>
+      <c r="J46" t="s">
+        <v>102</v>
+      </c>
+      <c r="K46" t="s">
+        <v>103</v>
+      </c>
+      <c r="L46" t="s">
+        <v>106</v>
+      </c>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
@@ -3221,19 +3268,19 @@
         <v>13</v>
       </c>
       <c r="C47">
-        <v>1</v>
+        <v>46</v>
       </c>
       <c r="D47" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="E47" t="s">
         <v>99</v>
       </c>
       <c r="F47" t="s">
-        <v>26</v>
+        <v>83</v>
       </c>
       <c r="G47" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="H47" t="s">
         <v>101</v>
@@ -3248,7 +3295,7 @@
         <v>103</v>
       </c>
       <c r="L47" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.35">
@@ -3259,20 +3306,19 @@
         <v>13</v>
       </c>
       <c r="C48">
-        <f>C47+1</f>
-        <v>2</v>
+        <v>47</v>
       </c>
       <c r="D48" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="E48" t="s">
         <v>99</v>
       </c>
       <c r="F48" t="s">
-        <v>26</v>
+        <v>83</v>
       </c>
       <c r="G48" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="H48" t="s">
         <v>101</v>
@@ -3281,13 +3327,13 @@
         <v>19</v>
       </c>
       <c r="J48" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="K48" t="s">
         <v>103</v>
       </c>
       <c r="L48" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.35">
@@ -3298,20 +3344,19 @@
         <v>13</v>
       </c>
       <c r="C49">
-        <f t="shared" ref="C49:C88" si="0">C48+1</f>
-        <v>3</v>
+        <v>48</v>
       </c>
       <c r="D49" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="E49" t="s">
-        <v>99</v>
+        <v>113</v>
       </c>
       <c r="F49" t="s">
-        <v>83</v>
+        <v>114</v>
       </c>
       <c r="G49" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="H49" t="s">
         <v>101</v>
@@ -3326,7 +3371,7 @@
         <v>103</v>
       </c>
       <c r="L49" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.35">
@@ -3337,17 +3382,16 @@
         <v>13</v>
       </c>
       <c r="C50">
-        <f t="shared" si="0"/>
-        <v>4</v>
+        <v>49</v>
       </c>
       <c r="D50" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="E50" t="s">
-        <v>99</v>
+        <v>113</v>
       </c>
       <c r="F50" t="s">
-        <v>83</v>
+        <v>26</v>
       </c>
       <c r="G50" t="s">
         <v>108</v>
@@ -3359,13 +3403,13 @@
         <v>19</v>
       </c>
       <c r="J50" t="s">
-        <v>111</v>
+        <v>102</v>
       </c>
       <c r="K50" t="s">
         <v>103</v>
       </c>
       <c r="L50" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.35">
@@ -3376,20 +3420,19 @@
         <v>13</v>
       </c>
       <c r="C51">
-        <f t="shared" si="0"/>
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="D51" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="E51" t="s">
         <v>113</v>
       </c>
       <c r="F51" t="s">
-        <v>114</v>
+        <v>26</v>
       </c>
       <c r="G51" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="H51" t="s">
         <v>101</v>
@@ -3398,13 +3441,13 @@
         <v>19</v>
       </c>
       <c r="J51" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="K51" t="s">
         <v>103</v>
       </c>
       <c r="L51" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.35">
@@ -3415,11 +3458,10 @@
         <v>13</v>
       </c>
       <c r="C52">
-        <f t="shared" si="0"/>
-        <v>6</v>
+        <v>51</v>
       </c>
       <c r="D52" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="E52" t="s">
         <v>113</v>
@@ -3437,13 +3479,13 @@
         <v>19</v>
       </c>
       <c r="J52" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="K52" t="s">
         <v>103</v>
       </c>
       <c r="L52" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.35">
@@ -3454,35 +3496,34 @@
         <v>13</v>
       </c>
       <c r="C53">
-        <f t="shared" si="0"/>
-        <v>7</v>
+        <v>52</v>
       </c>
       <c r="D53" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="E53" t="s">
-        <v>113</v>
+        <v>15</v>
       </c>
       <c r="F53" t="s">
-        <v>26</v>
+        <v>74</v>
       </c>
       <c r="G53" t="s">
         <v>108</v>
       </c>
       <c r="H53" t="s">
-        <v>101</v>
+        <v>123</v>
       </c>
       <c r="I53" t="s">
         <v>19</v>
       </c>
       <c r="J53" t="s">
-        <v>111</v>
+        <v>102</v>
       </c>
       <c r="K53" t="s">
         <v>103</v>
       </c>
       <c r="L53" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.35">
@@ -3493,20 +3534,19 @@
         <v>13</v>
       </c>
       <c r="C54">
-        <f t="shared" si="0"/>
-        <v>8</v>
+        <v>53</v>
       </c>
       <c r="D54" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="E54" t="s">
-        <v>113</v>
+        <v>15</v>
       </c>
       <c r="F54" t="s">
         <v>26</v>
       </c>
       <c r="G54" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="H54" t="s">
         <v>101</v>
@@ -3515,13 +3555,13 @@
         <v>19</v>
       </c>
       <c r="J54" t="s">
-        <v>111</v>
+        <v>102</v>
       </c>
       <c r="K54" t="s">
         <v>103</v>
       </c>
       <c r="L54" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.35">
@@ -3532,23 +3572,22 @@
         <v>13</v>
       </c>
       <c r="C55">
-        <f t="shared" si="0"/>
-        <v>9</v>
+        <v>54</v>
       </c>
       <c r="D55" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="E55" t="s">
         <v>15</v>
       </c>
       <c r="F55" t="s">
-        <v>74</v>
+        <v>26</v>
       </c>
       <c r="G55" t="s">
         <v>108</v>
       </c>
       <c r="H55" t="s">
-        <v>123</v>
+        <v>101</v>
       </c>
       <c r="I55" t="s">
         <v>19</v>
@@ -3560,7 +3599,7 @@
         <v>103</v>
       </c>
       <c r="L55" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.35">
@@ -3571,23 +3610,22 @@
         <v>13</v>
       </c>
       <c r="C56">
-        <f t="shared" si="0"/>
-        <v>10</v>
+        <v>55</v>
       </c>
       <c r="D56" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="E56" t="s">
         <v>15</v>
       </c>
       <c r="F56" t="s">
-        <v>26</v>
+        <v>74</v>
       </c>
       <c r="G56" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="H56" t="s">
-        <v>101</v>
+        <v>123</v>
       </c>
       <c r="I56" t="s">
         <v>19</v>
@@ -3599,7 +3637,7 @@
         <v>103</v>
       </c>
       <c r="L56" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.35">
@@ -3610,17 +3648,16 @@
         <v>13</v>
       </c>
       <c r="C57">
-        <f t="shared" si="0"/>
-        <v>11</v>
+        <v>56</v>
       </c>
       <c r="D57" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="E57" t="s">
         <v>15</v>
       </c>
       <c r="F57" t="s">
-        <v>26</v>
+        <v>83</v>
       </c>
       <c r="G57" t="s">
         <v>108</v>
@@ -3637,8 +3674,8 @@
       <c r="K57" t="s">
         <v>103</v>
       </c>
-      <c r="L57" t="s">
-        <v>128</v>
+      <c r="L57" s="8" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.35">
@@ -3649,23 +3686,22 @@
         <v>13</v>
       </c>
       <c r="C58">
-        <f t="shared" si="0"/>
-        <v>12</v>
+        <v>57</v>
       </c>
       <c r="D58" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="E58" t="s">
         <v>15</v>
       </c>
       <c r="F58" t="s">
-        <v>74</v>
+        <v>26</v>
       </c>
       <c r="G58" t="s">
         <v>108</v>
       </c>
       <c r="H58" t="s">
-        <v>123</v>
+        <v>101</v>
       </c>
       <c r="I58" t="s">
         <v>19</v>
@@ -3676,8 +3712,8 @@
       <c r="K58" t="s">
         <v>103</v>
       </c>
-      <c r="L58" t="s">
-        <v>130</v>
+      <c r="L58" s="8" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.35">
@@ -3688,11 +3724,10 @@
         <v>13</v>
       </c>
       <c r="C59">
-        <f t="shared" si="0"/>
-        <v>13</v>
+        <v>58</v>
       </c>
       <c r="D59" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="E59" t="s">
         <v>15</v>
@@ -3701,7 +3736,7 @@
         <v>83</v>
       </c>
       <c r="G59" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="H59" t="s">
         <v>101</v>
@@ -3715,8 +3750,8 @@
       <c r="K59" t="s">
         <v>103</v>
       </c>
-      <c r="L59" s="8" t="s">
-        <v>132</v>
+      <c r="L59" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.35">
@@ -3727,11 +3762,10 @@
         <v>13</v>
       </c>
       <c r="C60">
-        <f t="shared" si="0"/>
-        <v>14</v>
+        <v>59</v>
       </c>
       <c r="D60" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="E60" t="s">
         <v>15</v>
@@ -3740,7 +3774,7 @@
         <v>26</v>
       </c>
       <c r="G60" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="H60" t="s">
         <v>101</v>
@@ -3754,8 +3788,8 @@
       <c r="K60" t="s">
         <v>103</v>
       </c>
-      <c r="L60" s="8" t="s">
-        <v>134</v>
+      <c r="L60" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.35">
@@ -3766,17 +3800,16 @@
         <v>13</v>
       </c>
       <c r="C61">
-        <f t="shared" si="0"/>
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="D61" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="E61" t="s">
         <v>15</v>
       </c>
       <c r="F61" t="s">
-        <v>83</v>
+        <v>26</v>
       </c>
       <c r="G61" t="s">
         <v>100</v>
@@ -3794,7 +3827,7 @@
         <v>103</v>
       </c>
       <c r="L61" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.35">
@@ -3805,11 +3838,10 @@
         <v>13</v>
       </c>
       <c r="C62">
-        <f t="shared" si="0"/>
-        <v>16</v>
+        <v>61</v>
       </c>
       <c r="D62" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="E62" t="s">
         <v>15</v>
@@ -3833,7 +3865,7 @@
         <v>103</v>
       </c>
       <c r="L62" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.35">
@@ -3844,11 +3876,10 @@
         <v>13</v>
       </c>
       <c r="C63">
-        <f t="shared" si="0"/>
-        <v>17</v>
+        <v>62</v>
       </c>
       <c r="D63" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="E63" t="s">
         <v>15</v>
@@ -3872,7 +3903,7 @@
         <v>103</v>
       </c>
       <c r="L63" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.35">
@@ -3883,20 +3914,19 @@
         <v>13</v>
       </c>
       <c r="C64">
-        <f t="shared" si="0"/>
-        <v>18</v>
+        <v>63</v>
       </c>
       <c r="D64" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="E64" t="s">
         <v>15</v>
       </c>
       <c r="F64" t="s">
-        <v>26</v>
+        <v>83</v>
       </c>
       <c r="G64" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="H64" t="s">
         <v>101</v>
@@ -3911,7 +3941,7 @@
         <v>103</v>
       </c>
       <c r="L64" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.35">
@@ -3922,35 +3952,34 @@
         <v>13</v>
       </c>
       <c r="C65">
-        <f t="shared" si="0"/>
-        <v>19</v>
+        <v>64</v>
       </c>
       <c r="D65" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="E65" t="s">
         <v>15</v>
       </c>
       <c r="F65" t="s">
-        <v>26</v>
+        <v>74</v>
       </c>
       <c r="G65" t="s">
         <v>100</v>
       </c>
       <c r="H65" t="s">
-        <v>101</v>
+        <v>123</v>
       </c>
       <c r="I65" t="s">
         <v>19</v>
       </c>
       <c r="J65" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="K65" t="s">
         <v>103</v>
       </c>
-      <c r="L65" t="s">
-        <v>144</v>
+      <c r="L65" s="8" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.35">
@@ -3961,35 +3990,34 @@
         <v>13</v>
       </c>
       <c r="C66">
-        <f t="shared" si="0"/>
-        <v>20</v>
+        <v>65</v>
       </c>
       <c r="D66" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="E66" t="s">
         <v>15</v>
       </c>
       <c r="F66" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="G66" t="s">
-        <v>108</v>
+        <v>150</v>
       </c>
       <c r="H66" t="s">
-        <v>101</v>
+        <v>123</v>
       </c>
       <c r="I66" t="s">
         <v>19</v>
       </c>
       <c r="J66" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="K66" t="s">
         <v>103</v>
       </c>
-      <c r="L66" t="s">
-        <v>146</v>
+      <c r="L66" s="8" t="s">
+        <v>151</v>
       </c>
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.35">
@@ -4000,35 +4028,34 @@
         <v>13</v>
       </c>
       <c r="C67">
-        <f t="shared" si="0"/>
-        <v>21</v>
+        <v>66</v>
       </c>
       <c r="D67" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="E67" t="s">
         <v>15</v>
       </c>
       <c r="F67" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="G67" t="s">
-        <v>100</v>
+        <v>153</v>
       </c>
       <c r="H67" t="s">
-        <v>123</v>
+        <v>101</v>
       </c>
       <c r="I67" t="s">
         <v>19</v>
       </c>
       <c r="J67" t="s">
-        <v>111</v>
+        <v>102</v>
       </c>
       <c r="K67" t="s">
         <v>103</v>
       </c>
-      <c r="L67" s="8" t="s">
-        <v>148</v>
+      <c r="L67" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.35">
@@ -4039,35 +4066,34 @@
         <v>13</v>
       </c>
       <c r="C68">
-        <f t="shared" si="0"/>
-        <v>22</v>
+        <v>67</v>
       </c>
       <c r="D68" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="E68" t="s">
         <v>15</v>
       </c>
       <c r="F68" t="s">
-        <v>74</v>
+        <v>26</v>
       </c>
       <c r="G68" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="H68" t="s">
-        <v>123</v>
+        <v>101</v>
       </c>
       <c r="I68" t="s">
         <v>19</v>
       </c>
       <c r="J68" t="s">
-        <v>111</v>
+        <v>102</v>
       </c>
       <c r="K68" t="s">
         <v>103</v>
       </c>
-      <c r="L68" s="8" t="s">
-        <v>151</v>
+      <c r="L68" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.35">
@@ -4078,11 +4104,10 @@
         <v>13</v>
       </c>
       <c r="C69">
-        <f t="shared" si="0"/>
-        <v>23</v>
+        <v>68</v>
       </c>
       <c r="D69" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="E69" t="s">
         <v>15</v>
@@ -4091,7 +4116,7 @@
         <v>83</v>
       </c>
       <c r="G69" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="H69" t="s">
         <v>101</v>
@@ -4106,7 +4131,7 @@
         <v>103</v>
       </c>
       <c r="L69" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.35">
@@ -4117,20 +4142,19 @@
         <v>13</v>
       </c>
       <c r="C70">
-        <f t="shared" si="0"/>
-        <v>24</v>
+        <v>69</v>
       </c>
       <c r="D70" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="E70" t="s">
         <v>15</v>
       </c>
       <c r="F70" t="s">
-        <v>26</v>
+        <v>83</v>
       </c>
       <c r="G70" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="H70" t="s">
         <v>101</v>
@@ -4145,7 +4169,7 @@
         <v>103</v>
       </c>
       <c r="L70" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.35">
@@ -4156,20 +4180,19 @@
         <v>13</v>
       </c>
       <c r="C71">
-        <f t="shared" si="0"/>
-        <v>25</v>
+        <v>70</v>
       </c>
       <c r="D71" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="E71" t="s">
         <v>15</v>
       </c>
       <c r="F71" t="s">
-        <v>83</v>
+        <v>26</v>
       </c>
       <c r="G71" t="s">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="H71" t="s">
         <v>101</v>
@@ -4183,8 +4206,8 @@
       <c r="K71" t="s">
         <v>103</v>
       </c>
-      <c r="L71" t="s">
-        <v>158</v>
+      <c r="L71" s="8" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.35">
@@ -4195,20 +4218,19 @@
         <v>13</v>
       </c>
       <c r="C72">
-        <f t="shared" si="0"/>
-        <v>26</v>
+        <v>71</v>
       </c>
       <c r="D72" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="E72" t="s">
         <v>15</v>
       </c>
       <c r="F72" t="s">
-        <v>83</v>
+        <v>26</v>
       </c>
       <c r="G72" t="s">
-        <v>150</v>
+        <v>108</v>
       </c>
       <c r="H72" t="s">
         <v>101</v>
@@ -4222,8 +4244,8 @@
       <c r="K72" t="s">
         <v>103</v>
       </c>
-      <c r="L72" t="s">
-        <v>160</v>
+      <c r="L72" s="8" t="s">
+        <v>164</v>
       </c>
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.35">
@@ -4234,23 +4256,22 @@
         <v>13</v>
       </c>
       <c r="C73">
-        <f t="shared" si="0"/>
-        <v>27</v>
+        <v>72</v>
       </c>
       <c r="D73" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="E73" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="F73" t="s">
-        <v>26</v>
+        <v>74</v>
       </c>
       <c r="G73" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="H73" t="s">
-        <v>101</v>
+        <v>123</v>
       </c>
       <c r="I73" t="s">
         <v>19</v>
@@ -4261,8 +4282,8 @@
       <c r="K73" t="s">
         <v>103</v>
       </c>
-      <c r="L73" s="8" t="s">
-        <v>162</v>
+      <c r="L73" t="s">
+        <v>166</v>
       </c>
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.35">
@@ -4273,17 +4294,16 @@
         <v>13</v>
       </c>
       <c r="C74">
-        <f t="shared" si="0"/>
-        <v>28</v>
+        <v>73</v>
       </c>
       <c r="D74" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="E74" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="F74" t="s">
-        <v>26</v>
+        <v>83</v>
       </c>
       <c r="G74" t="s">
         <v>108</v>
@@ -4300,8 +4320,8 @@
       <c r="K74" t="s">
         <v>103</v>
       </c>
-      <c r="L74" s="8" t="s">
-        <v>164</v>
+      <c r="L74" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.35">
@@ -4312,23 +4332,22 @@
         <v>13</v>
       </c>
       <c r="C75">
-        <f t="shared" si="0"/>
-        <v>29</v>
+        <v>74</v>
       </c>
       <c r="D75" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="E75" t="s">
         <v>23</v>
       </c>
       <c r="F75" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="G75" t="s">
         <v>108</v>
       </c>
       <c r="H75" t="s">
-        <v>123</v>
+        <v>101</v>
       </c>
       <c r="I75" t="s">
         <v>19</v>
@@ -4340,7 +4359,7 @@
         <v>103</v>
       </c>
       <c r="L75" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.35">
@@ -4351,11 +4370,10 @@
         <v>13</v>
       </c>
       <c r="C76">
-        <f t="shared" si="0"/>
-        <v>30</v>
+        <v>75</v>
       </c>
       <c r="D76" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="E76" t="s">
         <v>23</v>
@@ -4379,7 +4397,7 @@
         <v>103</v>
       </c>
       <c r="L76" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.35">
@@ -4390,20 +4408,19 @@
         <v>13</v>
       </c>
       <c r="C77">
-        <f t="shared" si="0"/>
-        <v>31</v>
+        <v>76</v>
       </c>
       <c r="D77" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="E77" t="s">
         <v>23</v>
       </c>
       <c r="F77" t="s">
-        <v>83</v>
+        <v>26</v>
       </c>
       <c r="G77" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="H77" t="s">
         <v>101</v>
@@ -4418,7 +4435,7 @@
         <v>103</v>
       </c>
       <c r="L77" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.35">
@@ -4429,17 +4446,16 @@
         <v>13</v>
       </c>
       <c r="C78">
-        <f t="shared" si="0"/>
-        <v>32</v>
+        <v>77</v>
       </c>
       <c r="D78" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="E78" t="s">
         <v>23</v>
       </c>
       <c r="F78" t="s">
-        <v>83</v>
+        <v>26</v>
       </c>
       <c r="G78" t="s">
         <v>108</v>
@@ -4457,7 +4473,7 @@
         <v>103</v>
       </c>
       <c r="L78" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
     </row>
     <row r="79" spans="1:12" x14ac:dyDescent="0.35">
@@ -4468,11 +4484,10 @@
         <v>13</v>
       </c>
       <c r="C79">
-        <f t="shared" si="0"/>
-        <v>33</v>
+        <v>78</v>
       </c>
       <c r="D79" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="E79" t="s">
         <v>23</v>
@@ -4481,7 +4496,7 @@
         <v>26</v>
       </c>
       <c r="G79" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="H79" t="s">
         <v>101</v>
@@ -4496,7 +4511,7 @@
         <v>103</v>
       </c>
       <c r="L79" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.35">
@@ -4507,11 +4522,10 @@
         <v>13</v>
       </c>
       <c r="C80">
-        <f t="shared" si="0"/>
-        <v>34</v>
+        <v>79</v>
       </c>
       <c r="D80" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="E80" t="s">
         <v>23</v>
@@ -4532,10 +4546,10 @@
         <v>102</v>
       </c>
       <c r="K80" t="s">
-        <v>103</v>
+        <v>180</v>
       </c>
       <c r="L80" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
     </row>
     <row r="81" spans="1:12" x14ac:dyDescent="0.35">
@@ -4546,11 +4560,10 @@
         <v>13</v>
       </c>
       <c r="C81">
-        <f t="shared" si="0"/>
-        <v>35</v>
+        <v>80</v>
       </c>
       <c r="D81" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="E81" t="s">
         <v>23</v>
@@ -4571,10 +4584,10 @@
         <v>102</v>
       </c>
       <c r="K81" t="s">
-        <v>103</v>
+        <v>180</v>
       </c>
       <c r="L81" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
     </row>
     <row r="82" spans="1:12" x14ac:dyDescent="0.35">
@@ -4585,20 +4598,19 @@
         <v>13</v>
       </c>
       <c r="C82">
-        <f t="shared" si="0"/>
-        <v>36</v>
+        <v>81</v>
       </c>
       <c r="D82" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="E82" t="s">
-        <v>23</v>
+        <v>80</v>
       </c>
       <c r="F82" t="s">
-        <v>26</v>
+        <v>83</v>
       </c>
       <c r="G82" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="H82" t="s">
         <v>101</v>
@@ -4610,10 +4622,10 @@
         <v>102</v>
       </c>
       <c r="K82" t="s">
-        <v>180</v>
+        <v>103</v>
       </c>
       <c r="L82" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
     </row>
     <row r="83" spans="1:12" x14ac:dyDescent="0.35">
@@ -4624,20 +4636,19 @@
         <v>13</v>
       </c>
       <c r="C83">
-        <f t="shared" si="0"/>
-        <v>37</v>
+        <v>82</v>
       </c>
       <c r="D83" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="E83" t="s">
-        <v>23</v>
+        <v>80</v>
       </c>
       <c r="F83" t="s">
-        <v>26</v>
+        <v>83</v>
       </c>
       <c r="G83" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="H83" t="s">
         <v>101</v>
@@ -4649,10 +4660,10 @@
         <v>102</v>
       </c>
       <c r="K83" t="s">
-        <v>180</v>
+        <v>103</v>
       </c>
       <c r="L83" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
     </row>
     <row r="84" spans="1:12" x14ac:dyDescent="0.35">
@@ -4663,20 +4674,19 @@
         <v>13</v>
       </c>
       <c r="C84">
-        <f t="shared" si="0"/>
-        <v>38</v>
+        <v>83</v>
       </c>
       <c r="D84" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="E84" t="s">
-        <v>80</v>
+        <v>189</v>
       </c>
       <c r="F84" t="s">
         <v>83</v>
       </c>
       <c r="G84" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="H84" t="s">
         <v>101</v>
@@ -4691,7 +4701,7 @@
         <v>103</v>
       </c>
       <c r="L84" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
     </row>
     <row r="85" spans="1:12" x14ac:dyDescent="0.35">
@@ -4702,20 +4712,19 @@
         <v>13</v>
       </c>
       <c r="C85">
-        <f t="shared" si="0"/>
-        <v>39</v>
+        <v>84</v>
       </c>
       <c r="D85" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="E85" t="s">
-        <v>80</v>
+        <v>189</v>
       </c>
       <c r="F85" t="s">
         <v>83</v>
       </c>
       <c r="G85" t="s">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="H85" t="s">
         <v>101</v>
@@ -4730,7 +4739,7 @@
         <v>103</v>
       </c>
       <c r="L85" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
     </row>
     <row r="86" spans="1:12" x14ac:dyDescent="0.35">
@@ -4741,11 +4750,10 @@
         <v>13</v>
       </c>
       <c r="C86">
-        <f t="shared" si="0"/>
-        <v>40</v>
+        <v>85</v>
       </c>
       <c r="D86" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="E86" t="s">
         <v>189</v>
@@ -4769,90 +4777,121 @@
         <v>103</v>
       </c>
       <c r="L86" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
     </row>
     <row r="87" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>12</v>
       </c>
-      <c r="B87" t="s">
-        <v>13</v>
+      <c r="B87" s="8" t="s">
+        <v>195</v>
       </c>
       <c r="C87">
-        <f t="shared" si="0"/>
-        <v>41</v>
-      </c>
-      <c r="D87" t="s">
-        <v>191</v>
-      </c>
-      <c r="E87" t="s">
-        <v>189</v>
-      </c>
-      <c r="F87" t="s">
-        <v>83</v>
-      </c>
-      <c r="G87" t="s">
-        <v>150</v>
-      </c>
-      <c r="H87" t="s">
-        <v>101</v>
+        <v>86</v>
+      </c>
+      <c r="D87" s="9" t="s">
+        <v>274</v>
+      </c>
+      <c r="E87" s="10" t="s">
+        <v>275</v>
+      </c>
+      <c r="F87" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="G87" s="10" t="s">
+        <v>276</v>
+      </c>
+      <c r="H87" s="10" t="s">
+        <v>123</v>
       </c>
       <c r="I87" t="s">
         <v>19</v>
       </c>
-      <c r="J87" t="s">
-        <v>102</v>
-      </c>
-      <c r="K87" t="s">
-        <v>103</v>
-      </c>
-      <c r="L87" t="s">
-        <v>192</v>
+      <c r="J87" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="K87" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="L87" s="19" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="88" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>12</v>
       </c>
-      <c r="B88" t="s">
-        <v>13</v>
+      <c r="B88" s="8" t="s">
+        <v>195</v>
       </c>
       <c r="C88">
-        <f t="shared" si="0"/>
-        <v>42</v>
-      </c>
-      <c r="D88" t="s">
-        <v>193</v>
-      </c>
-      <c r="E88" t="s">
-        <v>189</v>
-      </c>
-      <c r="F88" t="s">
+        <v>87</v>
+      </c>
+      <c r="D88" s="9" t="s">
+        <v>278</v>
+      </c>
+      <c r="E88" s="10" t="s">
+        <v>275</v>
+      </c>
+      <c r="F88" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="G88" s="10" t="s">
+        <v>150</v>
+      </c>
+      <c r="H88" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="I88" t="s">
+        <v>19</v>
+      </c>
+      <c r="J88" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="K88" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="L88" s="19" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="89" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A89" t="s">
+        <v>12</v>
+      </c>
+      <c r="B89" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="C89">
+        <v>88</v>
+      </c>
+      <c r="D89" s="9" t="s">
+        <v>280</v>
+      </c>
+      <c r="E89" s="10" t="s">
+        <v>197</v>
+      </c>
+      <c r="F89" s="10" t="s">
         <v>83</v>
       </c>
-      <c r="G88" t="s">
+      <c r="G89" s="10" t="s">
         <v>108</v>
       </c>
-      <c r="H88" t="s">
-        <v>101</v>
-      </c>
-      <c r="I88" t="s">
-        <v>19</v>
-      </c>
-      <c r="J88" t="s">
+      <c r="H89" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="I89" t="s">
+        <v>19</v>
+      </c>
+      <c r="J89" s="8" t="s">
         <v>102</v>
       </c>
-      <c r="K88" t="s">
-        <v>103</v>
-      </c>
-      <c r="L88" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="89" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A89" s="15" t="s">
-        <v>319</v>
+      <c r="K89" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="L89" s="19" t="s">
+        <v>281</v>
       </c>
     </row>
     <row r="90" spans="1:12" x14ac:dyDescent="0.35">
@@ -4862,96 +4901,96 @@
       <c r="B90" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="C90" s="8">
-        <v>1</v>
+      <c r="C90">
+        <v>89</v>
       </c>
       <c r="D90" s="9" t="s">
-        <v>274</v>
+        <v>282</v>
       </c>
       <c r="E90" s="10" t="s">
-        <v>275</v>
+        <v>197</v>
       </c>
       <c r="F90" s="10" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="G90" s="10" t="s">
-        <v>276</v>
+        <v>108</v>
       </c>
       <c r="H90" s="10" t="s">
-        <v>123</v>
+        <v>101</v>
       </c>
       <c r="I90" t="s">
         <v>19</v>
       </c>
       <c r="J90" s="8" t="s">
-        <v>111</v>
+        <v>102</v>
       </c>
       <c r="K90" s="10" t="s">
         <v>103</v>
       </c>
-      <c r="L90" s="16" t="s">
-        <v>277</v>
+      <c r="L90" s="19" t="s">
+        <v>283</v>
       </c>
     </row>
     <row r="91" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A91" t="s">
+      <c r="A91" s="8" t="s">
         <v>12</v>
       </c>
       <c r="B91" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="C91" s="8">
-        <v>2</v>
+      <c r="C91">
+        <v>90</v>
       </c>
       <c r="D91" s="9" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>275</v>
+        <v>197</v>
       </c>
       <c r="F91" s="10" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="G91" s="10" t="s">
         <v>150</v>
       </c>
       <c r="H91" s="10" t="s">
-        <v>123</v>
+        <v>101</v>
       </c>
       <c r="I91" t="s">
         <v>19</v>
       </c>
       <c r="J91" s="8" t="s">
-        <v>111</v>
+        <v>20</v>
       </c>
       <c r="K91" s="10" t="s">
         <v>103</v>
       </c>
-      <c r="L91" s="16" t="s">
-        <v>279</v>
+      <c r="L91" s="19" t="s">
+        <v>285</v>
       </c>
     </row>
     <row r="92" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A92" t="s">
+      <c r="A92" s="8" t="s">
         <v>12</v>
       </c>
       <c r="B92" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="C92" s="8">
-        <v>3</v>
+      <c r="C92">
+        <v>91</v>
       </c>
       <c r="D92" s="9" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="E92" s="10" t="s">
         <v>197</v>
       </c>
       <c r="F92" s="10" t="s">
-        <v>83</v>
+        <v>26</v>
       </c>
       <c r="G92" s="10" t="s">
-        <v>108</v>
+        <v>150</v>
       </c>
       <c r="H92" s="10" t="s">
         <v>101</v>
@@ -4960,109 +4999,109 @@
         <v>19</v>
       </c>
       <c r="J92" s="8" t="s">
-        <v>102</v>
+        <v>20</v>
       </c>
       <c r="K92" s="10" t="s">
         <v>103</v>
       </c>
-      <c r="L92" s="16" t="s">
-        <v>281</v>
+      <c r="L92" s="19" t="s">
+        <v>287</v>
       </c>
     </row>
     <row r="93" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>12</v>
       </c>
-      <c r="B93" s="8" t="s">
+      <c r="B93" t="s">
         <v>195</v>
       </c>
-      <c r="C93" s="8">
-        <v>4</v>
-      </c>
-      <c r="D93" s="9" t="s">
-        <v>282</v>
-      </c>
-      <c r="E93" s="10" t="s">
+      <c r="C93">
+        <v>92</v>
+      </c>
+      <c r="D93" t="s">
+        <v>288</v>
+      </c>
+      <c r="E93" t="s">
         <v>197</v>
       </c>
-      <c r="F93" s="10" t="s">
+      <c r="F93" t="s">
         <v>26</v>
       </c>
-      <c r="G93" s="10" t="s">
+      <c r="G93" t="s">
         <v>108</v>
       </c>
-      <c r="H93" s="10" t="s">
+      <c r="H93" t="s">
         <v>101</v>
       </c>
       <c r="I93" t="s">
         <v>19</v>
       </c>
-      <c r="J93" s="8" t="s">
+      <c r="J93" t="s">
         <v>102</v>
       </c>
-      <c r="K93" s="10" t="s">
-        <v>103</v>
-      </c>
-      <c r="L93" s="16" t="s">
-        <v>283</v>
+      <c r="K93" t="s">
+        <v>103</v>
+      </c>
+      <c r="L93" s="20" t="s">
+        <v>289</v>
       </c>
     </row>
     <row r="94" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A94" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="B94" s="8" t="s">
+      <c r="A94" t="s">
+        <v>12</v>
+      </c>
+      <c r="B94" t="s">
         <v>195</v>
       </c>
-      <c r="C94" s="8">
-        <v>5</v>
-      </c>
-      <c r="D94" s="9" t="s">
-        <v>284</v>
-      </c>
-      <c r="E94" s="10" t="s">
+      <c r="C94">
+        <v>93</v>
+      </c>
+      <c r="D94" t="s">
+        <v>290</v>
+      </c>
+      <c r="E94" t="s">
         <v>197</v>
       </c>
-      <c r="F94" s="10" t="s">
+      <c r="F94" t="s">
         <v>26</v>
       </c>
-      <c r="G94" s="10" t="s">
+      <c r="G94" t="s">
         <v>150</v>
       </c>
-      <c r="H94" s="10" t="s">
+      <c r="H94" t="s">
         <v>101</v>
       </c>
       <c r="I94" t="s">
         <v>19</v>
       </c>
-      <c r="J94" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="K94" s="10" t="s">
-        <v>103</v>
-      </c>
-      <c r="L94" s="16" t="s">
-        <v>285</v>
+      <c r="J94" t="s">
+        <v>102</v>
+      </c>
+      <c r="K94" t="s">
+        <v>103</v>
+      </c>
+      <c r="L94" s="20" t="s">
+        <v>291</v>
       </c>
     </row>
     <row r="95" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A95" s="8" t="s">
+      <c r="A95" t="s">
         <v>12</v>
       </c>
       <c r="B95" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="C95" s="8">
-        <v>6</v>
+      <c r="C95">
+        <v>94</v>
       </c>
       <c r="D95" s="9" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>197</v>
+        <v>275</v>
       </c>
       <c r="F95" s="10" t="s">
-        <v>26</v>
+        <v>83</v>
       </c>
       <c r="G95" s="10" t="s">
         <v>150</v>
@@ -5074,112 +5113,112 @@
         <v>19</v>
       </c>
       <c r="J95" s="8" t="s">
-        <v>20</v>
+        <v>111</v>
       </c>
       <c r="K95" s="10" t="s">
         <v>103</v>
       </c>
-      <c r="L95" s="16" t="s">
-        <v>287</v>
+      <c r="L95" s="19" t="s">
+        <v>293</v>
       </c>
     </row>
     <row r="96" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>12</v>
       </c>
-      <c r="B96" t="s">
+      <c r="B96" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="C96" s="8">
-        <v>7</v>
-      </c>
-      <c r="D96" t="s">
-        <v>288</v>
-      </c>
-      <c r="E96" t="s">
-        <v>197</v>
-      </c>
-      <c r="F96" t="s">
-        <v>26</v>
-      </c>
-      <c r="G96" t="s">
-        <v>108</v>
-      </c>
-      <c r="H96" t="s">
+      <c r="C96">
+        <v>95</v>
+      </c>
+      <c r="D96" s="9" t="s">
+        <v>294</v>
+      </c>
+      <c r="E96" s="10" t="s">
+        <v>275</v>
+      </c>
+      <c r="F96" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="G96" s="10" t="s">
+        <v>150</v>
+      </c>
+      <c r="H96" s="10" t="s">
         <v>101</v>
       </c>
       <c r="I96" t="s">
         <v>19</v>
       </c>
-      <c r="J96" t="s">
-        <v>102</v>
-      </c>
-      <c r="K96" t="s">
-        <v>103</v>
-      </c>
-      <c r="L96" s="17" t="s">
-        <v>289</v>
+      <c r="J96" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="K96" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="L96" s="19" t="s">
+        <v>295</v>
       </c>
     </row>
     <row r="97" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>12</v>
       </c>
-      <c r="B97" t="s">
+      <c r="B97" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="C97" s="8">
-        <v>8</v>
-      </c>
-      <c r="D97" t="s">
-        <v>290</v>
-      </c>
-      <c r="E97" t="s">
-        <v>197</v>
-      </c>
-      <c r="F97" t="s">
-        <v>26</v>
-      </c>
-      <c r="G97" t="s">
-        <v>150</v>
-      </c>
-      <c r="H97" t="s">
-        <v>101</v>
+      <c r="C97">
+        <v>96</v>
+      </c>
+      <c r="D97" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="E97" s="10" t="s">
+        <v>275</v>
+      </c>
+      <c r="F97" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="G97" s="10" t="s">
+        <v>276</v>
+      </c>
+      <c r="H97" s="10" t="s">
+        <v>123</v>
       </c>
       <c r="I97" t="s">
         <v>19</v>
       </c>
-      <c r="J97" t="s">
-        <v>102</v>
-      </c>
-      <c r="K97" t="s">
-        <v>103</v>
-      </c>
-      <c r="L97" s="17" t="s">
-        <v>291</v>
+      <c r="J97" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="K97" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="L97" s="19" t="s">
+        <v>297</v>
       </c>
     </row>
     <row r="98" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>12</v>
       </c>
-      <c r="B98" s="8" t="s">
-        <v>195</v>
-      </c>
-      <c r="C98" s="8">
-        <v>9</v>
-      </c>
-      <c r="D98" s="9" t="s">
-        <v>292</v>
-      </c>
-      <c r="E98" s="10" t="s">
+      <c r="B98" t="s">
+        <v>298</v>
+      </c>
+      <c r="C98">
+        <v>97</v>
+      </c>
+      <c r="D98" s="17" t="s">
+        <v>299</v>
+      </c>
+      <c r="E98" s="18" t="s">
         <v>275</v>
       </c>
-      <c r="F98" s="10" t="s">
-        <v>83</v>
-      </c>
-      <c r="G98" s="10" t="s">
-        <v>150</v>
+      <c r="F98" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="G98" s="18" t="s">
+        <v>108</v>
       </c>
       <c r="H98" s="10" t="s">
         <v>101</v>
@@ -5187,37 +5226,37 @@
       <c r="I98" t="s">
         <v>19</v>
       </c>
-      <c r="J98" s="8" t="s">
-        <v>111</v>
-      </c>
-      <c r="K98" s="10" t="s">
-        <v>103</v>
-      </c>
-      <c r="L98" s="16" t="s">
-        <v>293</v>
+      <c r="J98" t="s">
+        <v>102</v>
+      </c>
+      <c r="K98" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="L98" s="19" t="s">
+        <v>300</v>
       </c>
     </row>
     <row r="99" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>12</v>
       </c>
-      <c r="B99" s="8" t="s">
-        <v>195</v>
-      </c>
-      <c r="C99" s="8">
-        <v>10</v>
-      </c>
-      <c r="D99" s="9" t="s">
-        <v>294</v>
-      </c>
-      <c r="E99" s="10" t="s">
+      <c r="B99" t="s">
+        <v>298</v>
+      </c>
+      <c r="C99">
+        <v>98</v>
+      </c>
+      <c r="D99" s="17" t="s">
+        <v>301</v>
+      </c>
+      <c r="E99" s="18" t="s">
         <v>275</v>
       </c>
-      <c r="F99" s="10" t="s">
-        <v>83</v>
-      </c>
-      <c r="G99" s="10" t="s">
-        <v>150</v>
+      <c r="F99" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="G99" s="18" t="s">
+        <v>108</v>
       </c>
       <c r="H99" s="10" t="s">
         <v>101</v>
@@ -5225,52 +5264,52 @@
       <c r="I99" t="s">
         <v>19</v>
       </c>
-      <c r="J99" s="8" t="s">
-        <v>111</v>
-      </c>
-      <c r="K99" s="10" t="s">
-        <v>103</v>
-      </c>
-      <c r="L99" s="16" t="s">
-        <v>295</v>
+      <c r="J99" t="s">
+        <v>102</v>
+      </c>
+      <c r="K99" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="L99" s="19" t="s">
+        <v>302</v>
       </c>
     </row>
     <row r="100" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>12</v>
       </c>
-      <c r="B100" s="8" t="s">
-        <v>195</v>
-      </c>
-      <c r="C100" s="8">
-        <v>11</v>
-      </c>
-      <c r="D100" s="9" t="s">
-        <v>296</v>
-      </c>
-      <c r="E100" s="10" t="s">
+      <c r="B100" t="s">
+        <v>298</v>
+      </c>
+      <c r="C100">
+        <v>99</v>
+      </c>
+      <c r="D100" s="17" t="s">
+        <v>303</v>
+      </c>
+      <c r="E100" s="18" t="s">
         <v>275</v>
       </c>
-      <c r="F100" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="G100" s="10" t="s">
-        <v>276</v>
+      <c r="F100" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="G100" s="18" t="s">
+        <v>150</v>
       </c>
       <c r="H100" s="10" t="s">
-        <v>123</v>
+        <v>101</v>
       </c>
       <c r="I100" t="s">
         <v>19</v>
       </c>
-      <c r="J100" s="8" t="s">
-        <v>111</v>
-      </c>
-      <c r="K100" s="10" t="s">
-        <v>103</v>
-      </c>
-      <c r="L100" s="16" t="s">
-        <v>297</v>
+      <c r="J100" t="s">
+        <v>102</v>
+      </c>
+      <c r="K100" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="L100" s="20" t="s">
+        <v>304</v>
       </c>
     </row>
     <row r="101" spans="1:12" x14ac:dyDescent="0.35">
@@ -5280,20 +5319,20 @@
       <c r="B101" t="s">
         <v>298</v>
       </c>
-      <c r="C101" s="8">
-        <v>12</v>
-      </c>
-      <c r="D101" s="18" t="s">
-        <v>299</v>
-      </c>
-      <c r="E101" s="19" t="s">
+      <c r="C101">
+        <v>100</v>
+      </c>
+      <c r="D101" s="17" t="s">
+        <v>305</v>
+      </c>
+      <c r="E101" s="18" t="s">
         <v>275</v>
       </c>
-      <c r="F101" s="20" t="s">
+      <c r="F101" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="G101" s="19" t="s">
-        <v>108</v>
+      <c r="G101" s="18" t="s">
+        <v>150</v>
       </c>
       <c r="H101" s="10" t="s">
         <v>101</v>
@@ -5304,11 +5343,11 @@
       <c r="J101" t="s">
         <v>102</v>
       </c>
-      <c r="K101" s="19" t="s">
-        <v>103</v>
-      </c>
-      <c r="L101" s="16" t="s">
-        <v>300</v>
+      <c r="K101" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="L101" s="20" t="s">
+        <v>306</v>
       </c>
     </row>
     <row r="102" spans="1:12" x14ac:dyDescent="0.35">
@@ -5318,20 +5357,20 @@
       <c r="B102" t="s">
         <v>298</v>
       </c>
-      <c r="C102" s="8">
-        <v>13</v>
-      </c>
-      <c r="D102" s="18" t="s">
-        <v>301</v>
-      </c>
-      <c r="E102" s="19" t="s">
+      <c r="C102">
+        <v>101</v>
+      </c>
+      <c r="D102" s="17" t="s">
+        <v>307</v>
+      </c>
+      <c r="E102" s="18" t="s">
         <v>275</v>
       </c>
-      <c r="F102" s="20" t="s">
+      <c r="F102" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="G102" s="19" t="s">
-        <v>108</v>
+      <c r="G102" s="18" t="s">
+        <v>150</v>
       </c>
       <c r="H102" s="10" t="s">
         <v>101</v>
@@ -5342,11 +5381,11 @@
       <c r="J102" t="s">
         <v>102</v>
       </c>
-      <c r="K102" s="19" t="s">
-        <v>103</v>
-      </c>
-      <c r="L102" s="16" t="s">
-        <v>302</v>
+      <c r="K102" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="L102" s="19" t="s">
+        <v>308</v>
       </c>
     </row>
     <row r="103" spans="1:12" x14ac:dyDescent="0.35">
@@ -5356,19 +5395,19 @@
       <c r="B103" t="s">
         <v>298</v>
       </c>
-      <c r="C103" s="8">
-        <v>14</v>
-      </c>
-      <c r="D103" s="18" t="s">
-        <v>303</v>
-      </c>
-      <c r="E103" s="19" t="s">
+      <c r="C103">
+        <v>102</v>
+      </c>
+      <c r="D103" s="17" t="s">
+        <v>309</v>
+      </c>
+      <c r="E103" s="18" t="s">
         <v>275</v>
       </c>
-      <c r="F103" s="20" t="s">
+      <c r="F103" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="G103" s="19" t="s">
+      <c r="G103" s="18" t="s">
         <v>150</v>
       </c>
       <c r="H103" s="10" t="s">
@@ -5380,11 +5419,11 @@
       <c r="J103" t="s">
         <v>102</v>
       </c>
-      <c r="K103" s="19" t="s">
-        <v>103</v>
-      </c>
-      <c r="L103" s="17" t="s">
-        <v>304</v>
+      <c r="K103" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="L103" s="19" t="s">
+        <v>310</v>
       </c>
     </row>
     <row r="104" spans="1:12" x14ac:dyDescent="0.35">
@@ -5394,20 +5433,20 @@
       <c r="B104" t="s">
         <v>298</v>
       </c>
-      <c r="C104" s="8">
-        <v>15</v>
-      </c>
-      <c r="D104" s="18" t="s">
-        <v>305</v>
-      </c>
-      <c r="E104" s="19" t="s">
+      <c r="C104">
+        <v>103</v>
+      </c>
+      <c r="D104" s="17" t="s">
+        <v>311</v>
+      </c>
+      <c r="E104" s="18" t="s">
         <v>275</v>
       </c>
-      <c r="F104" s="20" t="s">
+      <c r="F104" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="G104" s="19" t="s">
-        <v>150</v>
+      <c r="G104" s="18" t="s">
+        <v>276</v>
       </c>
       <c r="H104" s="10" t="s">
         <v>101</v>
@@ -5418,11 +5457,11 @@
       <c r="J104" t="s">
         <v>102</v>
       </c>
-      <c r="K104" s="19" t="s">
-        <v>103</v>
-      </c>
-      <c r="L104" s="17" t="s">
-        <v>306</v>
+      <c r="K104" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="L104" s="19" t="s">
+        <v>312</v>
       </c>
     </row>
     <row r="105" spans="1:12" x14ac:dyDescent="0.35">
@@ -5432,20 +5471,20 @@
       <c r="B105" t="s">
         <v>298</v>
       </c>
-      <c r="C105" s="8">
-        <v>16</v>
-      </c>
-      <c r="D105" s="18" t="s">
-        <v>307</v>
-      </c>
-      <c r="E105" s="19" t="s">
+      <c r="C105">
+        <v>104</v>
+      </c>
+      <c r="D105" s="17" t="s">
+        <v>313</v>
+      </c>
+      <c r="E105" s="18" t="s">
         <v>275</v>
       </c>
-      <c r="F105" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="G105" s="19" t="s">
-        <v>150</v>
+      <c r="F105" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="G105" s="18" t="s">
+        <v>276</v>
       </c>
       <c r="H105" s="10" t="s">
         <v>101</v>
@@ -5454,13 +5493,13 @@
         <v>19</v>
       </c>
       <c r="J105" t="s">
-        <v>102</v>
-      </c>
-      <c r="K105" s="19" t="s">
-        <v>103</v>
-      </c>
-      <c r="L105" s="16" t="s">
-        <v>308</v>
+        <v>111</v>
+      </c>
+      <c r="K105" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="L105" s="19" t="s">
+        <v>314</v>
       </c>
     </row>
     <row r="106" spans="1:12" x14ac:dyDescent="0.35">
@@ -5468,60 +5507,60 @@
         <v>12</v>
       </c>
       <c r="B106" t="s">
-        <v>298</v>
-      </c>
-      <c r="C106" s="8">
-        <v>17</v>
-      </c>
-      <c r="D106" s="18" t="s">
-        <v>309</v>
-      </c>
-      <c r="E106" s="19" t="s">
+        <v>195</v>
+      </c>
+      <c r="C106">
+        <v>105</v>
+      </c>
+      <c r="D106" t="s">
+        <v>315</v>
+      </c>
+      <c r="E106" t="s">
         <v>275</v>
       </c>
-      <c r="F106" s="20" t="s">
+      <c r="F106" t="s">
+        <v>83</v>
+      </c>
+      <c r="G106" t="s">
+        <v>100</v>
+      </c>
+      <c r="H106" t="s">
+        <v>101</v>
+      </c>
+      <c r="I106" t="s">
+        <v>19</v>
+      </c>
+      <c r="J106" t="s">
+        <v>111</v>
+      </c>
+      <c r="K106" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="L106" s="20" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="107" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A107" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B107" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="C107">
+        <v>106</v>
+      </c>
+      <c r="D107" s="9" t="s">
+        <v>196</v>
+      </c>
+      <c r="E107" s="10" t="s">
+        <v>197</v>
+      </c>
+      <c r="F107" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="G106" s="19" t="s">
-        <v>150</v>
-      </c>
-      <c r="H106" s="10" t="s">
-        <v>101</v>
-      </c>
-      <c r="I106" t="s">
-        <v>19</v>
-      </c>
-      <c r="J106" t="s">
-        <v>102</v>
-      </c>
-      <c r="K106" s="19" t="s">
-        <v>103</v>
-      </c>
-      <c r="L106" s="16" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="107" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A107" t="s">
-        <v>12</v>
-      </c>
-      <c r="B107" t="s">
-        <v>298</v>
-      </c>
-      <c r="C107" s="8">
-        <v>18</v>
-      </c>
-      <c r="D107" s="18" t="s">
-        <v>311</v>
-      </c>
-      <c r="E107" s="19" t="s">
-        <v>275</v>
-      </c>
-      <c r="F107" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="G107" s="19" t="s">
-        <v>276</v>
+      <c r="G107" s="10" t="s">
+        <v>100</v>
       </c>
       <c r="H107" s="10" t="s">
         <v>101</v>
@@ -5529,37 +5568,37 @@
       <c r="I107" t="s">
         <v>19</v>
       </c>
-      <c r="J107" t="s">
-        <v>102</v>
-      </c>
-      <c r="K107" s="19" t="s">
-        <v>103</v>
-      </c>
-      <c r="L107" s="16" t="s">
-        <v>312</v>
+      <c r="J107" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="K107" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="L107" s="19" t="s">
+        <v>198</v>
       </c>
     </row>
     <row r="108" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A108" t="s">
-        <v>12</v>
-      </c>
-      <c r="B108" t="s">
-        <v>298</v>
-      </c>
-      <c r="C108" s="8">
-        <v>19</v>
-      </c>
-      <c r="D108" s="18" t="s">
-        <v>313</v>
-      </c>
-      <c r="E108" s="19" t="s">
-        <v>275</v>
-      </c>
-      <c r="F108" s="20" t="s">
+      <c r="A108" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B108" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="C108">
+        <v>107</v>
+      </c>
+      <c r="D108" s="9" t="s">
+        <v>199</v>
+      </c>
+      <c r="E108" s="10" t="s">
+        <v>197</v>
+      </c>
+      <c r="F108" s="10" t="s">
         <v>83</v>
       </c>
-      <c r="G108" s="19" t="s">
-        <v>276</v>
+      <c r="G108" s="10" t="s">
+        <v>200</v>
       </c>
       <c r="H108" s="10" t="s">
         <v>101</v>
@@ -5567,57 +5606,90 @@
       <c r="I108" t="s">
         <v>19</v>
       </c>
-      <c r="J108" t="s">
-        <v>111</v>
-      </c>
-      <c r="K108" s="19" t="s">
-        <v>103</v>
-      </c>
-      <c r="L108" s="16" t="s">
-        <v>314</v>
+      <c r="J108" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="K108" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="L108" s="11" t="s">
+        <v>201</v>
       </c>
     </row>
     <row r="109" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A109" t="s">
-        <v>12</v>
-      </c>
-      <c r="B109" t="s">
+      <c r="A109" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B109" s="8" t="s">
         <v>195</v>
       </c>
       <c r="C109">
-        <v>20</v>
-      </c>
-      <c r="D109" t="s">
-        <v>315</v>
-      </c>
-      <c r="E109" t="s">
-        <v>275</v>
-      </c>
-      <c r="F109" t="s">
+        <v>108</v>
+      </c>
+      <c r="D109" s="9" t="s">
+        <v>202</v>
+      </c>
+      <c r="E109" s="10" t="s">
+        <v>197</v>
+      </c>
+      <c r="F109" s="10" t="s">
         <v>83</v>
       </c>
-      <c r="G109" t="s">
-        <v>100</v>
-      </c>
-      <c r="H109" t="s">
+      <c r="G109" s="10" t="s">
+        <v>203</v>
+      </c>
+      <c r="H109" s="10" t="s">
         <v>101</v>
       </c>
       <c r="I109" t="s">
         <v>19</v>
       </c>
-      <c r="J109" t="s">
-        <v>111</v>
-      </c>
-      <c r="K109" s="19" t="s">
-        <v>103</v>
-      </c>
-      <c r="L109" s="17" t="s">
-        <v>316</v>
+      <c r="J109" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="K109" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="L109" s="11" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="110" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A110" s="15" t="s">
-        <v>320</v>
+      <c r="A110" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B110" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="C110">
+        <v>109</v>
+      </c>
+      <c r="D110" s="9" t="s">
+        <v>205</v>
+      </c>
+      <c r="E110" s="10" t="s">
+        <v>197</v>
+      </c>
+      <c r="F110" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="G110" s="10" t="s">
+        <v>200</v>
+      </c>
+      <c r="H110" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="I110" t="s">
+        <v>19</v>
+      </c>
+      <c r="J110" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="K110" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="L110" s="11" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="111" spans="1:12" x14ac:dyDescent="0.35">
@@ -5627,23 +5699,23 @@
       <c r="B111" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="C111" s="8">
-        <v>1</v>
+      <c r="C111">
+        <v>110</v>
       </c>
       <c r="D111" s="9" t="s">
-        <v>196</v>
+        <v>207</v>
       </c>
       <c r="E111" s="10" t="s">
         <v>197</v>
       </c>
       <c r="F111" s="10" t="s">
-        <v>26</v>
+        <v>74</v>
       </c>
       <c r="G111" s="10" t="s">
-        <v>100</v>
+        <v>203</v>
       </c>
       <c r="H111" s="10" t="s">
-        <v>101</v>
+        <v>123</v>
       </c>
       <c r="I111" t="s">
         <v>19</v>
@@ -5654,8 +5726,8 @@
       <c r="K111" s="10" t="s">
         <v>103</v>
       </c>
-      <c r="L111" s="11" t="s">
-        <v>198</v>
+      <c r="L111" s="8" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="112" spans="1:12" x14ac:dyDescent="0.35">
@@ -5665,11 +5737,11 @@
       <c r="B112" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="C112" s="8">
-        <v>2</v>
+      <c r="C112">
+        <v>111</v>
       </c>
       <c r="D112" s="9" t="s">
-        <v>199</v>
+        <v>209</v>
       </c>
       <c r="E112" s="10" t="s">
         <v>197</v>
@@ -5693,7 +5765,7 @@
         <v>103</v>
       </c>
       <c r="L112" s="11" t="s">
-        <v>201</v>
+        <v>210</v>
       </c>
     </row>
     <row r="113" spans="1:12" x14ac:dyDescent="0.35">
@@ -5703,11 +5775,11 @@
       <c r="B113" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="C113" s="8">
-        <v>3</v>
-      </c>
-      <c r="D113" s="9" t="s">
-        <v>202</v>
+      <c r="C113">
+        <v>112</v>
+      </c>
+      <c r="D113" s="8" t="s">
+        <v>211</v>
       </c>
       <c r="E113" s="10" t="s">
         <v>197</v>
@@ -5730,8 +5802,8 @@
       <c r="K113" s="10" t="s">
         <v>103</v>
       </c>
-      <c r="L113" s="11" t="s">
-        <v>204</v>
+      <c r="L113" s="12" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="114" spans="1:12" x14ac:dyDescent="0.35">
@@ -5741,23 +5813,23 @@
       <c r="B114" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="C114" s="8">
-        <v>4</v>
+      <c r="C114">
+        <v>113</v>
       </c>
       <c r="D114" s="9" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="E114" s="10" t="s">
         <v>197</v>
       </c>
       <c r="F114" s="10" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="G114" s="10" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="H114" s="10" t="s">
-        <v>123</v>
+        <v>101</v>
       </c>
       <c r="I114" t="s">
         <v>19</v>
@@ -5769,7 +5841,7 @@
         <v>103</v>
       </c>
       <c r="L114" s="11" t="s">
-        <v>206</v>
+        <v>214</v>
       </c>
     </row>
     <row r="115" spans="1:12" x14ac:dyDescent="0.35">
@@ -5779,23 +5851,23 @@
       <c r="B115" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="C115" s="8">
-        <v>5</v>
+      <c r="C115">
+        <v>114</v>
       </c>
       <c r="D115" s="9" t="s">
-        <v>207</v>
+        <v>215</v>
       </c>
       <c r="E115" s="10" t="s">
         <v>197</v>
       </c>
       <c r="F115" s="10" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="G115" s="10" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="H115" s="10" t="s">
-        <v>123</v>
+        <v>101</v>
       </c>
       <c r="I115" t="s">
         <v>19</v>
@@ -5806,8 +5878,8 @@
       <c r="K115" s="10" t="s">
         <v>103</v>
       </c>
-      <c r="L115" s="8" t="s">
-        <v>208</v>
+      <c r="L115" s="11" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="116" spans="1:12" x14ac:dyDescent="0.35">
@@ -5817,11 +5889,11 @@
       <c r="B116" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="C116" s="8">
-        <v>6</v>
+      <c r="C116">
+        <v>115</v>
       </c>
       <c r="D116" s="9" t="s">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="E116" s="10" t="s">
         <v>197</v>
@@ -5845,7 +5917,7 @@
         <v>103</v>
       </c>
       <c r="L116" s="11" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
     </row>
     <row r="117" spans="1:12" x14ac:dyDescent="0.35">
@@ -5855,11 +5927,11 @@
       <c r="B117" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="C117" s="8">
-        <v>7</v>
-      </c>
-      <c r="D117" s="8" t="s">
-        <v>211</v>
+      <c r="C117">
+        <v>116</v>
+      </c>
+      <c r="D117" s="9" t="s">
+        <v>219</v>
       </c>
       <c r="E117" s="10" t="s">
         <v>197</v>
@@ -5868,7 +5940,7 @@
         <v>83</v>
       </c>
       <c r="G117" s="10" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="H117" s="10" t="s">
         <v>101</v>
@@ -5882,8 +5954,8 @@
       <c r="K117" s="10" t="s">
         <v>103</v>
       </c>
-      <c r="L117" s="12" t="s">
-        <v>212</v>
+      <c r="L117" s="11" t="s">
+        <v>220</v>
       </c>
     </row>
     <row r="118" spans="1:12" x14ac:dyDescent="0.35">
@@ -5893,11 +5965,11 @@
       <c r="B118" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="C118" s="8">
-        <v>8</v>
+      <c r="C118">
+        <v>117</v>
       </c>
       <c r="D118" s="9" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="E118" s="10" t="s">
         <v>197</v>
@@ -5920,8 +5992,8 @@
       <c r="K118" s="10" t="s">
         <v>103</v>
       </c>
-      <c r="L118" s="11" t="s">
-        <v>214</v>
+      <c r="L118" s="12" t="s">
+        <v>222</v>
       </c>
     </row>
     <row r="119" spans="1:12" x14ac:dyDescent="0.35">
@@ -5931,11 +6003,11 @@
       <c r="B119" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="C119" s="8">
-        <v>9</v>
-      </c>
-      <c r="D119" s="9" t="s">
-        <v>215</v>
+      <c r="C119">
+        <v>118</v>
+      </c>
+      <c r="D119" s="8" t="s">
+        <v>223</v>
       </c>
       <c r="E119" s="10" t="s">
         <v>197</v>
@@ -5958,8 +6030,8 @@
       <c r="K119" s="10" t="s">
         <v>103</v>
       </c>
-      <c r="L119" s="11" t="s">
-        <v>216</v>
+      <c r="L119" s="8" t="s">
+        <v>224</v>
       </c>
     </row>
     <row r="120" spans="1:12" x14ac:dyDescent="0.35">
@@ -5969,11 +6041,11 @@
       <c r="B120" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="C120" s="8">
-        <v>10</v>
+      <c r="C120">
+        <v>119</v>
       </c>
       <c r="D120" s="9" t="s">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="E120" s="10" t="s">
         <v>197</v>
@@ -5982,7 +6054,7 @@
         <v>83</v>
       </c>
       <c r="G120" s="10" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="H120" s="10" t="s">
         <v>101</v>
@@ -5996,8 +6068,8 @@
       <c r="K120" s="10" t="s">
         <v>103</v>
       </c>
-      <c r="L120" s="11" t="s">
-        <v>218</v>
+      <c r="L120" s="8" t="s">
+        <v>226</v>
       </c>
     </row>
     <row r="121" spans="1:12" x14ac:dyDescent="0.35">
@@ -6007,11 +6079,11 @@
       <c r="B121" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="C121" s="8">
-        <v>11</v>
+      <c r="C121">
+        <v>120</v>
       </c>
       <c r="D121" s="9" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="E121" s="10" t="s">
         <v>197</v>
@@ -6034,8 +6106,8 @@
       <c r="K121" s="10" t="s">
         <v>103</v>
       </c>
-      <c r="L121" s="11" t="s">
-        <v>220</v>
+      <c r="L121" s="8" t="s">
+        <v>228</v>
       </c>
     </row>
     <row r="122" spans="1:12" x14ac:dyDescent="0.35">
@@ -6045,11 +6117,11 @@
       <c r="B122" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="C122" s="8">
-        <v>12</v>
+      <c r="C122">
+        <v>121</v>
       </c>
       <c r="D122" s="9" t="s">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="E122" s="10" t="s">
         <v>197</v>
@@ -6058,7 +6130,7 @@
         <v>83</v>
       </c>
       <c r="G122" s="10" t="s">
-        <v>203</v>
+        <v>108</v>
       </c>
       <c r="H122" s="10" t="s">
         <v>101</v>
@@ -6072,8 +6144,8 @@
       <c r="K122" s="10" t="s">
         <v>103</v>
       </c>
-      <c r="L122" s="12" t="s">
-        <v>222</v>
+      <c r="L122" s="11" t="s">
+        <v>230</v>
       </c>
     </row>
     <row r="123" spans="1:12" x14ac:dyDescent="0.35">
@@ -6083,23 +6155,23 @@
       <c r="B123" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="C123" s="8">
-        <v>13</v>
-      </c>
-      <c r="D123" s="8" t="s">
-        <v>223</v>
+      <c r="C123">
+        <v>122</v>
+      </c>
+      <c r="D123" s="9" t="s">
+        <v>231</v>
       </c>
       <c r="E123" s="10" t="s">
         <v>197</v>
       </c>
       <c r="F123" s="10" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="G123" s="10" t="s">
         <v>200</v>
       </c>
       <c r="H123" s="10" t="s">
-        <v>101</v>
+        <v>123</v>
       </c>
       <c r="I123" t="s">
         <v>19</v>
@@ -6110,8 +6182,8 @@
       <c r="K123" s="10" t="s">
         <v>103</v>
       </c>
-      <c r="L123" s="8" t="s">
-        <v>224</v>
+      <c r="L123" s="11" t="s">
+        <v>232</v>
       </c>
     </row>
     <row r="124" spans="1:12" x14ac:dyDescent="0.35">
@@ -6121,23 +6193,23 @@
       <c r="B124" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="C124" s="8">
-        <v>14</v>
+      <c r="C124">
+        <v>123</v>
       </c>
       <c r="D124" s="9" t="s">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="E124" s="10" t="s">
         <v>197</v>
       </c>
       <c r="F124" s="10" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="G124" s="10" t="s">
         <v>203</v>
       </c>
       <c r="H124" s="10" t="s">
-        <v>101</v>
+        <v>123</v>
       </c>
       <c r="I124" t="s">
         <v>19</v>
@@ -6148,8 +6220,8 @@
       <c r="K124" s="10" t="s">
         <v>103</v>
       </c>
-      <c r="L124" s="8" t="s">
-        <v>226</v>
+      <c r="L124" s="11" t="s">
+        <v>234</v>
       </c>
     </row>
     <row r="125" spans="1:12" x14ac:dyDescent="0.35">
@@ -6159,20 +6231,20 @@
       <c r="B125" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="C125" s="8">
-        <v>15</v>
+      <c r="C125">
+        <v>124</v>
       </c>
       <c r="D125" s="9" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="E125" s="10" t="s">
-        <v>197</v>
+        <v>236</v>
       </c>
       <c r="F125" s="10" t="s">
-        <v>83</v>
+        <v>114</v>
       </c>
       <c r="G125" s="10" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="H125" s="10" t="s">
         <v>101</v>
@@ -6186,8 +6258,8 @@
       <c r="K125" s="10" t="s">
         <v>103</v>
       </c>
-      <c r="L125" s="8" t="s">
-        <v>228</v>
+      <c r="L125" s="11" t="s">
+        <v>237</v>
       </c>
     </row>
     <row r="126" spans="1:12" x14ac:dyDescent="0.35">
@@ -6197,26 +6269,26 @@
       <c r="B126" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="C126" s="8">
+      <c r="C126">
+        <v>125</v>
+      </c>
+      <c r="D126" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="E126" s="10" t="s">
+        <v>236</v>
+      </c>
+      <c r="F126" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="D126" s="9" t="s">
-        <v>229</v>
-      </c>
-      <c r="E126" s="10" t="s">
-        <v>197</v>
-      </c>
-      <c r="F126" s="10" t="s">
-        <v>83</v>
-      </c>
       <c r="G126" s="10" t="s">
-        <v>108</v>
+        <v>203</v>
       </c>
       <c r="H126" s="10" t="s">
-        <v>101</v>
-      </c>
-      <c r="I126" t="s">
-        <v>19</v>
+        <v>123</v>
+      </c>
+      <c r="I126" s="10" t="s">
+        <v>236</v>
       </c>
       <c r="J126" s="8" t="s">
         <v>84</v>
@@ -6225,7 +6297,7 @@
         <v>103</v>
       </c>
       <c r="L126" s="11" t="s">
-        <v>230</v>
+        <v>239</v>
       </c>
     </row>
     <row r="127" spans="1:12" x14ac:dyDescent="0.35">
@@ -6235,26 +6307,26 @@
       <c r="B127" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="C127" s="8">
-        <v>17</v>
+      <c r="C127">
+        <v>126</v>
       </c>
       <c r="D127" s="9" t="s">
-        <v>231</v>
+        <v>240</v>
       </c>
       <c r="E127" s="10" t="s">
-        <v>197</v>
+        <v>236</v>
       </c>
       <c r="F127" s="10" t="s">
-        <v>74</v>
+        <v>16</v>
       </c>
       <c r="G127" s="10" t="s">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="H127" s="10" t="s">
         <v>123</v>
       </c>
-      <c r="I127" t="s">
-        <v>19</v>
+      <c r="I127" s="10" t="s">
+        <v>236</v>
       </c>
       <c r="J127" s="8" t="s">
         <v>84</v>
@@ -6263,7 +6335,7 @@
         <v>103</v>
       </c>
       <c r="L127" s="11" t="s">
-        <v>232</v>
+        <v>241</v>
       </c>
     </row>
     <row r="128" spans="1:12" x14ac:dyDescent="0.35">
@@ -6273,26 +6345,26 @@
       <c r="B128" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="C128" s="8">
-        <v>18</v>
+      <c r="C128">
+        <v>127</v>
       </c>
       <c r="D128" s="9" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="E128" s="10" t="s">
-        <v>197</v>
+        <v>236</v>
       </c>
       <c r="F128" s="10" t="s">
-        <v>74</v>
+        <v>16</v>
       </c>
       <c r="G128" s="10" t="s">
-        <v>203</v>
+        <v>153</v>
       </c>
       <c r="H128" s="10" t="s">
         <v>123</v>
       </c>
-      <c r="I128" t="s">
-        <v>19</v>
+      <c r="I128" s="10" t="s">
+        <v>236</v>
       </c>
       <c r="J128" s="8" t="s">
         <v>84</v>
@@ -6301,7 +6373,7 @@
         <v>103</v>
       </c>
       <c r="L128" s="11" t="s">
-        <v>234</v>
+        <v>243</v>
       </c>
     </row>
     <row r="129" spans="1:12" x14ac:dyDescent="0.35">
@@ -6311,26 +6383,26 @@
       <c r="B129" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="C129" s="8">
-        <v>19</v>
+      <c r="C129">
+        <v>128</v>
       </c>
       <c r="D129" s="9" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="E129" s="10" t="s">
         <v>236</v>
       </c>
       <c r="F129" s="10" t="s">
-        <v>114</v>
+        <v>16</v>
       </c>
       <c r="G129" s="10" t="s">
-        <v>203</v>
+        <v>153</v>
       </c>
       <c r="H129" s="10" t="s">
-        <v>101</v>
-      </c>
-      <c r="I129" t="s">
-        <v>19</v>
+        <v>123</v>
+      </c>
+      <c r="I129" s="10" t="s">
+        <v>236</v>
       </c>
       <c r="J129" s="8" t="s">
         <v>84</v>
@@ -6338,8 +6410,8 @@
       <c r="K129" s="10" t="s">
         <v>103</v>
       </c>
-      <c r="L129" s="11" t="s">
-        <v>237</v>
+      <c r="L129" t="s">
+        <v>245</v>
       </c>
     </row>
     <row r="130" spans="1:12" x14ac:dyDescent="0.35">
@@ -6349,11 +6421,11 @@
       <c r="B130" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="C130" s="8">
-        <v>20</v>
+      <c r="C130">
+        <v>129</v>
       </c>
       <c r="D130" s="9" t="s">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="E130" s="10" t="s">
         <v>236</v>
@@ -6362,7 +6434,7 @@
         <v>16</v>
       </c>
       <c r="G130" s="10" t="s">
-        <v>203</v>
+        <v>150</v>
       </c>
       <c r="H130" s="10" t="s">
         <v>123</v>
@@ -6377,7 +6449,7 @@
         <v>103</v>
       </c>
       <c r="L130" s="11" t="s">
-        <v>239</v>
+        <v>247</v>
       </c>
     </row>
     <row r="131" spans="1:12" x14ac:dyDescent="0.35">
@@ -6387,11 +6459,11 @@
       <c r="B131" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="C131" s="8">
-        <v>21</v>
+      <c r="C131">
+        <v>130</v>
       </c>
       <c r="D131" s="9" t="s">
-        <v>240</v>
+        <v>248</v>
       </c>
       <c r="E131" s="10" t="s">
         <v>236</v>
@@ -6400,7 +6472,7 @@
         <v>16</v>
       </c>
       <c r="G131" s="10" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="H131" s="10" t="s">
         <v>123</v>
@@ -6415,7 +6487,7 @@
         <v>103</v>
       </c>
       <c r="L131" s="11" t="s">
-        <v>241</v>
+        <v>249</v>
       </c>
     </row>
     <row r="132" spans="1:12" x14ac:dyDescent="0.35">
@@ -6425,11 +6497,11 @@
       <c r="B132" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="C132" s="8">
-        <v>22</v>
+      <c r="C132">
+        <v>131</v>
       </c>
       <c r="D132" s="9" t="s">
-        <v>242</v>
+        <v>250</v>
       </c>
       <c r="E132" s="10" t="s">
         <v>236</v>
@@ -6438,7 +6510,7 @@
         <v>16</v>
       </c>
       <c r="G132" s="10" t="s">
-        <v>153</v>
+        <v>108</v>
       </c>
       <c r="H132" s="10" t="s">
         <v>123</v>
@@ -6453,7 +6525,7 @@
         <v>103</v>
       </c>
       <c r="L132" s="11" t="s">
-        <v>243</v>
+        <v>251</v>
       </c>
     </row>
     <row r="133" spans="1:12" x14ac:dyDescent="0.35">
@@ -6463,11 +6535,11 @@
       <c r="B133" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="C133" s="8">
-        <v>23</v>
+      <c r="C133">
+        <v>132</v>
       </c>
       <c r="D133" s="9" t="s">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="E133" s="10" t="s">
         <v>236</v>
@@ -6490,8 +6562,8 @@
       <c r="K133" s="10" t="s">
         <v>103</v>
       </c>
-      <c r="L133" t="s">
-        <v>245</v>
+      <c r="L133" s="11" t="s">
+        <v>253</v>
       </c>
     </row>
     <row r="134" spans="1:12" x14ac:dyDescent="0.35">
@@ -6501,11 +6573,11 @@
       <c r="B134" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="C134" s="8">
-        <v>24</v>
+      <c r="C134">
+        <v>133</v>
       </c>
       <c r="D134" s="9" t="s">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="E134" s="10" t="s">
         <v>236</v>
@@ -6514,7 +6586,7 @@
         <v>16</v>
       </c>
       <c r="G134" s="10" t="s">
-        <v>150</v>
+        <v>108</v>
       </c>
       <c r="H134" s="10" t="s">
         <v>123</v>
@@ -6529,7 +6601,7 @@
         <v>103</v>
       </c>
       <c r="L134" s="11" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
     </row>
     <row r="135" spans="1:12" x14ac:dyDescent="0.35">
@@ -6539,26 +6611,26 @@
       <c r="B135" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="C135" s="8">
-        <v>25</v>
-      </c>
-      <c r="D135" s="9" t="s">
-        <v>248</v>
+      <c r="C135">
+        <v>134</v>
+      </c>
+      <c r="D135" s="13" t="s">
+        <v>256</v>
       </c>
       <c r="E135" s="10" t="s">
-        <v>236</v>
+        <v>197</v>
       </c>
       <c r="F135" s="10" t="s">
-        <v>16</v>
+        <v>83</v>
       </c>
       <c r="G135" s="10" t="s">
-        <v>108</v>
+        <v>200</v>
       </c>
       <c r="H135" s="10" t="s">
-        <v>123</v>
-      </c>
-      <c r="I135" s="10" t="s">
-        <v>236</v>
+        <v>101</v>
+      </c>
+      <c r="I135" s="8" t="s">
+        <v>19</v>
       </c>
       <c r="J135" s="8" t="s">
         <v>84</v>
@@ -6567,7 +6639,7 @@
         <v>103</v>
       </c>
       <c r="L135" s="11" t="s">
-        <v>249</v>
+        <v>257</v>
       </c>
     </row>
     <row r="136" spans="1:12" x14ac:dyDescent="0.35">
@@ -6577,26 +6649,26 @@
       <c r="B136" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="C136" s="8">
+      <c r="C136">
+        <v>135</v>
+      </c>
+      <c r="D136" s="13" t="s">
+        <v>258</v>
+      </c>
+      <c r="E136" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="F136" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="D136" s="9" t="s">
-        <v>250</v>
-      </c>
-      <c r="E136" s="10" t="s">
-        <v>236</v>
-      </c>
-      <c r="F136" s="10" t="s">
-        <v>16</v>
-      </c>
       <c r="G136" s="10" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="H136" s="10" t="s">
-        <v>123</v>
-      </c>
-      <c r="I136" s="10" t="s">
-        <v>236</v>
+        <v>101</v>
+      </c>
+      <c r="I136" t="s">
+        <v>19</v>
       </c>
       <c r="J136" s="8" t="s">
         <v>84</v>
@@ -6605,7 +6677,7 @@
         <v>103</v>
       </c>
       <c r="L136" s="11" t="s">
-        <v>251</v>
+        <v>259</v>
       </c>
     </row>
     <row r="137" spans="1:12" x14ac:dyDescent="0.35">
@@ -6615,26 +6687,26 @@
       <c r="B137" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="C137" s="8">
-        <v>27</v>
+      <c r="C137">
+        <v>136</v>
       </c>
       <c r="D137" s="9" t="s">
-        <v>252</v>
+        <v>260</v>
       </c>
       <c r="E137" s="10" t="s">
-        <v>236</v>
+        <v>80</v>
       </c>
       <c r="F137" s="10" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="G137" s="10" t="s">
         <v>153</v>
       </c>
       <c r="H137" s="10" t="s">
-        <v>123</v>
-      </c>
-      <c r="I137" s="10" t="s">
-        <v>236</v>
+        <v>101</v>
+      </c>
+      <c r="I137" t="s">
+        <v>19</v>
       </c>
       <c r="J137" s="8" t="s">
         <v>84</v>
@@ -6643,7 +6715,7 @@
         <v>103</v>
       </c>
       <c r="L137" s="11" t="s">
-        <v>253</v>
+        <v>261</v>
       </c>
     </row>
     <row r="138" spans="1:12" x14ac:dyDescent="0.35">
@@ -6653,26 +6725,26 @@
       <c r="B138" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="C138" s="8">
-        <v>28</v>
+      <c r="C138">
+        <v>137</v>
       </c>
       <c r="D138" s="9" t="s">
-        <v>254</v>
+        <v>262</v>
       </c>
       <c r="E138" s="10" t="s">
-        <v>236</v>
+        <v>80</v>
       </c>
       <c r="F138" s="10" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="G138" s="10" t="s">
-        <v>108</v>
+        <v>150</v>
       </c>
       <c r="H138" s="10" t="s">
-        <v>123</v>
-      </c>
-      <c r="I138" s="10" t="s">
-        <v>236</v>
+        <v>101</v>
+      </c>
+      <c r="I138" t="s">
+        <v>19</v>
       </c>
       <c r="J138" s="8" t="s">
         <v>84</v>
@@ -6681,7 +6753,7 @@
         <v>103</v>
       </c>
       <c r="L138" s="11" t="s">
-        <v>255</v>
+        <v>263</v>
       </c>
     </row>
     <row r="139" spans="1:12" x14ac:dyDescent="0.35">
@@ -6691,25 +6763,25 @@
       <c r="B139" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="C139" s="8">
-        <v>29</v>
-      </c>
-      <c r="D139" s="13" t="s">
-        <v>256</v>
+      <c r="C139">
+        <v>138</v>
+      </c>
+      <c r="D139" s="9" t="s">
+        <v>264</v>
       </c>
       <c r="E139" s="10" t="s">
-        <v>197</v>
+        <v>80</v>
       </c>
       <c r="F139" s="10" t="s">
-        <v>83</v>
+        <v>26</v>
       </c>
       <c r="G139" s="10" t="s">
-        <v>200</v>
+        <v>108</v>
       </c>
       <c r="H139" s="10" t="s">
         <v>101</v>
       </c>
-      <c r="I139" s="8" t="s">
+      <c r="I139" t="s">
         <v>19</v>
       </c>
       <c r="J139" s="8" t="s">
@@ -6719,7 +6791,7 @@
         <v>103</v>
       </c>
       <c r="L139" s="11" t="s">
-        <v>257</v>
+        <v>265</v>
       </c>
     </row>
     <row r="140" spans="1:12" x14ac:dyDescent="0.35">
@@ -6729,23 +6801,23 @@
       <c r="B140" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="C140" s="8">
-        <v>30</v>
-      </c>
-      <c r="D140" s="13" t="s">
-        <v>258</v>
+      <c r="C140">
+        <v>139</v>
+      </c>
+      <c r="D140" s="9" t="s">
+        <v>266</v>
       </c>
       <c r="E140" s="10" t="s">
-        <v>80</v>
+        <v>197</v>
       </c>
       <c r="F140" s="10" t="s">
-        <v>26</v>
+        <v>74</v>
       </c>
       <c r="G140" s="10" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="H140" s="10" t="s">
-        <v>101</v>
+        <v>123</v>
       </c>
       <c r="I140" t="s">
         <v>19</v>
@@ -6757,7 +6829,7 @@
         <v>103</v>
       </c>
       <c r="L140" s="11" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
     </row>
     <row r="141" spans="1:12" x14ac:dyDescent="0.35">
@@ -6767,20 +6839,20 @@
       <c r="B141" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="C141" s="8">
-        <v>31</v>
+      <c r="C141">
+        <v>140</v>
       </c>
       <c r="D141" s="9" t="s">
-        <v>260</v>
+        <v>268</v>
       </c>
       <c r="E141" s="10" t="s">
         <v>80</v>
       </c>
       <c r="F141" s="10" t="s">
-        <v>26</v>
+        <v>83</v>
       </c>
       <c r="G141" s="10" t="s">
-        <v>153</v>
+        <v>100</v>
       </c>
       <c r="H141" s="10" t="s">
         <v>101</v>
@@ -6795,7 +6867,7 @@
         <v>103</v>
       </c>
       <c r="L141" s="11" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
     </row>
     <row r="142" spans="1:12" x14ac:dyDescent="0.35">
@@ -6805,20 +6877,20 @@
       <c r="B142" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="C142" s="8">
-        <v>32</v>
+      <c r="C142">
+        <v>141</v>
       </c>
       <c r="D142" s="9" t="s">
-        <v>262</v>
+        <v>270</v>
       </c>
       <c r="E142" s="10" t="s">
-        <v>80</v>
+        <v>197</v>
       </c>
       <c r="F142" s="10" t="s">
-        <v>26</v>
+        <v>83</v>
       </c>
       <c r="G142" s="10" t="s">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="H142" s="10" t="s">
         <v>101</v>
@@ -6832,8 +6904,8 @@
       <c r="K142" s="10" t="s">
         <v>103</v>
       </c>
-      <c r="L142" s="11" t="s">
-        <v>263</v>
+      <c r="L142" t="s">
+        <v>271</v>
       </c>
     </row>
     <row r="143" spans="1:12" x14ac:dyDescent="0.35">
@@ -6843,20 +6915,20 @@
       <c r="B143" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="C143" s="8">
-        <v>33</v>
+      <c r="C143">
+        <v>142</v>
       </c>
       <c r="D143" s="9" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
       <c r="E143" s="10" t="s">
-        <v>80</v>
+        <v>197</v>
       </c>
       <c r="F143" s="10" t="s">
-        <v>26</v>
+        <v>83</v>
       </c>
       <c r="G143" s="10" t="s">
-        <v>108</v>
+        <v>203</v>
       </c>
       <c r="H143" s="10" t="s">
         <v>101</v>
@@ -6871,158 +6943,6 @@
         <v>103</v>
       </c>
       <c r="L143" s="11" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="144" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A144" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="B144" s="8" t="s">
-        <v>195</v>
-      </c>
-      <c r="C144" s="8">
-        <v>34</v>
-      </c>
-      <c r="D144" s="9" t="s">
-        <v>266</v>
-      </c>
-      <c r="E144" s="10" t="s">
-        <v>197</v>
-      </c>
-      <c r="F144" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="G144" s="10" t="s">
-        <v>108</v>
-      </c>
-      <c r="H144" s="10" t="s">
-        <v>123</v>
-      </c>
-      <c r="I144" t="s">
-        <v>19</v>
-      </c>
-      <c r="J144" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="K144" s="10" t="s">
-        <v>103</v>
-      </c>
-      <c r="L144" s="11" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="145" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A145" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="B145" s="8" t="s">
-        <v>195</v>
-      </c>
-      <c r="C145" s="8">
-        <v>35</v>
-      </c>
-      <c r="D145" s="9" t="s">
-        <v>268</v>
-      </c>
-      <c r="E145" s="10" t="s">
-        <v>80</v>
-      </c>
-      <c r="F145" s="10" t="s">
-        <v>83</v>
-      </c>
-      <c r="G145" s="10" t="s">
-        <v>100</v>
-      </c>
-      <c r="H145" s="10" t="s">
-        <v>101</v>
-      </c>
-      <c r="I145" t="s">
-        <v>19</v>
-      </c>
-      <c r="J145" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="K145" s="10" t="s">
-        <v>103</v>
-      </c>
-      <c r="L145" s="11" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="146" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A146" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="B146" s="8" t="s">
-        <v>195</v>
-      </c>
-      <c r="C146" s="8">
-        <v>36</v>
-      </c>
-      <c r="D146" s="9" t="s">
-        <v>270</v>
-      </c>
-      <c r="E146" s="10" t="s">
-        <v>197</v>
-      </c>
-      <c r="F146" s="10" t="s">
-        <v>83</v>
-      </c>
-      <c r="G146" s="10" t="s">
-        <v>200</v>
-      </c>
-      <c r="H146" s="10" t="s">
-        <v>101</v>
-      </c>
-      <c r="I146" t="s">
-        <v>19</v>
-      </c>
-      <c r="J146" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="K146" s="10" t="s">
-        <v>103</v>
-      </c>
-      <c r="L146" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="147" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A147" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="B147" s="8" t="s">
-        <v>195</v>
-      </c>
-      <c r="C147" s="8">
-        <v>37</v>
-      </c>
-      <c r="D147" s="9" t="s">
-        <v>272</v>
-      </c>
-      <c r="E147" s="10" t="s">
-        <v>197</v>
-      </c>
-      <c r="F147" s="10" t="s">
-        <v>83</v>
-      </c>
-      <c r="G147" s="10" t="s">
-        <v>203</v>
-      </c>
-      <c r="H147" s="10" t="s">
-        <v>101</v>
-      </c>
-      <c r="I147" t="s">
-        <v>19</v>
-      </c>
-      <c r="J147" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="K147" s="10" t="s">
-        <v>103</v>
-      </c>
-      <c r="L147" s="11" t="s">
         <v>273</v>
       </c>
     </row>
@@ -8789,7 +8709,7 @@
         <v>13</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>44</v>
       </c>
       <c r="D2" t="s">
         <v>98</v>
@@ -8827,8 +8747,7 @@
         <v>13</v>
       </c>
       <c r="C3">
-        <f>C2+1</f>
-        <v>2</v>
+        <v>45</v>
       </c>
       <c r="D3" t="s">
         <v>105</v>
@@ -8866,8 +8785,7 @@
         <v>13</v>
       </c>
       <c r="C4">
-        <f t="shared" ref="C4:C43" si="0">C3+1</f>
-        <v>3</v>
+        <v>46</v>
       </c>
       <c r="D4" t="s">
         <v>107</v>
@@ -8905,8 +8823,7 @@
         <v>13</v>
       </c>
       <c r="C5">
-        <f t="shared" si="0"/>
-        <v>4</v>
+        <v>47</v>
       </c>
       <c r="D5" t="s">
         <v>110</v>
@@ -8944,8 +8861,7 @@
         <v>13</v>
       </c>
       <c r="C6">
-        <f t="shared" si="0"/>
-        <v>5</v>
+        <v>48</v>
       </c>
       <c r="D6" t="s">
         <v>113</v>
@@ -8954,7 +8870,7 @@
         <v>113</v>
       </c>
       <c r="F6" t="s">
-        <v>114</v>
+        <v>26</v>
       </c>
       <c r="G6" t="s">
         <v>100</v>
@@ -8983,8 +8899,7 @@
         <v>13</v>
       </c>
       <c r="C7">
-        <f t="shared" si="0"/>
-        <v>6</v>
+        <v>49</v>
       </c>
       <c r="D7" t="s">
         <v>116</v>
@@ -9022,8 +8937,7 @@
         <v>13</v>
       </c>
       <c r="C8">
-        <f t="shared" si="0"/>
-        <v>7</v>
+        <v>50</v>
       </c>
       <c r="D8" t="s">
         <v>118</v>
@@ -9061,8 +8975,7 @@
         <v>13</v>
       </c>
       <c r="C9">
-        <f t="shared" si="0"/>
-        <v>8</v>
+        <v>51</v>
       </c>
       <c r="D9" t="s">
         <v>120</v>
@@ -9100,8 +9013,7 @@
         <v>13</v>
       </c>
       <c r="C10">
-        <f t="shared" si="0"/>
-        <v>9</v>
+        <v>52</v>
       </c>
       <c r="D10" t="s">
         <v>122</v>
@@ -9139,8 +9051,7 @@
         <v>13</v>
       </c>
       <c r="C11">
-        <f t="shared" si="0"/>
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="D11" t="s">
         <v>125</v>
@@ -9178,8 +9089,7 @@
         <v>13</v>
       </c>
       <c r="C12">
-        <f t="shared" si="0"/>
-        <v>11</v>
+        <v>54</v>
       </c>
       <c r="D12" t="s">
         <v>127</v>
@@ -9217,8 +9127,7 @@
         <v>13</v>
       </c>
       <c r="C13">
-        <f t="shared" si="0"/>
-        <v>12</v>
+        <v>55</v>
       </c>
       <c r="D13" t="s">
         <v>129</v>
@@ -9256,8 +9165,7 @@
         <v>13</v>
       </c>
       <c r="C14">
-        <f t="shared" si="0"/>
-        <v>13</v>
+        <v>56</v>
       </c>
       <c r="D14" t="s">
         <v>131</v>
@@ -9295,8 +9203,7 @@
         <v>13</v>
       </c>
       <c r="C15">
-        <f t="shared" si="0"/>
-        <v>14</v>
+        <v>57</v>
       </c>
       <c r="D15" t="s">
         <v>133</v>
@@ -9334,8 +9241,7 @@
         <v>13</v>
       </c>
       <c r="C16">
-        <f t="shared" si="0"/>
-        <v>15</v>
+        <v>58</v>
       </c>
       <c r="D16" t="s">
         <v>135</v>
@@ -9373,8 +9279,7 @@
         <v>13</v>
       </c>
       <c r="C17">
-        <f t="shared" si="0"/>
-        <v>16</v>
+        <v>59</v>
       </c>
       <c r="D17" t="s">
         <v>137</v>
@@ -9412,8 +9317,7 @@
         <v>13</v>
       </c>
       <c r="C18">
-        <f t="shared" si="0"/>
-        <v>17</v>
+        <v>60</v>
       </c>
       <c r="D18" t="s">
         <v>139</v>
@@ -9451,8 +9355,7 @@
         <v>13</v>
       </c>
       <c r="C19">
-        <f t="shared" si="0"/>
-        <v>18</v>
+        <v>61</v>
       </c>
       <c r="D19" t="s">
         <v>141</v>
@@ -9490,8 +9393,7 @@
         <v>13</v>
       </c>
       <c r="C20">
-        <f t="shared" si="0"/>
-        <v>19</v>
+        <v>62</v>
       </c>
       <c r="D20" t="s">
         <v>143</v>
@@ -9529,8 +9431,7 @@
         <v>13</v>
       </c>
       <c r="C21">
-        <f t="shared" si="0"/>
-        <v>20</v>
+        <v>63</v>
       </c>
       <c r="D21" t="s">
         <v>145</v>
@@ -9568,8 +9469,7 @@
         <v>13</v>
       </c>
       <c r="C22">
-        <f t="shared" si="0"/>
-        <v>21</v>
+        <v>64</v>
       </c>
       <c r="D22" t="s">
         <v>147</v>
@@ -9607,8 +9507,7 @@
         <v>13</v>
       </c>
       <c r="C23">
-        <f t="shared" si="0"/>
-        <v>22</v>
+        <v>65</v>
       </c>
       <c r="D23" t="s">
         <v>149</v>
@@ -9646,8 +9545,7 @@
         <v>13</v>
       </c>
       <c r="C24">
-        <f t="shared" si="0"/>
-        <v>23</v>
+        <v>66</v>
       </c>
       <c r="D24" t="s">
         <v>152</v>
@@ -9685,8 +9583,7 @@
         <v>13</v>
       </c>
       <c r="C25">
-        <f t="shared" si="0"/>
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="D25" t="s">
         <v>155</v>
@@ -9724,8 +9621,7 @@
         <v>13</v>
       </c>
       <c r="C26">
-        <f t="shared" si="0"/>
-        <v>25</v>
+        <v>68</v>
       </c>
       <c r="D26" t="s">
         <v>157</v>
@@ -9763,8 +9659,7 @@
         <v>13</v>
       </c>
       <c r="C27">
-        <f t="shared" si="0"/>
-        <v>26</v>
+        <v>69</v>
       </c>
       <c r="D27" t="s">
         <v>159</v>
@@ -9802,8 +9697,7 @@
         <v>13</v>
       </c>
       <c r="C28">
-        <f t="shared" si="0"/>
-        <v>27</v>
+        <v>70</v>
       </c>
       <c r="D28" t="s">
         <v>161</v>
@@ -9841,8 +9735,7 @@
         <v>13</v>
       </c>
       <c r="C29">
-        <f t="shared" si="0"/>
-        <v>28</v>
+        <v>71</v>
       </c>
       <c r="D29" t="s">
         <v>163</v>
@@ -9880,8 +9773,7 @@
         <v>13</v>
       </c>
       <c r="C30">
-        <f t="shared" si="0"/>
-        <v>29</v>
+        <v>72</v>
       </c>
       <c r="D30" t="s">
         <v>165</v>
@@ -9919,8 +9811,7 @@
         <v>13</v>
       </c>
       <c r="C31">
-        <f t="shared" si="0"/>
-        <v>30</v>
+        <v>73</v>
       </c>
       <c r="D31" t="s">
         <v>167</v>
@@ -9958,8 +9849,7 @@
         <v>13</v>
       </c>
       <c r="C32">
-        <f t="shared" si="0"/>
-        <v>31</v>
+        <v>74</v>
       </c>
       <c r="D32" t="s">
         <v>169</v>
@@ -9997,8 +9887,7 @@
         <v>13</v>
       </c>
       <c r="C33">
-        <f t="shared" si="0"/>
-        <v>32</v>
+        <v>75</v>
       </c>
       <c r="D33" t="s">
         <v>171</v>
@@ -10036,8 +9925,7 @@
         <v>13</v>
       </c>
       <c r="C34">
-        <f t="shared" si="0"/>
-        <v>33</v>
+        <v>76</v>
       </c>
       <c r="D34" t="s">
         <v>173</v>
@@ -10075,8 +9963,7 @@
         <v>13</v>
       </c>
       <c r="C35">
-        <f t="shared" si="0"/>
-        <v>34</v>
+        <v>77</v>
       </c>
       <c r="D35" t="s">
         <v>175</v>
@@ -10114,8 +10001,7 @@
         <v>13</v>
       </c>
       <c r="C36">
-        <f t="shared" si="0"/>
-        <v>35</v>
+        <v>78</v>
       </c>
       <c r="D36" t="s">
         <v>177</v>
@@ -10153,8 +10039,7 @@
         <v>13</v>
       </c>
       <c r="C37">
-        <f t="shared" si="0"/>
-        <v>36</v>
+        <v>79</v>
       </c>
       <c r="D37" t="s">
         <v>179</v>
@@ -10192,8 +10077,7 @@
         <v>13</v>
       </c>
       <c r="C38">
-        <f t="shared" si="0"/>
-        <v>37</v>
+        <v>80</v>
       </c>
       <c r="D38" t="s">
         <v>182</v>
@@ -10231,8 +10115,7 @@
         <v>13</v>
       </c>
       <c r="C39">
-        <f t="shared" si="0"/>
-        <v>38</v>
+        <v>81</v>
       </c>
       <c r="D39" t="s">
         <v>184</v>
@@ -10270,8 +10153,7 @@
         <v>13</v>
       </c>
       <c r="C40">
-        <f t="shared" si="0"/>
-        <v>39</v>
+        <v>82</v>
       </c>
       <c r="D40" t="s">
         <v>186</v>
@@ -10309,8 +10191,7 @@
         <v>13</v>
       </c>
       <c r="C41">
-        <f t="shared" si="0"/>
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="D41" t="s">
         <v>188</v>
@@ -10348,8 +10229,7 @@
         <v>13</v>
       </c>
       <c r="C42">
-        <f t="shared" si="0"/>
-        <v>41</v>
+        <v>84</v>
       </c>
       <c r="D42" t="s">
         <v>191</v>
@@ -10387,8 +10267,7 @@
         <v>13</v>
       </c>
       <c r="C43">
-        <f t="shared" si="0"/>
-        <v>42</v>
+        <v>85</v>
       </c>
       <c r="D43" t="s">
         <v>193</v>
@@ -10425,7 +10304,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E6501C2-1F4E-44C1-926E-7B80FAB5E9FA}">
-  <dimension ref="A1:L21"/>
+  <dimension ref="A1:L22"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="4" max="4" width="38" customWidth="1"/>
@@ -10482,8 +10361,8 @@
       <c r="B2" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="C2" s="8">
-        <v>1</v>
+      <c r="C2">
+        <v>86</v>
       </c>
       <c r="D2" s="9" t="s">
         <v>274</v>
@@ -10509,7 +10388,7 @@
       <c r="K2" s="10" t="s">
         <v>103</v>
       </c>
-      <c r="L2" s="16" t="s">
+      <c r="L2" s="19" t="s">
         <v>277</v>
       </c>
     </row>
@@ -10520,8 +10399,8 @@
       <c r="B3" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="C3" s="8">
-        <v>2</v>
+      <c r="C3">
+        <v>87</v>
       </c>
       <c r="D3" s="9" t="s">
         <v>278</v>
@@ -10547,7 +10426,7 @@
       <c r="K3" s="10" t="s">
         <v>103</v>
       </c>
-      <c r="L3" s="16" t="s">
+      <c r="L3" s="19" t="s">
         <v>279</v>
       </c>
     </row>
@@ -10558,8 +10437,8 @@
       <c r="B4" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="C4" s="8">
-        <v>3</v>
+      <c r="C4">
+        <v>88</v>
       </c>
       <c r="D4" s="9" t="s">
         <v>280</v>
@@ -10585,7 +10464,7 @@
       <c r="K4" s="10" t="s">
         <v>103</v>
       </c>
-      <c r="L4" s="16" t="s">
+      <c r="L4" s="19" t="s">
         <v>281</v>
       </c>
     </row>
@@ -10596,8 +10475,8 @@
       <c r="B5" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="C5" s="8">
-        <v>4</v>
+      <c r="C5">
+        <v>89</v>
       </c>
       <c r="D5" s="9" t="s">
         <v>282</v>
@@ -10623,7 +10502,7 @@
       <c r="K5" s="10" t="s">
         <v>103</v>
       </c>
-      <c r="L5" s="16" t="s">
+      <c r="L5" s="19" t="s">
         <v>283</v>
       </c>
     </row>
@@ -10634,8 +10513,8 @@
       <c r="B6" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="C6" s="8">
-        <v>5</v>
+      <c r="C6">
+        <v>90</v>
       </c>
       <c r="D6" s="9" t="s">
         <v>284</v>
@@ -10661,7 +10540,7 @@
       <c r="K6" s="10" t="s">
         <v>103</v>
       </c>
-      <c r="L6" s="16" t="s">
+      <c r="L6" s="19" t="s">
         <v>287</v>
       </c>
     </row>
@@ -10672,8 +10551,8 @@
       <c r="B7" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="C7" s="8">
-        <v>6</v>
+      <c r="C7">
+        <v>91</v>
       </c>
       <c r="D7" s="9" t="s">
         <v>286</v>
@@ -10699,7 +10578,7 @@
       <c r="K7" s="10" t="s">
         <v>103</v>
       </c>
-      <c r="L7" s="16" t="s">
+      <c r="L7" s="19" t="s">
         <v>285</v>
       </c>
     </row>
@@ -10710,8 +10589,8 @@
       <c r="B8" t="s">
         <v>195</v>
       </c>
-      <c r="C8" s="8">
-        <v>7</v>
+      <c r="C8">
+        <v>92</v>
       </c>
       <c r="D8" t="s">
         <v>288</v>
@@ -10737,7 +10616,7 @@
       <c r="K8" t="s">
         <v>103</v>
       </c>
-      <c r="L8" s="17" t="s">
+      <c r="L8" s="20" t="s">
         <v>289</v>
       </c>
     </row>
@@ -10748,8 +10627,8 @@
       <c r="B9" t="s">
         <v>195</v>
       </c>
-      <c r="C9" s="8">
-        <v>8</v>
+      <c r="C9">
+        <v>93</v>
       </c>
       <c r="D9" t="s">
         <v>290</v>
@@ -10775,7 +10654,7 @@
       <c r="K9" t="s">
         <v>103</v>
       </c>
-      <c r="L9" s="17" t="s">
+      <c r="L9" s="20" t="s">
         <v>291</v>
       </c>
     </row>
@@ -10786,8 +10665,8 @@
       <c r="B10" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="C10" s="8">
-        <v>9</v>
+      <c r="C10">
+        <v>94</v>
       </c>
       <c r="D10" s="9" t="s">
         <v>292</v>
@@ -10813,7 +10692,7 @@
       <c r="K10" s="10" t="s">
         <v>103</v>
       </c>
-      <c r="L10" s="16" t="s">
+      <c r="L10" s="19" t="s">
         <v>293</v>
       </c>
     </row>
@@ -10824,8 +10703,8 @@
       <c r="B11" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="C11" s="8">
-        <v>10</v>
+      <c r="C11">
+        <v>95</v>
       </c>
       <c r="D11" s="9" t="s">
         <v>294</v>
@@ -10851,7 +10730,7 @@
       <c r="K11" s="10" t="s">
         <v>103</v>
       </c>
-      <c r="L11" s="16" t="s">
+      <c r="L11" s="19" t="s">
         <v>295</v>
       </c>
     </row>
@@ -10862,8 +10741,8 @@
       <c r="B12" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="C12" s="8">
-        <v>11</v>
+      <c r="C12">
+        <v>96</v>
       </c>
       <c r="D12" s="9" t="s">
         <v>296</v>
@@ -10889,7 +10768,7 @@
       <c r="K12" s="10" t="s">
         <v>103</v>
       </c>
-      <c r="L12" s="16" t="s">
+      <c r="L12" s="19" t="s">
         <v>297</v>
       </c>
     </row>
@@ -10900,19 +10779,19 @@
       <c r="B13" t="s">
         <v>298</v>
       </c>
-      <c r="C13" s="8">
-        <v>12</v>
-      </c>
-      <c r="D13" s="18" t="s">
+      <c r="C13">
+        <v>97</v>
+      </c>
+      <c r="D13" s="17" t="s">
         <v>299</v>
       </c>
-      <c r="E13" s="19" t="s">
+      <c r="E13" s="18" t="s">
         <v>275</v>
       </c>
-      <c r="F13" s="20" t="s">
+      <c r="F13" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="G13" s="19" t="s">
+      <c r="G13" s="18" t="s">
         <v>108</v>
       </c>
       <c r="H13" s="10" t="s">
@@ -10924,10 +10803,10 @@
       <c r="J13" t="s">
         <v>102</v>
       </c>
-      <c r="K13" s="19" t="s">
-        <v>103</v>
-      </c>
-      <c r="L13" s="16" t="s">
+      <c r="K13" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="L13" s="19" t="s">
         <v>300</v>
       </c>
     </row>
@@ -10938,19 +10817,19 @@
       <c r="B14" t="s">
         <v>298</v>
       </c>
-      <c r="C14" s="8">
-        <v>13</v>
-      </c>
-      <c r="D14" s="18" t="s">
+      <c r="C14">
+        <v>98</v>
+      </c>
+      <c r="D14" s="17" t="s">
         <v>301</v>
       </c>
-      <c r="E14" s="19" t="s">
+      <c r="E14" s="18" t="s">
         <v>275</v>
       </c>
-      <c r="F14" s="20" t="s">
+      <c r="F14" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="G14" s="19" t="s">
+      <c r="G14" s="18" t="s">
         <v>108</v>
       </c>
       <c r="H14" s="10" t="s">
@@ -10962,10 +10841,10 @@
       <c r="J14" t="s">
         <v>102</v>
       </c>
-      <c r="K14" s="19" t="s">
-        <v>103</v>
-      </c>
-      <c r="L14" s="16" t="s">
+      <c r="K14" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="L14" s="19" t="s">
         <v>302</v>
       </c>
     </row>
@@ -10976,19 +10855,19 @@
       <c r="B15" t="s">
         <v>298</v>
       </c>
-      <c r="C15" s="8">
-        <v>14</v>
-      </c>
-      <c r="D15" s="18" t="s">
+      <c r="C15">
+        <v>99</v>
+      </c>
+      <c r="D15" s="17" t="s">
         <v>303</v>
       </c>
-      <c r="E15" s="19" t="s">
+      <c r="E15" s="18" t="s">
         <v>275</v>
       </c>
-      <c r="F15" s="20" t="s">
+      <c r="F15" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="G15" s="19" t="s">
+      <c r="G15" s="18" t="s">
         <v>150</v>
       </c>
       <c r="H15" s="10" t="s">
@@ -11000,10 +10879,10 @@
       <c r="J15" t="s">
         <v>102</v>
       </c>
-      <c r="K15" s="19" t="s">
-        <v>103</v>
-      </c>
-      <c r="L15" s="17" t="s">
+      <c r="K15" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="L15" s="20" t="s">
         <v>304</v>
       </c>
     </row>
@@ -11014,19 +10893,19 @@
       <c r="B16" t="s">
         <v>298</v>
       </c>
-      <c r="C16" s="8">
-        <v>15</v>
-      </c>
-      <c r="D16" s="18" t="s">
+      <c r="C16">
+        <v>100</v>
+      </c>
+      <c r="D16" s="17" t="s">
         <v>305</v>
       </c>
-      <c r="E16" s="19" t="s">
+      <c r="E16" s="18" t="s">
         <v>275</v>
       </c>
-      <c r="F16" s="20" t="s">
+      <c r="F16" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="G16" s="19" t="s">
+      <c r="G16" s="18" t="s">
         <v>150</v>
       </c>
       <c r="H16" s="10" t="s">
@@ -11038,10 +10917,10 @@
       <c r="J16" t="s">
         <v>102</v>
       </c>
-      <c r="K16" s="19" t="s">
-        <v>103</v>
-      </c>
-      <c r="L16" s="17" t="s">
+      <c r="K16" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="L16" s="20" t="s">
         <v>306</v>
       </c>
     </row>
@@ -11052,19 +10931,19 @@
       <c r="B17" t="s">
         <v>298</v>
       </c>
-      <c r="C17" s="8">
-        <v>16</v>
-      </c>
-      <c r="D17" s="18" t="s">
+      <c r="C17">
+        <v>101</v>
+      </c>
+      <c r="D17" s="17" t="s">
         <v>307</v>
       </c>
-      <c r="E17" s="19" t="s">
+      <c r="E17" s="18" t="s">
         <v>275</v>
       </c>
-      <c r="F17" s="20" t="s">
+      <c r="F17" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="G17" s="19" t="s">
+      <c r="G17" s="18" t="s">
         <v>150</v>
       </c>
       <c r="H17" s="10" t="s">
@@ -11076,10 +10955,10 @@
       <c r="J17" t="s">
         <v>102</v>
       </c>
-      <c r="K17" s="19" t="s">
-        <v>103</v>
-      </c>
-      <c r="L17" s="16" t="s">
+      <c r="K17" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="L17" s="19" t="s">
         <v>308</v>
       </c>
     </row>
@@ -11090,19 +10969,19 @@
       <c r="B18" t="s">
         <v>298</v>
       </c>
-      <c r="C18" s="8">
-        <v>17</v>
-      </c>
-      <c r="D18" s="18" t="s">
+      <c r="C18">
+        <v>102</v>
+      </c>
+      <c r="D18" s="17" t="s">
         <v>309</v>
       </c>
-      <c r="E18" s="19" t="s">
+      <c r="E18" s="18" t="s">
         <v>275</v>
       </c>
-      <c r="F18" s="20" t="s">
+      <c r="F18" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="G18" s="19" t="s">
+      <c r="G18" s="18" t="s">
         <v>150</v>
       </c>
       <c r="H18" s="10" t="s">
@@ -11114,10 +10993,10 @@
       <c r="J18" t="s">
         <v>102</v>
       </c>
-      <c r="K18" s="19" t="s">
-        <v>103</v>
-      </c>
-      <c r="L18" s="16" t="s">
+      <c r="K18" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="L18" s="19" t="s">
         <v>310</v>
       </c>
     </row>
@@ -11128,19 +11007,19 @@
       <c r="B19" t="s">
         <v>298</v>
       </c>
-      <c r="C19" s="8">
-        <v>18</v>
-      </c>
-      <c r="D19" s="18" t="s">
+      <c r="C19">
+        <v>103</v>
+      </c>
+      <c r="D19" s="17" t="s">
         <v>311</v>
       </c>
-      <c r="E19" s="19" t="s">
+      <c r="E19" s="18" t="s">
         <v>275</v>
       </c>
-      <c r="F19" s="20" t="s">
+      <c r="F19" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="G19" s="19" t="s">
+      <c r="G19" s="18" t="s">
         <v>276</v>
       </c>
       <c r="H19" s="10" t="s">
@@ -11152,10 +11031,10 @@
       <c r="J19" t="s">
         <v>102</v>
       </c>
-      <c r="K19" s="19" t="s">
-        <v>103</v>
-      </c>
-      <c r="L19" s="16" t="s">
+      <c r="K19" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="L19" s="19" t="s">
         <v>312</v>
       </c>
     </row>
@@ -11166,19 +11045,19 @@
       <c r="B20" t="s">
         <v>298</v>
       </c>
-      <c r="C20" s="8">
-        <v>19</v>
-      </c>
-      <c r="D20" s="18" t="s">
+      <c r="C20">
+        <v>104</v>
+      </c>
+      <c r="D20" s="17" t="s">
         <v>313</v>
       </c>
-      <c r="E20" s="19" t="s">
+      <c r="E20" s="18" t="s">
         <v>275</v>
       </c>
-      <c r="F20" s="20" t="s">
+      <c r="F20" s="16" t="s">
         <v>83</v>
       </c>
-      <c r="G20" s="19" t="s">
+      <c r="G20" s="18" t="s">
         <v>276</v>
       </c>
       <c r="H20" s="10" t="s">
@@ -11190,10 +11069,10 @@
       <c r="J20" t="s">
         <v>111</v>
       </c>
-      <c r="K20" s="19" t="s">
-        <v>103</v>
-      </c>
-      <c r="L20" s="16" t="s">
+      <c r="K20" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="L20" s="19" t="s">
         <v>314</v>
       </c>
     </row>
@@ -11205,7 +11084,7 @@
         <v>195</v>
       </c>
       <c r="C21">
-        <v>20</v>
+        <v>105</v>
       </c>
       <c r="D21" t="s">
         <v>315</v>
@@ -11228,12 +11107,15 @@
       <c r="J21" t="s">
         <v>111</v>
       </c>
-      <c r="K21" s="19" t="s">
-        <v>103</v>
-      </c>
-      <c r="L21" s="17" t="s">
+      <c r="K21" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="L21" s="20" t="s">
         <v>316</v>
       </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="L22" s="20"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -11297,8 +11179,8 @@
       <c r="B2" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="C2" s="8">
-        <v>1</v>
+      <c r="C2">
+        <v>106</v>
       </c>
       <c r="D2" s="9" t="s">
         <v>196</v>
@@ -11335,8 +11217,8 @@
       <c r="B3" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="C3" s="8">
-        <v>2</v>
+      <c r="C3">
+        <v>107</v>
       </c>
       <c r="D3" s="9" t="s">
         <v>199</v>
@@ -11373,8 +11255,8 @@
       <c r="B4" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="C4" s="8">
-        <v>3</v>
+      <c r="C4">
+        <v>108</v>
       </c>
       <c r="D4" s="9" t="s">
         <v>202</v>
@@ -11411,8 +11293,8 @@
       <c r="B5" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="C5" s="8">
-        <v>4</v>
+      <c r="C5">
+        <v>109</v>
       </c>
       <c r="D5" s="9" t="s">
         <v>205</v>
@@ -11449,8 +11331,8 @@
       <c r="B6" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="C6" s="8">
-        <v>5</v>
+      <c r="C6">
+        <v>110</v>
       </c>
       <c r="D6" s="9" t="s">
         <v>207</v>
@@ -11487,8 +11369,8 @@
       <c r="B7" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="C7" s="8">
-        <v>6</v>
+      <c r="C7">
+        <v>111</v>
       </c>
       <c r="D7" s="9" t="s">
         <v>209</v>
@@ -11525,8 +11407,8 @@
       <c r="B8" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="C8" s="8">
-        <v>7</v>
+      <c r="C8">
+        <v>112</v>
       </c>
       <c r="D8" s="8" t="s">
         <v>211</v>
@@ -11563,8 +11445,8 @@
       <c r="B9" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="C9" s="8">
-        <v>8</v>
+      <c r="C9">
+        <v>113</v>
       </c>
       <c r="D9" s="9" t="s">
         <v>213</v>
@@ -11601,8 +11483,8 @@
       <c r="B10" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="C10" s="8">
-        <v>9</v>
+      <c r="C10">
+        <v>114</v>
       </c>
       <c r="D10" s="9" t="s">
         <v>215</v>
@@ -11639,8 +11521,8 @@
       <c r="B11" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="C11" s="8">
-        <v>10</v>
+      <c r="C11">
+        <v>115</v>
       </c>
       <c r="D11" s="9" t="s">
         <v>217</v>
@@ -11677,8 +11559,8 @@
       <c r="B12" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="C12" s="8">
-        <v>11</v>
+      <c r="C12">
+        <v>116</v>
       </c>
       <c r="D12" s="9" t="s">
         <v>219</v>
@@ -11715,8 +11597,8 @@
       <c r="B13" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="C13" s="8">
-        <v>12</v>
+      <c r="C13">
+        <v>117</v>
       </c>
       <c r="D13" s="9" t="s">
         <v>221</v>
@@ -11753,8 +11635,8 @@
       <c r="B14" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="C14" s="8">
-        <v>13</v>
+      <c r="C14">
+        <v>118</v>
       </c>
       <c r="D14" s="8" t="s">
         <v>223</v>
@@ -11791,8 +11673,8 @@
       <c r="B15" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="C15" s="8">
-        <v>14</v>
+      <c r="C15">
+        <v>119</v>
       </c>
       <c r="D15" s="9" t="s">
         <v>225</v>
@@ -11829,8 +11711,8 @@
       <c r="B16" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="C16" s="8">
-        <v>15</v>
+      <c r="C16">
+        <v>120</v>
       </c>
       <c r="D16" s="9" t="s">
         <v>227</v>
@@ -11867,8 +11749,8 @@
       <c r="B17" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="C17" s="8">
-        <v>16</v>
+      <c r="C17">
+        <v>121</v>
       </c>
       <c r="D17" s="9" t="s">
         <v>229</v>
@@ -11905,8 +11787,8 @@
       <c r="B18" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="C18" s="8">
-        <v>17</v>
+      <c r="C18">
+        <v>122</v>
       </c>
       <c r="D18" s="9" t="s">
         <v>231</v>
@@ -11943,8 +11825,8 @@
       <c r="B19" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="C19" s="8">
-        <v>18</v>
+      <c r="C19">
+        <v>123</v>
       </c>
       <c r="D19" s="9" t="s">
         <v>233</v>
@@ -11981,8 +11863,8 @@
       <c r="B20" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="C20" s="8">
-        <v>19</v>
+      <c r="C20">
+        <v>124</v>
       </c>
       <c r="D20" s="9" t="s">
         <v>235</v>
@@ -12019,8 +11901,8 @@
       <c r="B21" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="C21" s="8">
-        <v>20</v>
+      <c r="C21">
+        <v>125</v>
       </c>
       <c r="D21" s="9" t="s">
         <v>238</v>
@@ -12057,8 +11939,8 @@
       <c r="B22" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="C22" s="8">
-        <v>21</v>
+      <c r="C22">
+        <v>126</v>
       </c>
       <c r="D22" s="9" t="s">
         <v>240</v>
@@ -12095,8 +11977,8 @@
       <c r="B23" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="C23" s="8">
-        <v>22</v>
+      <c r="C23">
+        <v>127</v>
       </c>
       <c r="D23" s="9" t="s">
         <v>242</v>
@@ -12133,8 +12015,8 @@
       <c r="B24" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="C24" s="8">
-        <v>23</v>
+      <c r="C24">
+        <v>128</v>
       </c>
       <c r="D24" s="9" t="s">
         <v>244</v>
@@ -12171,8 +12053,8 @@
       <c r="B25" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="C25" s="8">
-        <v>24</v>
+      <c r="C25">
+        <v>129</v>
       </c>
       <c r="D25" s="9" t="s">
         <v>246</v>
@@ -12209,8 +12091,8 @@
       <c r="B26" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="C26" s="8">
-        <v>25</v>
+      <c r="C26">
+        <v>130</v>
       </c>
       <c r="D26" s="9" t="s">
         <v>248</v>
@@ -12247,8 +12129,8 @@
       <c r="B27" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="C27" s="8">
-        <v>26</v>
+      <c r="C27">
+        <v>131</v>
       </c>
       <c r="D27" s="9" t="s">
         <v>250</v>
@@ -12285,8 +12167,8 @@
       <c r="B28" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="C28" s="8">
-        <v>27</v>
+      <c r="C28">
+        <v>132</v>
       </c>
       <c r="D28" s="9" t="s">
         <v>252</v>
@@ -12323,8 +12205,8 @@
       <c r="B29" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="C29" s="8">
-        <v>28</v>
+      <c r="C29">
+        <v>133</v>
       </c>
       <c r="D29" s="9" t="s">
         <v>254</v>
@@ -12361,8 +12243,8 @@
       <c r="B30" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="C30" s="8">
-        <v>29</v>
+      <c r="C30">
+        <v>134</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>256</v>
@@ -12399,8 +12281,8 @@
       <c r="B31" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="C31" s="8">
-        <v>30</v>
+      <c r="C31">
+        <v>135</v>
       </c>
       <c r="D31" s="13" t="s">
         <v>258</v>
@@ -12437,8 +12319,8 @@
       <c r="B32" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="C32" s="8">
-        <v>31</v>
+      <c r="C32">
+        <v>136</v>
       </c>
       <c r="D32" s="9" t="s">
         <v>260</v>
@@ -12475,8 +12357,8 @@
       <c r="B33" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="C33" s="8">
-        <v>32</v>
+      <c r="C33">
+        <v>137</v>
       </c>
       <c r="D33" s="9" t="s">
         <v>262</v>
@@ -12513,8 +12395,8 @@
       <c r="B34" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="C34" s="8">
-        <v>33</v>
+      <c r="C34">
+        <v>138</v>
       </c>
       <c r="D34" s="9" t="s">
         <v>264</v>
@@ -12551,8 +12433,8 @@
       <c r="B35" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="C35" s="8">
-        <v>34</v>
+      <c r="C35">
+        <v>139</v>
       </c>
       <c r="D35" s="9" t="s">
         <v>266</v>
@@ -12589,8 +12471,8 @@
       <c r="B36" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="C36" s="8">
-        <v>35</v>
+      <c r="C36">
+        <v>140</v>
       </c>
       <c r="D36" s="9" t="s">
         <v>268</v>
@@ -12627,8 +12509,8 @@
       <c r="B37" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="C37" s="8">
-        <v>36</v>
+      <c r="C37">
+        <v>141</v>
       </c>
       <c r="D37" s="9" t="s">
         <v>270</v>
@@ -12665,8 +12547,8 @@
       <c r="B38" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="C38" s="8">
-        <v>37</v>
+      <c r="C38">
+        <v>142</v>
       </c>
       <c r="D38" s="9" t="s">
         <v>272</v>

--- a/docs/CDOP_SCHEMA.xlsx
+++ b/docs/CDOP_SCHEMA.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rockmtnins-my.sharepoint.com/personal/sebastian_weeks_rmi_org/Documents/Documents/CDOP Resources/UseCase_Category CSVs_JSONs/Master Version/5_20_26/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ghoffman\Other-GitHub\Carbon-Data-Open-Protocol\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="260" documentId="8_{836F5BCB-B55D-4CBC-976C-021D78BB22A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8DF6AF08-429A-40B0-9308-08C98546F4AF}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A21B714A-6CD9-4FF5-A0BA-B8A575A27B6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{743398AF-A4FE-47C4-9368-972E95242EBF}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{743398AF-A4FE-47C4-9368-972E95242EBF}"/>
   </bookViews>
   <sheets>
     <sheet name="Full List" sheetId="5" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3184" uniqueCount="317">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3184" uniqueCount="316">
   <si>
     <t>schema</t>
   </si>
@@ -564,9 +564,6 @@
     <t>attestations</t>
   </si>
   <si>
-    <t>list of attestations (e.g, child labor, labor worker attestation), if verified credentials are supported</t>
-  </si>
-  <si>
     <t>carbon_concession_contract_length</t>
   </si>
   <si>
@@ -639,9 +636,6 @@
     <t>land_right_attestation</t>
   </si>
   <si>
-    <t>Indicate the possesion of evidence of land rights</t>
-  </si>
-  <si>
     <t>land_rights_documentation</t>
   </si>
   <si>
@@ -651,9 +645,6 @@
     <t>land_ownership_attestation</t>
   </si>
   <si>
-    <t>Indicate the possesion of evidence of land ownership</t>
-  </si>
-  <si>
     <t>land_ownership_documentation</t>
   </si>
   <si>
@@ -663,9 +654,6 @@
     <t>legal_compliance_attestation</t>
   </si>
   <si>
-    <t>Indicate posession of legal compliance documentation and of explanation of how legislation informed and/or influenced project design</t>
-  </si>
-  <si>
     <t>legal_compliance_documentation</t>
   </si>
   <si>
@@ -738,9 +726,6 @@
     <t>previous_project_crediting_program_name</t>
   </si>
   <si>
-    <t>Select which crediting program(s) the project has recieved or seeking/has receieved or sought credits from</t>
-  </si>
-  <si>
     <t>Registration number for project under other crediting program</t>
   </si>
   <si>
@@ -777,9 +762,6 @@
     <t>public_comment_summary</t>
   </si>
   <si>
-    <t>Summary of outcomes of public comment procress</t>
-  </si>
-  <si>
     <t>forecast_annual_issuance</t>
   </si>
   <si>
@@ -987,10 +969,25 @@
     <t>previous_project_registration_id</t>
   </si>
   <si>
-    <t>Select which crediting program(s) the project has received or seeking/has receieved or sought credits from</t>
-  </si>
-  <si>
     <t>Registry recognition of cultural site designation</t>
+  </si>
+  <si>
+    <t>Summary of outcomes of public comment process</t>
+  </si>
+  <si>
+    <t>Indicate the possession of evidence of land ownership</t>
+  </si>
+  <si>
+    <t>Indicate the possession of evidence of land rights</t>
+  </si>
+  <si>
+    <t>Indicate possession of legal compliance documentation and of explanation of how legislation informed and/or influenced project design</t>
+  </si>
+  <si>
+    <t>Select which crediting program(s) the project has received or seeking/has received or sought credits from</t>
+  </si>
+  <si>
+    <t>list of attestations (e.g., child labor, labor worker attestation), if verified credentials are supported</t>
   </si>
 </sst>
 </file>
@@ -1496,22 +1493,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{752D3095-90A4-45FF-BD20-0492A3C6EFAC}">
   <dimension ref="A1:L143"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="21.1796875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="29.81640625" customWidth="1"/>
+    <col min="2" max="2" width="21.21875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="29.77734375" customWidth="1"/>
     <col min="5" max="5" width="17" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.54296875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.453125" customWidth="1"/>
-    <col min="8" max="8" width="17.54296875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.44140625" customWidth="1"/>
+    <col min="8" max="8" width="17.5546875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="25" customWidth="1"/>
-    <col min="10" max="10" width="12.1796875" customWidth="1"/>
-    <col min="11" max="11" width="14.1796875" customWidth="1"/>
+    <col min="10" max="10" width="12.21875" customWidth="1"/>
+    <col min="11" max="11" width="14.21875" customWidth="1"/>
     <col min="12" max="12" width="88" customWidth="1"/>
-    <col min="13" max="18" width="9.1796875" customWidth="1"/>
+    <col min="13" max="18" width="9.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1549,7 +1546,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -1560,7 +1557,7 @@
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="E2" t="s">
         <v>14</v>
@@ -1587,7 +1584,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -1598,10 +1595,10 @@
         <v>2</v>
       </c>
       <c r="D3" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="E3" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="F3" t="s">
         <v>15</v>
@@ -1625,7 +1622,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -1636,7 +1633,7 @@
         <v>3</v>
       </c>
       <c r="D4" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="E4" t="s">
         <v>24</v>
@@ -1663,7 +1660,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -1674,7 +1671,7 @@
         <v>4</v>
       </c>
       <c r="D5" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="E5" t="s">
         <v>14</v>
@@ -1701,7 +1698,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -1712,10 +1709,10 @@
         <v>5</v>
       </c>
       <c r="D6" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="E6" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="F6" t="s">
         <v>15</v>
@@ -1739,7 +1736,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -1750,7 +1747,7 @@
         <v>6</v>
       </c>
       <c r="D7" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="E7" t="s">
         <v>24</v>
@@ -1777,7 +1774,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -1788,7 +1785,7 @@
         <v>7</v>
       </c>
       <c r="D8" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="E8" t="s">
         <v>14</v>
@@ -1815,7 +1812,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -1826,10 +1823,10 @@
         <v>8</v>
       </c>
       <c r="D9" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="E9" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="F9" t="s">
         <v>25</v>
@@ -1853,7 +1850,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -1864,7 +1861,7 @@
         <v>9</v>
       </c>
       <c r="D10" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="E10" t="s">
         <v>24</v>
@@ -1891,7 +1888,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>12</v>
       </c>
@@ -1902,7 +1899,7 @@
         <v>10</v>
       </c>
       <c r="D11" t="s">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="E11" t="s">
         <v>14</v>
@@ -1929,7 +1926,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>12</v>
       </c>
@@ -1940,10 +1937,10 @@
         <v>11</v>
       </c>
       <c r="D12" t="s">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="E12" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="F12" t="s">
         <v>25</v>
@@ -1967,7 +1964,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>12</v>
       </c>
@@ -1978,7 +1975,7 @@
         <v>12</v>
       </c>
       <c r="D13" t="s">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="E13" t="s">
         <v>24</v>
@@ -2005,7 +2002,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>12</v>
       </c>
@@ -2016,7 +2013,7 @@
         <v>13</v>
       </c>
       <c r="D14" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="E14" t="s">
         <v>14</v>
@@ -2043,7 +2040,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>12</v>
       </c>
@@ -2054,7 +2051,7 @@
         <v>14</v>
       </c>
       <c r="D15" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
       <c r="E15" t="s">
         <v>14</v>
@@ -2081,7 +2078,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>12</v>
       </c>
@@ -2092,10 +2089,10 @@
         <v>15</v>
       </c>
       <c r="D16" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="E16" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="F16" t="s">
         <v>25</v>
@@ -2119,7 +2116,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>12</v>
       </c>
@@ -2130,10 +2127,10 @@
         <v>16</v>
       </c>
       <c r="D17" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
       <c r="E17" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="F17" t="s">
         <v>25</v>
@@ -2157,7 +2154,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>12</v>
       </c>
@@ -2168,7 +2165,7 @@
         <v>17</v>
       </c>
       <c r="D18" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="E18" t="s">
         <v>24</v>
@@ -2195,7 +2192,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>12</v>
       </c>
@@ -2206,7 +2203,7 @@
         <v>18</v>
       </c>
       <c r="D19" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
       <c r="E19" t="s">
         <v>24</v>
@@ -2233,7 +2230,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>12</v>
       </c>
@@ -2244,7 +2241,7 @@
         <v>19</v>
       </c>
       <c r="D20" t="s">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="E20" t="s">
         <v>14</v>
@@ -2271,7 +2268,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>12</v>
       </c>
@@ -2282,10 +2279,10 @@
         <v>20</v>
       </c>
       <c r="D21" t="s">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="E21" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="F21" t="s">
         <v>25</v>
@@ -2309,7 +2306,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>12</v>
       </c>
@@ -2320,7 +2317,7 @@
         <v>21</v>
       </c>
       <c r="D22" t="s">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="E22" t="s">
         <v>24</v>
@@ -2347,7 +2344,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>12</v>
       </c>
@@ -2358,7 +2355,7 @@
         <v>22</v>
       </c>
       <c r="D23" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="E23" t="s">
         <v>14</v>
@@ -2385,7 +2382,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>12</v>
       </c>
@@ -2396,7 +2393,7 @@
         <v>23</v>
       </c>
       <c r="D24" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="E24" t="s">
         <v>22</v>
@@ -2423,7 +2420,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>12</v>
       </c>
@@ -2434,7 +2431,7 @@
         <v>24</v>
       </c>
       <c r="D25" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="E25" t="s">
         <v>24</v>
@@ -2461,7 +2458,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>12</v>
       </c>
@@ -2472,7 +2469,7 @@
         <v>25</v>
       </c>
       <c r="D26" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="E26" t="s">
         <v>14</v>
@@ -2499,7 +2496,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>12</v>
       </c>
@@ -2510,10 +2507,10 @@
         <v>26</v>
       </c>
       <c r="D27" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="E27" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="F27" t="s">
         <v>25</v>
@@ -2537,7 +2534,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>12</v>
       </c>
@@ -2548,7 +2545,7 @@
         <v>27</v>
       </c>
       <c r="D28" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="E28" t="s">
         <v>24</v>
@@ -2575,7 +2572,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>12</v>
       </c>
@@ -2613,7 +2610,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>12</v>
       </c>
@@ -2627,7 +2624,7 @@
         <v>55</v>
       </c>
       <c r="E30" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="F30" t="s">
         <v>25</v>
@@ -2651,7 +2648,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>12</v>
       </c>
@@ -2689,7 +2686,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>12</v>
       </c>
@@ -2700,7 +2697,7 @@
         <v>31</v>
       </c>
       <c r="D32" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="E32" t="s">
         <v>14</v>
@@ -2727,7 +2724,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>12</v>
       </c>
@@ -2738,10 +2735,10 @@
         <v>32</v>
       </c>
       <c r="D33" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="E33" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="F33" t="s">
         <v>25</v>
@@ -2765,7 +2762,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>12</v>
       </c>
@@ -2776,7 +2773,7 @@
         <v>33</v>
       </c>
       <c r="D34" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="E34" t="s">
         <v>24</v>
@@ -2803,7 +2800,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>12</v>
       </c>
@@ -2814,10 +2811,10 @@
         <v>34</v>
       </c>
       <c r="D35" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="E35" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="F35" t="s">
         <v>62</v>
@@ -2841,7 +2838,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>12</v>
       </c>
@@ -2852,10 +2849,10 @@
         <v>35</v>
       </c>
       <c r="D36" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="E36" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="F36" s="4" t="s">
         <v>62</v>
@@ -2879,7 +2876,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>12</v>
       </c>
@@ -2890,10 +2887,10 @@
         <v>36</v>
       </c>
       <c r="D37" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="E37" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="F37" t="s">
         <v>62</v>
@@ -2917,7 +2914,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>12</v>
       </c>
@@ -2928,10 +2925,10 @@
         <v>37</v>
       </c>
       <c r="D38" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="E38" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="F38" t="s">
         <v>68</v>
@@ -2955,7 +2952,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>12</v>
       </c>
@@ -2966,10 +2963,10 @@
         <v>38</v>
       </c>
       <c r="D39" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="E39" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="F39" t="s">
         <v>62</v>
@@ -2993,7 +2990,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>12</v>
       </c>
@@ -3004,10 +3001,10 @@
         <v>39</v>
       </c>
       <c r="D40" t="s">
+        <v>294</v>
+      </c>
+      <c r="E40" t="s">
         <v>300</v>
-      </c>
-      <c r="E40" t="s">
-        <v>306</v>
       </c>
       <c r="F40" t="s">
         <v>62</v>
@@ -3031,7 +3028,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>12</v>
       </c>
@@ -3042,10 +3039,10 @@
         <v>40</v>
       </c>
       <c r="D41" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="E41" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="F41" t="s">
         <v>68</v>
@@ -3069,7 +3066,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>12</v>
       </c>
@@ -3080,10 +3077,10 @@
         <v>41</v>
       </c>
       <c r="D42" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="E42" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="F42" t="s">
         <v>68</v>
@@ -3107,7 +3104,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>12</v>
       </c>
@@ -3118,10 +3115,10 @@
         <v>42</v>
       </c>
       <c r="D43" t="s">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="E43" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="F43" t="s">
         <v>15</v>
@@ -3145,7 +3142,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>12</v>
       </c>
@@ -3156,10 +3153,10 @@
         <v>43</v>
       </c>
       <c r="D44" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="E44" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="F44" s="4" t="s">
         <v>62</v>
@@ -3183,7 +3180,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>12</v>
       </c>
@@ -3197,7 +3194,7 @@
         <v>77</v>
       </c>
       <c r="E45" t="s">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="F45" t="s">
         <v>25</v>
@@ -3221,7 +3218,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>12</v>
       </c>
@@ -3235,7 +3232,7 @@
         <v>83</v>
       </c>
       <c r="E46" t="s">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="F46" t="s">
         <v>25</v>
@@ -3259,7 +3256,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>12</v>
       </c>
@@ -3273,7 +3270,7 @@
         <v>85</v>
       </c>
       <c r="E47" t="s">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="F47" t="s">
         <v>68</v>
@@ -3297,7 +3294,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>12</v>
       </c>
@@ -3311,7 +3308,7 @@
         <v>88</v>
       </c>
       <c r="E48" t="s">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="F48" t="s">
         <v>68</v>
@@ -3335,7 +3332,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>12</v>
       </c>
@@ -3373,7 +3370,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>12</v>
       </c>
@@ -3411,7 +3408,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>12</v>
       </c>
@@ -3449,7 +3446,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>12</v>
       </c>
@@ -3487,7 +3484,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>12</v>
       </c>
@@ -3525,7 +3522,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>12</v>
       </c>
@@ -3563,7 +3560,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>12</v>
       </c>
@@ -3601,7 +3598,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>12</v>
       </c>
@@ -3639,7 +3636,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>12</v>
       </c>
@@ -3677,7 +3674,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>12</v>
       </c>
@@ -3715,7 +3712,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>12</v>
       </c>
@@ -3753,7 +3750,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>12</v>
       </c>
@@ -3791,7 +3788,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>12</v>
       </c>
@@ -3829,7 +3826,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>12</v>
       </c>
@@ -3867,7 +3864,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>12</v>
       </c>
@@ -3905,7 +3902,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>12</v>
       </c>
@@ -3943,7 +3940,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>12</v>
       </c>
@@ -3981,7 +3978,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>12</v>
       </c>
@@ -4019,7 +4016,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>12</v>
       </c>
@@ -4057,7 +4054,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="68" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>12</v>
       </c>
@@ -4095,7 +4092,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>12</v>
       </c>
@@ -4133,7 +4130,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="70" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>12</v>
       </c>
@@ -4171,7 +4168,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="71" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>12</v>
       </c>
@@ -4209,7 +4206,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>12</v>
       </c>
@@ -4247,7 +4244,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="73" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>12</v>
       </c>
@@ -4261,7 +4258,7 @@
         <v>142</v>
       </c>
       <c r="E73" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="F73" t="s">
         <v>62</v>
@@ -4285,7 +4282,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="74" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>12</v>
       </c>
@@ -4299,7 +4296,7 @@
         <v>144</v>
       </c>
       <c r="E74" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="F74" t="s">
         <v>68</v>
@@ -4323,7 +4320,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="75" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>12</v>
       </c>
@@ -4337,7 +4334,7 @@
         <v>146</v>
       </c>
       <c r="E75" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="F75" t="s">
         <v>68</v>
@@ -4361,7 +4358,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="76" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>12</v>
       </c>
@@ -4375,7 +4372,7 @@
         <v>148</v>
       </c>
       <c r="E76" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="F76" t="s">
         <v>68</v>
@@ -4399,7 +4396,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="77" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>12</v>
       </c>
@@ -4413,7 +4410,7 @@
         <v>150</v>
       </c>
       <c r="E77" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="F77" t="s">
         <v>25</v>
@@ -4437,7 +4434,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="78" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>12</v>
       </c>
@@ -4451,7 +4448,7 @@
         <v>152</v>
       </c>
       <c r="E78" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="F78" t="s">
         <v>25</v>
@@ -4475,7 +4472,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="79" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>12</v>
       </c>
@@ -4489,7 +4486,7 @@
         <v>154</v>
       </c>
       <c r="E79" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="F79" t="s">
         <v>25</v>
@@ -4513,7 +4510,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="80" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>12</v>
       </c>
@@ -4527,7 +4524,7 @@
         <v>156</v>
       </c>
       <c r="E80" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="F80" t="s">
         <v>25</v>
@@ -4551,7 +4548,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="81" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>12</v>
       </c>
@@ -4565,7 +4562,7 @@
         <v>159</v>
       </c>
       <c r="E81" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="F81" t="s">
         <v>25</v>
@@ -4589,7 +4586,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="82" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>12</v>
       </c>
@@ -4627,7 +4624,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="83" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>12</v>
       </c>
@@ -4665,7 +4662,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="84" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>12</v>
       </c>
@@ -4703,7 +4700,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="85" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>12</v>
       </c>
@@ -4741,7 +4738,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="86" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>12</v>
       </c>
@@ -4779,7 +4776,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="87" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>12</v>
       </c>
@@ -4790,16 +4787,16 @@
         <v>86</v>
       </c>
       <c r="D87" s="9" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="F87" s="10" t="s">
         <v>15</v>
       </c>
       <c r="G87" s="10" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="H87" s="10" t="s">
         <v>100</v>
@@ -4814,10 +4811,10 @@
         <v>81</v>
       </c>
       <c r="L87" s="18" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="88" spans="1:12" x14ac:dyDescent="0.35">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="88" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>12</v>
       </c>
@@ -4828,10 +4825,10 @@
         <v>87</v>
       </c>
       <c r="D88" s="9" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="E88" s="10" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="F88" s="10" t="s">
         <v>15</v>
@@ -4852,10 +4849,10 @@
         <v>81</v>
       </c>
       <c r="L88" s="18" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="89" spans="1:12" x14ac:dyDescent="0.35">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="89" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>12</v>
       </c>
@@ -4866,7 +4863,7 @@
         <v>88</v>
       </c>
       <c r="D89" s="9" t="s">
-        <v>309</v>
+        <v>303</v>
       </c>
       <c r="E89" s="10" t="s">
         <v>14</v>
@@ -4890,10 +4887,10 @@
         <v>81</v>
       </c>
       <c r="L89" s="18" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="90" spans="1:12" x14ac:dyDescent="0.35">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="90" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>12</v>
       </c>
@@ -4904,7 +4901,7 @@
         <v>89</v>
       </c>
       <c r="D90" s="9" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="E90" s="10" t="s">
         <v>14</v>
@@ -4928,10 +4925,10 @@
         <v>81</v>
       </c>
       <c r="L90" s="18" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="91" spans="1:12" x14ac:dyDescent="0.35">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="91" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A91" s="8" t="s">
         <v>12</v>
       </c>
@@ -4942,7 +4939,7 @@
         <v>90</v>
       </c>
       <c r="D91" s="9" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="E91" s="10" t="s">
         <v>14</v>
@@ -4966,10 +4963,10 @@
         <v>81</v>
       </c>
       <c r="L91" s="18" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="92" spans="1:12" x14ac:dyDescent="0.35">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="92" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A92" s="8" t="s">
         <v>12</v>
       </c>
@@ -4980,7 +4977,7 @@
         <v>91</v>
       </c>
       <c r="D92" s="9" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="E92" s="10" t="s">
         <v>14</v>
@@ -5004,10 +5001,10 @@
         <v>81</v>
       </c>
       <c r="L92" s="18" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="93" spans="1:12" x14ac:dyDescent="0.35">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="93" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>12</v>
       </c>
@@ -5018,7 +5015,7 @@
         <v>92</v>
       </c>
       <c r="D93" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="E93" s="10" t="s">
         <v>14</v>
@@ -5042,10 +5039,10 @@
         <v>81</v>
       </c>
       <c r="L93" s="19" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="94" spans="1:12" x14ac:dyDescent="0.35">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="94" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>12</v>
       </c>
@@ -5056,7 +5053,7 @@
         <v>93</v>
       </c>
       <c r="D94" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="E94" s="10" t="s">
         <v>14</v>
@@ -5080,10 +5077,10 @@
         <v>81</v>
       </c>
       <c r="L94" s="19" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="95" spans="1:12" x14ac:dyDescent="0.35">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="95" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>12</v>
       </c>
@@ -5094,10 +5091,10 @@
         <v>94</v>
       </c>
       <c r="D95" s="9" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="F95" s="10" t="s">
         <v>68</v>
@@ -5118,10 +5115,10 @@
         <v>81</v>
       </c>
       <c r="L95" s="18" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="96" spans="1:12" x14ac:dyDescent="0.35">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="96" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>12</v>
       </c>
@@ -5132,10 +5129,10 @@
         <v>95</v>
       </c>
       <c r="D96" s="9" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="E96" s="10" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="F96" s="10" t="s">
         <v>68</v>
@@ -5156,10 +5153,10 @@
         <v>81</v>
       </c>
       <c r="L96" s="18" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="97" spans="1:12" x14ac:dyDescent="0.35">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="97" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>12</v>
       </c>
@@ -5170,16 +5167,16 @@
         <v>96</v>
       </c>
       <c r="D97" s="9" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="E97" s="10" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="F97" s="10" t="s">
         <v>15</v>
       </c>
       <c r="G97" s="10" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="H97" s="10" t="s">
         <v>100</v>
@@ -5194,24 +5191,24 @@
         <v>81</v>
       </c>
       <c r="L97" s="18" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="98" spans="1:12" x14ac:dyDescent="0.35">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="98" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>12</v>
       </c>
       <c r="B98" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="C98">
         <v>97</v>
       </c>
       <c r="D98" s="13" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="E98" s="10" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="F98" s="20" t="s">
         <v>25</v>
@@ -5232,24 +5229,24 @@
         <v>81</v>
       </c>
       <c r="L98" s="18" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="99" spans="1:12" x14ac:dyDescent="0.35">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="99" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>12</v>
       </c>
       <c r="B99" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="C99">
         <v>98</v>
       </c>
       <c r="D99" s="13" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="E99" s="10" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="F99" s="20" t="s">
         <v>25</v>
@@ -5270,24 +5267,24 @@
         <v>81</v>
       </c>
       <c r="L99" s="18" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="100" spans="1:12" x14ac:dyDescent="0.35">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="100" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>12</v>
       </c>
       <c r="B100" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="C100">
         <v>99</v>
       </c>
       <c r="D100" s="13" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="E100" s="10" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="F100" s="20" t="s">
         <v>25</v>
@@ -5308,24 +5305,24 @@
         <v>81</v>
       </c>
       <c r="L100" s="19" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="101" spans="1:12" x14ac:dyDescent="0.35">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="101" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>12</v>
       </c>
       <c r="B101" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="C101">
         <v>100</v>
       </c>
       <c r="D101" s="13" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="E101" s="10" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="F101" s="20" t="s">
         <v>25</v>
@@ -5346,24 +5343,24 @@
         <v>81</v>
       </c>
       <c r="L101" s="19" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="102" spans="1:12" x14ac:dyDescent="0.35">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="102" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>12</v>
       </c>
       <c r="B102" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="C102">
         <v>101</v>
       </c>
       <c r="D102" s="13" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="E102" s="10" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="F102" s="20" t="s">
         <v>25</v>
@@ -5384,24 +5381,24 @@
         <v>81</v>
       </c>
       <c r="L102" s="18" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="103" spans="1:12" x14ac:dyDescent="0.35">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="103" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>12</v>
       </c>
       <c r="B103" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="C103">
         <v>102</v>
       </c>
       <c r="D103" s="13" t="s">
-        <v>277</v>
+        <v>271</v>
       </c>
       <c r="E103" s="10" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="F103" s="20" t="s">
         <v>25</v>
@@ -5422,30 +5419,30 @@
         <v>81</v>
       </c>
       <c r="L103" s="18" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="104" spans="1:12" x14ac:dyDescent="0.35">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="104" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>12</v>
       </c>
       <c r="B104" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="C104">
         <v>103</v>
       </c>
       <c r="D104" s="13" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="E104" s="10" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="F104" s="20" t="s">
         <v>25</v>
       </c>
       <c r="G104" s="17" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="H104" s="10" t="s">
         <v>79</v>
@@ -5460,30 +5457,30 @@
         <v>81</v>
       </c>
       <c r="L104" s="18" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="105" spans="1:12" x14ac:dyDescent="0.35">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="105" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>12</v>
       </c>
       <c r="B105" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="C105">
         <v>104</v>
       </c>
       <c r="D105" s="13" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="E105" s="10" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="F105" s="16" t="s">
         <v>68</v>
       </c>
       <c r="G105" s="17" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="H105" s="10" t="s">
         <v>79</v>
@@ -5498,10 +5495,10 @@
         <v>81</v>
       </c>
       <c r="L105" s="18" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="106" spans="1:12" x14ac:dyDescent="0.35">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="106" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>12</v>
       </c>
@@ -5512,10 +5509,10 @@
         <v>105</v>
       </c>
       <c r="D106" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="E106" s="10" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="F106" t="s">
         <v>68</v>
@@ -5536,10 +5533,10 @@
         <v>81</v>
       </c>
       <c r="L106" s="19" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="107" spans="1:12" x14ac:dyDescent="0.35">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="107" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A107" s="8" t="s">
         <v>12</v>
       </c>
@@ -5574,10 +5571,10 @@
         <v>81</v>
       </c>
       <c r="L107" s="18" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="108" spans="1:12" x14ac:dyDescent="0.35">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="108" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A108" s="8" t="s">
         <v>12</v>
       </c>
@@ -5588,7 +5585,7 @@
         <v>107</v>
       </c>
       <c r="D108" s="9" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E108" s="10" t="s">
         <v>14</v>
@@ -5597,7 +5594,7 @@
         <v>68</v>
       </c>
       <c r="G108" s="10" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H108" s="10" t="s">
         <v>79</v>
@@ -5612,10 +5609,10 @@
         <v>81</v>
       </c>
       <c r="L108" s="11" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="109" spans="1:12" x14ac:dyDescent="0.35">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="109" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A109" s="8" t="s">
         <v>12</v>
       </c>
@@ -5626,7 +5623,7 @@
         <v>108</v>
       </c>
       <c r="D109" s="9" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E109" s="10" t="s">
         <v>14</v>
@@ -5635,7 +5632,7 @@
         <v>68</v>
       </c>
       <c r="G109" s="10" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H109" s="10" t="s">
         <v>79</v>
@@ -5650,10 +5647,10 @@
         <v>81</v>
       </c>
       <c r="L109" s="11" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="110" spans="1:12" x14ac:dyDescent="0.35">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="110" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A110" s="8" t="s">
         <v>12</v>
       </c>
@@ -5664,7 +5661,7 @@
         <v>109</v>
       </c>
       <c r="D110" s="9" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E110" s="10" t="s">
         <v>14</v>
@@ -5673,7 +5670,7 @@
         <v>62</v>
       </c>
       <c r="G110" s="10" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H110" s="10" t="s">
         <v>100</v>
@@ -5688,10 +5685,10 @@
         <v>81</v>
       </c>
       <c r="L110" s="11" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="111" spans="1:12" x14ac:dyDescent="0.35">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="111" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A111" s="8" t="s">
         <v>12</v>
       </c>
@@ -5702,7 +5699,7 @@
         <v>110</v>
       </c>
       <c r="D111" s="9" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E111" s="10" t="s">
         <v>14</v>
@@ -5711,7 +5708,7 @@
         <v>62</v>
       </c>
       <c r="G111" s="10" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H111" s="10" t="s">
         <v>100</v>
@@ -5726,10 +5723,10 @@
         <v>81</v>
       </c>
       <c r="L111" s="8" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="112" spans="1:12" x14ac:dyDescent="0.35">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="112" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A112" s="8" t="s">
         <v>12</v>
       </c>
@@ -5740,7 +5737,7 @@
         <v>111</v>
       </c>
       <c r="D112" s="9" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E112" s="10" t="s">
         <v>14</v>
@@ -5749,7 +5746,7 @@
         <v>68</v>
       </c>
       <c r="G112" s="10" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H112" s="10" t="s">
         <v>79</v>
@@ -5764,10 +5761,10 @@
         <v>81</v>
       </c>
       <c r="L112" s="11" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="113" spans="1:12" x14ac:dyDescent="0.35">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="113" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A113" s="8" t="s">
         <v>12</v>
       </c>
@@ -5778,7 +5775,7 @@
         <v>112</v>
       </c>
       <c r="D113" s="8" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E113" s="10" t="s">
         <v>14</v>
@@ -5787,7 +5784,7 @@
         <v>68</v>
       </c>
       <c r="G113" s="10" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H113" s="10" t="s">
         <v>79</v>
@@ -5802,10 +5799,10 @@
         <v>81</v>
       </c>
       <c r="L113" s="12" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="114" spans="1:12" x14ac:dyDescent="0.35">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="114" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A114" s="8" t="s">
         <v>12</v>
       </c>
@@ -5816,7 +5813,7 @@
         <v>113</v>
       </c>
       <c r="D114" s="9" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E114" s="10" t="s">
         <v>14</v>
@@ -5825,7 +5822,7 @@
         <v>68</v>
       </c>
       <c r="G114" s="10" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H114" s="10" t="s">
         <v>79</v>
@@ -5840,10 +5837,10 @@
         <v>81</v>
       </c>
       <c r="L114" s="11" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="115" spans="1:12" x14ac:dyDescent="0.35">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="115" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A115" s="8" t="s">
         <v>12</v>
       </c>
@@ -5854,7 +5851,7 @@
         <v>114</v>
       </c>
       <c r="D115" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E115" s="10" t="s">
         <v>14</v>
@@ -5863,7 +5860,7 @@
         <v>68</v>
       </c>
       <c r="G115" s="10" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H115" s="10" t="s">
         <v>79</v>
@@ -5878,10 +5875,10 @@
         <v>81</v>
       </c>
       <c r="L115" s="11" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="116" spans="1:12" x14ac:dyDescent="0.35">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="116" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A116" s="8" t="s">
         <v>12</v>
       </c>
@@ -5892,7 +5889,7 @@
         <v>115</v>
       </c>
       <c r="D116" s="9" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E116" s="10" t="s">
         <v>14</v>
@@ -5901,7 +5898,7 @@
         <v>68</v>
       </c>
       <c r="G116" s="10" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H116" s="10" t="s">
         <v>79</v>
@@ -5916,10 +5913,10 @@
         <v>81</v>
       </c>
       <c r="L116" s="11" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="117" spans="1:12" x14ac:dyDescent="0.35">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="117" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A117" s="8" t="s">
         <v>12</v>
       </c>
@@ -5930,7 +5927,7 @@
         <v>116</v>
       </c>
       <c r="D117" s="9" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E117" s="10" t="s">
         <v>14</v>
@@ -5939,7 +5936,7 @@
         <v>68</v>
       </c>
       <c r="G117" s="10" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H117" s="10" t="s">
         <v>79</v>
@@ -5954,10 +5951,10 @@
         <v>81</v>
       </c>
       <c r="L117" s="11" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="118" spans="1:12" x14ac:dyDescent="0.35">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="118" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A118" s="8" t="s">
         <v>12</v>
       </c>
@@ -5968,7 +5965,7 @@
         <v>117</v>
       </c>
       <c r="D118" s="9" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E118" s="10" t="s">
         <v>14</v>
@@ -5977,7 +5974,7 @@
         <v>68</v>
       </c>
       <c r="G118" s="10" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H118" s="10" t="s">
         <v>79</v>
@@ -5992,10 +5989,10 @@
         <v>81</v>
       </c>
       <c r="L118" s="12" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="119" spans="1:12" x14ac:dyDescent="0.35">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="119" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A119" s="8" t="s">
         <v>12</v>
       </c>
@@ -6006,7 +6003,7 @@
         <v>118</v>
       </c>
       <c r="D119" s="8" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E119" s="10" t="s">
         <v>14</v>
@@ -6015,7 +6012,7 @@
         <v>68</v>
       </c>
       <c r="G119" s="10" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H119" s="10" t="s">
         <v>79</v>
@@ -6030,10 +6027,10 @@
         <v>81</v>
       </c>
       <c r="L119" s="8" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="120" spans="1:12" x14ac:dyDescent="0.35">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="120" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A120" s="8" t="s">
         <v>12</v>
       </c>
@@ -6044,7 +6041,7 @@
         <v>119</v>
       </c>
       <c r="D120" s="9" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E120" s="10" t="s">
         <v>14</v>
@@ -6053,7 +6050,7 @@
         <v>68</v>
       </c>
       <c r="G120" s="10" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H120" s="10" t="s">
         <v>79</v>
@@ -6068,10 +6065,10 @@
         <v>81</v>
       </c>
       <c r="L120" s="8" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="121" spans="1:12" x14ac:dyDescent="0.35">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="121" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A121" s="8" t="s">
         <v>12</v>
       </c>
@@ -6082,7 +6079,7 @@
         <v>120</v>
       </c>
       <c r="D121" s="9" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="E121" s="10" t="s">
         <v>14</v>
@@ -6091,7 +6088,7 @@
         <v>68</v>
       </c>
       <c r="G121" s="10" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H121" s="10" t="s">
         <v>79</v>
@@ -6106,10 +6103,10 @@
         <v>81</v>
       </c>
       <c r="L121" s="8" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="122" spans="1:12" x14ac:dyDescent="0.35">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="122" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A122" s="8" t="s">
         <v>12</v>
       </c>
@@ -6120,7 +6117,7 @@
         <v>121</v>
       </c>
       <c r="D122" s="9" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="E122" s="10" t="s">
         <v>14</v>
@@ -6144,10 +6141,10 @@
         <v>81</v>
       </c>
       <c r="L122" s="11" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="123" spans="1:12" x14ac:dyDescent="0.35">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="123" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A123" s="8" t="s">
         <v>12</v>
       </c>
@@ -6158,7 +6155,7 @@
         <v>122</v>
       </c>
       <c r="D123" s="9" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="E123" s="10" t="s">
         <v>14</v>
@@ -6167,7 +6164,7 @@
         <v>62</v>
       </c>
       <c r="G123" s="10" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H123" s="10" t="s">
         <v>100</v>
@@ -6182,10 +6179,10 @@
         <v>81</v>
       </c>
       <c r="L123" s="11" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="124" spans="1:12" x14ac:dyDescent="0.35">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="124" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A124" s="8" t="s">
         <v>12</v>
       </c>
@@ -6196,7 +6193,7 @@
         <v>123</v>
       </c>
       <c r="D124" s="9" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="E124" s="10" t="s">
         <v>14</v>
@@ -6205,7 +6202,7 @@
         <v>62</v>
       </c>
       <c r="G124" s="10" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H124" s="10" t="s">
         <v>100</v>
@@ -6220,10 +6217,10 @@
         <v>81</v>
       </c>
       <c r="L124" s="11" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="125" spans="1:12" x14ac:dyDescent="0.35">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="125" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A125" s="8" t="s">
         <v>12</v>
       </c>
@@ -6234,16 +6231,16 @@
         <v>124</v>
       </c>
       <c r="D125" s="9" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="E125" s="10" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="F125" s="10" t="s">
         <v>25</v>
       </c>
       <c r="G125" s="10" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H125" s="10" t="s">
         <v>79</v>
@@ -6258,10 +6255,10 @@
         <v>81</v>
       </c>
       <c r="L125" s="11" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="126" spans="1:12" x14ac:dyDescent="0.35">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="126" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A126" s="8" t="s">
         <v>12</v>
       </c>
@@ -6272,22 +6269,22 @@
         <v>125</v>
       </c>
       <c r="D126" s="9" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="E126" s="10" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="F126" s="10" t="s">
         <v>15</v>
       </c>
       <c r="G126" s="10" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H126" s="10" t="s">
         <v>100</v>
       </c>
       <c r="I126" s="10" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="J126" s="8" t="s">
         <v>69</v>
@@ -6296,10 +6293,10 @@
         <v>81</v>
       </c>
       <c r="L126" s="11" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="127" spans="1:12" x14ac:dyDescent="0.35">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="127" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A127" s="8" t="s">
         <v>12</v>
       </c>
@@ -6310,10 +6307,10 @@
         <v>126</v>
       </c>
       <c r="D127" s="9" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="E127" s="10" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="F127" s="10" t="s">
         <v>15</v>
@@ -6325,7 +6322,7 @@
         <v>100</v>
       </c>
       <c r="I127" s="10" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="J127" s="8" t="s">
         <v>69</v>
@@ -6334,10 +6331,10 @@
         <v>81</v>
       </c>
       <c r="L127" s="11" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="128" spans="1:12" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="128" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A128" s="8" t="s">
         <v>12</v>
       </c>
@@ -6348,10 +6345,10 @@
         <v>127</v>
       </c>
       <c r="D128" s="9" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="E128" s="10" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="F128" s="10" t="s">
         <v>15</v>
@@ -6363,7 +6360,7 @@
         <v>100</v>
       </c>
       <c r="I128" s="10" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="J128" s="8" t="s">
         <v>69</v>
@@ -6372,10 +6369,10 @@
         <v>81</v>
       </c>
       <c r="L128" s="11" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="129" spans="1:12" x14ac:dyDescent="0.35">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="129" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A129" s="8" t="s">
         <v>12</v>
       </c>
@@ -6386,10 +6383,10 @@
         <v>128</v>
       </c>
       <c r="D129" s="9" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="E129" s="10" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="F129" s="10" t="s">
         <v>15</v>
@@ -6401,7 +6398,7 @@
         <v>100</v>
       </c>
       <c r="I129" s="10" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="J129" s="8" t="s">
         <v>69</v>
@@ -6410,10 +6407,10 @@
         <v>81</v>
       </c>
       <c r="L129" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="130" spans="1:12" x14ac:dyDescent="0.35">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="130" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A130" s="8" t="s">
         <v>12</v>
       </c>
@@ -6424,10 +6421,10 @@
         <v>129</v>
       </c>
       <c r="D130" s="9" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="E130" s="10" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="F130" s="10" t="s">
         <v>15</v>
@@ -6439,7 +6436,7 @@
         <v>100</v>
       </c>
       <c r="I130" s="10" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="J130" s="8" t="s">
         <v>69</v>
@@ -6448,10 +6445,10 @@
         <v>81</v>
       </c>
       <c r="L130" s="11" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="131" spans="1:12" x14ac:dyDescent="0.35">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="131" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A131" s="8" t="s">
         <v>12</v>
       </c>
@@ -6462,10 +6459,10 @@
         <v>130</v>
       </c>
       <c r="D131" s="9" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="E131" s="10" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="F131" s="10" t="s">
         <v>15</v>
@@ -6477,7 +6474,7 @@
         <v>100</v>
       </c>
       <c r="I131" s="10" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="J131" s="8" t="s">
         <v>69</v>
@@ -6486,10 +6483,10 @@
         <v>81</v>
       </c>
       <c r="L131" s="11" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="132" spans="1:12" x14ac:dyDescent="0.35">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="132" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A132" s="8" t="s">
         <v>12</v>
       </c>
@@ -6500,10 +6497,10 @@
         <v>131</v>
       </c>
       <c r="D132" s="9" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="E132" s="10" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="F132" s="10" t="s">
         <v>15</v>
@@ -6515,7 +6512,7 @@
         <v>100</v>
       </c>
       <c r="I132" s="10" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="J132" s="8" t="s">
         <v>69</v>
@@ -6524,10 +6521,10 @@
         <v>81</v>
       </c>
       <c r="L132" s="11" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="133" spans="1:12" x14ac:dyDescent="0.35">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="133" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A133" s="8" t="s">
         <v>12</v>
       </c>
@@ -6538,10 +6535,10 @@
         <v>132</v>
       </c>
       <c r="D133" s="9" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="E133" s="10" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="F133" s="10" t="s">
         <v>15</v>
@@ -6553,7 +6550,7 @@
         <v>100</v>
       </c>
       <c r="I133" s="10" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="J133" s="8" t="s">
         <v>69</v>
@@ -6562,10 +6559,10 @@
         <v>81</v>
       </c>
       <c r="L133" s="11" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="134" spans="1:12" x14ac:dyDescent="0.35">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="134" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A134" s="8" t="s">
         <v>12</v>
       </c>
@@ -6576,10 +6573,10 @@
         <v>133</v>
       </c>
       <c r="D134" s="9" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="E134" s="10" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="F134" s="10" t="s">
         <v>15</v>
@@ -6591,7 +6588,7 @@
         <v>100</v>
       </c>
       <c r="I134" s="10" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="J134" s="8" t="s">
         <v>69</v>
@@ -6600,10 +6597,10 @@
         <v>81</v>
       </c>
       <c r="L134" s="11" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="135" spans="1:12" x14ac:dyDescent="0.35">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="135" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A135" s="8" t="s">
         <v>12</v>
       </c>
@@ -6614,7 +6611,7 @@
         <v>134</v>
       </c>
       <c r="D135" s="13" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="E135" s="10" t="s">
         <v>14</v>
@@ -6623,7 +6620,7 @@
         <v>68</v>
       </c>
       <c r="G135" s="10" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H135" s="10" t="s">
         <v>79</v>
@@ -6638,10 +6635,10 @@
         <v>81</v>
       </c>
       <c r="L135" s="11" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="136" spans="1:12" x14ac:dyDescent="0.35">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="136" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A136" s="8" t="s">
         <v>12</v>
       </c>
@@ -6652,7 +6649,7 @@
         <v>135</v>
       </c>
       <c r="D136" s="13" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="E136" s="10" t="s">
         <v>66</v>
@@ -6676,10 +6673,10 @@
         <v>81</v>
       </c>
       <c r="L136" s="11" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="137" spans="1:12" x14ac:dyDescent="0.35">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="137" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A137" s="8" t="s">
         <v>12</v>
       </c>
@@ -6690,7 +6687,7 @@
         <v>136</v>
       </c>
       <c r="D137" s="9" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="E137" s="10" t="s">
         <v>66</v>
@@ -6714,10 +6711,10 @@
         <v>81</v>
       </c>
       <c r="L137" s="11" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="138" spans="1:12" x14ac:dyDescent="0.35">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="138" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A138" s="8" t="s">
         <v>12</v>
       </c>
@@ -6728,7 +6725,7 @@
         <v>137</v>
       </c>
       <c r="D138" s="9" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="E138" s="10" t="s">
         <v>66</v>
@@ -6752,10 +6749,10 @@
         <v>81</v>
       </c>
       <c r="L138" s="11" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="139" spans="1:12" x14ac:dyDescent="0.35">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="139" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A139" s="8" t="s">
         <v>12</v>
       </c>
@@ -6766,7 +6763,7 @@
         <v>138</v>
       </c>
       <c r="D139" s="9" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="E139" s="10" t="s">
         <v>66</v>
@@ -6790,10 +6787,10 @@
         <v>81</v>
       </c>
       <c r="L139" s="11" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="140" spans="1:12" x14ac:dyDescent="0.35">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="140" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A140" s="8" t="s">
         <v>12</v>
       </c>
@@ -6804,7 +6801,7 @@
         <v>139</v>
       </c>
       <c r="D140" s="9" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="E140" s="10" t="s">
         <v>14</v>
@@ -6828,10 +6825,10 @@
         <v>81</v>
       </c>
       <c r="L140" s="11" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="141" spans="1:12" x14ac:dyDescent="0.35">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="141" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A141" s="8" t="s">
         <v>12</v>
       </c>
@@ -6842,7 +6839,7 @@
         <v>140</v>
       </c>
       <c r="D141" s="9" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="E141" s="10" t="s">
         <v>66</v>
@@ -6866,10 +6863,10 @@
         <v>81</v>
       </c>
       <c r="L141" s="11" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="142" spans="1:12" x14ac:dyDescent="0.35">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="142" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A142" s="8" t="s">
         <v>12</v>
       </c>
@@ -6880,7 +6877,7 @@
         <v>141</v>
       </c>
       <c r="D142" s="9" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="E142" s="10" t="s">
         <v>14</v>
@@ -6889,7 +6886,7 @@
         <v>68</v>
       </c>
       <c r="G142" s="10" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H142" s="10" t="s">
         <v>79</v>
@@ -6904,10 +6901,10 @@
         <v>81</v>
       </c>
       <c r="L142" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="143" spans="1:12" x14ac:dyDescent="0.35">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="143" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A143" s="8" t="s">
         <v>12</v>
       </c>
@@ -6918,7 +6915,7 @@
         <v>142</v>
       </c>
       <c r="D143" s="9" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="E143" s="10" t="s">
         <v>14</v>
@@ -6927,7 +6924,7 @@
         <v>68</v>
       </c>
       <c r="G143" s="10" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H143" s="10" t="s">
         <v>79</v>
@@ -6942,7 +6939,7 @@
         <v>81</v>
       </c>
       <c r="L143" s="11" t="s">
-        <v>245</v>
+        <v>310</v>
       </c>
     </row>
   </sheetData>
@@ -6953,22 +6950,22 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02C7B195-9C28-4152-A7C9-DCCF3DB8F404}">
   <dimension ref="A1:L44"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="21.1796875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="29.81640625" customWidth="1"/>
+    <col min="2" max="2" width="21.21875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="29.77734375" customWidth="1"/>
     <col min="5" max="5" width="17" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.54296875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.453125" customWidth="1"/>
-    <col min="8" max="8" width="17.54296875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.44140625" customWidth="1"/>
+    <col min="8" max="8" width="17.5546875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="25" customWidth="1"/>
-    <col min="10" max="10" width="12.1796875" customWidth="1"/>
-    <col min="11" max="11" width="14.1796875" customWidth="1"/>
+    <col min="10" max="10" width="12.21875" customWidth="1"/>
+    <col min="11" max="11" width="14.21875" customWidth="1"/>
     <col min="12" max="12" width="88" customWidth="1"/>
-    <col min="13" max="18" width="9.1796875" customWidth="1"/>
+    <col min="13" max="18" width="9.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -7006,7 +7003,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -7017,7 +7014,7 @@
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="E2" t="s">
         <v>14</v>
@@ -7044,7 +7041,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -7055,10 +7052,10 @@
         <v>2</v>
       </c>
       <c r="D3" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="E3" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="F3" t="s">
         <v>15</v>
@@ -7082,7 +7079,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -7093,7 +7090,7 @@
         <v>3</v>
       </c>
       <c r="D4" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="E4" t="s">
         <v>24</v>
@@ -7120,7 +7117,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -7131,7 +7128,7 @@
         <v>4</v>
       </c>
       <c r="D5" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="E5" t="s">
         <v>14</v>
@@ -7158,7 +7155,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -7169,10 +7166,10 @@
         <v>5</v>
       </c>
       <c r="D6" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="E6" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="F6" t="s">
         <v>15</v>
@@ -7196,7 +7193,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -7207,7 +7204,7 @@
         <v>6</v>
       </c>
       <c r="D7" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="E7" t="s">
         <v>24</v>
@@ -7234,7 +7231,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -7245,7 +7242,7 @@
         <v>7</v>
       </c>
       <c r="D8" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="E8" t="s">
         <v>14</v>
@@ -7272,7 +7269,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -7283,10 +7280,10 @@
         <v>8</v>
       </c>
       <c r="D9" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="E9" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="F9" t="s">
         <v>25</v>
@@ -7310,7 +7307,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -7321,7 +7318,7 @@
         <v>9</v>
       </c>
       <c r="D10" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="E10" t="s">
         <v>24</v>
@@ -7348,7 +7345,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>12</v>
       </c>
@@ -7359,7 +7356,7 @@
         <v>10</v>
       </c>
       <c r="D11" t="s">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="E11" t="s">
         <v>14</v>
@@ -7386,7 +7383,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>12</v>
       </c>
@@ -7397,10 +7394,10 @@
         <v>11</v>
       </c>
       <c r="D12" t="s">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="E12" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="F12" t="s">
         <v>25</v>
@@ -7424,7 +7421,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>12</v>
       </c>
@@ -7435,7 +7432,7 @@
         <v>12</v>
       </c>
       <c r="D13" t="s">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="E13" t="s">
         <v>24</v>
@@ -7462,7 +7459,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>12</v>
       </c>
@@ -7473,7 +7470,7 @@
         <v>13</v>
       </c>
       <c r="D14" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="E14" t="s">
         <v>14</v>
@@ -7500,7 +7497,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>12</v>
       </c>
@@ -7511,7 +7508,7 @@
         <v>14</v>
       </c>
       <c r="D15" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
       <c r="E15" t="s">
         <v>14</v>
@@ -7538,7 +7535,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>12</v>
       </c>
@@ -7549,10 +7546,10 @@
         <v>15</v>
       </c>
       <c r="D16" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="E16" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="F16" t="s">
         <v>25</v>
@@ -7576,7 +7573,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>12</v>
       </c>
@@ -7587,10 +7584,10 @@
         <v>16</v>
       </c>
       <c r="D17" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
       <c r="E17" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="F17" t="s">
         <v>25</v>
@@ -7614,7 +7611,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>12</v>
       </c>
@@ -7625,7 +7622,7 @@
         <v>17</v>
       </c>
       <c r="D18" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="E18" t="s">
         <v>24</v>
@@ -7652,7 +7649,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>12</v>
       </c>
@@ -7663,7 +7660,7 @@
         <v>18</v>
       </c>
       <c r="D19" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
       <c r="E19" t="s">
         <v>24</v>
@@ -7690,7 +7687,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>12</v>
       </c>
@@ -7701,7 +7698,7 @@
         <v>19</v>
       </c>
       <c r="D20" t="s">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="E20" t="s">
         <v>14</v>
@@ -7728,7 +7725,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>12</v>
       </c>
@@ -7739,10 +7736,10 @@
         <v>20</v>
       </c>
       <c r="D21" t="s">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="E21" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="F21" t="s">
         <v>25</v>
@@ -7766,7 +7763,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>12</v>
       </c>
@@ -7777,7 +7774,7 @@
         <v>21</v>
       </c>
       <c r="D22" t="s">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="E22" t="s">
         <v>24</v>
@@ -7804,7 +7801,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>12</v>
       </c>
@@ -7815,7 +7812,7 @@
         <v>22</v>
       </c>
       <c r="D23" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="E23" t="s">
         <v>14</v>
@@ -7842,7 +7839,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>12</v>
       </c>
@@ -7853,7 +7850,7 @@
         <v>23</v>
       </c>
       <c r="D24" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="E24" t="s">
         <v>22</v>
@@ -7880,7 +7877,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>12</v>
       </c>
@@ -7891,7 +7888,7 @@
         <v>24</v>
       </c>
       <c r="D25" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="E25" t="s">
         <v>24</v>
@@ -7918,7 +7915,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>12</v>
       </c>
@@ -7929,7 +7926,7 @@
         <v>25</v>
       </c>
       <c r="D26" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="E26" t="s">
         <v>14</v>
@@ -7956,7 +7953,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>12</v>
       </c>
@@ -7967,10 +7964,10 @@
         <v>26</v>
       </c>
       <c r="D27" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="E27" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="F27" t="s">
         <v>25</v>
@@ -7994,7 +7991,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>12</v>
       </c>
@@ -8005,7 +8002,7 @@
         <v>27</v>
       </c>
       <c r="D28" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="E28" t="s">
         <v>24</v>
@@ -8032,7 +8029,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>12</v>
       </c>
@@ -8070,7 +8067,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>12</v>
       </c>
@@ -8084,7 +8081,7 @@
         <v>55</v>
       </c>
       <c r="E30" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="F30" t="s">
         <v>25</v>
@@ -8108,7 +8105,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>12</v>
       </c>
@@ -8146,7 +8143,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>12</v>
       </c>
@@ -8157,7 +8154,7 @@
         <v>31</v>
       </c>
       <c r="D32" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="E32" t="s">
         <v>14</v>
@@ -8184,7 +8181,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>12</v>
       </c>
@@ -8195,10 +8192,10 @@
         <v>32</v>
       </c>
       <c r="D33" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="E33" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="F33" t="s">
         <v>25</v>
@@ -8222,7 +8219,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>12</v>
       </c>
@@ -8233,7 +8230,7 @@
         <v>33</v>
       </c>
       <c r="D34" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="E34" t="s">
         <v>24</v>
@@ -8260,7 +8257,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>12</v>
       </c>
@@ -8271,10 +8268,10 @@
         <v>34</v>
       </c>
       <c r="D35" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="E35" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="F35" t="s">
         <v>62</v>
@@ -8298,7 +8295,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>12</v>
       </c>
@@ -8309,10 +8306,10 @@
         <v>35</v>
       </c>
       <c r="D36" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="E36" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="F36" s="4" t="s">
         <v>62</v>
@@ -8336,7 +8333,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>12</v>
       </c>
@@ -8347,10 +8344,10 @@
         <v>36</v>
       </c>
       <c r="D37" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="E37" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="F37" t="s">
         <v>62</v>
@@ -8374,7 +8371,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>12</v>
       </c>
@@ -8385,10 +8382,10 @@
         <v>37</v>
       </c>
       <c r="D38" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="E38" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="F38" t="s">
         <v>68</v>
@@ -8412,7 +8409,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>12</v>
       </c>
@@ -8423,10 +8420,10 @@
         <v>38</v>
       </c>
       <c r="D39" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="E39" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="F39" t="s">
         <v>62</v>
@@ -8450,7 +8447,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>12</v>
       </c>
@@ -8461,10 +8458,10 @@
         <v>39</v>
       </c>
       <c r="D40" t="s">
+        <v>294</v>
+      </c>
+      <c r="E40" t="s">
         <v>300</v>
-      </c>
-      <c r="E40" t="s">
-        <v>306</v>
       </c>
       <c r="F40" t="s">
         <v>62</v>
@@ -8488,7 +8485,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>12</v>
       </c>
@@ -8499,10 +8496,10 @@
         <v>40</v>
       </c>
       <c r="D41" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="E41" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="F41" t="s">
         <v>68</v>
@@ -8526,7 +8523,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>12</v>
       </c>
@@ -8537,10 +8534,10 @@
         <v>41</v>
       </c>
       <c r="D42" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="E42" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="F42" t="s">
         <v>68</v>
@@ -8564,7 +8561,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>12</v>
       </c>
@@ -8575,10 +8572,10 @@
         <v>42</v>
       </c>
       <c r="D43" t="s">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="E43" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="F43" t="s">
         <v>15</v>
@@ -8602,7 +8599,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>12</v>
       </c>
@@ -8613,10 +8610,10 @@
         <v>43</v>
       </c>
       <c r="D44" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="E44" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="F44" s="4" t="s">
         <v>62</v>
@@ -8648,21 +8645,21 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA328016-6EE1-4F6F-84C5-5395FF87B11C}">
   <dimension ref="A1:L43"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="7.81640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="52.26953125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="21.26953125" customWidth="1"/>
-    <col min="6" max="6" width="10.54296875" customWidth="1"/>
-    <col min="7" max="7" width="14.1796875" customWidth="1"/>
-    <col min="8" max="8" width="17.54296875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="16.1796875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.453125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.1796875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="93.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.77734375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="52.21875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.21875" customWidth="1"/>
+    <col min="6" max="6" width="10.5546875" customWidth="1"/>
+    <col min="7" max="7" width="14.21875" customWidth="1"/>
+    <col min="8" max="8" width="17.5546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.21875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.21875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="93.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:12" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -8700,7 +8697,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -8714,7 +8711,7 @@
         <v>77</v>
       </c>
       <c r="E2" t="s">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="F2" t="s">
         <v>25</v>
@@ -8738,7 +8735,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -8752,7 +8749,7 @@
         <v>83</v>
       </c>
       <c r="E3" t="s">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="F3" t="s">
         <v>25</v>
@@ -8776,7 +8773,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -8790,7 +8787,7 @@
         <v>85</v>
       </c>
       <c r="E4" t="s">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="F4" t="s">
         <v>68</v>
@@ -8814,7 +8811,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -8828,7 +8825,7 @@
         <v>88</v>
       </c>
       <c r="E5" t="s">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="F5" t="s">
         <v>68</v>
@@ -8852,7 +8849,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -8890,7 +8887,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -8928,7 +8925,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -8966,7 +8963,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -9004,7 +9001,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -9042,7 +9039,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>12</v>
       </c>
@@ -9080,7 +9077,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>12</v>
       </c>
@@ -9118,7 +9115,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>12</v>
       </c>
@@ -9156,7 +9153,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>12</v>
       </c>
@@ -9194,7 +9191,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>12</v>
       </c>
@@ -9232,7 +9229,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>12</v>
       </c>
@@ -9270,7 +9267,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>12</v>
       </c>
@@ -9308,7 +9305,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>12</v>
       </c>
@@ -9346,7 +9343,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>12</v>
       </c>
@@ -9384,7 +9381,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>12</v>
       </c>
@@ -9422,7 +9419,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>12</v>
       </c>
@@ -9460,7 +9457,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>12</v>
       </c>
@@ -9498,7 +9495,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>12</v>
       </c>
@@ -9536,7 +9533,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>12</v>
       </c>
@@ -9574,7 +9571,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>12</v>
       </c>
@@ -9612,7 +9609,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>12</v>
       </c>
@@ -9650,7 +9647,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>12</v>
       </c>
@@ -9688,7 +9685,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>12</v>
       </c>
@@ -9726,7 +9723,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>12</v>
       </c>
@@ -9764,7 +9761,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>12</v>
       </c>
@@ -9778,7 +9775,7 @@
         <v>142</v>
       </c>
       <c r="E30" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="F30" t="s">
         <v>62</v>
@@ -9802,7 +9799,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>12</v>
       </c>
@@ -9816,7 +9813,7 @@
         <v>144</v>
       </c>
       <c r="E31" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="F31" t="s">
         <v>68</v>
@@ -9840,7 +9837,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>12</v>
       </c>
@@ -9854,7 +9851,7 @@
         <v>146</v>
       </c>
       <c r="E32" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="F32" t="s">
         <v>68</v>
@@ -9878,7 +9875,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>12</v>
       </c>
@@ -9892,7 +9889,7 @@
         <v>148</v>
       </c>
       <c r="E33" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="F33" t="s">
         <v>68</v>
@@ -9916,7 +9913,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>12</v>
       </c>
@@ -9930,7 +9927,7 @@
         <v>150</v>
       </c>
       <c r="E34" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="F34" t="s">
         <v>25</v>
@@ -9954,7 +9951,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>12</v>
       </c>
@@ -9968,7 +9965,7 @@
         <v>152</v>
       </c>
       <c r="E35" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="F35" t="s">
         <v>25</v>
@@ -9992,7 +9989,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>12</v>
       </c>
@@ -10006,7 +10003,7 @@
         <v>154</v>
       </c>
       <c r="E36" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="F36" t="s">
         <v>25</v>
@@ -10030,7 +10027,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>12</v>
       </c>
@@ -10044,7 +10041,7 @@
         <v>156</v>
       </c>
       <c r="E37" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="F37" t="s">
         <v>25</v>
@@ -10068,7 +10065,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>12</v>
       </c>
@@ -10082,7 +10079,7 @@
         <v>159</v>
       </c>
       <c r="E38" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="F38" t="s">
         <v>25</v>
@@ -10106,7 +10103,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>12</v>
       </c>
@@ -10144,7 +10141,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>12</v>
       </c>
@@ -10182,7 +10179,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>12</v>
       </c>
@@ -10220,7 +10217,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>12</v>
       </c>
@@ -10258,7 +10255,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>12</v>
       </c>
@@ -10304,18 +10301,18 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E6501C2-1F4E-44C1-926E-7B80FAB5E9FA}">
   <dimension ref="A1:L22"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="4" max="4" width="38" customWidth="1"/>
-    <col min="5" max="5" width="22.81640625" customWidth="1"/>
-    <col min="8" max="8" width="18.81640625" customWidth="1"/>
-    <col min="9" max="9" width="14.81640625" customWidth="1"/>
-    <col min="10" max="10" width="18.54296875" customWidth="1"/>
-    <col min="11" max="11" width="15.7265625" customWidth="1"/>
+    <col min="5" max="5" width="22.77734375" customWidth="1"/>
+    <col min="8" max="8" width="18.77734375" customWidth="1"/>
+    <col min="9" max="9" width="14.77734375" customWidth="1"/>
+    <col min="10" max="10" width="18.5546875" customWidth="1"/>
+    <col min="11" max="11" width="15.77734375" customWidth="1"/>
     <col min="12" max="12" width="54" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -10353,7 +10350,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -10364,16 +10361,16 @@
         <v>86</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="E2" s="10" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="F2" s="10" t="s">
         <v>15</v>
       </c>
       <c r="G2" s="10" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="H2" s="10" t="s">
         <v>100</v>
@@ -10388,10 +10385,10 @@
         <v>81</v>
       </c>
       <c r="L2" s="18" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -10402,10 +10399,10 @@
         <v>87</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="F3" s="10" t="s">
         <v>15</v>
@@ -10426,10 +10423,10 @@
         <v>81</v>
       </c>
       <c r="L3" s="18" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -10440,7 +10437,7 @@
         <v>88</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>309</v>
+        <v>303</v>
       </c>
       <c r="E4" s="10" t="s">
         <v>14</v>
@@ -10464,10 +10461,10 @@
         <v>81</v>
       </c>
       <c r="L4" s="18" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -10478,7 +10475,7 @@
         <v>89</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>14</v>
@@ -10502,10 +10499,10 @@
         <v>81</v>
       </c>
       <c r="L5" s="18" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" s="8" t="s">
         <v>12</v>
       </c>
@@ -10516,7 +10513,7 @@
         <v>90</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="E6" s="10" t="s">
         <v>14</v>
@@ -10540,10 +10537,10 @@
         <v>81</v>
       </c>
       <c r="L6" s="18" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" s="8" t="s">
         <v>12</v>
       </c>
@@ -10554,7 +10551,7 @@
         <v>91</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>14</v>
@@ -10578,10 +10575,10 @@
         <v>81</v>
       </c>
       <c r="L7" s="18" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -10592,7 +10589,7 @@
         <v>92</v>
       </c>
       <c r="D8" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="E8" s="10" t="s">
         <v>14</v>
@@ -10616,10 +10613,10 @@
         <v>81</v>
       </c>
       <c r="L8" s="19" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -10630,7 +10627,7 @@
         <v>93</v>
       </c>
       <c r="D9" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>14</v>
@@ -10654,10 +10651,10 @@
         <v>81</v>
       </c>
       <c r="L9" s="19" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -10668,10 +10665,10 @@
         <v>94</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="F10" s="10" t="s">
         <v>68</v>
@@ -10692,10 +10689,10 @@
         <v>81</v>
       </c>
       <c r="L10" s="18" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>12</v>
       </c>
@@ -10706,10 +10703,10 @@
         <v>95</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="F11" s="10" t="s">
         <v>68</v>
@@ -10730,10 +10727,10 @@
         <v>81</v>
       </c>
       <c r="L11" s="18" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>12</v>
       </c>
@@ -10744,16 +10741,16 @@
         <v>96</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="F12" s="10" t="s">
         <v>15</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="H12" s="10" t="s">
         <v>100</v>
@@ -10768,24 +10765,24 @@
         <v>81</v>
       </c>
       <c r="L12" s="18" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="C13">
         <v>97</v>
       </c>
       <c r="D13" s="13" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="F13" s="16" t="s">
         <v>25</v>
@@ -10806,24 +10803,24 @@
         <v>81</v>
       </c>
       <c r="L13" s="18" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="C14">
         <v>98</v>
       </c>
       <c r="D14" s="13" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="F14" s="16" t="s">
         <v>25</v>
@@ -10844,24 +10841,24 @@
         <v>81</v>
       </c>
       <c r="L14" s="18" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="C15">
         <v>99</v>
       </c>
       <c r="D15" s="13" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="F15" s="16" t="s">
         <v>25</v>
@@ -10882,24 +10879,24 @@
         <v>81</v>
       </c>
       <c r="L15" s="19" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>12</v>
       </c>
       <c r="B16" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="C16">
         <v>100</v>
       </c>
       <c r="D16" s="13" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="F16" s="16" t="s">
         <v>25</v>
@@ -10920,24 +10917,24 @@
         <v>81</v>
       </c>
       <c r="L16" s="19" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.35">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>12</v>
       </c>
       <c r="B17" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="C17">
         <v>101</v>
       </c>
       <c r="D17" s="13" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="F17" s="16" t="s">
         <v>25</v>
@@ -10958,24 +10955,24 @@
         <v>81</v>
       </c>
       <c r="L17" s="18" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.35">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>12</v>
       </c>
       <c r="B18" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="C18">
         <v>102</v>
       </c>
       <c r="D18" s="13" t="s">
-        <v>277</v>
+        <v>271</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="F18" s="16" t="s">
         <v>25</v>
@@ -10996,30 +10993,30 @@
         <v>81</v>
       </c>
       <c r="L18" s="18" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.35">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>12</v>
       </c>
       <c r="B19" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="C19">
         <v>103</v>
       </c>
       <c r="D19" s="13" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="F19" s="16" t="s">
         <v>25</v>
       </c>
       <c r="G19" s="17" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="H19" s="10" t="s">
         <v>79</v>
@@ -11034,30 +11031,30 @@
         <v>81</v>
       </c>
       <c r="L19" s="18" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.35">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>12</v>
       </c>
       <c r="B20" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="C20">
         <v>104</v>
       </c>
       <c r="D20" s="13" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="F20" s="16" t="s">
         <v>68</v>
       </c>
       <c r="G20" s="17" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="H20" s="10" t="s">
         <v>79</v>
@@ -11072,10 +11069,10 @@
         <v>81</v>
       </c>
       <c r="L20" s="18" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.35">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>12</v>
       </c>
@@ -11086,10 +11083,10 @@
         <v>105</v>
       </c>
       <c r="D21" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="F21" t="s">
         <v>68</v>
@@ -11110,10 +11107,10 @@
         <v>81</v>
       </c>
       <c r="L21" s="19" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.35">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="L22" s="19"/>
     </row>
   </sheetData>
@@ -11124,16 +11121,16 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2CE0DD1A-FCA4-41B6-815F-1DF4FD2DD0A1}">
   <dimension ref="A1:L46"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
-    <col min="2" max="2" width="10.81640625" customWidth="1"/>
-    <col min="3" max="3" width="9.26953125" customWidth="1"/>
-    <col min="4" max="4" width="38.54296875" customWidth="1"/>
+    <col min="2" max="2" width="10.77734375" customWidth="1"/>
+    <col min="3" max="3" width="9.21875" customWidth="1"/>
+    <col min="4" max="4" width="38.5546875" customWidth="1"/>
     <col min="5" max="12" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -11171,7 +11168,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="8" t="s">
         <v>12</v>
       </c>
@@ -11206,10 +11203,10 @@
         <v>81</v>
       </c>
       <c r="L2" s="11" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" s="8" t="s">
         <v>12</v>
       </c>
@@ -11220,7 +11217,7 @@
         <v>107</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E3" s="10" t="s">
         <v>14</v>
@@ -11229,7 +11226,7 @@
         <v>68</v>
       </c>
       <c r="G3" s="10" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H3" s="10" t="s">
         <v>79</v>
@@ -11244,10 +11241,10 @@
         <v>81</v>
       </c>
       <c r="L3" s="11" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" s="8" t="s">
         <v>12</v>
       </c>
@@ -11258,7 +11255,7 @@
         <v>108</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E4" s="10" t="s">
         <v>14</v>
@@ -11267,7 +11264,7 @@
         <v>68</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H4" s="10" t="s">
         <v>79</v>
@@ -11282,10 +11279,10 @@
         <v>81</v>
       </c>
       <c r="L4" s="11" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" s="8" t="s">
         <v>12</v>
       </c>
@@ -11296,7 +11293,7 @@
         <v>109</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>14</v>
@@ -11305,7 +11302,7 @@
         <v>62</v>
       </c>
       <c r="G5" s="10" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H5" s="10" t="s">
         <v>100</v>
@@ -11320,10 +11317,10 @@
         <v>81</v>
       </c>
       <c r="L5" s="11" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" s="8" t="s">
         <v>12</v>
       </c>
@@ -11334,7 +11331,7 @@
         <v>110</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E6" s="10" t="s">
         <v>14</v>
@@ -11343,7 +11340,7 @@
         <v>62</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H6" s="10" t="s">
         <v>100</v>
@@ -11358,10 +11355,10 @@
         <v>81</v>
       </c>
       <c r="L6" s="8" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" s="8" t="s">
         <v>12</v>
       </c>
@@ -11372,7 +11369,7 @@
         <v>111</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>14</v>
@@ -11381,7 +11378,7 @@
         <v>68</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H7" s="10" t="s">
         <v>79</v>
@@ -11396,10 +11393,10 @@
         <v>81</v>
       </c>
       <c r="L7" s="11" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" s="8" t="s">
         <v>12</v>
       </c>
@@ -11410,7 +11407,7 @@
         <v>112</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E8" s="10" t="s">
         <v>14</v>
@@ -11419,7 +11416,7 @@
         <v>68</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H8" s="10" t="s">
         <v>79</v>
@@ -11434,10 +11431,10 @@
         <v>81</v>
       </c>
       <c r="L8" s="12" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" s="8" t="s">
         <v>12</v>
       </c>
@@ -11448,7 +11445,7 @@
         <v>113</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>14</v>
@@ -11457,7 +11454,7 @@
         <v>68</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H9" s="10" t="s">
         <v>79</v>
@@ -11472,10 +11469,10 @@
         <v>81</v>
       </c>
       <c r="L9" s="11" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" s="8" t="s">
         <v>12</v>
       </c>
@@ -11486,7 +11483,7 @@
         <v>114</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E10" s="10" t="s">
         <v>14</v>
@@ -11495,7 +11492,7 @@
         <v>68</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H10" s="10" t="s">
         <v>79</v>
@@ -11510,10 +11507,10 @@
         <v>81</v>
       </c>
       <c r="L10" s="11" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" s="8" t="s">
         <v>12</v>
       </c>
@@ -11524,7 +11521,7 @@
         <v>115</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>14</v>
@@ -11533,7 +11530,7 @@
         <v>68</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H11" s="10" t="s">
         <v>79</v>
@@ -11548,10 +11545,10 @@
         <v>81</v>
       </c>
       <c r="L11" s="11" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" s="8" t="s">
         <v>12</v>
       </c>
@@ -11562,7 +11559,7 @@
         <v>116</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E12" s="10" t="s">
         <v>14</v>
@@ -11571,7 +11568,7 @@
         <v>68</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H12" s="10" t="s">
         <v>79</v>
@@ -11586,10 +11583,10 @@
         <v>81</v>
       </c>
       <c r="L12" s="11" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" s="8" t="s">
         <v>12</v>
       </c>
@@ -11600,7 +11597,7 @@
         <v>117</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>14</v>
@@ -11609,7 +11606,7 @@
         <v>68</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H13" s="10" t="s">
         <v>79</v>
@@ -11624,10 +11621,10 @@
         <v>81</v>
       </c>
       <c r="L13" s="12" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" s="8" t="s">
         <v>12</v>
       </c>
@@ -11638,7 +11635,7 @@
         <v>118</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E14" s="10" t="s">
         <v>14</v>
@@ -11647,7 +11644,7 @@
         <v>68</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H14" s="10" t="s">
         <v>79</v>
@@ -11662,10 +11659,10 @@
         <v>81</v>
       </c>
       <c r="L14" s="8" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" s="8" t="s">
         <v>12</v>
       </c>
@@ -11676,7 +11673,7 @@
         <v>119</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>14</v>
@@ -11685,7 +11682,7 @@
         <v>68</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H15" s="10" t="s">
         <v>79</v>
@@ -11700,10 +11697,10 @@
         <v>81</v>
       </c>
       <c r="L15" s="8" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" s="8" t="s">
         <v>12</v>
       </c>
@@ -11714,7 +11711,7 @@
         <v>120</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="E16" s="10" t="s">
         <v>14</v>
@@ -11723,7 +11720,7 @@
         <v>68</v>
       </c>
       <c r="G16" s="10" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H16" s="10" t="s">
         <v>79</v>
@@ -11738,10 +11735,10 @@
         <v>81</v>
       </c>
       <c r="L16" s="8" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.35">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" s="8" t="s">
         <v>12</v>
       </c>
@@ -11752,7 +11749,7 @@
         <v>121</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>14</v>
@@ -11776,10 +11773,10 @@
         <v>81</v>
       </c>
       <c r="L17" s="11" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.35">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" s="8" t="s">
         <v>12</v>
       </c>
@@ -11790,7 +11787,7 @@
         <v>122</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="E18" s="10" t="s">
         <v>14</v>
@@ -11799,7 +11796,7 @@
         <v>62</v>
       </c>
       <c r="G18" s="10" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H18" s="10" t="s">
         <v>100</v>
@@ -11814,10 +11811,10 @@
         <v>81</v>
       </c>
       <c r="L18" s="11" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.35">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19" s="8" t="s">
         <v>12</v>
       </c>
@@ -11828,7 +11825,7 @@
         <v>123</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>14</v>
@@ -11837,7 +11834,7 @@
         <v>62</v>
       </c>
       <c r="G19" s="10" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H19" s="10" t="s">
         <v>100</v>
@@ -11852,10 +11849,10 @@
         <v>81</v>
       </c>
       <c r="L19" s="11" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.35">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20" s="8" t="s">
         <v>12</v>
       </c>
@@ -11866,16 +11863,16 @@
         <v>124</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="F20" s="10" t="s">
         <v>25</v>
       </c>
       <c r="G20" s="10" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H20" s="10" t="s">
         <v>79</v>
@@ -11890,10 +11887,10 @@
         <v>81</v>
       </c>
       <c r="L20" s="11" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.35">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21" s="8" t="s">
         <v>12</v>
       </c>
@@ -11904,22 +11901,22 @@
         <v>125</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="F21" s="10" t="s">
         <v>15</v>
       </c>
       <c r="G21" s="10" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H21" s="10" t="s">
         <v>100</v>
       </c>
       <c r="I21" s="10" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="J21" s="8" t="s">
         <v>69</v>
@@ -11928,10 +11925,10 @@
         <v>81</v>
       </c>
       <c r="L21" s="11" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.35">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22" s="8" t="s">
         <v>12</v>
       </c>
@@ -11942,10 +11939,10 @@
         <v>126</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="E22" s="10" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="F22" s="10" t="s">
         <v>15</v>
@@ -11957,7 +11954,7 @@
         <v>100</v>
       </c>
       <c r="I22" s="10" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="J22" s="8" t="s">
         <v>69</v>
@@ -11966,10 +11963,10 @@
         <v>81</v>
       </c>
       <c r="L22" s="11" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23" s="8" t="s">
         <v>12</v>
       </c>
@@ -11980,10 +11977,10 @@
         <v>127</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="F23" s="10" t="s">
         <v>15</v>
@@ -11995,7 +11992,7 @@
         <v>100</v>
       </c>
       <c r="I23" s="10" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="J23" s="8" t="s">
         <v>69</v>
@@ -12004,10 +12001,10 @@
         <v>81</v>
       </c>
       <c r="L23" s="11" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.35">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24" s="8" t="s">
         <v>12</v>
       </c>
@@ -12018,10 +12015,10 @@
         <v>128</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="F24" s="10" t="s">
         <v>15</v>
@@ -12033,7 +12030,7 @@
         <v>100</v>
       </c>
       <c r="I24" s="10" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="J24" s="8" t="s">
         <v>69</v>
@@ -12042,10 +12039,10 @@
         <v>81</v>
       </c>
       <c r="L24" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.35">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25" s="8" t="s">
         <v>12</v>
       </c>
@@ -12056,10 +12053,10 @@
         <v>129</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="F25" s="10" t="s">
         <v>15</v>
@@ -12071,7 +12068,7 @@
         <v>100</v>
       </c>
       <c r="I25" s="10" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="J25" s="8" t="s">
         <v>69</v>
@@ -12080,10 +12077,10 @@
         <v>81</v>
       </c>
       <c r="L25" s="11" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.35">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A26" s="8" t="s">
         <v>12</v>
       </c>
@@ -12094,10 +12091,10 @@
         <v>130</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="E26" s="10" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="F26" s="10" t="s">
         <v>15</v>
@@ -12109,7 +12106,7 @@
         <v>100</v>
       </c>
       <c r="I26" s="10" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="J26" s="8" t="s">
         <v>69</v>
@@ -12118,10 +12115,10 @@
         <v>81</v>
       </c>
       <c r="L26" s="11" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.35">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27" s="8" t="s">
         <v>12</v>
       </c>
@@ -12132,10 +12129,10 @@
         <v>131</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="F27" s="10" t="s">
         <v>15</v>
@@ -12147,7 +12144,7 @@
         <v>100</v>
       </c>
       <c r="I27" s="10" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="J27" s="8" t="s">
         <v>69</v>
@@ -12156,10 +12153,10 @@
         <v>81</v>
       </c>
       <c r="L27" s="11" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.35">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28" s="8" t="s">
         <v>12</v>
       </c>
@@ -12170,10 +12167,10 @@
         <v>132</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="E28" s="10" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="F28" s="10" t="s">
         <v>15</v>
@@ -12185,7 +12182,7 @@
         <v>100</v>
       </c>
       <c r="I28" s="10" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="J28" s="8" t="s">
         <v>69</v>
@@ -12194,10 +12191,10 @@
         <v>81</v>
       </c>
       <c r="L28" s="11" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.35">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A29" s="8" t="s">
         <v>12</v>
       </c>
@@ -12208,10 +12205,10 @@
         <v>133</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="F29" s="10" t="s">
         <v>15</v>
@@ -12223,7 +12220,7 @@
         <v>100</v>
       </c>
       <c r="I29" s="10" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="J29" s="8" t="s">
         <v>69</v>
@@ -12232,10 +12229,10 @@
         <v>81</v>
       </c>
       <c r="L29" s="11" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.35">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A30" s="8" t="s">
         <v>12</v>
       </c>
@@ -12246,7 +12243,7 @@
         <v>134</v>
       </c>
       <c r="D30" s="13" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="E30" s="10" t="s">
         <v>14</v>
@@ -12255,7 +12252,7 @@
         <v>68</v>
       </c>
       <c r="G30" s="10" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H30" s="10" t="s">
         <v>79</v>
@@ -12270,10 +12267,10 @@
         <v>81</v>
       </c>
       <c r="L30" s="11" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.35">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A31" s="8" t="s">
         <v>12</v>
       </c>
@@ -12284,7 +12281,7 @@
         <v>135</v>
       </c>
       <c r="D31" s="13" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="E31" s="10" t="s">
         <v>66</v>
@@ -12308,10 +12305,10 @@
         <v>81</v>
       </c>
       <c r="L31" s="11" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.35">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A32" s="8" t="s">
         <v>12</v>
       </c>
@@ -12322,7 +12319,7 @@
         <v>136</v>
       </c>
       <c r="D32" s="9" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="E32" s="10" t="s">
         <v>66</v>
@@ -12346,10 +12343,10 @@
         <v>81</v>
       </c>
       <c r="L32" s="11" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.35">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A33" s="8" t="s">
         <v>12</v>
       </c>
@@ -12360,7 +12357,7 @@
         <v>137</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="E33" s="10" t="s">
         <v>66</v>
@@ -12384,10 +12381,10 @@
         <v>81</v>
       </c>
       <c r="L33" s="11" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.35">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A34" s="8" t="s">
         <v>12</v>
       </c>
@@ -12398,7 +12395,7 @@
         <v>138</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="E34" s="10" t="s">
         <v>66</v>
@@ -12422,10 +12419,10 @@
         <v>81</v>
       </c>
       <c r="L34" s="11" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.35">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A35" s="8" t="s">
         <v>12</v>
       </c>
@@ -12436,7 +12433,7 @@
         <v>139</v>
       </c>
       <c r="D35" s="9" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="E35" s="10" t="s">
         <v>14</v>
@@ -12460,10 +12457,10 @@
         <v>81</v>
       </c>
       <c r="L35" s="11" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.35">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A36" s="8" t="s">
         <v>12</v>
       </c>
@@ -12474,7 +12471,7 @@
         <v>140</v>
       </c>
       <c r="D36" s="9" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="E36" s="10" t="s">
         <v>66</v>
@@ -12498,10 +12495,10 @@
         <v>81</v>
       </c>
       <c r="L36" s="11" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.35">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A37" s="8" t="s">
         <v>12</v>
       </c>
@@ -12512,7 +12509,7 @@
         <v>141</v>
       </c>
       <c r="D37" s="9" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="E37" s="10" t="s">
         <v>14</v>
@@ -12521,7 +12518,7 @@
         <v>68</v>
       </c>
       <c r="G37" s="10" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H37" s="10" t="s">
         <v>79</v>
@@ -12536,10 +12533,10 @@
         <v>81</v>
       </c>
       <c r="L37" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.35">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A38" s="8" t="s">
         <v>12</v>
       </c>
@@ -12550,7 +12547,7 @@
         <v>142</v>
       </c>
       <c r="D38" s="9" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="E38" s="10" t="s">
         <v>14</v>
@@ -12559,7 +12556,7 @@
         <v>68</v>
       </c>
       <c r="G38" s="10" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H38" s="10" t="s">
         <v>79</v>
@@ -12574,31 +12571,31 @@
         <v>81</v>
       </c>
       <c r="L38" s="11" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.35">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
       <c r="D39" s="14"/>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
       <c r="D40" s="14"/>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
       <c r="D41" s="14"/>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
       <c r="D42" s="14"/>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
       <c r="D43" s="14"/>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
       <c r="D44" s="14"/>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
       <c r="D45" s="15"/>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
       <c r="D46" s="15"/>
     </row>
   </sheetData>

--- a/docs/CDOP_SCHEMA.xlsx
+++ b/docs/CDOP_SCHEMA.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ghoffman\Other-GitHub\Carbon-Data-Open-Protocol\docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nikodem_lacki/Documents/work/Carbon-Data-Open-Protocol/Carbon-Data-Open-Protocol/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A21B714A-6CD9-4FF5-A0BA-B8A575A27B6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB2C76EC-64A6-094D-8D1D-959D7E8DB494}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{743398AF-A4FE-47C4-9368-972E95242EBF}"/>
+    <workbookView xWindow="1320" yWindow="600" windowWidth="33940" windowHeight="15180" activeTab="5" xr2:uid="{743398AF-A4FE-47C4-9368-972E95242EBF}"/>
   </bookViews>
   <sheets>
     <sheet name="Full List" sheetId="5" r:id="rId1"/>
@@ -18,6 +18,7 @@
     <sheet name="Project Approach &amp; Details" sheetId="2" r:id="rId3"/>
     <sheet name="Issuances" sheetId="3" r:id="rId4"/>
     <sheet name="Disclosures" sheetId="4" r:id="rId5"/>
+    <sheet name="Unit Description" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3184" uniqueCount="316">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3350" uniqueCount="354">
   <si>
     <t>schema</t>
   </si>
@@ -988,6 +989,120 @@
   </si>
   <si>
     <t>list of attestations (e.g., child labor, labor worker attestation), if verified credentials are supported</t>
+  </si>
+  <si>
+    <t>current registry project id</t>
+  </si>
+  <si>
+    <t>Project</t>
+  </si>
+  <si>
+    <t>Registry</t>
+  </si>
+  <si>
+    <t>Identifier used to track the project in the current registry.</t>
+  </si>
+  <si>
+    <t>metric</t>
+  </si>
+  <si>
+    <t>Unit</t>
+  </si>
+  <si>
+    <t>Project developer</t>
+  </si>
+  <si>
+    <t>Unit of measurment for quantifying the reduction or removal</t>
+  </si>
+  <si>
+    <t>owner account id</t>
+  </si>
+  <si>
+    <t>GUID</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>identifier for the owner of the unit</t>
+  </si>
+  <si>
+    <t>retirement beneficiary</t>
+  </si>
+  <si>
+    <t>Entity name on behalf of which the retirement occurred</t>
+  </si>
+  <si>
+    <t>retirement detail</t>
+  </si>
+  <si>
+    <t>Additional context describing the retirements</t>
+  </si>
+  <si>
+    <t>serial number</t>
+  </si>
+  <si>
+    <t>Serial number of the unit</t>
+  </si>
+  <si>
+    <t>source serial number</t>
+  </si>
+  <si>
+    <t>Identifier used to track the unit to the original issuance it was part of.</t>
+  </si>
+  <si>
+    <t>status</t>
+  </si>
+  <si>
+    <t>Unit state, indicating which lifecycle the unit is currently in</t>
+  </si>
+  <si>
+    <t>status reason</t>
+  </si>
+  <si>
+    <t>String</t>
+  </si>
+  <si>
+    <t>User Input</t>
+  </si>
+  <si>
+    <t>Select the status that best desribes the current state of the units.</t>
+  </si>
+  <si>
+    <t>type</t>
+  </si>
+  <si>
+    <t>Descirbes the type of unit.</t>
+  </si>
+  <si>
+    <t>quantity</t>
+  </si>
+  <si>
+    <t>Quantity of units included in the credit block that a particular record represents</t>
+  </si>
+  <si>
+    <t>block end</t>
+  </si>
+  <si>
+    <t>Carbon Crediting Program/ Standard Setters</t>
+  </si>
+  <si>
+    <t>Number indicating the last unit within a credit block</t>
+  </si>
+  <si>
+    <t>block start</t>
+  </si>
+  <si>
+    <t>Number indicating the first unit within a credit block</t>
+  </si>
+  <si>
+    <t>vintage</t>
+  </si>
+  <si>
+    <t>Vintage</t>
+  </si>
+  <si>
+    <t>Temporal period when the envrionmental benefit occurred</t>
   </si>
 </sst>
 </file>
@@ -1493,22 +1608,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{752D3095-90A4-45FF-BD20-0492A3C6EFAC}">
   <dimension ref="A1:L143"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="21.21875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="29.77734375" customWidth="1"/>
+    <col min="2" max="2" width="21.1640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="29.83203125" customWidth="1"/>
     <col min="5" max="5" width="17" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.44140625" customWidth="1"/>
-    <col min="8" max="8" width="17.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.5" customWidth="1"/>
+    <col min="8" max="8" width="17.5" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="25" customWidth="1"/>
-    <col min="10" max="10" width="12.21875" customWidth="1"/>
-    <col min="11" max="11" width="14.21875" customWidth="1"/>
+    <col min="10" max="10" width="12.1640625" customWidth="1"/>
+    <col min="11" max="11" width="14.1640625" customWidth="1"/>
     <col min="12" max="12" width="88" customWidth="1"/>
-    <col min="13" max="18" width="9.21875" customWidth="1"/>
+    <col min="13" max="18" width="9.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1546,7 +1661,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -1584,7 +1699,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -1622,7 +1737,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -1660,7 +1775,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -1698,7 +1813,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -1736,7 +1851,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -1774,7 +1889,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -1812,7 +1927,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -1850,7 +1965,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -1888,7 +2003,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>12</v>
       </c>
@@ -1926,7 +2041,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>12</v>
       </c>
@@ -1964,7 +2079,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>12</v>
       </c>
@@ -2002,7 +2117,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>12</v>
       </c>
@@ -2040,7 +2155,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>12</v>
       </c>
@@ -2078,7 +2193,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>12</v>
       </c>
@@ -2116,7 +2231,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>12</v>
       </c>
@@ -2154,7 +2269,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>12</v>
       </c>
@@ -2192,7 +2307,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>12</v>
       </c>
@@ -2230,7 +2345,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>12</v>
       </c>
@@ -2268,7 +2383,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>12</v>
       </c>
@@ -2306,7 +2421,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>12</v>
       </c>
@@ -2344,7 +2459,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>12</v>
       </c>
@@ -2382,7 +2497,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>12</v>
       </c>
@@ -2420,7 +2535,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>12</v>
       </c>
@@ -2458,7 +2573,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>12</v>
       </c>
@@ -2496,7 +2611,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>12</v>
       </c>
@@ -2534,7 +2649,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>12</v>
       </c>
@@ -2572,7 +2687,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>12</v>
       </c>
@@ -2610,7 +2725,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>12</v>
       </c>
@@ -2648,7 +2763,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>12</v>
       </c>
@@ -2686,7 +2801,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>12</v>
       </c>
@@ -2724,7 +2839,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>12</v>
       </c>
@@ -2762,7 +2877,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>12</v>
       </c>
@@ -2800,7 +2915,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>12</v>
       </c>
@@ -2838,7 +2953,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>12</v>
       </c>
@@ -2876,7 +2991,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>12</v>
       </c>
@@ -2914,7 +3029,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>12</v>
       </c>
@@ -2952,7 +3067,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>12</v>
       </c>
@@ -2990,7 +3105,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>12</v>
       </c>
@@ -3028,7 +3143,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>12</v>
       </c>
@@ -3066,7 +3181,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>12</v>
       </c>
@@ -3104,7 +3219,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>12</v>
       </c>
@@ -3142,7 +3257,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>12</v>
       </c>
@@ -3180,7 +3295,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>12</v>
       </c>
@@ -3218,7 +3333,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>12</v>
       </c>
@@ -3256,7 +3371,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>12</v>
       </c>
@@ -3294,7 +3409,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>12</v>
       </c>
@@ -3332,7 +3447,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>12</v>
       </c>
@@ -3370,7 +3485,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>12</v>
       </c>
@@ -3408,7 +3523,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>12</v>
       </c>
@@ -3446,7 +3561,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>12</v>
       </c>
@@ -3484,7 +3599,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>12</v>
       </c>
@@ -3522,7 +3637,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>12</v>
       </c>
@@ -3560,7 +3675,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>12</v>
       </c>
@@ -3598,7 +3713,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>12</v>
       </c>
@@ -3636,7 +3751,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>12</v>
       </c>
@@ -3674,7 +3789,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>12</v>
       </c>
@@ -3712,7 +3827,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>12</v>
       </c>
@@ -3750,7 +3865,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>12</v>
       </c>
@@ -3788,7 +3903,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>12</v>
       </c>
@@ -3826,7 +3941,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>12</v>
       </c>
@@ -3864,7 +3979,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>12</v>
       </c>
@@ -3902,7 +4017,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>12</v>
       </c>
@@ -3940,7 +4055,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>12</v>
       </c>
@@ -3978,7 +4093,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>12</v>
       </c>
@@ -4016,7 +4131,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>12</v>
       </c>
@@ -4054,7 +4169,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="68" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>12</v>
       </c>
@@ -4092,7 +4207,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>12</v>
       </c>
@@ -4130,7 +4245,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="70" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>12</v>
       </c>
@@ -4168,7 +4283,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="71" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>12</v>
       </c>
@@ -4206,7 +4321,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>12</v>
       </c>
@@ -4244,7 +4359,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="73" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>12</v>
       </c>
@@ -4282,7 +4397,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="74" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>12</v>
       </c>
@@ -4320,7 +4435,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="75" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>12</v>
       </c>
@@ -4358,7 +4473,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="76" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>12</v>
       </c>
@@ -4396,7 +4511,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="77" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>12</v>
       </c>
@@ -4434,7 +4549,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="78" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>12</v>
       </c>
@@ -4472,7 +4587,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="79" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>12</v>
       </c>
@@ -4510,7 +4625,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="80" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>12</v>
       </c>
@@ -4548,7 +4663,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="81" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>12</v>
       </c>
@@ -4586,7 +4701,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="82" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>12</v>
       </c>
@@ -4624,7 +4739,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="83" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
         <v>12</v>
       </c>
@@ -4662,7 +4777,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="84" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
         <v>12</v>
       </c>
@@ -4700,7 +4815,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="85" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
         <v>12</v>
       </c>
@@ -4738,7 +4853,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="86" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
         <v>12</v>
       </c>
@@ -4776,7 +4891,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="87" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
         <v>12</v>
       </c>
@@ -4814,7 +4929,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="88" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
         <v>12</v>
       </c>
@@ -4852,7 +4967,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="89" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
         <v>12</v>
       </c>
@@ -4890,7 +5005,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="90" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
         <v>12</v>
       </c>
@@ -4928,7 +5043,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="91" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A91" s="8" t="s">
         <v>12</v>
       </c>
@@ -4966,7 +5081,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="92" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A92" s="8" t="s">
         <v>12</v>
       </c>
@@ -5004,7 +5119,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="93" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
         <v>12</v>
       </c>
@@ -5042,7 +5157,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="94" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
         <v>12</v>
       </c>
@@ -5080,7 +5195,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="95" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
         <v>12</v>
       </c>
@@ -5118,7 +5233,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="96" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
         <v>12</v>
       </c>
@@ -5156,7 +5271,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="97" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
         <v>12</v>
       </c>
@@ -5194,7 +5309,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="98" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
         <v>12</v>
       </c>
@@ -5232,7 +5347,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="99" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
         <v>12</v>
       </c>
@@ -5270,7 +5385,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="100" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
         <v>12</v>
       </c>
@@ -5308,7 +5423,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="101" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
         <v>12</v>
       </c>
@@ -5346,7 +5461,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="102" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
         <v>12</v>
       </c>
@@ -5384,7 +5499,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="103" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
         <v>12</v>
       </c>
@@ -5422,7 +5537,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="104" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
         <v>12</v>
       </c>
@@ -5460,7 +5575,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="105" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
         <v>12</v>
       </c>
@@ -5498,7 +5613,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="106" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
         <v>12</v>
       </c>
@@ -5536,7 +5651,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="107" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A107" s="8" t="s">
         <v>12</v>
       </c>
@@ -5574,7 +5689,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="108" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A108" s="8" t="s">
         <v>12</v>
       </c>
@@ -5612,7 +5727,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="109" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A109" s="8" t="s">
         <v>12</v>
       </c>
@@ -5650,7 +5765,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="110" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A110" s="8" t="s">
         <v>12</v>
       </c>
@@ -5688,7 +5803,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="111" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A111" s="8" t="s">
         <v>12</v>
       </c>
@@ -5726,7 +5841,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="112" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A112" s="8" t="s">
         <v>12</v>
       </c>
@@ -5764,7 +5879,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="113" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A113" s="8" t="s">
         <v>12</v>
       </c>
@@ -5802,7 +5917,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="114" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A114" s="8" t="s">
         <v>12</v>
       </c>
@@ -5840,7 +5955,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="115" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A115" s="8" t="s">
         <v>12</v>
       </c>
@@ -5878,7 +5993,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="116" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A116" s="8" t="s">
         <v>12</v>
       </c>
@@ -5916,7 +6031,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="117" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A117" s="8" t="s">
         <v>12</v>
       </c>
@@ -5954,7 +6069,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="118" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A118" s="8" t="s">
         <v>12</v>
       </c>
@@ -5992,7 +6107,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="119" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A119" s="8" t="s">
         <v>12</v>
       </c>
@@ -6030,7 +6145,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="120" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A120" s="8" t="s">
         <v>12</v>
       </c>
@@ -6068,7 +6183,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="121" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A121" s="8" t="s">
         <v>12</v>
       </c>
@@ -6106,7 +6221,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="122" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A122" s="8" t="s">
         <v>12</v>
       </c>
@@ -6144,7 +6259,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="123" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A123" s="8" t="s">
         <v>12</v>
       </c>
@@ -6182,7 +6297,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="124" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A124" s="8" t="s">
         <v>12</v>
       </c>
@@ -6220,7 +6335,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="125" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A125" s="8" t="s">
         <v>12</v>
       </c>
@@ -6258,7 +6373,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="126" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A126" s="8" t="s">
         <v>12</v>
       </c>
@@ -6296,7 +6411,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="127" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A127" s="8" t="s">
         <v>12</v>
       </c>
@@ -6334,7 +6449,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="128" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A128" s="8" t="s">
         <v>12</v>
       </c>
@@ -6372,7 +6487,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="129" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A129" s="8" t="s">
         <v>12</v>
       </c>
@@ -6410,7 +6525,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="130" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A130" s="8" t="s">
         <v>12</v>
       </c>
@@ -6448,7 +6563,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="131" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A131" s="8" t="s">
         <v>12</v>
       </c>
@@ -6486,7 +6601,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="132" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A132" s="8" t="s">
         <v>12</v>
       </c>
@@ -6524,7 +6639,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="133" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A133" s="8" t="s">
         <v>12</v>
       </c>
@@ -6562,7 +6677,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="134" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A134" s="8" t="s">
         <v>12</v>
       </c>
@@ -6600,7 +6715,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="135" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A135" s="8" t="s">
         <v>12</v>
       </c>
@@ -6638,7 +6753,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="136" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A136" s="8" t="s">
         <v>12</v>
       </c>
@@ -6676,7 +6791,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="137" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A137" s="8" t="s">
         <v>12</v>
       </c>
@@ -6714,7 +6829,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="138" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A138" s="8" t="s">
         <v>12</v>
       </c>
@@ -6752,7 +6867,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="139" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A139" s="8" t="s">
         <v>12</v>
       </c>
@@ -6790,7 +6905,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="140" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A140" s="8" t="s">
         <v>12</v>
       </c>
@@ -6828,7 +6943,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="141" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A141" s="8" t="s">
         <v>12</v>
       </c>
@@ -6866,7 +6981,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="142" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A142" s="8" t="s">
         <v>12</v>
       </c>
@@ -6904,7 +7019,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="143" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A143" s="8" t="s">
         <v>12</v>
       </c>
@@ -6950,22 +7065,22 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02C7B195-9C28-4152-A7C9-DCCF3DB8F404}">
   <dimension ref="A1:L44"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="21.21875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="29.77734375" customWidth="1"/>
+    <col min="2" max="2" width="21.1640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="29.83203125" customWidth="1"/>
     <col min="5" max="5" width="17" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.44140625" customWidth="1"/>
-    <col min="8" max="8" width="17.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.5" customWidth="1"/>
+    <col min="8" max="8" width="17.5" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="25" customWidth="1"/>
-    <col min="10" max="10" width="12.21875" customWidth="1"/>
-    <col min="11" max="11" width="14.21875" customWidth="1"/>
+    <col min="10" max="10" width="12.1640625" customWidth="1"/>
+    <col min="11" max="11" width="14.1640625" customWidth="1"/>
     <col min="12" max="12" width="88" customWidth="1"/>
-    <col min="13" max="18" width="9.21875" customWidth="1"/>
+    <col min="13" max="18" width="9.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -7003,7 +7118,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -7041,7 +7156,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -7079,7 +7194,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -7117,7 +7232,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -7155,7 +7270,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -7193,7 +7308,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -7231,7 +7346,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -7269,7 +7384,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -7307,7 +7422,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -7345,7 +7460,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>12</v>
       </c>
@@ -7383,7 +7498,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>12</v>
       </c>
@@ -7421,7 +7536,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>12</v>
       </c>
@@ -7459,7 +7574,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>12</v>
       </c>
@@ -7497,7 +7612,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>12</v>
       </c>
@@ -7535,7 +7650,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>12</v>
       </c>
@@ -7573,7 +7688,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>12</v>
       </c>
@@ -7611,7 +7726,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>12</v>
       </c>
@@ -7649,7 +7764,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>12</v>
       </c>
@@ -7687,7 +7802,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>12</v>
       </c>
@@ -7725,7 +7840,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>12</v>
       </c>
@@ -7763,7 +7878,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>12</v>
       </c>
@@ -7801,7 +7916,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>12</v>
       </c>
@@ -7839,7 +7954,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>12</v>
       </c>
@@ -7877,7 +7992,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>12</v>
       </c>
@@ -7915,7 +8030,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>12</v>
       </c>
@@ -7953,7 +8068,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>12</v>
       </c>
@@ -7991,7 +8106,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>12</v>
       </c>
@@ -8029,7 +8144,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>12</v>
       </c>
@@ -8067,7 +8182,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>12</v>
       </c>
@@ -8105,7 +8220,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>12</v>
       </c>
@@ -8143,7 +8258,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>12</v>
       </c>
@@ -8181,7 +8296,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>12</v>
       </c>
@@ -8219,7 +8334,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>12</v>
       </c>
@@ -8257,7 +8372,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>12</v>
       </c>
@@ -8295,7 +8410,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>12</v>
       </c>
@@ -8333,7 +8448,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>12</v>
       </c>
@@ -8371,7 +8486,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>12</v>
       </c>
@@ -8409,7 +8524,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>12</v>
       </c>
@@ -8447,7 +8562,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>12</v>
       </c>
@@ -8485,7 +8600,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>12</v>
       </c>
@@ -8523,7 +8638,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>12</v>
       </c>
@@ -8561,7 +8676,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>12</v>
       </c>
@@ -8599,7 +8714,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>12</v>
       </c>
@@ -8645,21 +8760,21 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA328016-6EE1-4F6F-84C5-5395FF87B11C}">
   <dimension ref="A1:L43"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="3" max="3" width="7.77734375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="52.21875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="21.21875" customWidth="1"/>
-    <col min="6" max="6" width="10.5546875" customWidth="1"/>
-    <col min="7" max="7" width="14.21875" customWidth="1"/>
-    <col min="8" max="8" width="17.5546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="16.21875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.21875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="93.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.83203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="52.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.1640625" customWidth="1"/>
+    <col min="6" max="6" width="10.5" customWidth="1"/>
+    <col min="7" max="7" width="14.1640625" customWidth="1"/>
+    <col min="8" max="8" width="17.5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.1640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.1640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="93.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -8697,7 +8812,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -8735,7 +8850,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -8773,7 +8888,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -8811,7 +8926,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -8849,7 +8964,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -8887,7 +9002,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -8925,7 +9040,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -8963,7 +9078,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -9001,7 +9116,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -9039,7 +9154,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>12</v>
       </c>
@@ -9077,7 +9192,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>12</v>
       </c>
@@ -9115,7 +9230,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>12</v>
       </c>
@@ -9153,7 +9268,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>12</v>
       </c>
@@ -9191,7 +9306,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>12</v>
       </c>
@@ -9229,7 +9344,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>12</v>
       </c>
@@ -9267,7 +9382,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>12</v>
       </c>
@@ -9305,7 +9420,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>12</v>
       </c>
@@ -9343,7 +9458,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>12</v>
       </c>
@@ -9381,7 +9496,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>12</v>
       </c>
@@ -9419,7 +9534,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>12</v>
       </c>
@@ -9457,7 +9572,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>12</v>
       </c>
@@ -9495,7 +9610,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>12</v>
       </c>
@@ -9533,7 +9648,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>12</v>
       </c>
@@ -9571,7 +9686,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>12</v>
       </c>
@@ -9609,7 +9724,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>12</v>
       </c>
@@ -9647,7 +9762,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>12</v>
       </c>
@@ -9685,7 +9800,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>12</v>
       </c>
@@ -9723,7 +9838,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>12</v>
       </c>
@@ -9761,7 +9876,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>12</v>
       </c>
@@ -9799,7 +9914,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>12</v>
       </c>
@@ -9837,7 +9952,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>12</v>
       </c>
@@ -9875,7 +9990,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>12</v>
       </c>
@@ -9913,7 +10028,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>12</v>
       </c>
@@ -9951,7 +10066,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>12</v>
       </c>
@@ -9989,7 +10104,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>12</v>
       </c>
@@ -10027,7 +10142,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>12</v>
       </c>
@@ -10065,7 +10180,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>12</v>
       </c>
@@ -10103,7 +10218,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>12</v>
       </c>
@@ -10141,7 +10256,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>12</v>
       </c>
@@ -10179,7 +10294,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>12</v>
       </c>
@@ -10217,7 +10332,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>12</v>
       </c>
@@ -10255,7 +10370,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>12</v>
       </c>
@@ -10301,18 +10416,18 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E6501C2-1F4E-44C1-926E-7B80FAB5E9FA}">
   <dimension ref="A1:L22"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="4" max="4" width="38" customWidth="1"/>
-    <col min="5" max="5" width="22.77734375" customWidth="1"/>
-    <col min="8" max="8" width="18.77734375" customWidth="1"/>
-    <col min="9" max="9" width="14.77734375" customWidth="1"/>
-    <col min="10" max="10" width="18.5546875" customWidth="1"/>
-    <col min="11" max="11" width="15.77734375" customWidth="1"/>
+    <col min="5" max="5" width="22.83203125" customWidth="1"/>
+    <col min="8" max="8" width="18.83203125" customWidth="1"/>
+    <col min="9" max="9" width="14.83203125" customWidth="1"/>
+    <col min="10" max="10" width="18.5" customWidth="1"/>
+    <col min="11" max="11" width="15.83203125" customWidth="1"/>
     <col min="12" max="12" width="54" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -10350,7 +10465,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -10388,7 +10503,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -10426,7 +10541,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -10464,7 +10579,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -10502,7 +10617,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6" s="8" t="s">
         <v>12</v>
       </c>
@@ -10540,7 +10655,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" s="8" t="s">
         <v>12</v>
       </c>
@@ -10578,7 +10693,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -10616,7 +10731,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -10654,7 +10769,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -10692,7 +10807,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>12</v>
       </c>
@@ -10730,7 +10845,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>12</v>
       </c>
@@ -10768,7 +10883,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>12</v>
       </c>
@@ -10806,7 +10921,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>12</v>
       </c>
@@ -10844,7 +10959,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>12</v>
       </c>
@@ -10882,7 +10997,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>12</v>
       </c>
@@ -10920,7 +11035,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>12</v>
       </c>
@@ -10958,7 +11073,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>12</v>
       </c>
@@ -10996,7 +11111,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>12</v>
       </c>
@@ -11034,7 +11149,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>12</v>
       </c>
@@ -11072,7 +11187,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>12</v>
       </c>
@@ -11110,7 +11225,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
       <c r="L22" s="19"/>
     </row>
   </sheetData>
@@ -11121,16 +11236,16 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2CE0DD1A-FCA4-41B6-815F-1DF4FD2DD0A1}">
   <dimension ref="A1:L46"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
-    <col min="2" max="2" width="10.77734375" customWidth="1"/>
-    <col min="3" max="3" width="9.21875" customWidth="1"/>
-    <col min="4" max="4" width="38.5546875" customWidth="1"/>
+    <col min="2" max="2" width="10.83203125" customWidth="1"/>
+    <col min="3" max="3" width="9.1640625" customWidth="1"/>
+    <col min="4" max="4" width="38.5" customWidth="1"/>
     <col min="5" max="12" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -11168,7 +11283,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" s="8" t="s">
         <v>12</v>
       </c>
@@ -11206,7 +11321,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A3" s="8" t="s">
         <v>12</v>
       </c>
@@ -11244,7 +11359,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" s="8" t="s">
         <v>12</v>
       </c>
@@ -11282,7 +11397,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="8" t="s">
         <v>12</v>
       </c>
@@ -11320,7 +11435,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6" s="8" t="s">
         <v>12</v>
       </c>
@@ -11358,7 +11473,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" s="8" t="s">
         <v>12</v>
       </c>
@@ -11396,7 +11511,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" s="8" t="s">
         <v>12</v>
       </c>
@@ -11434,7 +11549,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A9" s="8" t="s">
         <v>12</v>
       </c>
@@ -11472,7 +11587,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A10" s="8" t="s">
         <v>12</v>
       </c>
@@ -11510,7 +11625,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A11" s="8" t="s">
         <v>12</v>
       </c>
@@ -11548,7 +11663,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A12" s="8" t="s">
         <v>12</v>
       </c>
@@ -11586,7 +11701,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A13" s="8" t="s">
         <v>12</v>
       </c>
@@ -11624,7 +11739,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A14" s="8" t="s">
         <v>12</v>
       </c>
@@ -11662,7 +11777,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A15" s="8" t="s">
         <v>12</v>
       </c>
@@ -11700,7 +11815,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A16" s="8" t="s">
         <v>12</v>
       </c>
@@ -11738,7 +11853,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A17" s="8" t="s">
         <v>12</v>
       </c>
@@ -11776,7 +11891,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A18" s="8" t="s">
         <v>12</v>
       </c>
@@ -11814,7 +11929,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A19" s="8" t="s">
         <v>12</v>
       </c>
@@ -11852,7 +11967,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A20" s="8" t="s">
         <v>12</v>
       </c>
@@ -11890,7 +12005,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A21" s="8" t="s">
         <v>12</v>
       </c>
@@ -11928,7 +12043,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A22" s="8" t="s">
         <v>12</v>
       </c>
@@ -11966,7 +12081,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A23" s="8" t="s">
         <v>12</v>
       </c>
@@ -12004,7 +12119,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A24" s="8" t="s">
         <v>12</v>
       </c>
@@ -12042,7 +12157,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A25" s="8" t="s">
         <v>12</v>
       </c>
@@ -12080,7 +12195,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A26" s="8" t="s">
         <v>12</v>
       </c>
@@ -12118,7 +12233,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A27" s="8" t="s">
         <v>12</v>
       </c>
@@ -12156,7 +12271,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A28" s="8" t="s">
         <v>12</v>
       </c>
@@ -12194,7 +12309,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A29" s="8" t="s">
         <v>12</v>
       </c>
@@ -12232,7 +12347,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A30" s="8" t="s">
         <v>12</v>
       </c>
@@ -12270,7 +12385,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A31" s="8" t="s">
         <v>12</v>
       </c>
@@ -12308,7 +12423,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A32" s="8" t="s">
         <v>12</v>
       </c>
@@ -12346,7 +12461,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A33" s="8" t="s">
         <v>12</v>
       </c>
@@ -12384,7 +12499,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A34" s="8" t="s">
         <v>12</v>
       </c>
@@ -12422,7 +12537,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A35" s="8" t="s">
         <v>12</v>
       </c>
@@ -12460,7 +12575,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A36" s="8" t="s">
         <v>12</v>
       </c>
@@ -12498,7 +12613,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A37" s="8" t="s">
         <v>12</v>
       </c>
@@ -12536,7 +12651,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A38" s="8" t="s">
         <v>12</v>
       </c>
@@ -12574,29 +12689,577 @@
         <v>310</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.2">
       <c r="D39" s="14"/>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.2">
       <c r="D40" s="14"/>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.2">
       <c r="D41" s="14"/>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.2">
       <c r="D42" s="14"/>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.2">
       <c r="D43" s="14"/>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.2">
       <c r="D44" s="14"/>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.2">
       <c r="D45" s="15"/>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.2">
       <c r="D46" s="15"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2977C247-05DC-724D-A00A-EDAB54DF4626}">
+  <dimension ref="A1:L15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="4" max="4" width="19" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="33.5" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="59.1640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" t="s">
+        <v>262</v>
+      </c>
+      <c r="D2" t="s">
+        <v>316</v>
+      </c>
+      <c r="E2" t="s">
+        <v>317</v>
+      </c>
+      <c r="F2" t="s">
+        <v>62</v>
+      </c>
+      <c r="G2" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2" t="s">
+        <v>100</v>
+      </c>
+      <c r="I2" t="s">
+        <v>318</v>
+      </c>
+      <c r="J2" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="K2" t="s">
+        <v>81</v>
+      </c>
+      <c r="L2" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" t="s">
+        <v>262</v>
+      </c>
+      <c r="D3" t="s">
+        <v>320</v>
+      </c>
+      <c r="E3" t="s">
+        <v>321</v>
+      </c>
+      <c r="F3" t="s">
+        <v>62</v>
+      </c>
+      <c r="G3" t="s">
+        <v>78</v>
+      </c>
+      <c r="H3" t="s">
+        <v>100</v>
+      </c>
+      <c r="I3" t="s">
+        <v>322</v>
+      </c>
+      <c r="J3" t="s">
+        <v>80</v>
+      </c>
+      <c r="K3" t="s">
+        <v>81</v>
+      </c>
+      <c r="L3" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>262</v>
+      </c>
+      <c r="D4" t="s">
+        <v>324</v>
+      </c>
+      <c r="E4" t="s">
+        <v>321</v>
+      </c>
+      <c r="F4" t="s">
+        <v>62</v>
+      </c>
+      <c r="G4" t="s">
+        <v>325</v>
+      </c>
+      <c r="H4" t="s">
+        <v>100</v>
+      </c>
+      <c r="I4" t="s">
+        <v>326</v>
+      </c>
+      <c r="J4" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="K4" t="s">
+        <v>157</v>
+      </c>
+      <c r="L4" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" t="s">
+        <v>262</v>
+      </c>
+      <c r="D5" t="s">
+        <v>328</v>
+      </c>
+      <c r="E5" t="s">
+        <v>321</v>
+      </c>
+      <c r="F5" t="s">
+        <v>62</v>
+      </c>
+      <c r="G5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H5" t="s">
+        <v>79</v>
+      </c>
+      <c r="I5" t="s">
+        <v>326</v>
+      </c>
+      <c r="J5" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="K5" t="s">
+        <v>81</v>
+      </c>
+      <c r="L5" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" t="s">
+        <v>262</v>
+      </c>
+      <c r="D6" t="s">
+        <v>330</v>
+      </c>
+      <c r="E6" t="s">
+        <v>321</v>
+      </c>
+      <c r="F6" t="s">
+        <v>62</v>
+      </c>
+      <c r="G6" t="s">
+        <v>86</v>
+      </c>
+      <c r="H6" t="s">
+        <v>79</v>
+      </c>
+      <c r="I6" t="s">
+        <v>326</v>
+      </c>
+      <c r="J6" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="K6" t="s">
+        <v>81</v>
+      </c>
+      <c r="L6" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" t="s">
+        <v>262</v>
+      </c>
+      <c r="D7" t="s">
+        <v>332</v>
+      </c>
+      <c r="E7" t="s">
+        <v>321</v>
+      </c>
+      <c r="F7" t="s">
+        <v>62</v>
+      </c>
+      <c r="G7" t="s">
+        <v>86</v>
+      </c>
+      <c r="H7" t="s">
+        <v>100</v>
+      </c>
+      <c r="I7" t="s">
+        <v>326</v>
+      </c>
+      <c r="J7" t="s">
+        <v>80</v>
+      </c>
+      <c r="K7" t="s">
+        <v>81</v>
+      </c>
+      <c r="L7" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
+        <v>262</v>
+      </c>
+      <c r="D8" t="s">
+        <v>334</v>
+      </c>
+      <c r="E8" t="s">
+        <v>321</v>
+      </c>
+      <c r="F8" t="s">
+        <v>68</v>
+      </c>
+      <c r="G8" t="s">
+        <v>86</v>
+      </c>
+      <c r="H8" t="s">
+        <v>79</v>
+      </c>
+      <c r="I8" t="s">
+        <v>326</v>
+      </c>
+      <c r="J8" t="s">
+        <v>80</v>
+      </c>
+      <c r="K8" t="s">
+        <v>81</v>
+      </c>
+      <c r="L8" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" t="s">
+        <v>262</v>
+      </c>
+      <c r="D9" t="s">
+        <v>336</v>
+      </c>
+      <c r="E9" t="s">
+        <v>321</v>
+      </c>
+      <c r="F9" t="s">
+        <v>62</v>
+      </c>
+      <c r="G9" t="s">
+        <v>78</v>
+      </c>
+      <c r="H9" t="s">
+        <v>100</v>
+      </c>
+      <c r="I9" t="s">
+        <v>326</v>
+      </c>
+      <c r="J9" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="K9" t="s">
+        <v>81</v>
+      </c>
+      <c r="L9" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10" t="s">
+        <v>262</v>
+      </c>
+      <c r="D10" t="s">
+        <v>338</v>
+      </c>
+      <c r="E10" t="s">
+        <v>321</v>
+      </c>
+      <c r="F10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G10" t="s">
+        <v>339</v>
+      </c>
+      <c r="H10" t="s">
+        <v>79</v>
+      </c>
+      <c r="I10" t="s">
+        <v>340</v>
+      </c>
+      <c r="J10" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="K10" t="s">
+        <v>157</v>
+      </c>
+      <c r="L10" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" t="s">
+        <v>262</v>
+      </c>
+      <c r="D11" t="s">
+        <v>342</v>
+      </c>
+      <c r="E11" t="s">
+        <v>321</v>
+      </c>
+      <c r="F11" t="s">
+        <v>15</v>
+      </c>
+      <c r="G11" t="s">
+        <v>78</v>
+      </c>
+      <c r="H11" t="s">
+        <v>100</v>
+      </c>
+      <c r="I11" t="s">
+        <v>322</v>
+      </c>
+      <c r="J11" t="s">
+        <v>80</v>
+      </c>
+      <c r="K11" t="s">
+        <v>81</v>
+      </c>
+      <c r="L11" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12" t="s">
+        <v>262</v>
+      </c>
+      <c r="D12" t="s">
+        <v>344</v>
+      </c>
+      <c r="E12" t="s">
+        <v>321</v>
+      </c>
+      <c r="F12" t="s">
+        <v>62</v>
+      </c>
+      <c r="G12" t="s">
+        <v>130</v>
+      </c>
+      <c r="H12" t="s">
+        <v>100</v>
+      </c>
+      <c r="I12" t="s">
+        <v>326</v>
+      </c>
+      <c r="J12" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="K12" t="s">
+        <v>81</v>
+      </c>
+      <c r="L12" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>262</v>
+      </c>
+      <c r="D13" t="s">
+        <v>346</v>
+      </c>
+      <c r="E13" t="s">
+        <v>321</v>
+      </c>
+      <c r="F13" t="s">
+        <v>62</v>
+      </c>
+      <c r="G13" t="s">
+        <v>130</v>
+      </c>
+      <c r="H13" t="s">
+        <v>100</v>
+      </c>
+      <c r="I13" t="s">
+        <v>347</v>
+      </c>
+      <c r="J13" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="K13" t="s">
+        <v>81</v>
+      </c>
+      <c r="L13" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>12</v>
+      </c>
+      <c r="B14" t="s">
+        <v>262</v>
+      </c>
+      <c r="D14" t="s">
+        <v>349</v>
+      </c>
+      <c r="E14" t="s">
+        <v>321</v>
+      </c>
+      <c r="F14" t="s">
+        <v>62</v>
+      </c>
+      <c r="G14" t="s">
+        <v>130</v>
+      </c>
+      <c r="H14" t="s">
+        <v>100</v>
+      </c>
+      <c r="I14" t="s">
+        <v>347</v>
+      </c>
+      <c r="J14" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="K14" t="s">
+        <v>81</v>
+      </c>
+      <c r="L14" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>12</v>
+      </c>
+      <c r="B15" t="s">
+        <v>262</v>
+      </c>
+      <c r="D15" t="s">
+        <v>351</v>
+      </c>
+      <c r="E15" t="s">
+        <v>352</v>
+      </c>
+      <c r="F15" t="s">
+        <v>15</v>
+      </c>
+      <c r="G15" t="s">
+        <v>127</v>
+      </c>
+      <c r="H15" t="s">
+        <v>100</v>
+      </c>
+      <c r="I15" t="s">
+        <v>322</v>
+      </c>
+      <c r="J15" t="s">
+        <v>80</v>
+      </c>
+      <c r="K15" t="s">
+        <v>81</v>
+      </c>
+      <c r="L15" t="s">
+        <v>353</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/docs/CDOP_SCHEMA.xlsx
+++ b/docs/CDOP_SCHEMA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nikodem_lacki/Documents/work/Carbon-Data-Open-Protocol/Carbon-Data-Open-Protocol/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB2C76EC-64A6-094D-8D1D-959D7E8DB494}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{034ACC84-3FB7-7D4F-8DFC-0EE4C24BC35C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1320" yWindow="600" windowWidth="33940" windowHeight="15180" activeTab="5" xr2:uid="{743398AF-A4FE-47C4-9368-972E95242EBF}"/>
+    <workbookView xWindow="16380" yWindow="14320" windowWidth="33940" windowHeight="15180" activeTab="5" xr2:uid="{743398AF-A4FE-47C4-9368-972E95242EBF}"/>
   </bookViews>
   <sheets>
     <sheet name="Full List" sheetId="5" r:id="rId1"/>
@@ -12778,6 +12778,9 @@
       <c r="B2" t="s">
         <v>262</v>
       </c>
+      <c r="C2">
+        <v>143</v>
+      </c>
       <c r="D2" t="s">
         <v>316</v>
       </c>
@@ -12813,6 +12816,9 @@
       <c r="B3" t="s">
         <v>262</v>
       </c>
+      <c r="C3">
+        <v>144</v>
+      </c>
       <c r="D3" t="s">
         <v>320</v>
       </c>
@@ -12848,6 +12854,9 @@
       <c r="B4" t="s">
         <v>262</v>
       </c>
+      <c r="C4">
+        <v>145</v>
+      </c>
       <c r="D4" t="s">
         <v>324</v>
       </c>
@@ -12883,6 +12892,9 @@
       <c r="B5" t="s">
         <v>262</v>
       </c>
+      <c r="C5">
+        <v>146</v>
+      </c>
       <c r="D5" t="s">
         <v>328</v>
       </c>
@@ -12890,7 +12902,7 @@
         <v>321</v>
       </c>
       <c r="F5" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="G5" t="s">
         <v>86</v>
@@ -12918,6 +12930,9 @@
       <c r="B6" t="s">
         <v>262</v>
       </c>
+      <c r="C6">
+        <v>147</v>
+      </c>
       <c r="D6" t="s">
         <v>330</v>
       </c>
@@ -12925,7 +12940,7 @@
         <v>321</v>
       </c>
       <c r="F6" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="G6" t="s">
         <v>86</v>
@@ -12953,6 +12968,9 @@
       <c r="B7" t="s">
         <v>262</v>
       </c>
+      <c r="C7">
+        <v>148</v>
+      </c>
       <c r="D7" t="s">
         <v>332</v>
       </c>
@@ -12988,6 +13006,9 @@
       <c r="B8" t="s">
         <v>262</v>
       </c>
+      <c r="C8">
+        <v>149</v>
+      </c>
       <c r="D8" t="s">
         <v>334</v>
       </c>
@@ -13023,6 +13044,9 @@
       <c r="B9" t="s">
         <v>262</v>
       </c>
+      <c r="C9">
+        <v>150</v>
+      </c>
       <c r="D9" t="s">
         <v>336</v>
       </c>
@@ -13058,6 +13082,9 @@
       <c r="B10" t="s">
         <v>262</v>
       </c>
+      <c r="C10">
+        <v>151</v>
+      </c>
       <c r="D10" t="s">
         <v>338</v>
       </c>
@@ -13065,7 +13092,7 @@
         <v>321</v>
       </c>
       <c r="F10" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="G10" t="s">
         <v>339</v>
@@ -13093,6 +13120,9 @@
       <c r="B11" t="s">
         <v>262</v>
       </c>
+      <c r="C11">
+        <v>152</v>
+      </c>
       <c r="D11" t="s">
         <v>342</v>
       </c>
@@ -13128,6 +13158,9 @@
       <c r="B12" t="s">
         <v>262</v>
       </c>
+      <c r="C12">
+        <v>153</v>
+      </c>
       <c r="D12" t="s">
         <v>344</v>
       </c>
@@ -13163,6 +13196,9 @@
       <c r="B13" t="s">
         <v>262</v>
       </c>
+      <c r="C13">
+        <v>154</v>
+      </c>
       <c r="D13" t="s">
         <v>346</v>
       </c>
@@ -13198,6 +13234,9 @@
       <c r="B14" t="s">
         <v>262</v>
       </c>
+      <c r="C14">
+        <v>155</v>
+      </c>
       <c r="D14" t="s">
         <v>349</v>
       </c>
@@ -13232,6 +13271,9 @@
       </c>
       <c r="B15" t="s">
         <v>262</v>
+      </c>
+      <c r="C15">
+        <v>156</v>
       </c>
       <c r="D15" t="s">
         <v>351</v>

--- a/docs/CDOP_SCHEMA.xlsx
+++ b/docs/CDOP_SCHEMA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ghoffman\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AA1516A1-730D-4B52-BA1A-5F15D817C559}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF6130C2-3D23-411F-9F95-C8F56C81D03C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{743398AF-A4FE-47C4-9368-972E95242EBF}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{743398AF-A4FE-47C4-9368-972E95242EBF}"/>
   </bookViews>
   <sheets>
     <sheet name="Full List" sheetId="5" r:id="rId1"/>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5925" uniqueCount="761">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5925" uniqueCount="763">
   <si>
     <t>schema</t>
   </si>
@@ -2374,6 +2374,12 @@
   </si>
   <si>
     <t xml:space="preserve">Mutable </t>
+  </si>
+  <si>
+    <t>unit.credit_block[].block_start</t>
+  </si>
+  <si>
+    <t>project.crediting_period[].current_crediting_period_duration</t>
   </si>
 </sst>
 </file>
@@ -21462,7 +21468,7 @@
         <v>445</v>
       </c>
       <c r="F15" t="s">
-        <v>540</v>
+        <v>761</v>
       </c>
       <c r="G15" t="s">
         <v>18</v>
@@ -21896,7 +21902,7 @@
         <v>16</v>
       </c>
       <c r="F9" t="s">
-        <v>548</v>
+        <v>762</v>
       </c>
       <c r="G9" t="s">
         <v>30</v>

--- a/docs/CDOP_SCHEMA.xlsx
+++ b/docs/CDOP_SCHEMA.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rockmtnins-my.sharepoint.com/personal/sebastian_weeks_rmi_org/Documents/Documents/CDOP Resources/UseCase_Category CSVs_JSONs/Master Version/7_31_26/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rockmtnins-my.sharepoint.com/personal/sebastian_weeks_rmi_org/Documents/Documents/CDOP Resources/UseCase_Category CSVs_JSONs/Master Version/Round 2 Pods for Testing/Fast Track Pods/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="115" documentId="8_{E4888AF0-8469-49B9-BF1F-D7429471A122}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{72629C6E-FAAF-4F87-B2E5-800C2876AE8E}"/>
+  <xr:revisionPtr revIDLastSave="471" documentId="8_{E4888AF0-8469-49B9-BF1F-D7429471A122}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{08F8C38D-0960-4BDB-AD51-6369C48E9E43}"/>
   <bookViews>
-    <workbookView xWindow="-28065" yWindow="540" windowWidth="27360" windowHeight="14955" firstSheet="6" activeTab="11" xr2:uid="{743398AF-A4FE-47C4-9368-972E95242EBF}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="12" activeTab="14" xr2:uid="{743398AF-A4FE-47C4-9368-972E95242EBF}"/>
   </bookViews>
   <sheets>
     <sheet name="Full List" sheetId="5" r:id="rId1"/>
@@ -25,6 +25,9 @@
     <sheet name="Durability_Permanence" sheetId="10" r:id="rId10"/>
     <sheet name="Project Finance" sheetId="11" r:id="rId11"/>
     <sheet name="Labels_Certifications" sheetId="12" r:id="rId12"/>
+    <sheet name="Registry_Metadata" sheetId="13" r:id="rId13"/>
+    <sheet name="Validation_Metadata" sheetId="14" r:id="rId14"/>
+    <sheet name="Verification_Metadata" sheetId="15" r:id="rId15"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Full List'!$A$1:$M$174</definedName>
@@ -50,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6394" uniqueCount="823">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7098" uniqueCount="1021">
   <si>
     <t>schema</t>
   </si>
@@ -2562,12 +2565,606 @@
   <si>
     <t>project.project_level[].project_level_compliance_potential_eligibility</t>
   </si>
+  <si>
+    <t>crediting program</t>
+  </si>
+  <si>
+    <t>Describes the current registry, that contains the information about the project, and units</t>
+  </si>
+  <si>
+    <t>Describes the first registry, where the project was registered</t>
+  </si>
+  <si>
+    <t>Describes the Crediting Program that the proejct is following for the implementationunits</t>
+  </si>
+  <si>
+    <t>Date of the last update</t>
+  </si>
+  <si>
+    <t>registry_identifier</t>
+  </si>
+  <si>
+    <t>registry_name</t>
+  </si>
+  <si>
+    <t>registry_link</t>
+  </si>
+  <si>
+    <t>original_registry_identifier</t>
+  </si>
+  <si>
+    <t>original_registry_name</t>
+  </si>
+  <si>
+    <t>original_registry_link</t>
+  </si>
+  <si>
+    <t>program_identifier</t>
+  </si>
+  <si>
+    <t>program_name</t>
+  </si>
+  <si>
+    <t>creation_date</t>
+  </si>
+  <si>
+    <t>update_date</t>
+  </si>
+  <si>
+    <t>Date that the project was first registered</t>
+  </si>
+  <si>
+    <t>registry.creation_date</t>
+  </si>
+  <si>
+    <t>registry.update_date</t>
+  </si>
+  <si>
+    <t>registry.identification[].registry_identifier</t>
+  </si>
+  <si>
+    <t>registry.identification[].registry_name</t>
+  </si>
+  <si>
+    <t>registry.identification[].registry_link</t>
+  </si>
+  <si>
+    <t>registry.original[].original_registry_identifier</t>
+  </si>
+  <si>
+    <t>registry.original[].original_registry_name</t>
+  </si>
+  <si>
+    <t>registry.original[].original_registry_link</t>
+  </si>
+  <si>
+    <t>registry.program[].program_identifier</t>
+  </si>
+  <si>
+    <t>registry.program[].program_name</t>
+  </si>
+  <si>
+    <t>current_validation_stage</t>
+  </si>
+  <si>
+    <t>current_validation_stage_status</t>
+  </si>
+  <si>
+    <t>date_previous_validation</t>
+  </si>
+  <si>
+    <t>date_validation_expiration</t>
+  </si>
+  <si>
+    <t>date_validation_planned</t>
+  </si>
+  <si>
+    <t>date_validation_requested</t>
+  </si>
+  <si>
+    <t>validation_body_accreditation</t>
+  </si>
+  <si>
+    <t>validation_body_id</t>
+  </si>
+  <si>
+    <t>validator_name</t>
+  </si>
+  <si>
+    <t>validation_body_sectoral_scopes</t>
+  </si>
+  <si>
+    <t>validation_body_selection</t>
+  </si>
+  <si>
+    <t>validation_body_team_members_and_roles</t>
+  </si>
+  <si>
+    <t>validation_is_planned</t>
+  </si>
+  <si>
+    <t>validation_period_end_date</t>
+  </si>
+  <si>
+    <t>validation_period_start_date</t>
+  </si>
+  <si>
+    <t>validation_report_link</t>
+  </si>
+  <si>
+    <t>validation_report_summary</t>
+  </si>
+  <si>
+    <t>validation_stage_description</t>
+  </si>
+  <si>
+    <t>validation_stage_document_link</t>
+  </si>
+  <si>
+    <t>validation_stages</t>
+  </si>
+  <si>
+    <t>validation_status</t>
+  </si>
+  <si>
+    <t>validation_report_version</t>
+  </si>
+  <si>
+    <t>Validation and Verification Body (VVB)/ Certification Bodies/ Third Party Auditors</t>
+  </si>
+  <si>
+    <t>Name of the current validation step</t>
+  </si>
+  <si>
+    <t>Status of the current validation step</t>
+  </si>
+  <si>
+    <t>Date of the previous validation event</t>
+  </si>
+  <si>
+    <t>Date validation expires</t>
+  </si>
+  <si>
+    <t>Planned date of the validation event</t>
+  </si>
+  <si>
+    <t>Date validation was requested</t>
+  </si>
+  <si>
+    <t>LCA has been completed</t>
+  </si>
+  <si>
+    <t>LCA is used to quantify emissions</t>
+  </si>
+  <si>
+    <t>Link to LCA report</t>
+  </si>
+  <si>
+    <t>Link to LCA repository</t>
+  </si>
+  <si>
+    <t>LCA results</t>
+  </si>
+  <si>
+    <t>Link to LCA system boundary figure</t>
+  </si>
+  <si>
+    <t>Overview description of LCA system boundary</t>
+  </si>
+  <si>
+    <t>Identification number of the validation event.</t>
+  </si>
+  <si>
+    <t>Type of validation being carried out</t>
+  </si>
+  <si>
+    <t>List any accreditations of the validation body</t>
+  </si>
+  <si>
+    <t>Identification number of the validation body</t>
+  </si>
+  <si>
+    <t>Name of the validation body</t>
+  </si>
+  <si>
+    <t>Name(s) of the validator(s)</t>
+  </si>
+  <si>
+    <t>List the sectoral scopes the validation body is accredited to validate</t>
+  </si>
+  <si>
+    <t>Describe how the validation body was selected</t>
+  </si>
+  <si>
+    <t>List the names of any other validation body team members and their roles (FIRST NAME - LAST NAME, ROLE)</t>
+  </si>
+  <si>
+    <t>Date of validation event</t>
+  </si>
+  <si>
+    <t>Indicate whether the valiation event is planned.</t>
+  </si>
+  <si>
+    <t>End date of the validation event. Estimate if needed.</t>
+  </si>
+  <si>
+    <t>Start date of the validation event</t>
+  </si>
+  <si>
+    <t>Link (URL) to the project's validation report (if applicable).</t>
+  </si>
+  <si>
+    <t>Enter the validation report's summary</t>
+  </si>
+  <si>
+    <t>Describe the stages of the validation event.</t>
+  </si>
+  <si>
+    <t>Link (URL) to the document that contains the description and details of the validation event stages</t>
+  </si>
+  <si>
+    <t>Select all validation event stages</t>
+  </si>
+  <si>
+    <t>Indicate whether the project has been validated.</t>
+  </si>
+  <si>
+    <t>Which version of the validation report is the current version</t>
+  </si>
+  <si>
+    <t>lca_completed</t>
+  </si>
+  <si>
+    <t>lca_emissions_quantification</t>
+  </si>
+  <si>
+    <t>lca_link</t>
+  </si>
+  <si>
+    <t>lca_repository</t>
+  </si>
+  <si>
+    <t>lca_results</t>
+  </si>
+  <si>
+    <t>lca_system_boundary_figure</t>
+  </si>
+  <si>
+    <t>lca_system_boundary_overview</t>
+  </si>
+  <si>
+    <t>validation _id</t>
+  </si>
+  <si>
+    <t>validation_body</t>
+  </si>
+  <si>
+    <t>validation.crediting_period[].current_crediting_period_end_date</t>
+  </si>
+  <si>
+    <t>project.validation_stage[].current_validation_stage</t>
+  </si>
+  <si>
+    <t>validation.stage[].validation_stage_document_link</t>
+  </si>
+  <si>
+    <t>validation.crediting_period[].current_crediting_period_number</t>
+  </si>
+  <si>
+    <t>project.validation_stage[].current_validation_stage_status</t>
+  </si>
+  <si>
+    <t>validation.crediting_period[].current_crediting_period_start_date</t>
+  </si>
+  <si>
+    <t>project.date[].date_previous_validation</t>
+  </si>
+  <si>
+    <t>validation.date[].date_validation_expiration</t>
+  </si>
+  <si>
+    <t>validation.date[].date_validation_planned</t>
+  </si>
+  <si>
+    <t>validation.date[].date_validation_requested</t>
+  </si>
+  <si>
+    <t>validation.lca[].lca_completed</t>
+  </si>
+  <si>
+    <t>validation.lca[].lca_emissions_quantification</t>
+  </si>
+  <si>
+    <t>validation.lca[].lca_link</t>
+  </si>
+  <si>
+    <t>validation.lca[].lca_repository</t>
+  </si>
+  <si>
+    <t>validation.lca[].lca_results</t>
+  </si>
+  <si>
+    <t>validation.lca[].lca_system_boundary_figure</t>
+  </si>
+  <si>
+    <t>validation.lca[].lca_system_boundary_overview</t>
+  </si>
+  <si>
+    <t>validation.validation_event[].validation _id</t>
+  </si>
+  <si>
+    <t>validation.validation_event[].validation_type</t>
+  </si>
+  <si>
+    <t>validation.validation_event[].validation_date</t>
+  </si>
+  <si>
+    <t>validation.validation_event[].validation_is_planned</t>
+  </si>
+  <si>
+    <t>validation.validation_event[].validation_period_end_date</t>
+  </si>
+  <si>
+    <t>validation.validation_event[].validation_period_start_date</t>
+  </si>
+  <si>
+    <t>validation.report[].validation_report_link</t>
+  </si>
+  <si>
+    <t>project.validation_status</t>
+  </si>
+  <si>
+    <t>validation.report[].validation_report_summary</t>
+  </si>
+  <si>
+    <t>validation.stage[].validation_stage_description</t>
+  </si>
+  <si>
+    <t>validation.stage[].validation_stages</t>
+  </si>
+  <si>
+    <t>validation.report[].validation_report_version</t>
+  </si>
+  <si>
+    <t>validation_body.details[].validation_body_accreditation</t>
+  </si>
+  <si>
+    <t>validation_body.details[].validation_body_id</t>
+  </si>
+  <si>
+    <t>validation_body.details[].validation_body_name</t>
+  </si>
+  <si>
+    <t>validation_body.details[].validator_name</t>
+  </si>
+  <si>
+    <t>validation_body.details[].validation_body_sectoral_scopes</t>
+  </si>
+  <si>
+    <t>validation_body.details[].validation_body_selection</t>
+  </si>
+  <si>
+    <t>validation_body.details[].validation_body_team_members_and_roles</t>
+  </si>
+  <si>
+    <t>verification_id</t>
+  </si>
+  <si>
+    <t>verification_claim_type</t>
+  </si>
+  <si>
+    <t>verification_project_id</t>
+  </si>
+  <si>
+    <t>verification_description</t>
+  </si>
+  <si>
+    <t>verification_reporting_period_start</t>
+  </si>
+  <si>
+    <t>verification_reporting_period_end</t>
+  </si>
+  <si>
+    <t>verification_date</t>
+  </si>
+  <si>
+    <t>verified_quantity</t>
+  </si>
+  <si>
+    <t>verification_quantity_uom</t>
+  </si>
+  <si>
+    <t>verification_body_name</t>
+  </si>
+  <si>
+    <t>verification_body_id</t>
+  </si>
+  <si>
+    <t>verification_applied_standard</t>
+  </si>
+  <si>
+    <t>verification_applied_methodology_protocol</t>
+  </si>
+  <si>
+    <t>verification_credential_issuer_id</t>
+  </si>
+  <si>
+    <t>verification_cryptographic_proof_type</t>
+  </si>
+  <si>
+    <t>verification_digital_signature_payload</t>
+  </si>
+  <si>
+    <t>verification_leakage_risk_mitigation</t>
+  </si>
+  <si>
+    <t>verification_leakage_risk_mitigation_strategy</t>
+  </si>
+  <si>
+    <t>verification_leakage_deduction_quantity</t>
+  </si>
+  <si>
+    <t>verification_uncertainty_deduction_margin</t>
+  </si>
+  <si>
+    <t>verification_buffer_pool_deduction_quantity</t>
+  </si>
+  <si>
+    <t>verification_audit_checkpoint_status</t>
+  </si>
+  <si>
+    <t>URI</t>
+  </si>
+  <si>
+    <t>Object/String</t>
+  </si>
+  <si>
+    <t>A globally unique identifier for the specific verification event or claim.</t>
+  </si>
+  <si>
+    <t>The classification of the claim being verified (e.g., CARBON_REMOVAL, EMISSION_REDUCTION, BIODIVERSITY).</t>
+  </si>
+  <si>
+    <t>The unique ID of the underlying project registered on the host registry.</t>
+  </si>
+  <si>
+    <t>A concise, human-readable summary of the verification scope and findings.</t>
+  </si>
+  <si>
+    <t>The start date of the monitoring/reporting period being verified.</t>
+  </si>
+  <si>
+    <t>The end date of the monitoring/reporting period being verified.</t>
+  </si>
+  <si>
+    <t>The official date the verification process was completed and signed off.</t>
+  </si>
+  <si>
+    <t>The final, audited, and verified net volume for this specific reporting period.</t>
+  </si>
+  <si>
+    <t>The Unit of Measure for the verified quantity (e.g., tCO2e, m3_biogas).</t>
+  </si>
+  <si>
+    <t>The official name of the third-party auditing entity/VVB.</t>
+  </si>
+  <si>
+    <t>The decentralized identifier (DID) or registry ID of the verification body.</t>
+  </si>
+  <si>
+    <t>The overarching registry framework (e.g., Verra_VCS_v4.5, Gold_Standard).</t>
+  </si>
+  <si>
+    <t>The specific methodology version applied (e.g., VM0047_v1.0, CAR_Soil_v1.1).</t>
+  </si>
+  <si>
+    <t>The direct, secure hyperlink to the official public verification report PDF.</t>
+  </si>
+  <si>
+    <t>The decentralized identifier (DID) of the entity issuing the digital verification token.</t>
+  </si>
+  <si>
+    <t>The security protocol used (e.g., Ed25519Signature2020, JSON-LD).</t>
+  </si>
+  <si>
+    <t>The actual cryptographic signature, payload hash, or verifiable presentation metadata.</t>
+  </si>
+  <si>
+    <t>Indicates if leakage risk is accounted for on this verification event</t>
+  </si>
+  <si>
+    <t>links to or summarizes the mitigation strategy for this verification event</t>
+  </si>
+  <si>
+    <t>Volume deducted for this specific reporting period to account for leakage.</t>
+  </si>
+  <si>
+    <t>Percentage or absolute deduction applied for this specific reporting period for uncertainty.</t>
+  </si>
+  <si>
+    <t>Volume deducted for this specific reporting period and contributed to the buffer pool.</t>
+  </si>
+  <si>
+    <t>Summary result of the checklist (e.g., PASS, PASS_WITH_RESERVATIONS, FAIL).</t>
+  </si>
+  <si>
+    <t>verification</t>
+  </si>
+  <si>
+    <t>verification.identification[].verification_id</t>
+  </si>
+  <si>
+    <t>verification.identification[].verification_claim_type</t>
+  </si>
+  <si>
+    <t>verification.identification[].verification_project_id</t>
+  </si>
+  <si>
+    <t>verification.identification[].verification_description</t>
+  </si>
+  <si>
+    <t>verification.reporting[].verification_reporting_period_start</t>
+  </si>
+  <si>
+    <t>verification.reporting[].verification_reporting_period_end</t>
+  </si>
+  <si>
+    <t>verification.reporting[].verification_date</t>
+  </si>
+  <si>
+    <t>verification.quantity[].verified_quantity</t>
+  </si>
+  <si>
+    <t>verification.quantity[].verification_quantity_uom</t>
+  </si>
+  <si>
+    <t>verification.body[].verification_body_name</t>
+  </si>
+  <si>
+    <t>verification.body[].verification_body_id</t>
+  </si>
+  <si>
+    <t>verification.standard[].verification_applied_standard</t>
+  </si>
+  <si>
+    <t>verification.standard[].verification_applied_methodology_protocol</t>
+  </si>
+  <si>
+    <t>verification.verification_report_url</t>
+  </si>
+  <si>
+    <t>verification.verification_credential_issuer_id</t>
+  </si>
+  <si>
+    <t>verification.verification_cryptographic_proof_type</t>
+  </si>
+  <si>
+    <t>verification.verification_digital_signature_payload</t>
+  </si>
+  <si>
+    <t>verification.leakage[].verification_leakage_risk_mitigation</t>
+  </si>
+  <si>
+    <t>verification.leakage[].verification_leakage_risk_mitigation_strategy</t>
+  </si>
+  <si>
+    <t>verification.leakage[].verification_leakage_deduction_quantity</t>
+  </si>
+  <si>
+    <t>verification.verification_uncertainty_deduction_margin</t>
+  </si>
+  <si>
+    <t>verification.verification_buffer_pool_deduction_quantity</t>
+  </si>
+  <si>
+    <t>verification.verification_audit_checkpoint_status</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2662,8 +3259,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF434343"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2703,6 +3307,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6F8F9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2754,7 +3370,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -2816,6 +3432,35 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -15950,7 +16595,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -15960,7 +16605,7 @@
       <c r="C2">
         <v>242</v>
       </c>
-      <c r="D2" s="32" t="s">
+      <c r="D2" s="6" t="s">
         <v>763</v>
       </c>
       <c r="E2" s="6" t="s">
@@ -15991,7 +16636,7 @@
         <v>785</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -16001,7 +16646,7 @@
       <c r="C3">
         <v>243</v>
       </c>
-      <c r="D3" s="32" t="s">
+      <c r="D3" s="6" t="s">
         <v>764</v>
       </c>
       <c r="E3" s="6" t="s">
@@ -16032,7 +16677,7 @@
         <v>786</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>13</v>
       </c>
@@ -16042,7 +16687,7 @@
       <c r="C4">
         <v>244</v>
       </c>
-      <c r="D4" s="32" t="s">
+      <c r="D4" s="6" t="s">
         <v>765</v>
       </c>
       <c r="E4" s="6" t="s">
@@ -16073,7 +16718,7 @@
         <v>787</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -16083,7 +16728,7 @@
       <c r="C5">
         <v>245</v>
       </c>
-      <c r="D5" s="32" t="s">
+      <c r="D5" s="6" t="s">
         <v>766</v>
       </c>
       <c r="E5" s="6" t="s">
@@ -16114,7 +16759,7 @@
         <v>788</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>13</v>
       </c>
@@ -16124,7 +16769,7 @@
       <c r="C6">
         <v>246</v>
       </c>
-      <c r="D6" s="32" t="s">
+      <c r="D6" s="6" t="s">
         <v>767</v>
       </c>
       <c r="E6" s="6" t="s">
@@ -16155,7 +16800,7 @@
         <v>789</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -16165,7 +16810,7 @@
       <c r="C7">
         <v>247</v>
       </c>
-      <c r="D7" s="32" t="s">
+      <c r="D7" s="6" t="s">
         <v>768</v>
       </c>
       <c r="E7" s="6" t="s">
@@ -16196,7 +16841,7 @@
         <v>790</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>13</v>
       </c>
@@ -16206,7 +16851,7 @@
       <c r="C8">
         <v>248</v>
       </c>
-      <c r="D8" s="32" t="s">
+      <c r="D8" s="6" t="s">
         <v>769</v>
       </c>
       <c r="E8" s="6" t="s">
@@ -16237,7 +16882,7 @@
         <v>791</v>
       </c>
     </row>
-    <row r="9" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>13</v>
       </c>
@@ -16247,7 +16892,7 @@
       <c r="C9">
         <v>249</v>
       </c>
-      <c r="D9" s="32" t="s">
+      <c r="D9" s="6" t="s">
         <v>770</v>
       </c>
       <c r="E9" s="6" t="s">
@@ -16278,7 +16923,7 @@
         <v>792</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>13</v>
       </c>
@@ -16288,7 +16933,7 @@
       <c r="C10">
         <v>250</v>
       </c>
-      <c r="D10" s="32" t="s">
+      <c r="D10" s="6" t="s">
         <v>771</v>
       </c>
       <c r="E10" s="6" t="s">
@@ -16319,7 +16964,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>13</v>
       </c>
@@ -16329,7 +16974,7 @@
       <c r="C11">
         <v>251</v>
       </c>
-      <c r="D11" s="32" t="s">
+      <c r="D11" s="6" t="s">
         <v>772</v>
       </c>
       <c r="E11" s="6" t="s">
@@ -16360,7 +17005,7 @@
         <v>794</v>
       </c>
     </row>
-    <row r="12" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>13</v>
       </c>
@@ -16370,7 +17015,7 @@
       <c r="C12">
         <v>252</v>
       </c>
-      <c r="D12" s="32" t="s">
+      <c r="D12" s="6" t="s">
         <v>773</v>
       </c>
       <c r="E12" s="6" t="s">
@@ -16401,7 +17046,7 @@
         <v>795</v>
       </c>
     </row>
-    <row r="13" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>13</v>
       </c>
@@ -16411,7 +17056,7 @@
       <c r="C13">
         <v>253</v>
       </c>
-      <c r="D13" s="32" t="s">
+      <c r="D13" s="6" t="s">
         <v>774</v>
       </c>
       <c r="E13" s="6" t="s">
@@ -16442,7 +17087,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="14" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>13</v>
       </c>
@@ -16452,7 +17097,7 @@
       <c r="C14">
         <v>254</v>
       </c>
-      <c r="D14" s="32" t="s">
+      <c r="D14" s="6" t="s">
         <v>775</v>
       </c>
       <c r="E14" s="6" t="s">
@@ -16483,7 +17128,7 @@
         <v>797</v>
       </c>
     </row>
-    <row r="15" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>13</v>
       </c>
@@ -16493,7 +17138,7 @@
       <c r="C15">
         <v>255</v>
       </c>
-      <c r="D15" s="32" t="s">
+      <c r="D15" s="6" t="s">
         <v>776</v>
       </c>
       <c r="E15" s="6" t="s">
@@ -16524,7 +17169,7 @@
         <v>798</v>
       </c>
     </row>
-    <row r="16" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>13</v>
       </c>
@@ -16534,7 +17179,7 @@
       <c r="C16">
         <v>256</v>
       </c>
-      <c r="D16" s="32" t="s">
+      <c r="D16" s="6" t="s">
         <v>777</v>
       </c>
       <c r="E16" s="6" t="s">
@@ -16565,7 +17210,7 @@
         <v>799</v>
       </c>
     </row>
-    <row r="17" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>13</v>
       </c>
@@ -16575,7 +17220,7 @@
       <c r="C17">
         <v>257</v>
       </c>
-      <c r="D17" s="32" t="s">
+      <c r="D17" s="6" t="s">
         <v>778</v>
       </c>
       <c r="E17" s="6" t="s">
@@ -16616,7 +17261,7 @@
       <c r="C18">
         <v>258</v>
       </c>
-      <c r="D18" s="32" t="s">
+      <c r="D18" s="6" t="s">
         <v>779</v>
       </c>
       <c r="E18" s="6" t="s">
@@ -16647,7 +17292,7 @@
         <v>801</v>
       </c>
     </row>
-    <row r="19" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>13</v>
       </c>
@@ -16657,7 +17302,7 @@
       <c r="C19">
         <v>259</v>
       </c>
-      <c r="D19" s="32" t="s">
+      <c r="D19" s="6" t="s">
         <v>780</v>
       </c>
       <c r="E19" s="6" t="s">
@@ -16688,7 +17333,7 @@
         <v>802</v>
       </c>
     </row>
-    <row r="20" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>13</v>
       </c>
@@ -16698,7 +17343,7 @@
       <c r="C20">
         <v>260</v>
       </c>
-      <c r="D20" s="32" t="s">
+      <c r="D20" s="6" t="s">
         <v>781</v>
       </c>
       <c r="E20" s="6" t="s">
@@ -16731,6 +17376,2536 @@
     </row>
   </sheetData>
   <phoneticPr fontId="12" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5DD793A8-CD91-4786-8377-89E3BC40F96B}">
+  <dimension ref="A1:M11"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="2" width="8.54296875" customWidth="1"/>
+    <col min="4" max="4" width="30.6328125" customWidth="1"/>
+    <col min="5" max="5" width="15.90625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="52.81640625" customWidth="1"/>
+    <col min="7" max="7" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12" customWidth="1"/>
+    <col min="9" max="9" width="16.6328125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.90625" customWidth="1"/>
+    <col min="12" max="12" width="13.1796875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="35.08984375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" t="s">
+        <v>275</v>
+      </c>
+      <c r="C2">
+        <v>261</v>
+      </c>
+      <c r="D2" s="25" t="s">
+        <v>828</v>
+      </c>
+      <c r="E2" t="s">
+        <v>116</v>
+      </c>
+      <c r="F2" t="s">
+        <v>841</v>
+      </c>
+      <c r="G2" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="H2" s="25" t="s">
+        <v>392</v>
+      </c>
+      <c r="I2" t="s">
+        <v>226</v>
+      </c>
+      <c r="J2" t="s">
+        <v>116</v>
+      </c>
+      <c r="L2" t="s">
+        <v>146</v>
+      </c>
+      <c r="M2" s="18" t="s">
+        <v>824</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" t="s">
+        <v>275</v>
+      </c>
+      <c r="C3">
+        <v>262</v>
+      </c>
+      <c r="D3" s="25" t="s">
+        <v>829</v>
+      </c>
+      <c r="E3" t="s">
+        <v>116</v>
+      </c>
+      <c r="F3" t="s">
+        <v>842</v>
+      </c>
+      <c r="G3" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="H3" s="25" t="s">
+        <v>159</v>
+      </c>
+      <c r="I3" t="s">
+        <v>226</v>
+      </c>
+      <c r="J3" t="s">
+        <v>116</v>
+      </c>
+      <c r="L3" t="s">
+        <v>146</v>
+      </c>
+      <c r="M3" s="18" t="s">
+        <v>824</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" t="s">
+        <v>275</v>
+      </c>
+      <c r="C4">
+        <v>263</v>
+      </c>
+      <c r="D4" s="25" t="s">
+        <v>830</v>
+      </c>
+      <c r="E4" t="s">
+        <v>116</v>
+      </c>
+      <c r="F4" t="s">
+        <v>843</v>
+      </c>
+      <c r="G4" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="H4" s="25" t="s">
+        <v>159</v>
+      </c>
+      <c r="I4" t="s">
+        <v>226</v>
+      </c>
+      <c r="J4" t="s">
+        <v>116</v>
+      </c>
+      <c r="L4" t="s">
+        <v>146</v>
+      </c>
+      <c r="M4" s="18" t="s">
+        <v>824</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" t="s">
+        <v>275</v>
+      </c>
+      <c r="C5">
+        <v>264</v>
+      </c>
+      <c r="D5" s="25" t="s">
+        <v>831</v>
+      </c>
+      <c r="E5" t="s">
+        <v>116</v>
+      </c>
+      <c r="F5" t="s">
+        <v>844</v>
+      </c>
+      <c r="G5" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="H5" s="25" t="s">
+        <v>392</v>
+      </c>
+      <c r="I5" t="s">
+        <v>226</v>
+      </c>
+      <c r="J5" t="s">
+        <v>116</v>
+      </c>
+      <c r="L5" t="s">
+        <v>146</v>
+      </c>
+      <c r="M5" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" t="s">
+        <v>275</v>
+      </c>
+      <c r="C6">
+        <v>265</v>
+      </c>
+      <c r="D6" s="25" t="s">
+        <v>832</v>
+      </c>
+      <c r="E6" t="s">
+        <v>116</v>
+      </c>
+      <c r="F6" t="s">
+        <v>845</v>
+      </c>
+      <c r="G6" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="H6" s="25" t="s">
+        <v>159</v>
+      </c>
+      <c r="I6" t="s">
+        <v>226</v>
+      </c>
+      <c r="J6" t="s">
+        <v>116</v>
+      </c>
+      <c r="L6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M6" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" t="s">
+        <v>275</v>
+      </c>
+      <c r="C7">
+        <v>266</v>
+      </c>
+      <c r="D7" s="25" t="s">
+        <v>833</v>
+      </c>
+      <c r="E7" t="s">
+        <v>116</v>
+      </c>
+      <c r="F7" t="s">
+        <v>846</v>
+      </c>
+      <c r="G7" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="H7" s="25" t="s">
+        <v>159</v>
+      </c>
+      <c r="I7" t="s">
+        <v>226</v>
+      </c>
+      <c r="J7" t="s">
+        <v>116</v>
+      </c>
+      <c r="L7" t="s">
+        <v>146</v>
+      </c>
+      <c r="M7" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" t="s">
+        <v>275</v>
+      </c>
+      <c r="C8">
+        <v>267</v>
+      </c>
+      <c r="D8" s="25" t="s">
+        <v>834</v>
+      </c>
+      <c r="E8" t="s">
+        <v>116</v>
+      </c>
+      <c r="F8" t="s">
+        <v>847</v>
+      </c>
+      <c r="G8" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="H8" s="25" t="s">
+        <v>392</v>
+      </c>
+      <c r="I8" t="s">
+        <v>226</v>
+      </c>
+      <c r="J8" t="s">
+        <v>823</v>
+      </c>
+      <c r="L8" t="s">
+        <v>146</v>
+      </c>
+      <c r="M8" s="18" t="s">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" t="s">
+        <v>275</v>
+      </c>
+      <c r="C9">
+        <v>268</v>
+      </c>
+      <c r="D9" s="25" t="s">
+        <v>835</v>
+      </c>
+      <c r="E9" t="s">
+        <v>116</v>
+      </c>
+      <c r="F9" t="s">
+        <v>848</v>
+      </c>
+      <c r="G9" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="H9" s="25" t="s">
+        <v>159</v>
+      </c>
+      <c r="I9" t="s">
+        <v>226</v>
+      </c>
+      <c r="J9" t="s">
+        <v>823</v>
+      </c>
+      <c r="L9" t="s">
+        <v>146</v>
+      </c>
+      <c r="M9" s="18" t="s">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" t="s">
+        <v>275</v>
+      </c>
+      <c r="C10">
+        <v>269</v>
+      </c>
+      <c r="D10" s="25" t="s">
+        <v>836</v>
+      </c>
+      <c r="E10" t="s">
+        <v>116</v>
+      </c>
+      <c r="F10" t="s">
+        <v>839</v>
+      </c>
+      <c r="G10" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="H10" s="25" t="s">
+        <v>219</v>
+      </c>
+      <c r="I10" t="s">
+        <v>226</v>
+      </c>
+      <c r="L10" t="s">
+        <v>146</v>
+      </c>
+      <c r="M10" s="18" t="s">
+        <v>838</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>13</v>
+      </c>
+      <c r="B11" t="s">
+        <v>275</v>
+      </c>
+      <c r="C11">
+        <v>270</v>
+      </c>
+      <c r="D11" s="25" t="s">
+        <v>837</v>
+      </c>
+      <c r="E11" t="s">
+        <v>116</v>
+      </c>
+      <c r="F11" t="s">
+        <v>840</v>
+      </c>
+      <c r="G11" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="H11" s="25" t="s">
+        <v>219</v>
+      </c>
+      <c r="I11" t="s">
+        <v>31</v>
+      </c>
+      <c r="L11" t="s">
+        <v>146</v>
+      </c>
+      <c r="M11" s="18" t="s">
+        <v>827</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF337E51-0D9D-46A6-9DB2-8DF5F9FC1667}">
+  <dimension ref="A1:M37"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="4" max="4" width="43.6328125" customWidth="1"/>
+    <col min="5" max="5" width="15.90625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="58.453125" customWidth="1"/>
+    <col min="7" max="7" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.90625" customWidth="1"/>
+    <col min="9" max="9" width="16.6328125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.26953125" customWidth="1"/>
+    <col min="12" max="12" width="13.1796875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="49.90625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" t="s">
+        <v>275</v>
+      </c>
+      <c r="C2">
+        <v>271</v>
+      </c>
+      <c r="D2" s="33" t="s">
+        <v>481</v>
+      </c>
+      <c r="E2" s="33" t="s">
+        <v>266</v>
+      </c>
+      <c r="F2" t="s">
+        <v>914</v>
+      </c>
+      <c r="G2" s="33" t="s">
+        <v>18</v>
+      </c>
+      <c r="H2" s="33" t="s">
+        <v>219</v>
+      </c>
+      <c r="I2" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="J2" s="6" t="s">
+        <v>445</v>
+      </c>
+      <c r="L2" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M2" s="6" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" t="s">
+        <v>275</v>
+      </c>
+      <c r="C3">
+        <v>272</v>
+      </c>
+      <c r="D3" s="33" t="s">
+        <v>483</v>
+      </c>
+      <c r="E3" s="33" t="s">
+        <v>266</v>
+      </c>
+      <c r="F3" t="s">
+        <v>917</v>
+      </c>
+      <c r="G3" s="33" t="s">
+        <v>18</v>
+      </c>
+      <c r="H3" s="33" t="s">
+        <v>392</v>
+      </c>
+      <c r="I3" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="J3" s="6" t="s">
+        <v>445</v>
+      </c>
+      <c r="L3" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M3" s="6" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" t="s">
+        <v>275</v>
+      </c>
+      <c r="C4">
+        <v>273</v>
+      </c>
+      <c r="D4" s="33" t="s">
+        <v>479</v>
+      </c>
+      <c r="E4" s="33" t="s">
+        <v>266</v>
+      </c>
+      <c r="F4" t="s">
+        <v>919</v>
+      </c>
+      <c r="G4" s="33" t="s">
+        <v>18</v>
+      </c>
+      <c r="H4" s="33" t="s">
+        <v>219</v>
+      </c>
+      <c r="I4" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="J4" s="6" t="s">
+        <v>445</v>
+      </c>
+      <c r="L4" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M4" s="6" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" t="s">
+        <v>275</v>
+      </c>
+      <c r="C5">
+        <v>274</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>849</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F5" t="s">
+        <v>915</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H5" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="I5" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="J5" s="6" t="s">
+        <v>445</v>
+      </c>
+      <c r="L5" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M5" s="6" t="s">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" t="s">
+        <v>275</v>
+      </c>
+      <c r="C6">
+        <v>275</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>850</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F6" t="s">
+        <v>918</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H6" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="I6" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="J6" s="6" t="s">
+        <v>445</v>
+      </c>
+      <c r="L6" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M6" s="6" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" t="s">
+        <v>275</v>
+      </c>
+      <c r="C7">
+        <v>276</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>851</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F7" t="s">
+        <v>920</v>
+      </c>
+      <c r="G7" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="H7" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="I7" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="J7" s="6" t="s">
+        <v>445</v>
+      </c>
+      <c r="L7" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M7" s="6" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" t="s">
+        <v>275</v>
+      </c>
+      <c r="C8">
+        <v>277</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>852</v>
+      </c>
+      <c r="E8" s="33" t="s">
+        <v>266</v>
+      </c>
+      <c r="F8" t="s">
+        <v>921</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H8" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="I8" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="J8" s="6" t="s">
+        <v>871</v>
+      </c>
+      <c r="L8" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M8" s="6" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" t="s">
+        <v>275</v>
+      </c>
+      <c r="C9">
+        <v>278</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>853</v>
+      </c>
+      <c r="E9" s="33" t="s">
+        <v>266</v>
+      </c>
+      <c r="F9" t="s">
+        <v>922</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H9" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="I9" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="J9" s="6" t="s">
+        <v>871</v>
+      </c>
+      <c r="L9" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M9" s="6" t="s">
+        <v>876</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" t="s">
+        <v>275</v>
+      </c>
+      <c r="C10">
+        <v>279</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>854</v>
+      </c>
+      <c r="E10" s="33" t="s">
+        <v>266</v>
+      </c>
+      <c r="F10" t="s">
+        <v>923</v>
+      </c>
+      <c r="G10" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H10" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="I10" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="J10" s="6" t="s">
+        <v>871</v>
+      </c>
+      <c r="L10" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M10" s="6" t="s">
+        <v>877</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>13</v>
+      </c>
+      <c r="B11" t="s">
+        <v>275</v>
+      </c>
+      <c r="C11">
+        <v>280</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>905</v>
+      </c>
+      <c r="E11" s="33" t="s">
+        <v>266</v>
+      </c>
+      <c r="F11" t="s">
+        <v>924</v>
+      </c>
+      <c r="G11" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="H11" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="I11" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="J11" s="6" t="s">
+        <v>871</v>
+      </c>
+      <c r="L11" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M11" s="6" t="s">
+        <v>878</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12" t="s">
+        <v>275</v>
+      </c>
+      <c r="C12">
+        <v>281</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>906</v>
+      </c>
+      <c r="E12" s="33" t="s">
+        <v>266</v>
+      </c>
+      <c r="F12" t="s">
+        <v>925</v>
+      </c>
+      <c r="G12" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="H12" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="I12" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="J12" s="6" t="s">
+        <v>871</v>
+      </c>
+      <c r="L12" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M12" s="6" t="s">
+        <v>879</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13" t="s">
+        <v>275</v>
+      </c>
+      <c r="C13">
+        <v>282</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>907</v>
+      </c>
+      <c r="E13" s="33" t="s">
+        <v>266</v>
+      </c>
+      <c r="F13" t="s">
+        <v>926</v>
+      </c>
+      <c r="G13" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="H13" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="I13" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="J13" s="6" t="s">
+        <v>871</v>
+      </c>
+      <c r="L13" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M13" s="6" t="s">
+        <v>880</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>275</v>
+      </c>
+      <c r="C14">
+        <v>283</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>908</v>
+      </c>
+      <c r="E14" s="33" t="s">
+        <v>266</v>
+      </c>
+      <c r="F14" t="s">
+        <v>927</v>
+      </c>
+      <c r="G14" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="H14" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="I14" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="J14" s="6" t="s">
+        <v>871</v>
+      </c>
+      <c r="L14" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M14" s="6" t="s">
+        <v>881</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>13</v>
+      </c>
+      <c r="B15" t="s">
+        <v>275</v>
+      </c>
+      <c r="C15">
+        <v>284</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>909</v>
+      </c>
+      <c r="E15" s="33" t="s">
+        <v>266</v>
+      </c>
+      <c r="F15" t="s">
+        <v>928</v>
+      </c>
+      <c r="G15" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="H15" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="I15" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="J15" s="6" t="s">
+        <v>871</v>
+      </c>
+      <c r="L15" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M15" s="6" t="s">
+        <v>882</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>13</v>
+      </c>
+      <c r="B16" t="s">
+        <v>275</v>
+      </c>
+      <c r="C16">
+        <v>285</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>910</v>
+      </c>
+      <c r="E16" s="33" t="s">
+        <v>266</v>
+      </c>
+      <c r="F16" t="s">
+        <v>929</v>
+      </c>
+      <c r="G16" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="H16" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="I16" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="J16" s="6" t="s">
+        <v>871</v>
+      </c>
+      <c r="L16" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M16" s="6" t="s">
+        <v>883</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>13</v>
+      </c>
+      <c r="B17" t="s">
+        <v>275</v>
+      </c>
+      <c r="C17">
+        <v>286</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>911</v>
+      </c>
+      <c r="E17" s="33" t="s">
+        <v>266</v>
+      </c>
+      <c r="F17" t="s">
+        <v>930</v>
+      </c>
+      <c r="G17" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="H17" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="I17" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="J17" s="6" t="s">
+        <v>871</v>
+      </c>
+      <c r="L17" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M17" s="6" t="s">
+        <v>884</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>13</v>
+      </c>
+      <c r="B18" t="s">
+        <v>275</v>
+      </c>
+      <c r="C18">
+        <v>287</v>
+      </c>
+      <c r="D18" s="33" t="s">
+        <v>912</v>
+      </c>
+      <c r="E18" s="33" t="s">
+        <v>266</v>
+      </c>
+      <c r="F18" t="s">
+        <v>931</v>
+      </c>
+      <c r="G18" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H18" s="6" t="s">
+        <v>392</v>
+      </c>
+      <c r="I18" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="J18" s="6" t="s">
+        <v>871</v>
+      </c>
+      <c r="L18" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M18" s="6" t="s">
+        <v>885</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>13</v>
+      </c>
+      <c r="B19" t="s">
+        <v>275</v>
+      </c>
+      <c r="C19">
+        <v>288</v>
+      </c>
+      <c r="D19" s="30" t="s">
+        <v>511</v>
+      </c>
+      <c r="E19" s="33" t="s">
+        <v>266</v>
+      </c>
+      <c r="F19" t="s">
+        <v>932</v>
+      </c>
+      <c r="G19" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H19" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="I19" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="J19" s="6" t="s">
+        <v>871</v>
+      </c>
+      <c r="L19" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M19" s="6" t="s">
+        <v>886</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>13</v>
+      </c>
+      <c r="B20" t="s">
+        <v>275</v>
+      </c>
+      <c r="C20">
+        <v>289</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>855</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>913</v>
+      </c>
+      <c r="F20" t="s">
+        <v>943</v>
+      </c>
+      <c r="G20" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="H20" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="I20" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="J20" s="6" t="s">
+        <v>871</v>
+      </c>
+      <c r="L20" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M20" s="6" t="s">
+        <v>887</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>13</v>
+      </c>
+      <c r="B21" t="s">
+        <v>275</v>
+      </c>
+      <c r="C21">
+        <v>290</v>
+      </c>
+      <c r="D21" s="17" t="s">
+        <v>856</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>913</v>
+      </c>
+      <c r="F21" t="s">
+        <v>944</v>
+      </c>
+      <c r="G21" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H21" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="I21" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="J21" s="6" t="s">
+        <v>871</v>
+      </c>
+      <c r="L21" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M21" s="6" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>13</v>
+      </c>
+      <c r="B22" t="s">
+        <v>275</v>
+      </c>
+      <c r="C22">
+        <v>291</v>
+      </c>
+      <c r="D22" s="17" t="s">
+        <v>265</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>913</v>
+      </c>
+      <c r="F22" t="s">
+        <v>945</v>
+      </c>
+      <c r="G22" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H22" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="I22" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="J22" s="6" t="s">
+        <v>871</v>
+      </c>
+      <c r="L22" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M22" s="6" t="s">
+        <v>889</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>13</v>
+      </c>
+      <c r="B23" t="s">
+        <v>275</v>
+      </c>
+      <c r="C23">
+        <v>292</v>
+      </c>
+      <c r="D23" s="17" t="s">
+        <v>857</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>913</v>
+      </c>
+      <c r="F23" t="s">
+        <v>946</v>
+      </c>
+      <c r="G23" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H23" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="I23" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="J23" s="6" t="s">
+        <v>871</v>
+      </c>
+      <c r="L23" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M23" s="6" t="s">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>13</v>
+      </c>
+      <c r="B24" t="s">
+        <v>275</v>
+      </c>
+      <c r="C24">
+        <v>293</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>858</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>913</v>
+      </c>
+      <c r="F24" t="s">
+        <v>947</v>
+      </c>
+      <c r="G24" s="6" t="s">
+        <v>564</v>
+      </c>
+      <c r="H24" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="I24" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="J24" s="6" t="s">
+        <v>871</v>
+      </c>
+      <c r="L24" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M24" s="6" t="s">
+        <v>891</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>13</v>
+      </c>
+      <c r="B25" t="s">
+        <v>275</v>
+      </c>
+      <c r="C25">
+        <v>294</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>859</v>
+      </c>
+      <c r="E25" s="6" t="s">
+        <v>913</v>
+      </c>
+      <c r="F25" t="s">
+        <v>948</v>
+      </c>
+      <c r="G25" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H25" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="I25" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="J25" s="6" t="s">
+        <v>871</v>
+      </c>
+      <c r="L25" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M25" s="6" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>13</v>
+      </c>
+      <c r="B26" t="s">
+        <v>275</v>
+      </c>
+      <c r="C26">
+        <v>295</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>860</v>
+      </c>
+      <c r="E26" s="6" t="s">
+        <v>913</v>
+      </c>
+      <c r="F26" t="s">
+        <v>949</v>
+      </c>
+      <c r="G26" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H26" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="I26" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="J26" s="6" t="s">
+        <v>871</v>
+      </c>
+      <c r="L26" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M26" s="6" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>13</v>
+      </c>
+      <c r="B27" t="s">
+        <v>275</v>
+      </c>
+      <c r="C27">
+        <v>296</v>
+      </c>
+      <c r="D27" s="17" t="s">
+        <v>269</v>
+      </c>
+      <c r="E27" s="33" t="s">
+        <v>266</v>
+      </c>
+      <c r="F27" t="s">
+        <v>933</v>
+      </c>
+      <c r="G27" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H27" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="I27" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="J27" s="6" t="s">
+        <v>871</v>
+      </c>
+      <c r="L27" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M27" s="6" t="s">
+        <v>894</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
+        <v>13</v>
+      </c>
+      <c r="B28" t="s">
+        <v>275</v>
+      </c>
+      <c r="C28">
+        <v>297</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>861</v>
+      </c>
+      <c r="E28" s="33" t="s">
+        <v>266</v>
+      </c>
+      <c r="F28" t="s">
+        <v>934</v>
+      </c>
+      <c r="G28" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H28" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="I28" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="J28" s="6" t="s">
+        <v>871</v>
+      </c>
+      <c r="L28" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M28" s="6" t="s">
+        <v>895</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
+        <v>13</v>
+      </c>
+      <c r="B29" t="s">
+        <v>275</v>
+      </c>
+      <c r="C29">
+        <v>298</v>
+      </c>
+      <c r="D29" s="6" t="s">
+        <v>862</v>
+      </c>
+      <c r="E29" s="33" t="s">
+        <v>266</v>
+      </c>
+      <c r="F29" t="s">
+        <v>935</v>
+      </c>
+      <c r="G29" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H29" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="I29" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="J29" s="6" t="s">
+        <v>871</v>
+      </c>
+      <c r="L29" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M29" s="6" t="s">
+        <v>896</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
+        <v>13</v>
+      </c>
+      <c r="B30" t="s">
+        <v>275</v>
+      </c>
+      <c r="C30">
+        <v>299</v>
+      </c>
+      <c r="D30" s="6" t="s">
+        <v>863</v>
+      </c>
+      <c r="E30" s="33" t="s">
+        <v>266</v>
+      </c>
+      <c r="F30" t="s">
+        <v>936</v>
+      </c>
+      <c r="G30" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H30" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="I30" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="J30" s="6" t="s">
+        <v>871</v>
+      </c>
+      <c r="L30" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M30" s="6" t="s">
+        <v>897</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>13</v>
+      </c>
+      <c r="B31" t="s">
+        <v>275</v>
+      </c>
+      <c r="C31">
+        <v>300</v>
+      </c>
+      <c r="D31" s="17" t="s">
+        <v>864</v>
+      </c>
+      <c r="E31" s="33" t="s">
+        <v>266</v>
+      </c>
+      <c r="F31" t="s">
+        <v>937</v>
+      </c>
+      <c r="G31" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="H31" s="17" t="s">
+        <v>159</v>
+      </c>
+      <c r="I31" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="J31" s="6" t="s">
+        <v>871</v>
+      </c>
+      <c r="L31" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M31" s="17" t="s">
+        <v>898</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
+        <v>13</v>
+      </c>
+      <c r="B32" t="s">
+        <v>275</v>
+      </c>
+      <c r="C32">
+        <v>301</v>
+      </c>
+      <c r="D32" s="6" t="s">
+        <v>865</v>
+      </c>
+      <c r="E32" s="33" t="s">
+        <v>266</v>
+      </c>
+      <c r="F32" t="s">
+        <v>939</v>
+      </c>
+      <c r="G32" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="H32" s="17" t="s">
+        <v>159</v>
+      </c>
+      <c r="I32" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="J32" s="6" t="s">
+        <v>871</v>
+      </c>
+      <c r="L32" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M32" s="6" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>13</v>
+      </c>
+      <c r="B33" t="s">
+        <v>275</v>
+      </c>
+      <c r="C33">
+        <v>302</v>
+      </c>
+      <c r="D33" s="6" t="s">
+        <v>866</v>
+      </c>
+      <c r="E33" s="33" t="s">
+        <v>266</v>
+      </c>
+      <c r="F33" t="s">
+        <v>940</v>
+      </c>
+      <c r="G33" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="H33" s="17" t="s">
+        <v>159</v>
+      </c>
+      <c r="I33" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="J33" s="6" t="s">
+        <v>871</v>
+      </c>
+      <c r="L33" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M33" s="6" t="s">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
+        <v>13</v>
+      </c>
+      <c r="B34" t="s">
+        <v>275</v>
+      </c>
+      <c r="C34">
+        <v>303</v>
+      </c>
+      <c r="D34" s="6" t="s">
+        <v>867</v>
+      </c>
+      <c r="E34" s="33" t="s">
+        <v>266</v>
+      </c>
+      <c r="F34" t="s">
+        <v>916</v>
+      </c>
+      <c r="G34" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="H34" s="17" t="s">
+        <v>159</v>
+      </c>
+      <c r="I34" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="J34" s="6" t="s">
+        <v>871</v>
+      </c>
+      <c r="L34" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M34" s="6" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
+        <v>13</v>
+      </c>
+      <c r="B35" t="s">
+        <v>275</v>
+      </c>
+      <c r="C35">
+        <v>304</v>
+      </c>
+      <c r="D35" s="6" t="s">
+        <v>868</v>
+      </c>
+      <c r="E35" s="33" t="s">
+        <v>266</v>
+      </c>
+      <c r="F35" t="s">
+        <v>941</v>
+      </c>
+      <c r="G35" s="6" t="s">
+        <v>564</v>
+      </c>
+      <c r="H35" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="I35" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="J35" s="6" t="s">
+        <v>871</v>
+      </c>
+      <c r="L35" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M35" s="6" t="s">
+        <v>902</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
+        <v>13</v>
+      </c>
+      <c r="B36" t="s">
+        <v>275</v>
+      </c>
+      <c r="C36">
+        <v>305</v>
+      </c>
+      <c r="D36" s="6" t="s">
+        <v>869</v>
+      </c>
+      <c r="E36" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F36" t="s">
+        <v>938</v>
+      </c>
+      <c r="G36" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H36" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="I36" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="J36" s="6" t="s">
+        <v>445</v>
+      </c>
+      <c r="L36" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M36" s="6" t="s">
+        <v>903</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A37" t="s">
+        <v>13</v>
+      </c>
+      <c r="B37" t="s">
+        <v>275</v>
+      </c>
+      <c r="C37">
+        <v>306</v>
+      </c>
+      <c r="D37" s="6" t="s">
+        <v>870</v>
+      </c>
+      <c r="E37" s="33" t="s">
+        <v>266</v>
+      </c>
+      <c r="F37" t="s">
+        <v>942</v>
+      </c>
+      <c r="G37" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="H37" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="I37" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="J37" s="6" t="s">
+        <v>871</v>
+      </c>
+      <c r="L37" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M37" s="6" t="s">
+        <v>904</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7A22D2F-6AFE-4D3D-A8D1-BBD797E61616}">
+  <dimension ref="A1:M24"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="4" max="4" width="37.90625" customWidth="1"/>
+    <col min="5" max="5" width="15.90625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="43.26953125" customWidth="1"/>
+    <col min="7" max="7" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.90625" customWidth="1"/>
+    <col min="9" max="9" width="16.6328125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.26953125" customWidth="1"/>
+    <col min="12" max="12" width="13.1796875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="49.90625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="C2" s="36">
+        <v>307</v>
+      </c>
+      <c r="D2" s="37" t="s">
+        <v>950</v>
+      </c>
+      <c r="E2" s="38" t="s">
+        <v>997</v>
+      </c>
+      <c r="F2" s="36" t="s">
+        <v>998</v>
+      </c>
+      <c r="G2" s="38" t="s">
+        <v>18</v>
+      </c>
+      <c r="H2" s="39" t="s">
+        <v>215</v>
+      </c>
+      <c r="I2" s="38" t="s">
+        <v>20</v>
+      </c>
+      <c r="M2" s="34" t="s">
+        <v>974</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="C3" s="36">
+        <v>308</v>
+      </c>
+      <c r="D3" s="40" t="s">
+        <v>951</v>
+      </c>
+      <c r="E3" s="41" t="s">
+        <v>997</v>
+      </c>
+      <c r="F3" s="36" t="s">
+        <v>999</v>
+      </c>
+      <c r="G3" s="41" t="s">
+        <v>18</v>
+      </c>
+      <c r="H3" s="42" t="s">
+        <v>143</v>
+      </c>
+      <c r="I3" s="41" t="s">
+        <v>20</v>
+      </c>
+      <c r="M3" s="35" t="s">
+        <v>975</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="C4" s="36">
+        <v>309</v>
+      </c>
+      <c r="D4" s="37" t="s">
+        <v>952</v>
+      </c>
+      <c r="E4" s="38" t="s">
+        <v>997</v>
+      </c>
+      <c r="F4" s="36" t="s">
+        <v>1000</v>
+      </c>
+      <c r="G4" s="38" t="s">
+        <v>18</v>
+      </c>
+      <c r="H4" s="39" t="s">
+        <v>215</v>
+      </c>
+      <c r="I4" s="38" t="s">
+        <v>20</v>
+      </c>
+      <c r="M4" s="34" t="s">
+        <v>976</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="C5" s="36">
+        <v>310</v>
+      </c>
+      <c r="D5" s="40" t="s">
+        <v>953</v>
+      </c>
+      <c r="E5" s="41" t="s">
+        <v>997</v>
+      </c>
+      <c r="F5" s="36" t="s">
+        <v>1001</v>
+      </c>
+      <c r="G5" s="41" t="s">
+        <v>18</v>
+      </c>
+      <c r="H5" s="42" t="s">
+        <v>215</v>
+      </c>
+      <c r="I5" s="41" t="s">
+        <v>20</v>
+      </c>
+      <c r="M5" s="35" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="C6" s="36">
+        <v>311</v>
+      </c>
+      <c r="D6" s="37" t="s">
+        <v>954</v>
+      </c>
+      <c r="E6" s="38" t="s">
+        <v>997</v>
+      </c>
+      <c r="F6" s="43" t="s">
+        <v>1002</v>
+      </c>
+      <c r="G6" s="38" t="s">
+        <v>18</v>
+      </c>
+      <c r="H6" s="39" t="s">
+        <v>219</v>
+      </c>
+      <c r="I6" s="38" t="s">
+        <v>20</v>
+      </c>
+      <c r="M6" s="34" t="s">
+        <v>978</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="C7" s="36">
+        <v>312</v>
+      </c>
+      <c r="D7" s="40" t="s">
+        <v>955</v>
+      </c>
+      <c r="E7" s="41" t="s">
+        <v>997</v>
+      </c>
+      <c r="F7" s="43" t="s">
+        <v>1003</v>
+      </c>
+      <c r="G7" s="41" t="s">
+        <v>18</v>
+      </c>
+      <c r="H7" s="42" t="s">
+        <v>219</v>
+      </c>
+      <c r="I7" s="41" t="s">
+        <v>20</v>
+      </c>
+      <c r="M7" s="35" t="s">
+        <v>979</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="C8" s="36">
+        <v>313</v>
+      </c>
+      <c r="D8" s="37" t="s">
+        <v>956</v>
+      </c>
+      <c r="E8" s="38" t="s">
+        <v>997</v>
+      </c>
+      <c r="F8" s="43" t="s">
+        <v>1004</v>
+      </c>
+      <c r="G8" s="38" t="s">
+        <v>18</v>
+      </c>
+      <c r="H8" s="39" t="s">
+        <v>219</v>
+      </c>
+      <c r="I8" s="38" t="s">
+        <v>20</v>
+      </c>
+      <c r="M8" s="34" t="s">
+        <v>980</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="C9" s="36">
+        <v>314</v>
+      </c>
+      <c r="D9" s="40" t="s">
+        <v>957</v>
+      </c>
+      <c r="E9" s="41" t="s">
+        <v>997</v>
+      </c>
+      <c r="F9" s="43" t="s">
+        <v>1005</v>
+      </c>
+      <c r="G9" s="41" t="s">
+        <v>18</v>
+      </c>
+      <c r="H9" s="42" t="s">
+        <v>316</v>
+      </c>
+      <c r="I9" s="41" t="s">
+        <v>20</v>
+      </c>
+      <c r="M9" s="35" t="s">
+        <v>981</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="C10" s="36">
+        <v>315</v>
+      </c>
+      <c r="D10" s="37" t="s">
+        <v>958</v>
+      </c>
+      <c r="E10" s="38" t="s">
+        <v>997</v>
+      </c>
+      <c r="F10" s="43" t="s">
+        <v>1006</v>
+      </c>
+      <c r="G10" s="38" t="s">
+        <v>18</v>
+      </c>
+      <c r="H10" s="39" t="s">
+        <v>143</v>
+      </c>
+      <c r="I10" s="38" t="s">
+        <v>20</v>
+      </c>
+      <c r="M10" s="34" t="s">
+        <v>982</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="C11" s="36">
+        <v>316</v>
+      </c>
+      <c r="D11" s="40" t="s">
+        <v>959</v>
+      </c>
+      <c r="E11" s="41" t="s">
+        <v>997</v>
+      </c>
+      <c r="F11" s="43" t="s">
+        <v>1007</v>
+      </c>
+      <c r="G11" s="41" t="s">
+        <v>18</v>
+      </c>
+      <c r="H11" s="42" t="s">
+        <v>215</v>
+      </c>
+      <c r="I11" s="41" t="s">
+        <v>20</v>
+      </c>
+      <c r="M11" s="35" t="s">
+        <v>983</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="C12" s="36">
+        <v>317</v>
+      </c>
+      <c r="D12" s="37" t="s">
+        <v>960</v>
+      </c>
+      <c r="E12" s="38" t="s">
+        <v>997</v>
+      </c>
+      <c r="F12" s="43" t="s">
+        <v>1008</v>
+      </c>
+      <c r="G12" s="38" t="s">
+        <v>18</v>
+      </c>
+      <c r="H12" s="39" t="s">
+        <v>215</v>
+      </c>
+      <c r="I12" s="38" t="s">
+        <v>20</v>
+      </c>
+      <c r="M12" s="34" t="s">
+        <v>984</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="C13" s="36">
+        <v>318</v>
+      </c>
+      <c r="D13" s="40" t="s">
+        <v>961</v>
+      </c>
+      <c r="E13" s="41" t="s">
+        <v>997</v>
+      </c>
+      <c r="F13" s="43" t="s">
+        <v>1009</v>
+      </c>
+      <c r="G13" s="41" t="s">
+        <v>18</v>
+      </c>
+      <c r="H13" s="42" t="s">
+        <v>215</v>
+      </c>
+      <c r="I13" s="41" t="s">
+        <v>20</v>
+      </c>
+      <c r="M13" s="35" t="s">
+        <v>985</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="C14" s="36">
+        <v>319</v>
+      </c>
+      <c r="D14" s="37" t="s">
+        <v>962</v>
+      </c>
+      <c r="E14" s="38" t="s">
+        <v>997</v>
+      </c>
+      <c r="F14" s="43" t="s">
+        <v>1010</v>
+      </c>
+      <c r="G14" s="38" t="s">
+        <v>30</v>
+      </c>
+      <c r="H14" s="39" t="s">
+        <v>215</v>
+      </c>
+      <c r="I14" s="38" t="s">
+        <v>144</v>
+      </c>
+      <c r="M14" s="34" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="C15" s="36">
+        <v>320</v>
+      </c>
+      <c r="D15" s="40" t="s">
+        <v>288</v>
+      </c>
+      <c r="E15" s="41" t="s">
+        <v>997</v>
+      </c>
+      <c r="F15" s="43" t="s">
+        <v>1011</v>
+      </c>
+      <c r="G15" s="41" t="s">
+        <v>564</v>
+      </c>
+      <c r="H15" s="42" t="s">
+        <v>972</v>
+      </c>
+      <c r="I15" s="41" t="s">
+        <v>20</v>
+      </c>
+      <c r="M15" s="35" t="s">
+        <v>987</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="C16" s="36">
+        <v>321</v>
+      </c>
+      <c r="D16" s="37" t="s">
+        <v>963</v>
+      </c>
+      <c r="E16" s="38" t="s">
+        <v>997</v>
+      </c>
+      <c r="F16" s="43" t="s">
+        <v>1012</v>
+      </c>
+      <c r="G16" s="38" t="s">
+        <v>18</v>
+      </c>
+      <c r="H16" s="39" t="s">
+        <v>215</v>
+      </c>
+      <c r="I16" s="38" t="s">
+        <v>20</v>
+      </c>
+      <c r="M16" s="34" t="s">
+        <v>988</v>
+      </c>
+    </row>
+    <row r="17" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="C17" s="36">
+        <v>322</v>
+      </c>
+      <c r="D17" s="40" t="s">
+        <v>964</v>
+      </c>
+      <c r="E17" s="41" t="s">
+        <v>997</v>
+      </c>
+      <c r="F17" s="43" t="s">
+        <v>1013</v>
+      </c>
+      <c r="G17" s="41" t="s">
+        <v>30</v>
+      </c>
+      <c r="H17" s="42" t="s">
+        <v>215</v>
+      </c>
+      <c r="I17" s="41" t="s">
+        <v>144</v>
+      </c>
+      <c r="M17" s="35" t="s">
+        <v>989</v>
+      </c>
+    </row>
+    <row r="18" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="C18" s="36">
+        <v>323</v>
+      </c>
+      <c r="D18" s="37" t="s">
+        <v>965</v>
+      </c>
+      <c r="E18" s="38" t="s">
+        <v>997</v>
+      </c>
+      <c r="F18" s="43" t="s">
+        <v>1014</v>
+      </c>
+      <c r="G18" s="41" t="s">
+        <v>30</v>
+      </c>
+      <c r="H18" s="39" t="s">
+        <v>973</v>
+      </c>
+      <c r="I18" s="38" t="s">
+        <v>144</v>
+      </c>
+      <c r="M18" s="34" t="s">
+        <v>990</v>
+      </c>
+    </row>
+    <row r="19" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="C19" s="36">
+        <v>324</v>
+      </c>
+      <c r="D19" s="40" t="s">
+        <v>966</v>
+      </c>
+      <c r="E19" s="41" t="s">
+        <v>997</v>
+      </c>
+      <c r="F19" s="43" t="s">
+        <v>1015</v>
+      </c>
+      <c r="G19" s="41" t="s">
+        <v>30</v>
+      </c>
+      <c r="H19" s="42" t="s">
+        <v>150</v>
+      </c>
+      <c r="I19" s="41" t="s">
+        <v>144</v>
+      </c>
+      <c r="M19" s="35" t="s">
+        <v>991</v>
+      </c>
+    </row>
+    <row r="20" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="C20" s="36">
+        <v>325</v>
+      </c>
+      <c r="D20" s="37" t="s">
+        <v>967</v>
+      </c>
+      <c r="E20" s="38" t="s">
+        <v>997</v>
+      </c>
+      <c r="F20" s="43" t="s">
+        <v>1016</v>
+      </c>
+      <c r="G20" s="41" t="s">
+        <v>30</v>
+      </c>
+      <c r="H20" s="39" t="s">
+        <v>215</v>
+      </c>
+      <c r="I20" s="38" t="s">
+        <v>144</v>
+      </c>
+      <c r="M20" s="34" t="s">
+        <v>992</v>
+      </c>
+    </row>
+    <row r="21" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="C21" s="36">
+        <v>326</v>
+      </c>
+      <c r="D21" s="40" t="s">
+        <v>968</v>
+      </c>
+      <c r="E21" s="41" t="s">
+        <v>997</v>
+      </c>
+      <c r="F21" s="43" t="s">
+        <v>1017</v>
+      </c>
+      <c r="G21" s="41" t="s">
+        <v>30</v>
+      </c>
+      <c r="H21" s="42" t="s">
+        <v>316</v>
+      </c>
+      <c r="I21" s="41" t="s">
+        <v>144</v>
+      </c>
+      <c r="M21" s="35" t="s">
+        <v>993</v>
+      </c>
+    </row>
+    <row r="22" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="C22" s="36">
+        <v>327</v>
+      </c>
+      <c r="D22" s="37" t="s">
+        <v>969</v>
+      </c>
+      <c r="E22" s="38" t="s">
+        <v>997</v>
+      </c>
+      <c r="F22" s="43" t="s">
+        <v>1018</v>
+      </c>
+      <c r="G22" s="41" t="s">
+        <v>30</v>
+      </c>
+      <c r="H22" s="39" t="s">
+        <v>316</v>
+      </c>
+      <c r="I22" s="38" t="s">
+        <v>144</v>
+      </c>
+      <c r="M22" s="34" t="s">
+        <v>994</v>
+      </c>
+    </row>
+    <row r="23" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="C23" s="36">
+        <v>328</v>
+      </c>
+      <c r="D23" s="40" t="s">
+        <v>970</v>
+      </c>
+      <c r="E23" s="41" t="s">
+        <v>997</v>
+      </c>
+      <c r="F23" s="43" t="s">
+        <v>1019</v>
+      </c>
+      <c r="G23" s="41" t="s">
+        <v>30</v>
+      </c>
+      <c r="H23" s="42" t="s">
+        <v>316</v>
+      </c>
+      <c r="I23" s="41" t="s">
+        <v>144</v>
+      </c>
+      <c r="M23" s="35" t="s">
+        <v>995</v>
+      </c>
+    </row>
+    <row r="24" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="C24" s="36">
+        <v>329</v>
+      </c>
+      <c r="D24" s="37" t="s">
+        <v>971</v>
+      </c>
+      <c r="E24" s="38" t="s">
+        <v>997</v>
+      </c>
+      <c r="F24" s="43" t="s">
+        <v>1020</v>
+      </c>
+      <c r="G24" s="41" t="s">
+        <v>30</v>
+      </c>
+      <c r="H24" s="39" t="s">
+        <v>143</v>
+      </c>
+      <c r="I24" s="38" t="s">
+        <v>144</v>
+      </c>
+      <c r="M24" s="34" t="s">
+        <v>996</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/docs/CDOP_SCHEMA.xlsx
+++ b/docs/CDOP_SCHEMA.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rockmtnins-my.sharepoint.com/personal/sebastian_weeks_rmi_org/Documents/Documents/CDOP Resources/UseCase_Category CSVs_JSONs/Master Version/7_31_26/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rockmtnins-my.sharepoint.com/personal/sebastian_weeks_rmi_org/Documents/Documents/CDOP Resources/UseCase_Category CSVs_JSONs/Master Version/Round 2 Pods for Testing/Fast Track Pods/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="115" documentId="8_{E4888AF0-8469-49B9-BF1F-D7429471A122}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{72629C6E-FAAF-4F87-B2E5-800C2876AE8E}"/>
+  <xr:revisionPtr revIDLastSave="472" documentId="8_{E4888AF0-8469-49B9-BF1F-D7429471A122}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{805E69B9-42B6-4388-969F-9DB549C29CA3}"/>
   <bookViews>
-    <workbookView xWindow="-28065" yWindow="540" windowWidth="27360" windowHeight="14955" firstSheet="6" activeTab="11" xr2:uid="{743398AF-A4FE-47C4-9368-972E95242EBF}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="3" xr2:uid="{743398AF-A4FE-47C4-9368-972E95242EBF}"/>
   </bookViews>
   <sheets>
     <sheet name="Full List" sheetId="5" r:id="rId1"/>
@@ -25,6 +25,9 @@
     <sheet name="Durability_Permanence" sheetId="10" r:id="rId10"/>
     <sheet name="Project Finance" sheetId="11" r:id="rId11"/>
     <sheet name="Labels_Certifications" sheetId="12" r:id="rId12"/>
+    <sheet name="Registry_Metadata" sheetId="13" r:id="rId13"/>
+    <sheet name="Validation_Metadata" sheetId="14" r:id="rId14"/>
+    <sheet name="Verification_Metadata" sheetId="15" r:id="rId15"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Full List'!$A$1:$M$174</definedName>
@@ -50,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6394" uniqueCount="823">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7098" uniqueCount="1020">
   <si>
     <t>schema</t>
   </si>
@@ -2562,12 +2565,603 @@
   <si>
     <t>project.project_level[].project_level_compliance_potential_eligibility</t>
   </si>
+  <si>
+    <t>crediting program</t>
+  </si>
+  <si>
+    <t>Describes the current registry, that contains the information about the project, and units</t>
+  </si>
+  <si>
+    <t>Describes the first registry, where the project was registered</t>
+  </si>
+  <si>
+    <t>Describes the Crediting Program that the proejct is following for the implementationunits</t>
+  </si>
+  <si>
+    <t>Date of the last update</t>
+  </si>
+  <si>
+    <t>registry_identifier</t>
+  </si>
+  <si>
+    <t>registry_name</t>
+  </si>
+  <si>
+    <t>registry_link</t>
+  </si>
+  <si>
+    <t>original_registry_identifier</t>
+  </si>
+  <si>
+    <t>original_registry_name</t>
+  </si>
+  <si>
+    <t>original_registry_link</t>
+  </si>
+  <si>
+    <t>program_identifier</t>
+  </si>
+  <si>
+    <t>program_name</t>
+  </si>
+  <si>
+    <t>creation_date</t>
+  </si>
+  <si>
+    <t>update_date</t>
+  </si>
+  <si>
+    <t>Date that the project was first registered</t>
+  </si>
+  <si>
+    <t>registry.creation_date</t>
+  </si>
+  <si>
+    <t>registry.update_date</t>
+  </si>
+  <si>
+    <t>registry.identification[].registry_identifier</t>
+  </si>
+  <si>
+    <t>registry.identification[].registry_name</t>
+  </si>
+  <si>
+    <t>registry.identification[].registry_link</t>
+  </si>
+  <si>
+    <t>registry.original[].original_registry_identifier</t>
+  </si>
+  <si>
+    <t>registry.original[].original_registry_name</t>
+  </si>
+  <si>
+    <t>registry.original[].original_registry_link</t>
+  </si>
+  <si>
+    <t>registry.program[].program_identifier</t>
+  </si>
+  <si>
+    <t>registry.program[].program_name</t>
+  </si>
+  <si>
+    <t>current_validation_stage</t>
+  </si>
+  <si>
+    <t>current_validation_stage_status</t>
+  </si>
+  <si>
+    <t>date_previous_validation</t>
+  </si>
+  <si>
+    <t>date_validation_expiration</t>
+  </si>
+  <si>
+    <t>date_validation_planned</t>
+  </si>
+  <si>
+    <t>date_validation_requested</t>
+  </si>
+  <si>
+    <t>validation_body_accreditation</t>
+  </si>
+  <si>
+    <t>validation_body_id</t>
+  </si>
+  <si>
+    <t>validator_name</t>
+  </si>
+  <si>
+    <t>validation_body_sectoral_scopes</t>
+  </si>
+  <si>
+    <t>validation_body_selection</t>
+  </si>
+  <si>
+    <t>validation_body_team_members_and_roles</t>
+  </si>
+  <si>
+    <t>validation_is_planned</t>
+  </si>
+  <si>
+    <t>validation_period_end_date</t>
+  </si>
+  <si>
+    <t>validation_period_start_date</t>
+  </si>
+  <si>
+    <t>validation_report_link</t>
+  </si>
+  <si>
+    <t>validation_report_summary</t>
+  </si>
+  <si>
+    <t>validation_stage_description</t>
+  </si>
+  <si>
+    <t>validation_stage_document_link</t>
+  </si>
+  <si>
+    <t>validation_stages</t>
+  </si>
+  <si>
+    <t>validation_status</t>
+  </si>
+  <si>
+    <t>validation_report_version</t>
+  </si>
+  <si>
+    <t>Validation and Verification Body (VVB)/ Certification Bodies/ Third Party Auditors</t>
+  </si>
+  <si>
+    <t>Name of the current validation step</t>
+  </si>
+  <si>
+    <t>Status of the current validation step</t>
+  </si>
+  <si>
+    <t>Date of the previous validation event</t>
+  </si>
+  <si>
+    <t>Date validation expires</t>
+  </si>
+  <si>
+    <t>Planned date of the validation event</t>
+  </si>
+  <si>
+    <t>Date validation was requested</t>
+  </si>
+  <si>
+    <t>LCA has been completed</t>
+  </si>
+  <si>
+    <t>LCA is used to quantify emissions</t>
+  </si>
+  <si>
+    <t>Link to LCA report</t>
+  </si>
+  <si>
+    <t>Link to LCA repository</t>
+  </si>
+  <si>
+    <t>LCA results</t>
+  </si>
+  <si>
+    <t>Link to LCA system boundary figure</t>
+  </si>
+  <si>
+    <t>Overview description of LCA system boundary</t>
+  </si>
+  <si>
+    <t>Identification number of the validation event.</t>
+  </si>
+  <si>
+    <t>Type of validation being carried out</t>
+  </si>
+  <si>
+    <t>List any accreditations of the validation body</t>
+  </si>
+  <si>
+    <t>Identification number of the validation body</t>
+  </si>
+  <si>
+    <t>Name of the validation body</t>
+  </si>
+  <si>
+    <t>Name(s) of the validator(s)</t>
+  </si>
+  <si>
+    <t>List the sectoral scopes the validation body is accredited to validate</t>
+  </si>
+  <si>
+    <t>Describe how the validation body was selected</t>
+  </si>
+  <si>
+    <t>List the names of any other validation body team members and their roles (FIRST NAME - LAST NAME, ROLE)</t>
+  </si>
+  <si>
+    <t>Date of validation event</t>
+  </si>
+  <si>
+    <t>Indicate whether the valiation event is planned.</t>
+  </si>
+  <si>
+    <t>End date of the validation event. Estimate if needed.</t>
+  </si>
+  <si>
+    <t>Start date of the validation event</t>
+  </si>
+  <si>
+    <t>Link (URL) to the project's validation report (if applicable).</t>
+  </si>
+  <si>
+    <t>Enter the validation report's summary</t>
+  </si>
+  <si>
+    <t>Describe the stages of the validation event.</t>
+  </si>
+  <si>
+    <t>Link (URL) to the document that contains the description and details of the validation event stages</t>
+  </si>
+  <si>
+    <t>Select all validation event stages</t>
+  </si>
+  <si>
+    <t>Indicate whether the project has been validated.</t>
+  </si>
+  <si>
+    <t>Which version of the validation report is the current version</t>
+  </si>
+  <si>
+    <t>lca_completed</t>
+  </si>
+  <si>
+    <t>lca_emissions_quantification</t>
+  </si>
+  <si>
+    <t>lca_link</t>
+  </si>
+  <si>
+    <t>lca_repository</t>
+  </si>
+  <si>
+    <t>lca_results</t>
+  </si>
+  <si>
+    <t>lca_system_boundary_figure</t>
+  </si>
+  <si>
+    <t>lca_system_boundary_overview</t>
+  </si>
+  <si>
+    <t>validation_body</t>
+  </si>
+  <si>
+    <t>validation.crediting_period[].current_crediting_period_end_date</t>
+  </si>
+  <si>
+    <t>project.validation_stage[].current_validation_stage</t>
+  </si>
+  <si>
+    <t>validation.stage[].validation_stage_document_link</t>
+  </si>
+  <si>
+    <t>validation.crediting_period[].current_crediting_period_number</t>
+  </si>
+  <si>
+    <t>project.validation_stage[].current_validation_stage_status</t>
+  </si>
+  <si>
+    <t>validation.crediting_period[].current_crediting_period_start_date</t>
+  </si>
+  <si>
+    <t>project.date[].date_previous_validation</t>
+  </si>
+  <si>
+    <t>validation.date[].date_validation_expiration</t>
+  </si>
+  <si>
+    <t>validation.date[].date_validation_planned</t>
+  </si>
+  <si>
+    <t>validation.date[].date_validation_requested</t>
+  </si>
+  <si>
+    <t>validation.lca[].lca_completed</t>
+  </si>
+  <si>
+    <t>validation.lca[].lca_emissions_quantification</t>
+  </si>
+  <si>
+    <t>validation.lca[].lca_link</t>
+  </si>
+  <si>
+    <t>validation.lca[].lca_repository</t>
+  </si>
+  <si>
+    <t>validation.lca[].lca_results</t>
+  </si>
+  <si>
+    <t>validation.lca[].lca_system_boundary_figure</t>
+  </si>
+  <si>
+    <t>validation.lca[].lca_system_boundary_overview</t>
+  </si>
+  <si>
+    <t>validation.validation_event[].validation _id</t>
+  </si>
+  <si>
+    <t>validation.validation_event[].validation_type</t>
+  </si>
+  <si>
+    <t>validation.validation_event[].validation_date</t>
+  </si>
+  <si>
+    <t>validation.validation_event[].validation_is_planned</t>
+  </si>
+  <si>
+    <t>validation.validation_event[].validation_period_end_date</t>
+  </si>
+  <si>
+    <t>validation.validation_event[].validation_period_start_date</t>
+  </si>
+  <si>
+    <t>validation.report[].validation_report_link</t>
+  </si>
+  <si>
+    <t>project.validation_status</t>
+  </si>
+  <si>
+    <t>validation.report[].validation_report_summary</t>
+  </si>
+  <si>
+    <t>validation.stage[].validation_stage_description</t>
+  </si>
+  <si>
+    <t>validation.stage[].validation_stages</t>
+  </si>
+  <si>
+    <t>validation.report[].validation_report_version</t>
+  </si>
+  <si>
+    <t>validation_body.details[].validation_body_accreditation</t>
+  </si>
+  <si>
+    <t>validation_body.details[].validation_body_id</t>
+  </si>
+  <si>
+    <t>validation_body.details[].validation_body_name</t>
+  </si>
+  <si>
+    <t>validation_body.details[].validator_name</t>
+  </si>
+  <si>
+    <t>validation_body.details[].validation_body_sectoral_scopes</t>
+  </si>
+  <si>
+    <t>validation_body.details[].validation_body_selection</t>
+  </si>
+  <si>
+    <t>validation_body.details[].validation_body_team_members_and_roles</t>
+  </si>
+  <si>
+    <t>verification_id</t>
+  </si>
+  <si>
+    <t>verification_claim_type</t>
+  </si>
+  <si>
+    <t>verification_project_id</t>
+  </si>
+  <si>
+    <t>verification_description</t>
+  </si>
+  <si>
+    <t>verification_reporting_period_start</t>
+  </si>
+  <si>
+    <t>verification_reporting_period_end</t>
+  </si>
+  <si>
+    <t>verification_date</t>
+  </si>
+  <si>
+    <t>verified_quantity</t>
+  </si>
+  <si>
+    <t>verification_quantity_uom</t>
+  </si>
+  <si>
+    <t>verification_body_name</t>
+  </si>
+  <si>
+    <t>verification_body_id</t>
+  </si>
+  <si>
+    <t>verification_applied_standard</t>
+  </si>
+  <si>
+    <t>verification_applied_methodology_protocol</t>
+  </si>
+  <si>
+    <t>verification_credential_issuer_id</t>
+  </si>
+  <si>
+    <t>verification_cryptographic_proof_type</t>
+  </si>
+  <si>
+    <t>verification_digital_signature_payload</t>
+  </si>
+  <si>
+    <t>verification_leakage_risk_mitigation</t>
+  </si>
+  <si>
+    <t>verification_leakage_risk_mitigation_strategy</t>
+  </si>
+  <si>
+    <t>verification_leakage_deduction_quantity</t>
+  </si>
+  <si>
+    <t>verification_uncertainty_deduction_margin</t>
+  </si>
+  <si>
+    <t>verification_buffer_pool_deduction_quantity</t>
+  </si>
+  <si>
+    <t>verification_audit_checkpoint_status</t>
+  </si>
+  <si>
+    <t>URI</t>
+  </si>
+  <si>
+    <t>Object/String</t>
+  </si>
+  <si>
+    <t>A globally unique identifier for the specific verification event or claim.</t>
+  </si>
+  <si>
+    <t>The classification of the claim being verified (e.g., CARBON_REMOVAL, EMISSION_REDUCTION, BIODIVERSITY).</t>
+  </si>
+  <si>
+    <t>The unique ID of the underlying project registered on the host registry.</t>
+  </si>
+  <si>
+    <t>A concise, human-readable summary of the verification scope and findings.</t>
+  </si>
+  <si>
+    <t>The start date of the monitoring/reporting period being verified.</t>
+  </si>
+  <si>
+    <t>The end date of the monitoring/reporting period being verified.</t>
+  </si>
+  <si>
+    <t>The official date the verification process was completed and signed off.</t>
+  </si>
+  <si>
+    <t>The final, audited, and verified net volume for this specific reporting period.</t>
+  </si>
+  <si>
+    <t>The Unit of Measure for the verified quantity (e.g., tCO2e, m3_biogas).</t>
+  </si>
+  <si>
+    <t>The official name of the third-party auditing entity/VVB.</t>
+  </si>
+  <si>
+    <t>The decentralized identifier (DID) or registry ID of the verification body.</t>
+  </si>
+  <si>
+    <t>The overarching registry framework (e.g., Verra_VCS_v4.5, Gold_Standard).</t>
+  </si>
+  <si>
+    <t>The specific methodology version applied (e.g., VM0047_v1.0, CAR_Soil_v1.1).</t>
+  </si>
+  <si>
+    <t>The direct, secure hyperlink to the official public verification report PDF.</t>
+  </si>
+  <si>
+    <t>The decentralized identifier (DID) of the entity issuing the digital verification token.</t>
+  </si>
+  <si>
+    <t>The security protocol used (e.g., Ed25519Signature2020, JSON-LD).</t>
+  </si>
+  <si>
+    <t>The actual cryptographic signature, payload hash, or verifiable presentation metadata.</t>
+  </si>
+  <si>
+    <t>Indicates if leakage risk is accounted for on this verification event</t>
+  </si>
+  <si>
+    <t>links to or summarizes the mitigation strategy for this verification event</t>
+  </si>
+  <si>
+    <t>Volume deducted for this specific reporting period to account for leakage.</t>
+  </si>
+  <si>
+    <t>Percentage or absolute deduction applied for this specific reporting period for uncertainty.</t>
+  </si>
+  <si>
+    <t>Volume deducted for this specific reporting period and contributed to the buffer pool.</t>
+  </si>
+  <si>
+    <t>Summary result of the checklist (e.g., PASS, PASS_WITH_RESERVATIONS, FAIL).</t>
+  </si>
+  <si>
+    <t>verification</t>
+  </si>
+  <si>
+    <t>verification.identification[].verification_id</t>
+  </si>
+  <si>
+    <t>verification.identification[].verification_claim_type</t>
+  </si>
+  <si>
+    <t>verification.identification[].verification_project_id</t>
+  </si>
+  <si>
+    <t>verification.identification[].verification_description</t>
+  </si>
+  <si>
+    <t>verification.reporting[].verification_reporting_period_start</t>
+  </si>
+  <si>
+    <t>verification.reporting[].verification_reporting_period_end</t>
+  </si>
+  <si>
+    <t>verification.reporting[].verification_date</t>
+  </si>
+  <si>
+    <t>verification.quantity[].verified_quantity</t>
+  </si>
+  <si>
+    <t>verification.quantity[].verification_quantity_uom</t>
+  </si>
+  <si>
+    <t>verification.body[].verification_body_name</t>
+  </si>
+  <si>
+    <t>verification.body[].verification_body_id</t>
+  </si>
+  <si>
+    <t>verification.standard[].verification_applied_standard</t>
+  </si>
+  <si>
+    <t>verification.standard[].verification_applied_methodology_protocol</t>
+  </si>
+  <si>
+    <t>verification.verification_report_url</t>
+  </si>
+  <si>
+    <t>verification.verification_credential_issuer_id</t>
+  </si>
+  <si>
+    <t>verification.verification_cryptographic_proof_type</t>
+  </si>
+  <si>
+    <t>verification.verification_digital_signature_payload</t>
+  </si>
+  <si>
+    <t>verification.leakage[].verification_leakage_risk_mitigation</t>
+  </si>
+  <si>
+    <t>verification.leakage[].verification_leakage_risk_mitigation_strategy</t>
+  </si>
+  <si>
+    <t>verification.leakage[].verification_leakage_deduction_quantity</t>
+  </si>
+  <si>
+    <t>verification.verification_uncertainty_deduction_margin</t>
+  </si>
+  <si>
+    <t>verification.verification_buffer_pool_deduction_quantity</t>
+  </si>
+  <si>
+    <t>verification.verification_audit_checkpoint_status</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2662,8 +3256,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF434343"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2703,6 +3304,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6F8F9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2754,7 +3367,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -2816,6 +3429,27 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -15950,7 +16584,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -15960,7 +16594,7 @@
       <c r="C2">
         <v>242</v>
       </c>
-      <c r="D2" s="32" t="s">
+      <c r="D2" s="6" t="s">
         <v>763</v>
       </c>
       <c r="E2" s="6" t="s">
@@ -15991,7 +16625,7 @@
         <v>785</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -16001,7 +16635,7 @@
       <c r="C3">
         <v>243</v>
       </c>
-      <c r="D3" s="32" t="s">
+      <c r="D3" s="6" t="s">
         <v>764</v>
       </c>
       <c r="E3" s="6" t="s">
@@ -16032,7 +16666,7 @@
         <v>786</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>13</v>
       </c>
@@ -16042,7 +16676,7 @@
       <c r="C4">
         <v>244</v>
       </c>
-      <c r="D4" s="32" t="s">
+      <c r="D4" s="6" t="s">
         <v>765</v>
       </c>
       <c r="E4" s="6" t="s">
@@ -16073,7 +16707,7 @@
         <v>787</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -16083,7 +16717,7 @@
       <c r="C5">
         <v>245</v>
       </c>
-      <c r="D5" s="32" t="s">
+      <c r="D5" s="6" t="s">
         <v>766</v>
       </c>
       <c r="E5" s="6" t="s">
@@ -16114,7 +16748,7 @@
         <v>788</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>13</v>
       </c>
@@ -16124,7 +16758,7 @@
       <c r="C6">
         <v>246</v>
       </c>
-      <c r="D6" s="32" t="s">
+      <c r="D6" s="6" t="s">
         <v>767</v>
       </c>
       <c r="E6" s="6" t="s">
@@ -16155,7 +16789,7 @@
         <v>789</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -16165,7 +16799,7 @@
       <c r="C7">
         <v>247</v>
       </c>
-      <c r="D7" s="32" t="s">
+      <c r="D7" s="6" t="s">
         <v>768</v>
       </c>
       <c r="E7" s="6" t="s">
@@ -16196,7 +16830,7 @@
         <v>790</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>13</v>
       </c>
@@ -16206,7 +16840,7 @@
       <c r="C8">
         <v>248</v>
       </c>
-      <c r="D8" s="32" t="s">
+      <c r="D8" s="6" t="s">
         <v>769</v>
       </c>
       <c r="E8" s="6" t="s">
@@ -16237,7 +16871,7 @@
         <v>791</v>
       </c>
     </row>
-    <row r="9" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>13</v>
       </c>
@@ -16247,7 +16881,7 @@
       <c r="C9">
         <v>249</v>
       </c>
-      <c r="D9" s="32" t="s">
+      <c r="D9" s="6" t="s">
         <v>770</v>
       </c>
       <c r="E9" s="6" t="s">
@@ -16278,7 +16912,7 @@
         <v>792</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>13</v>
       </c>
@@ -16288,7 +16922,7 @@
       <c r="C10">
         <v>250</v>
       </c>
-      <c r="D10" s="32" t="s">
+      <c r="D10" s="6" t="s">
         <v>771</v>
       </c>
       <c r="E10" s="6" t="s">
@@ -16319,7 +16953,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>13</v>
       </c>
@@ -16329,7 +16963,7 @@
       <c r="C11">
         <v>251</v>
       </c>
-      <c r="D11" s="32" t="s">
+      <c r="D11" s="6" t="s">
         <v>772</v>
       </c>
       <c r="E11" s="6" t="s">
@@ -16360,7 +16994,7 @@
         <v>794</v>
       </c>
     </row>
-    <row r="12" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>13</v>
       </c>
@@ -16370,7 +17004,7 @@
       <c r="C12">
         <v>252</v>
       </c>
-      <c r="D12" s="32" t="s">
+      <c r="D12" s="6" t="s">
         <v>773</v>
       </c>
       <c r="E12" s="6" t="s">
@@ -16401,7 +17035,7 @@
         <v>795</v>
       </c>
     </row>
-    <row r="13" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>13</v>
       </c>
@@ -16411,7 +17045,7 @@
       <c r="C13">
         <v>253</v>
       </c>
-      <c r="D13" s="32" t="s">
+      <c r="D13" s="6" t="s">
         <v>774</v>
       </c>
       <c r="E13" s="6" t="s">
@@ -16442,7 +17076,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="14" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>13</v>
       </c>
@@ -16452,7 +17086,7 @@
       <c r="C14">
         <v>254</v>
       </c>
-      <c r="D14" s="32" t="s">
+      <c r="D14" s="6" t="s">
         <v>775</v>
       </c>
       <c r="E14" s="6" t="s">
@@ -16483,7 +17117,7 @@
         <v>797</v>
       </c>
     </row>
-    <row r="15" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>13</v>
       </c>
@@ -16493,7 +17127,7 @@
       <c r="C15">
         <v>255</v>
       </c>
-      <c r="D15" s="32" t="s">
+      <c r="D15" s="6" t="s">
         <v>776</v>
       </c>
       <c r="E15" s="6" t="s">
@@ -16524,7 +17158,7 @@
         <v>798</v>
       </c>
     </row>
-    <row r="16" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>13</v>
       </c>
@@ -16534,7 +17168,7 @@
       <c r="C16">
         <v>256</v>
       </c>
-      <c r="D16" s="32" t="s">
+      <c r="D16" s="6" t="s">
         <v>777</v>
       </c>
       <c r="E16" s="6" t="s">
@@ -16565,7 +17199,7 @@
         <v>799</v>
       </c>
     </row>
-    <row r="17" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>13</v>
       </c>
@@ -16575,7 +17209,7 @@
       <c r="C17">
         <v>257</v>
       </c>
-      <c r="D17" s="32" t="s">
+      <c r="D17" s="6" t="s">
         <v>778</v>
       </c>
       <c r="E17" s="6" t="s">
@@ -16616,7 +17250,7 @@
       <c r="C18">
         <v>258</v>
       </c>
-      <c r="D18" s="32" t="s">
+      <c r="D18" s="6" t="s">
         <v>779</v>
       </c>
       <c r="E18" s="6" t="s">
@@ -16647,7 +17281,7 @@
         <v>801</v>
       </c>
     </row>
-    <row r="19" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>13</v>
       </c>
@@ -16657,7 +17291,7 @@
       <c r="C19">
         <v>259</v>
       </c>
-      <c r="D19" s="32" t="s">
+      <c r="D19" s="6" t="s">
         <v>780</v>
       </c>
       <c r="E19" s="6" t="s">
@@ -16688,7 +17322,7 @@
         <v>802</v>
       </c>
     </row>
-    <row r="20" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>13</v>
       </c>
@@ -16698,7 +17332,7 @@
       <c r="C20">
         <v>260</v>
       </c>
-      <c r="D20" s="32" t="s">
+      <c r="D20" s="6" t="s">
         <v>781</v>
       </c>
       <c r="E20" s="6" t="s">
@@ -16731,6 +17365,2536 @@
     </row>
   </sheetData>
   <phoneticPr fontId="12" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5DD793A8-CD91-4786-8377-89E3BC40F96B}">
+  <dimension ref="A1:M11"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="2" width="8.54296875" customWidth="1"/>
+    <col min="4" max="4" width="30.6328125" customWidth="1"/>
+    <col min="5" max="5" width="15.90625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="52.81640625" customWidth="1"/>
+    <col min="7" max="7" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12" customWidth="1"/>
+    <col min="9" max="9" width="16.6328125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.90625" customWidth="1"/>
+    <col min="12" max="12" width="13.1796875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="35.08984375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" t="s">
+        <v>275</v>
+      </c>
+      <c r="C2">
+        <v>261</v>
+      </c>
+      <c r="D2" s="25" t="s">
+        <v>828</v>
+      </c>
+      <c r="E2" t="s">
+        <v>116</v>
+      </c>
+      <c r="F2" t="s">
+        <v>841</v>
+      </c>
+      <c r="G2" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="H2" s="25" t="s">
+        <v>392</v>
+      </c>
+      <c r="I2" t="s">
+        <v>226</v>
+      </c>
+      <c r="J2" t="s">
+        <v>116</v>
+      </c>
+      <c r="L2" t="s">
+        <v>146</v>
+      </c>
+      <c r="M2" s="18" t="s">
+        <v>824</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" t="s">
+        <v>275</v>
+      </c>
+      <c r="C3">
+        <v>262</v>
+      </c>
+      <c r="D3" s="25" t="s">
+        <v>829</v>
+      </c>
+      <c r="E3" t="s">
+        <v>116</v>
+      </c>
+      <c r="F3" t="s">
+        <v>842</v>
+      </c>
+      <c r="G3" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="H3" s="25" t="s">
+        <v>159</v>
+      </c>
+      <c r="I3" t="s">
+        <v>226</v>
+      </c>
+      <c r="J3" t="s">
+        <v>116</v>
+      </c>
+      <c r="L3" t="s">
+        <v>146</v>
+      </c>
+      <c r="M3" s="18" t="s">
+        <v>824</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" t="s">
+        <v>275</v>
+      </c>
+      <c r="C4">
+        <v>263</v>
+      </c>
+      <c r="D4" s="25" t="s">
+        <v>830</v>
+      </c>
+      <c r="E4" t="s">
+        <v>116</v>
+      </c>
+      <c r="F4" t="s">
+        <v>843</v>
+      </c>
+      <c r="G4" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="H4" s="25" t="s">
+        <v>159</v>
+      </c>
+      <c r="I4" t="s">
+        <v>226</v>
+      </c>
+      <c r="J4" t="s">
+        <v>116</v>
+      </c>
+      <c r="L4" t="s">
+        <v>146</v>
+      </c>
+      <c r="M4" s="18" t="s">
+        <v>824</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" t="s">
+        <v>275</v>
+      </c>
+      <c r="C5">
+        <v>264</v>
+      </c>
+      <c r="D5" s="25" t="s">
+        <v>831</v>
+      </c>
+      <c r="E5" t="s">
+        <v>116</v>
+      </c>
+      <c r="F5" t="s">
+        <v>844</v>
+      </c>
+      <c r="G5" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="H5" s="25" t="s">
+        <v>392</v>
+      </c>
+      <c r="I5" t="s">
+        <v>226</v>
+      </c>
+      <c r="J5" t="s">
+        <v>116</v>
+      </c>
+      <c r="L5" t="s">
+        <v>146</v>
+      </c>
+      <c r="M5" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" t="s">
+        <v>275</v>
+      </c>
+      <c r="C6">
+        <v>265</v>
+      </c>
+      <c r="D6" s="25" t="s">
+        <v>832</v>
+      </c>
+      <c r="E6" t="s">
+        <v>116</v>
+      </c>
+      <c r="F6" t="s">
+        <v>845</v>
+      </c>
+      <c r="G6" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="H6" s="25" t="s">
+        <v>159</v>
+      </c>
+      <c r="I6" t="s">
+        <v>226</v>
+      </c>
+      <c r="J6" t="s">
+        <v>116</v>
+      </c>
+      <c r="L6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M6" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" t="s">
+        <v>275</v>
+      </c>
+      <c r="C7">
+        <v>266</v>
+      </c>
+      <c r="D7" s="25" t="s">
+        <v>833</v>
+      </c>
+      <c r="E7" t="s">
+        <v>116</v>
+      </c>
+      <c r="F7" t="s">
+        <v>846</v>
+      </c>
+      <c r="G7" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="H7" s="25" t="s">
+        <v>159</v>
+      </c>
+      <c r="I7" t="s">
+        <v>226</v>
+      </c>
+      <c r="J7" t="s">
+        <v>116</v>
+      </c>
+      <c r="L7" t="s">
+        <v>146</v>
+      </c>
+      <c r="M7" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" t="s">
+        <v>275</v>
+      </c>
+      <c r="C8">
+        <v>267</v>
+      </c>
+      <c r="D8" s="25" t="s">
+        <v>834</v>
+      </c>
+      <c r="E8" t="s">
+        <v>116</v>
+      </c>
+      <c r="F8" t="s">
+        <v>847</v>
+      </c>
+      <c r="G8" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="H8" s="25" t="s">
+        <v>392</v>
+      </c>
+      <c r="I8" t="s">
+        <v>226</v>
+      </c>
+      <c r="J8" t="s">
+        <v>823</v>
+      </c>
+      <c r="L8" t="s">
+        <v>146</v>
+      </c>
+      <c r="M8" s="18" t="s">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" t="s">
+        <v>275</v>
+      </c>
+      <c r="C9">
+        <v>268</v>
+      </c>
+      <c r="D9" s="25" t="s">
+        <v>835</v>
+      </c>
+      <c r="E9" t="s">
+        <v>116</v>
+      </c>
+      <c r="F9" t="s">
+        <v>848</v>
+      </c>
+      <c r="G9" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="H9" s="25" t="s">
+        <v>159</v>
+      </c>
+      <c r="I9" t="s">
+        <v>226</v>
+      </c>
+      <c r="J9" t="s">
+        <v>823</v>
+      </c>
+      <c r="L9" t="s">
+        <v>146</v>
+      </c>
+      <c r="M9" s="18" t="s">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" t="s">
+        <v>275</v>
+      </c>
+      <c r="C10">
+        <v>269</v>
+      </c>
+      <c r="D10" s="25" t="s">
+        <v>836</v>
+      </c>
+      <c r="E10" t="s">
+        <v>116</v>
+      </c>
+      <c r="F10" t="s">
+        <v>839</v>
+      </c>
+      <c r="G10" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="H10" s="25" t="s">
+        <v>219</v>
+      </c>
+      <c r="I10" t="s">
+        <v>226</v>
+      </c>
+      <c r="L10" t="s">
+        <v>146</v>
+      </c>
+      <c r="M10" s="18" t="s">
+        <v>838</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>13</v>
+      </c>
+      <c r="B11" t="s">
+        <v>275</v>
+      </c>
+      <c r="C11">
+        <v>270</v>
+      </c>
+      <c r="D11" s="25" t="s">
+        <v>837</v>
+      </c>
+      <c r="E11" t="s">
+        <v>116</v>
+      </c>
+      <c r="F11" t="s">
+        <v>840</v>
+      </c>
+      <c r="G11" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="H11" s="25" t="s">
+        <v>219</v>
+      </c>
+      <c r="I11" t="s">
+        <v>31</v>
+      </c>
+      <c r="L11" t="s">
+        <v>146</v>
+      </c>
+      <c r="M11" s="18" t="s">
+        <v>827</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF337E51-0D9D-46A6-9DB2-8DF5F9FC1667}">
+  <dimension ref="A1:M37"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="4" max="4" width="43.6328125" customWidth="1"/>
+    <col min="5" max="5" width="15.90625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="58.453125" customWidth="1"/>
+    <col min="7" max="7" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.90625" customWidth="1"/>
+    <col min="9" max="9" width="16.6328125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.26953125" customWidth="1"/>
+    <col min="12" max="12" width="13.1796875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="49.90625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" t="s">
+        <v>275</v>
+      </c>
+      <c r="C2">
+        <v>271</v>
+      </c>
+      <c r="D2" s="33" t="s">
+        <v>481</v>
+      </c>
+      <c r="E2" s="33" t="s">
+        <v>266</v>
+      </c>
+      <c r="F2" t="s">
+        <v>913</v>
+      </c>
+      <c r="G2" s="33" t="s">
+        <v>18</v>
+      </c>
+      <c r="H2" s="33" t="s">
+        <v>219</v>
+      </c>
+      <c r="I2" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="J2" s="6" t="s">
+        <v>445</v>
+      </c>
+      <c r="L2" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M2" s="6" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" t="s">
+        <v>275</v>
+      </c>
+      <c r="C3">
+        <v>272</v>
+      </c>
+      <c r="D3" s="33" t="s">
+        <v>483</v>
+      </c>
+      <c r="E3" s="33" t="s">
+        <v>266</v>
+      </c>
+      <c r="F3" t="s">
+        <v>916</v>
+      </c>
+      <c r="G3" s="33" t="s">
+        <v>18</v>
+      </c>
+      <c r="H3" s="33" t="s">
+        <v>392</v>
+      </c>
+      <c r="I3" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="J3" s="6" t="s">
+        <v>445</v>
+      </c>
+      <c r="L3" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M3" s="6" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" t="s">
+        <v>275</v>
+      </c>
+      <c r="C4">
+        <v>273</v>
+      </c>
+      <c r="D4" s="33" t="s">
+        <v>479</v>
+      </c>
+      <c r="E4" s="33" t="s">
+        <v>266</v>
+      </c>
+      <c r="F4" t="s">
+        <v>918</v>
+      </c>
+      <c r="G4" s="33" t="s">
+        <v>18</v>
+      </c>
+      <c r="H4" s="33" t="s">
+        <v>219</v>
+      </c>
+      <c r="I4" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="J4" s="6" t="s">
+        <v>445</v>
+      </c>
+      <c r="L4" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M4" s="6" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" t="s">
+        <v>275</v>
+      </c>
+      <c r="C5">
+        <v>274</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>849</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F5" t="s">
+        <v>914</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H5" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="I5" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="J5" s="6" t="s">
+        <v>445</v>
+      </c>
+      <c r="L5" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M5" s="6" t="s">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" t="s">
+        <v>275</v>
+      </c>
+      <c r="C6">
+        <v>275</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>850</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F6" t="s">
+        <v>917</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H6" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="I6" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="J6" s="6" t="s">
+        <v>445</v>
+      </c>
+      <c r="L6" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M6" s="6" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" t="s">
+        <v>275</v>
+      </c>
+      <c r="C7">
+        <v>276</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>851</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F7" t="s">
+        <v>919</v>
+      </c>
+      <c r="G7" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="H7" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="I7" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="J7" s="6" t="s">
+        <v>445</v>
+      </c>
+      <c r="L7" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M7" s="6" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" t="s">
+        <v>275</v>
+      </c>
+      <c r="C8">
+        <v>277</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>852</v>
+      </c>
+      <c r="E8" s="33" t="s">
+        <v>266</v>
+      </c>
+      <c r="F8" t="s">
+        <v>920</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H8" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="I8" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="J8" s="6" t="s">
+        <v>871</v>
+      </c>
+      <c r="L8" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M8" s="6" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" t="s">
+        <v>275</v>
+      </c>
+      <c r="C9">
+        <v>278</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>853</v>
+      </c>
+      <c r="E9" s="33" t="s">
+        <v>266</v>
+      </c>
+      <c r="F9" t="s">
+        <v>921</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H9" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="I9" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="J9" s="6" t="s">
+        <v>871</v>
+      </c>
+      <c r="L9" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M9" s="6" t="s">
+        <v>876</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" t="s">
+        <v>275</v>
+      </c>
+      <c r="C10">
+        <v>279</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>854</v>
+      </c>
+      <c r="E10" s="33" t="s">
+        <v>266</v>
+      </c>
+      <c r="F10" t="s">
+        <v>922</v>
+      </c>
+      <c r="G10" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H10" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="I10" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="J10" s="6" t="s">
+        <v>871</v>
+      </c>
+      <c r="L10" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M10" s="6" t="s">
+        <v>877</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>13</v>
+      </c>
+      <c r="B11" t="s">
+        <v>275</v>
+      </c>
+      <c r="C11">
+        <v>280</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>905</v>
+      </c>
+      <c r="E11" s="33" t="s">
+        <v>266</v>
+      </c>
+      <c r="F11" t="s">
+        <v>923</v>
+      </c>
+      <c r="G11" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="H11" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="I11" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="J11" s="6" t="s">
+        <v>871</v>
+      </c>
+      <c r="L11" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M11" s="6" t="s">
+        <v>878</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12" t="s">
+        <v>275</v>
+      </c>
+      <c r="C12">
+        <v>281</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>906</v>
+      </c>
+      <c r="E12" s="33" t="s">
+        <v>266</v>
+      </c>
+      <c r="F12" t="s">
+        <v>924</v>
+      </c>
+      <c r="G12" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="H12" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="I12" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="J12" s="6" t="s">
+        <v>871</v>
+      </c>
+      <c r="L12" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M12" s="6" t="s">
+        <v>879</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13" t="s">
+        <v>275</v>
+      </c>
+      <c r="C13">
+        <v>282</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>907</v>
+      </c>
+      <c r="E13" s="33" t="s">
+        <v>266</v>
+      </c>
+      <c r="F13" t="s">
+        <v>925</v>
+      </c>
+      <c r="G13" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="H13" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="I13" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="J13" s="6" t="s">
+        <v>871</v>
+      </c>
+      <c r="L13" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M13" s="6" t="s">
+        <v>880</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>275</v>
+      </c>
+      <c r="C14">
+        <v>283</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>908</v>
+      </c>
+      <c r="E14" s="33" t="s">
+        <v>266</v>
+      </c>
+      <c r="F14" t="s">
+        <v>926</v>
+      </c>
+      <c r="G14" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="H14" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="I14" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="J14" s="6" t="s">
+        <v>871</v>
+      </c>
+      <c r="L14" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M14" s="6" t="s">
+        <v>881</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>13</v>
+      </c>
+      <c r="B15" t="s">
+        <v>275</v>
+      </c>
+      <c r="C15">
+        <v>284</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>909</v>
+      </c>
+      <c r="E15" s="33" t="s">
+        <v>266</v>
+      </c>
+      <c r="F15" t="s">
+        <v>927</v>
+      </c>
+      <c r="G15" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="H15" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="I15" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="J15" s="6" t="s">
+        <v>871</v>
+      </c>
+      <c r="L15" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M15" s="6" t="s">
+        <v>882</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>13</v>
+      </c>
+      <c r="B16" t="s">
+        <v>275</v>
+      </c>
+      <c r="C16">
+        <v>285</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>910</v>
+      </c>
+      <c r="E16" s="33" t="s">
+        <v>266</v>
+      </c>
+      <c r="F16" t="s">
+        <v>928</v>
+      </c>
+      <c r="G16" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="H16" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="I16" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="J16" s="6" t="s">
+        <v>871</v>
+      </c>
+      <c r="L16" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M16" s="6" t="s">
+        <v>883</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>13</v>
+      </c>
+      <c r="B17" t="s">
+        <v>275</v>
+      </c>
+      <c r="C17">
+        <v>286</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>911</v>
+      </c>
+      <c r="E17" s="33" t="s">
+        <v>266</v>
+      </c>
+      <c r="F17" t="s">
+        <v>929</v>
+      </c>
+      <c r="G17" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="H17" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="I17" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="J17" s="6" t="s">
+        <v>871</v>
+      </c>
+      <c r="L17" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M17" s="6" t="s">
+        <v>884</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>13</v>
+      </c>
+      <c r="B18" t="s">
+        <v>275</v>
+      </c>
+      <c r="C18">
+        <v>287</v>
+      </c>
+      <c r="D18" s="33" t="s">
+        <v>477</v>
+      </c>
+      <c r="E18" s="33" t="s">
+        <v>266</v>
+      </c>
+      <c r="F18" t="s">
+        <v>930</v>
+      </c>
+      <c r="G18" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H18" s="6" t="s">
+        <v>392</v>
+      </c>
+      <c r="I18" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="J18" s="6" t="s">
+        <v>871</v>
+      </c>
+      <c r="L18" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M18" s="6" t="s">
+        <v>885</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>13</v>
+      </c>
+      <c r="B19" t="s">
+        <v>275</v>
+      </c>
+      <c r="C19">
+        <v>288</v>
+      </c>
+      <c r="D19" s="30" t="s">
+        <v>511</v>
+      </c>
+      <c r="E19" s="33" t="s">
+        <v>266</v>
+      </c>
+      <c r="F19" t="s">
+        <v>931</v>
+      </c>
+      <c r="G19" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H19" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="I19" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="J19" s="6" t="s">
+        <v>871</v>
+      </c>
+      <c r="L19" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M19" s="6" t="s">
+        <v>886</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>13</v>
+      </c>
+      <c r="B20" t="s">
+        <v>275</v>
+      </c>
+      <c r="C20">
+        <v>289</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>855</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>912</v>
+      </c>
+      <c r="F20" t="s">
+        <v>942</v>
+      </c>
+      <c r="G20" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="H20" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="I20" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="J20" s="6" t="s">
+        <v>871</v>
+      </c>
+      <c r="L20" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M20" s="6" t="s">
+        <v>887</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>13</v>
+      </c>
+      <c r="B21" t="s">
+        <v>275</v>
+      </c>
+      <c r="C21">
+        <v>290</v>
+      </c>
+      <c r="D21" s="17" t="s">
+        <v>856</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>912</v>
+      </c>
+      <c r="F21" t="s">
+        <v>943</v>
+      </c>
+      <c r="G21" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H21" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="I21" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="J21" s="6" t="s">
+        <v>871</v>
+      </c>
+      <c r="L21" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M21" s="6" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>13</v>
+      </c>
+      <c r="B22" t="s">
+        <v>275</v>
+      </c>
+      <c r="C22">
+        <v>291</v>
+      </c>
+      <c r="D22" s="17" t="s">
+        <v>265</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>912</v>
+      </c>
+      <c r="F22" t="s">
+        <v>944</v>
+      </c>
+      <c r="G22" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H22" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="I22" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="J22" s="6" t="s">
+        <v>871</v>
+      </c>
+      <c r="L22" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M22" s="6" t="s">
+        <v>889</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>13</v>
+      </c>
+      <c r="B23" t="s">
+        <v>275</v>
+      </c>
+      <c r="C23">
+        <v>292</v>
+      </c>
+      <c r="D23" s="17" t="s">
+        <v>857</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>912</v>
+      </c>
+      <c r="F23" t="s">
+        <v>945</v>
+      </c>
+      <c r="G23" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H23" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="I23" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="J23" s="6" t="s">
+        <v>871</v>
+      </c>
+      <c r="L23" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M23" s="6" t="s">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>13</v>
+      </c>
+      <c r="B24" t="s">
+        <v>275</v>
+      </c>
+      <c r="C24">
+        <v>293</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>858</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>912</v>
+      </c>
+      <c r="F24" t="s">
+        <v>946</v>
+      </c>
+      <c r="G24" s="6" t="s">
+        <v>564</v>
+      </c>
+      <c r="H24" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="I24" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="J24" s="6" t="s">
+        <v>871</v>
+      </c>
+      <c r="L24" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M24" s="6" t="s">
+        <v>891</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>13</v>
+      </c>
+      <c r="B25" t="s">
+        <v>275</v>
+      </c>
+      <c r="C25">
+        <v>294</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>859</v>
+      </c>
+      <c r="E25" s="6" t="s">
+        <v>912</v>
+      </c>
+      <c r="F25" t="s">
+        <v>947</v>
+      </c>
+      <c r="G25" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H25" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="I25" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="J25" s="6" t="s">
+        <v>871</v>
+      </c>
+      <c r="L25" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M25" s="6" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>13</v>
+      </c>
+      <c r="B26" t="s">
+        <v>275</v>
+      </c>
+      <c r="C26">
+        <v>295</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>860</v>
+      </c>
+      <c r="E26" s="6" t="s">
+        <v>912</v>
+      </c>
+      <c r="F26" t="s">
+        <v>948</v>
+      </c>
+      <c r="G26" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H26" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="I26" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="J26" s="6" t="s">
+        <v>871</v>
+      </c>
+      <c r="L26" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M26" s="6" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>13</v>
+      </c>
+      <c r="B27" t="s">
+        <v>275</v>
+      </c>
+      <c r="C27">
+        <v>296</v>
+      </c>
+      <c r="D27" s="17" t="s">
+        <v>269</v>
+      </c>
+      <c r="E27" s="33" t="s">
+        <v>266</v>
+      </c>
+      <c r="F27" t="s">
+        <v>932</v>
+      </c>
+      <c r="G27" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H27" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="I27" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="J27" s="6" t="s">
+        <v>871</v>
+      </c>
+      <c r="L27" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M27" s="6" t="s">
+        <v>894</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
+        <v>13</v>
+      </c>
+      <c r="B28" t="s">
+        <v>275</v>
+      </c>
+      <c r="C28">
+        <v>297</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>861</v>
+      </c>
+      <c r="E28" s="33" t="s">
+        <v>266</v>
+      </c>
+      <c r="F28" t="s">
+        <v>933</v>
+      </c>
+      <c r="G28" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H28" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="I28" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="J28" s="6" t="s">
+        <v>871</v>
+      </c>
+      <c r="L28" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M28" s="6" t="s">
+        <v>895</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
+        <v>13</v>
+      </c>
+      <c r="B29" t="s">
+        <v>275</v>
+      </c>
+      <c r="C29">
+        <v>298</v>
+      </c>
+      <c r="D29" s="6" t="s">
+        <v>862</v>
+      </c>
+      <c r="E29" s="33" t="s">
+        <v>266</v>
+      </c>
+      <c r="F29" t="s">
+        <v>934</v>
+      </c>
+      <c r="G29" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H29" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="I29" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="J29" s="6" t="s">
+        <v>871</v>
+      </c>
+      <c r="L29" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M29" s="6" t="s">
+        <v>896</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
+        <v>13</v>
+      </c>
+      <c r="B30" t="s">
+        <v>275</v>
+      </c>
+      <c r="C30">
+        <v>299</v>
+      </c>
+      <c r="D30" s="6" t="s">
+        <v>863</v>
+      </c>
+      <c r="E30" s="33" t="s">
+        <v>266</v>
+      </c>
+      <c r="F30" t="s">
+        <v>935</v>
+      </c>
+      <c r="G30" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H30" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="I30" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="J30" s="6" t="s">
+        <v>871</v>
+      </c>
+      <c r="L30" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M30" s="6" t="s">
+        <v>897</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>13</v>
+      </c>
+      <c r="B31" t="s">
+        <v>275</v>
+      </c>
+      <c r="C31">
+        <v>300</v>
+      </c>
+      <c r="D31" s="17" t="s">
+        <v>864</v>
+      </c>
+      <c r="E31" s="33" t="s">
+        <v>266</v>
+      </c>
+      <c r="F31" t="s">
+        <v>936</v>
+      </c>
+      <c r="G31" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="H31" s="17" t="s">
+        <v>159</v>
+      </c>
+      <c r="I31" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="J31" s="6" t="s">
+        <v>871</v>
+      </c>
+      <c r="L31" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M31" s="17" t="s">
+        <v>898</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
+        <v>13</v>
+      </c>
+      <c r="B32" t="s">
+        <v>275</v>
+      </c>
+      <c r="C32">
+        <v>301</v>
+      </c>
+      <c r="D32" s="6" t="s">
+        <v>865</v>
+      </c>
+      <c r="E32" s="33" t="s">
+        <v>266</v>
+      </c>
+      <c r="F32" t="s">
+        <v>938</v>
+      </c>
+      <c r="G32" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="H32" s="17" t="s">
+        <v>159</v>
+      </c>
+      <c r="I32" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="J32" s="6" t="s">
+        <v>871</v>
+      </c>
+      <c r="L32" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M32" s="6" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>13</v>
+      </c>
+      <c r="B33" t="s">
+        <v>275</v>
+      </c>
+      <c r="C33">
+        <v>302</v>
+      </c>
+      <c r="D33" s="6" t="s">
+        <v>866</v>
+      </c>
+      <c r="E33" s="33" t="s">
+        <v>266</v>
+      </c>
+      <c r="F33" t="s">
+        <v>939</v>
+      </c>
+      <c r="G33" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="H33" s="17" t="s">
+        <v>159</v>
+      </c>
+      <c r="I33" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="J33" s="6" t="s">
+        <v>871</v>
+      </c>
+      <c r="L33" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M33" s="6" t="s">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
+        <v>13</v>
+      </c>
+      <c r="B34" t="s">
+        <v>275</v>
+      </c>
+      <c r="C34">
+        <v>303</v>
+      </c>
+      <c r="D34" s="6" t="s">
+        <v>867</v>
+      </c>
+      <c r="E34" s="33" t="s">
+        <v>266</v>
+      </c>
+      <c r="F34" t="s">
+        <v>915</v>
+      </c>
+      <c r="G34" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="H34" s="17" t="s">
+        <v>159</v>
+      </c>
+      <c r="I34" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="J34" s="6" t="s">
+        <v>871</v>
+      </c>
+      <c r="L34" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M34" s="6" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
+        <v>13</v>
+      </c>
+      <c r="B35" t="s">
+        <v>275</v>
+      </c>
+      <c r="C35">
+        <v>304</v>
+      </c>
+      <c r="D35" s="6" t="s">
+        <v>868</v>
+      </c>
+      <c r="E35" s="33" t="s">
+        <v>266</v>
+      </c>
+      <c r="F35" t="s">
+        <v>940</v>
+      </c>
+      <c r="G35" s="6" t="s">
+        <v>564</v>
+      </c>
+      <c r="H35" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="I35" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="J35" s="6" t="s">
+        <v>871</v>
+      </c>
+      <c r="L35" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M35" s="6" t="s">
+        <v>902</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
+        <v>13</v>
+      </c>
+      <c r="B36" t="s">
+        <v>275</v>
+      </c>
+      <c r="C36">
+        <v>305</v>
+      </c>
+      <c r="D36" s="6" t="s">
+        <v>869</v>
+      </c>
+      <c r="E36" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F36" t="s">
+        <v>937</v>
+      </c>
+      <c r="G36" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H36" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="I36" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="J36" s="6" t="s">
+        <v>445</v>
+      </c>
+      <c r="L36" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M36" s="6" t="s">
+        <v>903</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A37" t="s">
+        <v>13</v>
+      </c>
+      <c r="B37" t="s">
+        <v>275</v>
+      </c>
+      <c r="C37">
+        <v>306</v>
+      </c>
+      <c r="D37" s="6" t="s">
+        <v>870</v>
+      </c>
+      <c r="E37" s="33" t="s">
+        <v>266</v>
+      </c>
+      <c r="F37" t="s">
+        <v>941</v>
+      </c>
+      <c r="G37" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="H37" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="I37" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="J37" s="6" t="s">
+        <v>871</v>
+      </c>
+      <c r="L37" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M37" s="6" t="s">
+        <v>904</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7A22D2F-6AFE-4D3D-A8D1-BBD797E61616}">
+  <dimension ref="A1:M24"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="4" max="4" width="37.90625" customWidth="1"/>
+    <col min="5" max="5" width="15.90625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="43.26953125" customWidth="1"/>
+    <col min="7" max="7" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.90625" customWidth="1"/>
+    <col min="9" max="9" width="16.6328125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.26953125" customWidth="1"/>
+    <col min="12" max="12" width="13.1796875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="49.90625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="C2">
+        <v>307</v>
+      </c>
+      <c r="D2" s="34" t="s">
+        <v>949</v>
+      </c>
+      <c r="E2" s="36" t="s">
+        <v>996</v>
+      </c>
+      <c r="F2" t="s">
+        <v>997</v>
+      </c>
+      <c r="G2" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="H2" s="37" t="s">
+        <v>215</v>
+      </c>
+      <c r="I2" s="36" t="s">
+        <v>20</v>
+      </c>
+      <c r="M2" s="34" t="s">
+        <v>973</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="C3">
+        <v>308</v>
+      </c>
+      <c r="D3" s="35" t="s">
+        <v>950</v>
+      </c>
+      <c r="E3" s="38" t="s">
+        <v>996</v>
+      </c>
+      <c r="F3" t="s">
+        <v>998</v>
+      </c>
+      <c r="G3" s="38" t="s">
+        <v>18</v>
+      </c>
+      <c r="H3" s="39" t="s">
+        <v>143</v>
+      </c>
+      <c r="I3" s="38" t="s">
+        <v>20</v>
+      </c>
+      <c r="M3" s="35" t="s">
+        <v>974</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="C4">
+        <v>309</v>
+      </c>
+      <c r="D4" s="34" t="s">
+        <v>951</v>
+      </c>
+      <c r="E4" s="36" t="s">
+        <v>996</v>
+      </c>
+      <c r="F4" t="s">
+        <v>999</v>
+      </c>
+      <c r="G4" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="H4" s="37" t="s">
+        <v>215</v>
+      </c>
+      <c r="I4" s="36" t="s">
+        <v>20</v>
+      </c>
+      <c r="M4" s="34" t="s">
+        <v>975</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="C5">
+        <v>310</v>
+      </c>
+      <c r="D5" s="35" t="s">
+        <v>952</v>
+      </c>
+      <c r="E5" s="38" t="s">
+        <v>996</v>
+      </c>
+      <c r="F5" t="s">
+        <v>1000</v>
+      </c>
+      <c r="G5" s="38" t="s">
+        <v>18</v>
+      </c>
+      <c r="H5" s="39" t="s">
+        <v>215</v>
+      </c>
+      <c r="I5" s="38" t="s">
+        <v>20</v>
+      </c>
+      <c r="M5" s="35" t="s">
+        <v>976</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="C6">
+        <v>311</v>
+      </c>
+      <c r="D6" s="34" t="s">
+        <v>953</v>
+      </c>
+      <c r="E6" s="36" t="s">
+        <v>996</v>
+      </c>
+      <c r="F6" t="s">
+        <v>1001</v>
+      </c>
+      <c r="G6" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="H6" s="37" t="s">
+        <v>219</v>
+      </c>
+      <c r="I6" s="36" t="s">
+        <v>20</v>
+      </c>
+      <c r="M6" s="34" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="C7">
+        <v>312</v>
+      </c>
+      <c r="D7" s="35" t="s">
+        <v>954</v>
+      </c>
+      <c r="E7" s="38" t="s">
+        <v>996</v>
+      </c>
+      <c r="F7" t="s">
+        <v>1002</v>
+      </c>
+      <c r="G7" s="38" t="s">
+        <v>18</v>
+      </c>
+      <c r="H7" s="39" t="s">
+        <v>219</v>
+      </c>
+      <c r="I7" s="38" t="s">
+        <v>20</v>
+      </c>
+      <c r="M7" s="35" t="s">
+        <v>978</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="C8">
+        <v>313</v>
+      </c>
+      <c r="D8" s="34" t="s">
+        <v>955</v>
+      </c>
+      <c r="E8" s="36" t="s">
+        <v>996</v>
+      </c>
+      <c r="F8" t="s">
+        <v>1003</v>
+      </c>
+      <c r="G8" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="H8" s="37" t="s">
+        <v>219</v>
+      </c>
+      <c r="I8" s="36" t="s">
+        <v>20</v>
+      </c>
+      <c r="M8" s="34" t="s">
+        <v>979</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="C9">
+        <v>314</v>
+      </c>
+      <c r="D9" s="35" t="s">
+        <v>956</v>
+      </c>
+      <c r="E9" s="38" t="s">
+        <v>996</v>
+      </c>
+      <c r="F9" t="s">
+        <v>1004</v>
+      </c>
+      <c r="G9" s="38" t="s">
+        <v>18</v>
+      </c>
+      <c r="H9" s="39" t="s">
+        <v>316</v>
+      </c>
+      <c r="I9" s="38" t="s">
+        <v>20</v>
+      </c>
+      <c r="M9" s="35" t="s">
+        <v>980</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="C10">
+        <v>315</v>
+      </c>
+      <c r="D10" s="34" t="s">
+        <v>957</v>
+      </c>
+      <c r="E10" s="36" t="s">
+        <v>996</v>
+      </c>
+      <c r="F10" t="s">
+        <v>1005</v>
+      </c>
+      <c r="G10" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="H10" s="37" t="s">
+        <v>143</v>
+      </c>
+      <c r="I10" s="36" t="s">
+        <v>20</v>
+      </c>
+      <c r="M10" s="34" t="s">
+        <v>981</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="C11">
+        <v>316</v>
+      </c>
+      <c r="D11" s="35" t="s">
+        <v>958</v>
+      </c>
+      <c r="E11" s="38" t="s">
+        <v>996</v>
+      </c>
+      <c r="F11" t="s">
+        <v>1006</v>
+      </c>
+      <c r="G11" s="38" t="s">
+        <v>18</v>
+      </c>
+      <c r="H11" s="39" t="s">
+        <v>215</v>
+      </c>
+      <c r="I11" s="38" t="s">
+        <v>20</v>
+      </c>
+      <c r="M11" s="35" t="s">
+        <v>982</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="C12">
+        <v>317</v>
+      </c>
+      <c r="D12" s="34" t="s">
+        <v>959</v>
+      </c>
+      <c r="E12" s="36" t="s">
+        <v>996</v>
+      </c>
+      <c r="F12" t="s">
+        <v>1007</v>
+      </c>
+      <c r="G12" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="H12" s="37" t="s">
+        <v>215</v>
+      </c>
+      <c r="I12" s="36" t="s">
+        <v>20</v>
+      </c>
+      <c r="M12" s="34" t="s">
+        <v>983</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="C13">
+        <v>318</v>
+      </c>
+      <c r="D13" s="35" t="s">
+        <v>960</v>
+      </c>
+      <c r="E13" s="38" t="s">
+        <v>996</v>
+      </c>
+      <c r="F13" t="s">
+        <v>1008</v>
+      </c>
+      <c r="G13" s="38" t="s">
+        <v>18</v>
+      </c>
+      <c r="H13" s="39" t="s">
+        <v>215</v>
+      </c>
+      <c r="I13" s="38" t="s">
+        <v>20</v>
+      </c>
+      <c r="M13" s="35" t="s">
+        <v>984</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="C14">
+        <v>319</v>
+      </c>
+      <c r="D14" s="34" t="s">
+        <v>961</v>
+      </c>
+      <c r="E14" s="36" t="s">
+        <v>996</v>
+      </c>
+      <c r="F14" t="s">
+        <v>1009</v>
+      </c>
+      <c r="G14" s="36" t="s">
+        <v>30</v>
+      </c>
+      <c r="H14" s="37" t="s">
+        <v>215</v>
+      </c>
+      <c r="I14" s="36" t="s">
+        <v>144</v>
+      </c>
+      <c r="M14" s="34" t="s">
+        <v>985</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="C15">
+        <v>320</v>
+      </c>
+      <c r="D15" s="35" t="s">
+        <v>288</v>
+      </c>
+      <c r="E15" s="38" t="s">
+        <v>996</v>
+      </c>
+      <c r="F15" t="s">
+        <v>1010</v>
+      </c>
+      <c r="G15" s="38" t="s">
+        <v>564</v>
+      </c>
+      <c r="H15" s="39" t="s">
+        <v>971</v>
+      </c>
+      <c r="I15" s="38" t="s">
+        <v>20</v>
+      </c>
+      <c r="M15" s="35" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="C16">
+        <v>321</v>
+      </c>
+      <c r="D16" s="34" t="s">
+        <v>962</v>
+      </c>
+      <c r="E16" s="36" t="s">
+        <v>996</v>
+      </c>
+      <c r="F16" t="s">
+        <v>1011</v>
+      </c>
+      <c r="G16" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="H16" s="37" t="s">
+        <v>215</v>
+      </c>
+      <c r="I16" s="36" t="s">
+        <v>20</v>
+      </c>
+      <c r="M16" s="34" t="s">
+        <v>987</v>
+      </c>
+    </row>
+    <row r="17" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="C17">
+        <v>322</v>
+      </c>
+      <c r="D17" s="35" t="s">
+        <v>963</v>
+      </c>
+      <c r="E17" s="38" t="s">
+        <v>996</v>
+      </c>
+      <c r="F17" t="s">
+        <v>1012</v>
+      </c>
+      <c r="G17" s="38" t="s">
+        <v>30</v>
+      </c>
+      <c r="H17" s="39" t="s">
+        <v>215</v>
+      </c>
+      <c r="I17" s="38" t="s">
+        <v>144</v>
+      </c>
+      <c r="M17" s="35" t="s">
+        <v>988</v>
+      </c>
+    </row>
+    <row r="18" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="C18">
+        <v>323</v>
+      </c>
+      <c r="D18" s="34" t="s">
+        <v>964</v>
+      </c>
+      <c r="E18" s="36" t="s">
+        <v>996</v>
+      </c>
+      <c r="F18" t="s">
+        <v>1013</v>
+      </c>
+      <c r="G18" s="38" t="s">
+        <v>30</v>
+      </c>
+      <c r="H18" s="37" t="s">
+        <v>972</v>
+      </c>
+      <c r="I18" s="36" t="s">
+        <v>144</v>
+      </c>
+      <c r="M18" s="34" t="s">
+        <v>989</v>
+      </c>
+    </row>
+    <row r="19" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="C19">
+        <v>324</v>
+      </c>
+      <c r="D19" s="35" t="s">
+        <v>965</v>
+      </c>
+      <c r="E19" s="38" t="s">
+        <v>996</v>
+      </c>
+      <c r="F19" t="s">
+        <v>1014</v>
+      </c>
+      <c r="G19" s="38" t="s">
+        <v>30</v>
+      </c>
+      <c r="H19" s="39" t="s">
+        <v>150</v>
+      </c>
+      <c r="I19" s="38" t="s">
+        <v>144</v>
+      </c>
+      <c r="M19" s="35" t="s">
+        <v>990</v>
+      </c>
+    </row>
+    <row r="20" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="C20">
+        <v>325</v>
+      </c>
+      <c r="D20" s="34" t="s">
+        <v>966</v>
+      </c>
+      <c r="E20" s="36" t="s">
+        <v>996</v>
+      </c>
+      <c r="F20" t="s">
+        <v>1015</v>
+      </c>
+      <c r="G20" s="38" t="s">
+        <v>30</v>
+      </c>
+      <c r="H20" s="37" t="s">
+        <v>215</v>
+      </c>
+      <c r="I20" s="36" t="s">
+        <v>144</v>
+      </c>
+      <c r="M20" s="34" t="s">
+        <v>991</v>
+      </c>
+    </row>
+    <row r="21" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="C21">
+        <v>326</v>
+      </c>
+      <c r="D21" s="35" t="s">
+        <v>967</v>
+      </c>
+      <c r="E21" s="38" t="s">
+        <v>996</v>
+      </c>
+      <c r="F21" t="s">
+        <v>1016</v>
+      </c>
+      <c r="G21" s="38" t="s">
+        <v>30</v>
+      </c>
+      <c r="H21" s="39" t="s">
+        <v>316</v>
+      </c>
+      <c r="I21" s="38" t="s">
+        <v>144</v>
+      </c>
+      <c r="M21" s="35" t="s">
+        <v>992</v>
+      </c>
+    </row>
+    <row r="22" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="C22">
+        <v>327</v>
+      </c>
+      <c r="D22" s="34" t="s">
+        <v>968</v>
+      </c>
+      <c r="E22" s="36" t="s">
+        <v>996</v>
+      </c>
+      <c r="F22" t="s">
+        <v>1017</v>
+      </c>
+      <c r="G22" s="38" t="s">
+        <v>30</v>
+      </c>
+      <c r="H22" s="37" t="s">
+        <v>316</v>
+      </c>
+      <c r="I22" s="36" t="s">
+        <v>144</v>
+      </c>
+      <c r="M22" s="34" t="s">
+        <v>993</v>
+      </c>
+    </row>
+    <row r="23" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="C23">
+        <v>328</v>
+      </c>
+      <c r="D23" s="35" t="s">
+        <v>969</v>
+      </c>
+      <c r="E23" s="38" t="s">
+        <v>996</v>
+      </c>
+      <c r="F23" t="s">
+        <v>1018</v>
+      </c>
+      <c r="G23" s="38" t="s">
+        <v>30</v>
+      </c>
+      <c r="H23" s="39" t="s">
+        <v>316</v>
+      </c>
+      <c r="I23" s="38" t="s">
+        <v>144</v>
+      </c>
+      <c r="M23" s="35" t="s">
+        <v>994</v>
+      </c>
+    </row>
+    <row r="24" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="C24">
+        <v>329</v>
+      </c>
+      <c r="D24" s="34" t="s">
+        <v>970</v>
+      </c>
+      <c r="E24" s="36" t="s">
+        <v>996</v>
+      </c>
+      <c r="F24" t="s">
+        <v>1019</v>
+      </c>
+      <c r="G24" s="38" t="s">
+        <v>30</v>
+      </c>
+      <c r="H24" s="37" t="s">
+        <v>143</v>
+      </c>
+      <c r="I24" s="36" t="s">
+        <v>144</v>
+      </c>
+      <c r="M24" s="34" t="s">
+        <v>995</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/docs/CDOP_SCHEMA.xlsx
+++ b/docs/CDOP_SCHEMA.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rockmtnins-my.sharepoint.com/personal/sebastian_weeks_rmi_org/Documents/Documents/CDOP Resources/UseCase_Category CSVs_JSONs/Master Version/Round 2 Pods for Testing/Fast Track Pods/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rockmtnins-my.sharepoint.com/personal/sebastian_weeks_rmi_org/Documents/Documents/CDOP Resources/UseCase_Category CSVs_JSONs/Master Version/8_25_26/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="472" documentId="8_{E4888AF0-8469-49B9-BF1F-D7429471A122}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{805E69B9-42B6-4388-969F-9DB549C29CA3}"/>
+  <xr:revisionPtr revIDLastSave="118" documentId="8_{E4888AF0-8469-49B9-BF1F-D7429471A122}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{51AF62E9-238E-47E0-BF18-8C0C7E464784}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="3" xr2:uid="{743398AF-A4FE-47C4-9368-972E95242EBF}"/>
+    <workbookView xWindow="-28215" yWindow="375" windowWidth="27555" windowHeight="15045" activeTab="11" xr2:uid="{743398AF-A4FE-47C4-9368-972E95242EBF}"/>
   </bookViews>
   <sheets>
     <sheet name="Full List" sheetId="5" r:id="rId1"/>
@@ -25,9 +25,6 @@
     <sheet name="Durability_Permanence" sheetId="10" r:id="rId10"/>
     <sheet name="Project Finance" sheetId="11" r:id="rId11"/>
     <sheet name="Labels_Certifications" sheetId="12" r:id="rId12"/>
-    <sheet name="Registry_Metadata" sheetId="13" r:id="rId13"/>
-    <sheet name="Validation_Metadata" sheetId="14" r:id="rId14"/>
-    <sheet name="Verification_Metadata" sheetId="15" r:id="rId15"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Full List'!$A$1:$M$174</definedName>
@@ -53,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7098" uniqueCount="1020">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6394" uniqueCount="824">
   <si>
     <t>schema</t>
   </si>
@@ -2566,602 +2563,14 @@
     <t>project.project_level[].project_level_compliance_potential_eligibility</t>
   </si>
   <si>
-    <t>crediting program</t>
-  </si>
-  <si>
-    <t>Describes the current registry, that contains the information about the project, and units</t>
-  </si>
-  <si>
-    <t>Describes the first registry, where the project was registered</t>
-  </si>
-  <si>
-    <t>Describes the Crediting Program that the proejct is following for the implementationunits</t>
-  </si>
-  <si>
-    <t>Date of the last update</t>
-  </si>
-  <si>
-    <t>registry_identifier</t>
-  </si>
-  <si>
-    <t>registry_name</t>
-  </si>
-  <si>
-    <t>registry_link</t>
-  </si>
-  <si>
-    <t>original_registry_identifier</t>
-  </si>
-  <si>
-    <t>original_registry_name</t>
-  </si>
-  <si>
-    <t>original_registry_link</t>
-  </si>
-  <si>
-    <t>program_identifier</t>
-  </si>
-  <si>
-    <t>program_name</t>
-  </si>
-  <si>
-    <t>creation_date</t>
-  </si>
-  <si>
-    <t>update_date</t>
-  </si>
-  <si>
-    <t>Date that the project was first registered</t>
-  </si>
-  <si>
-    <t>registry.creation_date</t>
-  </si>
-  <si>
-    <t>registry.update_date</t>
-  </si>
-  <si>
-    <t>registry.identification[].registry_identifier</t>
-  </si>
-  <si>
-    <t>registry.identification[].registry_name</t>
-  </si>
-  <si>
-    <t>registry.identification[].registry_link</t>
-  </si>
-  <si>
-    <t>registry.original[].original_registry_identifier</t>
-  </si>
-  <si>
-    <t>registry.original[].original_registry_name</t>
-  </si>
-  <si>
-    <t>registry.original[].original_registry_link</t>
-  </si>
-  <si>
-    <t>registry.program[].program_identifier</t>
-  </si>
-  <si>
-    <t>registry.program[].program_name</t>
-  </si>
-  <si>
-    <t>current_validation_stage</t>
-  </si>
-  <si>
-    <t>current_validation_stage_status</t>
-  </si>
-  <si>
-    <t>date_previous_validation</t>
-  </si>
-  <si>
-    <t>date_validation_expiration</t>
-  </si>
-  <si>
-    <t>date_validation_planned</t>
-  </si>
-  <si>
-    <t>date_validation_requested</t>
-  </si>
-  <si>
-    <t>validation_body_accreditation</t>
-  </si>
-  <si>
-    <t>validation_body_id</t>
-  </si>
-  <si>
-    <t>validator_name</t>
-  </si>
-  <si>
-    <t>validation_body_sectoral_scopes</t>
-  </si>
-  <si>
-    <t>validation_body_selection</t>
-  </si>
-  <si>
-    <t>validation_body_team_members_and_roles</t>
-  </si>
-  <si>
-    <t>validation_is_planned</t>
-  </si>
-  <si>
-    <t>validation_period_end_date</t>
-  </si>
-  <si>
-    <t>validation_period_start_date</t>
-  </si>
-  <si>
-    <t>validation_report_link</t>
-  </si>
-  <si>
-    <t>validation_report_summary</t>
-  </si>
-  <si>
-    <t>validation_stage_description</t>
-  </si>
-  <si>
-    <t>validation_stage_document_link</t>
-  </si>
-  <si>
-    <t>validation_stages</t>
-  </si>
-  <si>
-    <t>validation_status</t>
-  </si>
-  <si>
-    <t>validation_report_version</t>
-  </si>
-  <si>
-    <t>Validation and Verification Body (VVB)/ Certification Bodies/ Third Party Auditors</t>
-  </si>
-  <si>
-    <t>Name of the current validation step</t>
-  </si>
-  <si>
-    <t>Status of the current validation step</t>
-  </si>
-  <si>
-    <t>Date of the previous validation event</t>
-  </si>
-  <si>
-    <t>Date validation expires</t>
-  </si>
-  <si>
-    <t>Planned date of the validation event</t>
-  </si>
-  <si>
-    <t>Date validation was requested</t>
-  </si>
-  <si>
-    <t>LCA has been completed</t>
-  </si>
-  <si>
-    <t>LCA is used to quantify emissions</t>
-  </si>
-  <si>
-    <t>Link to LCA report</t>
-  </si>
-  <si>
-    <t>Link to LCA repository</t>
-  </si>
-  <si>
-    <t>LCA results</t>
-  </si>
-  <si>
-    <t>Link to LCA system boundary figure</t>
-  </si>
-  <si>
-    <t>Overview description of LCA system boundary</t>
-  </si>
-  <si>
-    <t>Identification number of the validation event.</t>
-  </si>
-  <si>
-    <t>Type of validation being carried out</t>
-  </si>
-  <si>
-    <t>List any accreditations of the validation body</t>
-  </si>
-  <si>
-    <t>Identification number of the validation body</t>
-  </si>
-  <si>
-    <t>Name of the validation body</t>
-  </si>
-  <si>
-    <t>Name(s) of the validator(s)</t>
-  </si>
-  <si>
-    <t>List the sectoral scopes the validation body is accredited to validate</t>
-  </si>
-  <si>
-    <t>Describe how the validation body was selected</t>
-  </si>
-  <si>
-    <t>List the names of any other validation body team members and their roles (FIRST NAME - LAST NAME, ROLE)</t>
-  </si>
-  <si>
-    <t>Date of validation event</t>
-  </si>
-  <si>
-    <t>Indicate whether the valiation event is planned.</t>
-  </si>
-  <si>
-    <t>End date of the validation event. Estimate if needed.</t>
-  </si>
-  <si>
-    <t>Start date of the validation event</t>
-  </si>
-  <si>
-    <t>Link (URL) to the project's validation report (if applicable).</t>
-  </si>
-  <si>
-    <t>Enter the validation report's summary</t>
-  </si>
-  <si>
-    <t>Describe the stages of the validation event.</t>
-  </si>
-  <si>
-    <t>Link (URL) to the document that contains the description and details of the validation event stages</t>
-  </si>
-  <si>
-    <t>Select all validation event stages</t>
-  </si>
-  <si>
-    <t>Indicate whether the project has been validated.</t>
-  </si>
-  <si>
-    <t>Which version of the validation report is the current version</t>
-  </si>
-  <si>
-    <t>lca_completed</t>
-  </si>
-  <si>
-    <t>lca_emissions_quantification</t>
-  </si>
-  <si>
-    <t>lca_link</t>
-  </si>
-  <si>
-    <t>lca_repository</t>
-  </si>
-  <si>
-    <t>lca_results</t>
-  </si>
-  <si>
-    <t>lca_system_boundary_figure</t>
-  </si>
-  <si>
-    <t>lca_system_boundary_overview</t>
-  </si>
-  <si>
-    <t>validation_body</t>
-  </si>
-  <si>
-    <t>validation.crediting_period[].current_crediting_period_end_date</t>
-  </si>
-  <si>
-    <t>project.validation_stage[].current_validation_stage</t>
-  </si>
-  <si>
-    <t>validation.stage[].validation_stage_document_link</t>
-  </si>
-  <si>
-    <t>validation.crediting_period[].current_crediting_period_number</t>
-  </si>
-  <si>
-    <t>project.validation_stage[].current_validation_stage_status</t>
-  </si>
-  <si>
-    <t>validation.crediting_period[].current_crediting_period_start_date</t>
-  </si>
-  <si>
-    <t>project.date[].date_previous_validation</t>
-  </si>
-  <si>
-    <t>validation.date[].date_validation_expiration</t>
-  </si>
-  <si>
-    <t>validation.date[].date_validation_planned</t>
-  </si>
-  <si>
-    <t>validation.date[].date_validation_requested</t>
-  </si>
-  <si>
-    <t>validation.lca[].lca_completed</t>
-  </si>
-  <si>
-    <t>validation.lca[].lca_emissions_quantification</t>
-  </si>
-  <si>
-    <t>validation.lca[].lca_link</t>
-  </si>
-  <si>
-    <t>validation.lca[].lca_repository</t>
-  </si>
-  <si>
-    <t>validation.lca[].lca_results</t>
-  </si>
-  <si>
-    <t>validation.lca[].lca_system_boundary_figure</t>
-  </si>
-  <si>
-    <t>validation.lca[].lca_system_boundary_overview</t>
-  </si>
-  <si>
-    <t>validation.validation_event[].validation _id</t>
-  </si>
-  <si>
-    <t>validation.validation_event[].validation_type</t>
-  </si>
-  <si>
-    <t>validation.validation_event[].validation_date</t>
-  </si>
-  <si>
-    <t>validation.validation_event[].validation_is_planned</t>
-  </si>
-  <si>
-    <t>validation.validation_event[].validation_period_end_date</t>
-  </si>
-  <si>
-    <t>validation.validation_event[].validation_period_start_date</t>
-  </si>
-  <si>
-    <t>validation.report[].validation_report_link</t>
-  </si>
-  <si>
-    <t>project.validation_status</t>
-  </si>
-  <si>
-    <t>validation.report[].validation_report_summary</t>
-  </si>
-  <si>
-    <t>validation.stage[].validation_stage_description</t>
-  </si>
-  <si>
-    <t>validation.stage[].validation_stages</t>
-  </si>
-  <si>
-    <t>validation.report[].validation_report_version</t>
-  </si>
-  <si>
-    <t>validation_body.details[].validation_body_accreditation</t>
-  </si>
-  <si>
-    <t>validation_body.details[].validation_body_id</t>
-  </si>
-  <si>
-    <t>validation_body.details[].validation_body_name</t>
-  </si>
-  <si>
-    <t>validation_body.details[].validator_name</t>
-  </si>
-  <si>
-    <t>validation_body.details[].validation_body_sectoral_scopes</t>
-  </si>
-  <si>
-    <t>validation_body.details[].validation_body_selection</t>
-  </si>
-  <si>
-    <t>validation_body.details[].validation_body_team_members_and_roles</t>
-  </si>
-  <si>
-    <t>verification_id</t>
-  </si>
-  <si>
-    <t>verification_claim_type</t>
-  </si>
-  <si>
-    <t>verification_project_id</t>
-  </si>
-  <si>
-    <t>verification_description</t>
-  </si>
-  <si>
-    <t>verification_reporting_period_start</t>
-  </si>
-  <si>
-    <t>verification_reporting_period_end</t>
-  </si>
-  <si>
-    <t>verification_date</t>
-  </si>
-  <si>
-    <t>verified_quantity</t>
-  </si>
-  <si>
-    <t>verification_quantity_uom</t>
-  </si>
-  <si>
-    <t>verification_body_name</t>
-  </si>
-  <si>
-    <t>verification_body_id</t>
-  </si>
-  <si>
-    <t>verification_applied_standard</t>
-  </si>
-  <si>
-    <t>verification_applied_methodology_protocol</t>
-  </si>
-  <si>
-    <t>verification_credential_issuer_id</t>
-  </si>
-  <si>
-    <t>verification_cryptographic_proof_type</t>
-  </si>
-  <si>
-    <t>verification_digital_signature_payload</t>
-  </si>
-  <si>
-    <t>verification_leakage_risk_mitigation</t>
-  </si>
-  <si>
-    <t>verification_leakage_risk_mitigation_strategy</t>
-  </si>
-  <si>
-    <t>verification_leakage_deduction_quantity</t>
-  </si>
-  <si>
-    <t>verification_uncertainty_deduction_margin</t>
-  </si>
-  <si>
-    <t>verification_buffer_pool_deduction_quantity</t>
-  </si>
-  <si>
-    <t>verification_audit_checkpoint_status</t>
-  </si>
-  <si>
-    <t>URI</t>
-  </si>
-  <si>
-    <t>Object/String</t>
-  </si>
-  <si>
-    <t>A globally unique identifier for the specific verification event or claim.</t>
-  </si>
-  <si>
-    <t>The classification of the claim being verified (e.g., CARBON_REMOVAL, EMISSION_REDUCTION, BIODIVERSITY).</t>
-  </si>
-  <si>
-    <t>The unique ID of the underlying project registered on the host registry.</t>
-  </si>
-  <si>
-    <t>A concise, human-readable summary of the verification scope and findings.</t>
-  </si>
-  <si>
-    <t>The start date of the monitoring/reporting period being verified.</t>
-  </si>
-  <si>
-    <t>The end date of the monitoring/reporting period being verified.</t>
-  </si>
-  <si>
-    <t>The official date the verification process was completed and signed off.</t>
-  </si>
-  <si>
-    <t>The final, audited, and verified net volume for this specific reporting period.</t>
-  </si>
-  <si>
-    <t>The Unit of Measure for the verified quantity (e.g., tCO2e, m3_biogas).</t>
-  </si>
-  <si>
-    <t>The official name of the third-party auditing entity/VVB.</t>
-  </si>
-  <si>
-    <t>The decentralized identifier (DID) or registry ID of the verification body.</t>
-  </si>
-  <si>
-    <t>The overarching registry framework (e.g., Verra_VCS_v4.5, Gold_Standard).</t>
-  </si>
-  <si>
-    <t>The specific methodology version applied (e.g., VM0047_v1.0, CAR_Soil_v1.1).</t>
-  </si>
-  <si>
-    <t>The direct, secure hyperlink to the official public verification report PDF.</t>
-  </si>
-  <si>
-    <t>The decentralized identifier (DID) of the entity issuing the digital verification token.</t>
-  </si>
-  <si>
-    <t>The security protocol used (e.g., Ed25519Signature2020, JSON-LD).</t>
-  </si>
-  <si>
-    <t>The actual cryptographic signature, payload hash, or verifiable presentation metadata.</t>
-  </si>
-  <si>
-    <t>Indicates if leakage risk is accounted for on this verification event</t>
-  </si>
-  <si>
-    <t>links to or summarizes the mitigation strategy for this verification event</t>
-  </si>
-  <si>
-    <t>Volume deducted for this specific reporting period to account for leakage.</t>
-  </si>
-  <si>
-    <t>Percentage or absolute deduction applied for this specific reporting period for uncertainty.</t>
-  </si>
-  <si>
-    <t>Volume deducted for this specific reporting period and contributed to the buffer pool.</t>
-  </si>
-  <si>
-    <t>Summary result of the checklist (e.g., PASS, PASS_WITH_RESERVATIONS, FAIL).</t>
-  </si>
-  <si>
-    <t>verification</t>
-  </si>
-  <si>
-    <t>verification.identification[].verification_id</t>
-  </si>
-  <si>
-    <t>verification.identification[].verification_claim_type</t>
-  </si>
-  <si>
-    <t>verification.identification[].verification_project_id</t>
-  </si>
-  <si>
-    <t>verification.identification[].verification_description</t>
-  </si>
-  <si>
-    <t>verification.reporting[].verification_reporting_period_start</t>
-  </si>
-  <si>
-    <t>verification.reporting[].verification_reporting_period_end</t>
-  </si>
-  <si>
-    <t>verification.reporting[].verification_date</t>
-  </si>
-  <si>
-    <t>verification.quantity[].verified_quantity</t>
-  </si>
-  <si>
-    <t>verification.quantity[].verification_quantity_uom</t>
-  </si>
-  <si>
-    <t>verification.body[].verification_body_name</t>
-  </si>
-  <si>
-    <t>verification.body[].verification_body_id</t>
-  </si>
-  <si>
-    <t>verification.standard[].verification_applied_standard</t>
-  </si>
-  <si>
-    <t>verification.standard[].verification_applied_methodology_protocol</t>
-  </si>
-  <si>
-    <t>verification.verification_report_url</t>
-  </si>
-  <si>
-    <t>verification.verification_credential_issuer_id</t>
-  </si>
-  <si>
-    <t>verification.verification_cryptographic_proof_type</t>
-  </si>
-  <si>
-    <t>verification.verification_digital_signature_payload</t>
-  </si>
-  <si>
-    <t>verification.leakage[].verification_leakage_risk_mitigation</t>
-  </si>
-  <si>
-    <t>verification.leakage[].verification_leakage_risk_mitigation_strategy</t>
-  </si>
-  <si>
-    <t>verification.leakage[].verification_leakage_deduction_quantity</t>
-  </si>
-  <si>
-    <t>verification.verification_uncertainty_deduction_margin</t>
-  </si>
-  <si>
-    <t>verification.verification_buffer_pool_deduction_quantity</t>
-  </si>
-  <si>
-    <t>verification.verification_audit_checkpoint_status</t>
+    <t>crediting_program.carbon_standard_level_accreditation</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3256,15 +2665,8 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF434343"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="10">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3304,18 +2706,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6F8F9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3367,7 +2757,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -3429,27 +2819,6 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -16584,7 +15953,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:13" ht="16" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -16594,14 +15963,14 @@
       <c r="C2">
         <v>242</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="32" t="s">
         <v>763</v>
       </c>
       <c r="E2" s="6" t="s">
         <v>141</v>
       </c>
       <c r="F2" t="s">
-        <v>804</v>
+        <v>823</v>
       </c>
       <c r="G2" t="s">
         <v>30</v>
@@ -16625,7 +15994,7 @@
         <v>785</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:13" ht="16" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -16635,7 +16004,7 @@
       <c r="C3">
         <v>243</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="32" t="s">
         <v>764</v>
       </c>
       <c r="E3" s="6" t="s">
@@ -16666,7 +16035,7 @@
         <v>786</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:13" ht="16" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>13</v>
       </c>
@@ -16676,7 +16045,7 @@
       <c r="C4">
         <v>244</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="32" t="s">
         <v>765</v>
       </c>
       <c r="E4" s="6" t="s">
@@ -16707,7 +16076,7 @@
         <v>787</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:13" ht="16" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -16717,7 +16086,7 @@
       <c r="C5">
         <v>245</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="32" t="s">
         <v>766</v>
       </c>
       <c r="E5" s="6" t="s">
@@ -16748,7 +16117,7 @@
         <v>788</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:13" ht="16" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
         <v>13</v>
       </c>
@@ -16758,7 +16127,7 @@
       <c r="C6">
         <v>246</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D6" s="32" t="s">
         <v>767</v>
       </c>
       <c r="E6" s="6" t="s">
@@ -16789,7 +16158,7 @@
         <v>789</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:13" ht="16" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -16799,7 +16168,7 @@
       <c r="C7">
         <v>247</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="D7" s="32" t="s">
         <v>768</v>
       </c>
       <c r="E7" s="6" t="s">
@@ -16830,7 +16199,7 @@
         <v>790</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:13" ht="16" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
         <v>13</v>
       </c>
@@ -16840,7 +16209,7 @@
       <c r="C8">
         <v>248</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="D8" s="32" t="s">
         <v>769</v>
       </c>
       <c r="E8" s="6" t="s">
@@ -16871,7 +16240,7 @@
         <v>791</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:13" ht="16" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
         <v>13</v>
       </c>
@@ -16881,7 +16250,7 @@
       <c r="C9">
         <v>249</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="D9" s="32" t="s">
         <v>770</v>
       </c>
       <c r="E9" s="6" t="s">
@@ -16912,7 +16281,7 @@
         <v>792</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:13" ht="16" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
         <v>13</v>
       </c>
@@ -16922,7 +16291,7 @@
       <c r="C10">
         <v>250</v>
       </c>
-      <c r="D10" s="6" t="s">
+      <c r="D10" s="32" t="s">
         <v>771</v>
       </c>
       <c r="E10" s="6" t="s">
@@ -16953,7 +16322,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:13" ht="16" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
         <v>13</v>
       </c>
@@ -16963,7 +16332,7 @@
       <c r="C11">
         <v>251</v>
       </c>
-      <c r="D11" s="6" t="s">
+      <c r="D11" s="32" t="s">
         <v>772</v>
       </c>
       <c r="E11" s="6" t="s">
@@ -16994,7 +16363,7 @@
         <v>794</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:13" ht="16" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
         <v>13</v>
       </c>
@@ -17004,7 +16373,7 @@
       <c r="C12">
         <v>252</v>
       </c>
-      <c r="D12" s="6" t="s">
+      <c r="D12" s="32" t="s">
         <v>773</v>
       </c>
       <c r="E12" s="6" t="s">
@@ -17035,7 +16404,7 @@
         <v>795</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:13" ht="16" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
         <v>13</v>
       </c>
@@ -17045,7 +16414,7 @@
       <c r="C13">
         <v>253</v>
       </c>
-      <c r="D13" s="6" t="s">
+      <c r="D13" s="32" t="s">
         <v>774</v>
       </c>
       <c r="E13" s="6" t="s">
@@ -17076,7 +16445,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:13" ht="16" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
         <v>13</v>
       </c>
@@ -17086,7 +16455,7 @@
       <c r="C14">
         <v>254</v>
       </c>
-      <c r="D14" s="6" t="s">
+      <c r="D14" s="32" t="s">
         <v>775</v>
       </c>
       <c r="E14" s="6" t="s">
@@ -17117,7 +16486,7 @@
         <v>797</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:13" ht="16" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
         <v>13</v>
       </c>
@@ -17127,7 +16496,7 @@
       <c r="C15">
         <v>255</v>
       </c>
-      <c r="D15" s="6" t="s">
+      <c r="D15" s="32" t="s">
         <v>776</v>
       </c>
       <c r="E15" s="6" t="s">
@@ -17158,7 +16527,7 @@
         <v>798</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:13" ht="16" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
         <v>13</v>
       </c>
@@ -17168,7 +16537,7 @@
       <c r="C16">
         <v>256</v>
       </c>
-      <c r="D16" s="6" t="s">
+      <c r="D16" s="32" t="s">
         <v>777</v>
       </c>
       <c r="E16" s="6" t="s">
@@ -17199,7 +16568,7 @@
         <v>799</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:13" ht="16" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
         <v>13</v>
       </c>
@@ -17209,7 +16578,7 @@
       <c r="C17">
         <v>257</v>
       </c>
-      <c r="D17" s="6" t="s">
+      <c r="D17" s="32" t="s">
         <v>778</v>
       </c>
       <c r="E17" s="6" t="s">
@@ -17250,7 +16619,7 @@
       <c r="C18">
         <v>258</v>
       </c>
-      <c r="D18" s="6" t="s">
+      <c r="D18" s="32" t="s">
         <v>779</v>
       </c>
       <c r="E18" s="6" t="s">
@@ -17281,7 +16650,7 @@
         <v>801</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:13" ht="16" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
         <v>13</v>
       </c>
@@ -17291,7 +16660,7 @@
       <c r="C19">
         <v>259</v>
       </c>
-      <c r="D19" s="6" t="s">
+      <c r="D19" s="32" t="s">
         <v>780</v>
       </c>
       <c r="E19" s="6" t="s">
@@ -17322,7 +16691,7 @@
         <v>802</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:13" ht="16" x14ac:dyDescent="0.4">
       <c r="A20" t="s">
         <v>13</v>
       </c>
@@ -17332,7 +16701,7 @@
       <c r="C20">
         <v>260</v>
       </c>
-      <c r="D20" s="6" t="s">
+      <c r="D20" s="32" t="s">
         <v>781</v>
       </c>
       <c r="E20" s="6" t="s">
@@ -17365,2536 +16734,6 @@
     </row>
   </sheetData>
   <phoneticPr fontId="12" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5DD793A8-CD91-4786-8377-89E3BC40F96B}">
-  <dimension ref="A1:M11"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="2" max="2" width="8.54296875" customWidth="1"/>
-    <col min="4" max="4" width="30.6328125" customWidth="1"/>
-    <col min="5" max="5" width="15.90625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="52.81640625" customWidth="1"/>
-    <col min="7" max="7" width="9.81640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12" customWidth="1"/>
-    <col min="9" max="9" width="16.6328125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.1796875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.90625" customWidth="1"/>
-    <col min="12" max="12" width="13.1796875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="35.08984375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="23" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>523</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B2" t="s">
-        <v>275</v>
-      </c>
-      <c r="C2">
-        <v>261</v>
-      </c>
-      <c r="D2" s="25" t="s">
-        <v>828</v>
-      </c>
-      <c r="E2" t="s">
-        <v>116</v>
-      </c>
-      <c r="F2" t="s">
-        <v>841</v>
-      </c>
-      <c r="G2" s="25" t="s">
-        <v>18</v>
-      </c>
-      <c r="H2" s="25" t="s">
-        <v>392</v>
-      </c>
-      <c r="I2" t="s">
-        <v>226</v>
-      </c>
-      <c r="J2" t="s">
-        <v>116</v>
-      </c>
-      <c r="L2" t="s">
-        <v>146</v>
-      </c>
-      <c r="M2" s="18" t="s">
-        <v>824</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B3" t="s">
-        <v>275</v>
-      </c>
-      <c r="C3">
-        <v>262</v>
-      </c>
-      <c r="D3" s="25" t="s">
-        <v>829</v>
-      </c>
-      <c r="E3" t="s">
-        <v>116</v>
-      </c>
-      <c r="F3" t="s">
-        <v>842</v>
-      </c>
-      <c r="G3" s="25" t="s">
-        <v>18</v>
-      </c>
-      <c r="H3" s="25" t="s">
-        <v>159</v>
-      </c>
-      <c r="I3" t="s">
-        <v>226</v>
-      </c>
-      <c r="J3" t="s">
-        <v>116</v>
-      </c>
-      <c r="L3" t="s">
-        <v>146</v>
-      </c>
-      <c r="M3" s="18" t="s">
-        <v>824</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B4" t="s">
-        <v>275</v>
-      </c>
-      <c r="C4">
-        <v>263</v>
-      </c>
-      <c r="D4" s="25" t="s">
-        <v>830</v>
-      </c>
-      <c r="E4" t="s">
-        <v>116</v>
-      </c>
-      <c r="F4" t="s">
-        <v>843</v>
-      </c>
-      <c r="G4" s="25" t="s">
-        <v>18</v>
-      </c>
-      <c r="H4" s="25" t="s">
-        <v>159</v>
-      </c>
-      <c r="I4" t="s">
-        <v>226</v>
-      </c>
-      <c r="J4" t="s">
-        <v>116</v>
-      </c>
-      <c r="L4" t="s">
-        <v>146</v>
-      </c>
-      <c r="M4" s="18" t="s">
-        <v>824</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" t="s">
-        <v>275</v>
-      </c>
-      <c r="C5">
-        <v>264</v>
-      </c>
-      <c r="D5" s="25" t="s">
-        <v>831</v>
-      </c>
-      <c r="E5" t="s">
-        <v>116</v>
-      </c>
-      <c r="F5" t="s">
-        <v>844</v>
-      </c>
-      <c r="G5" s="25" t="s">
-        <v>18</v>
-      </c>
-      <c r="H5" s="25" t="s">
-        <v>392</v>
-      </c>
-      <c r="I5" t="s">
-        <v>226</v>
-      </c>
-      <c r="J5" t="s">
-        <v>116</v>
-      </c>
-      <c r="L5" t="s">
-        <v>146</v>
-      </c>
-      <c r="M5" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" t="s">
-        <v>275</v>
-      </c>
-      <c r="C6">
-        <v>265</v>
-      </c>
-      <c r="D6" s="25" t="s">
-        <v>832</v>
-      </c>
-      <c r="E6" t="s">
-        <v>116</v>
-      </c>
-      <c r="F6" t="s">
-        <v>845</v>
-      </c>
-      <c r="G6" s="25" t="s">
-        <v>18</v>
-      </c>
-      <c r="H6" s="25" t="s">
-        <v>159</v>
-      </c>
-      <c r="I6" t="s">
-        <v>226</v>
-      </c>
-      <c r="J6" t="s">
-        <v>116</v>
-      </c>
-      <c r="L6" t="s">
-        <v>146</v>
-      </c>
-      <c r="M6" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>13</v>
-      </c>
-      <c r="B7" t="s">
-        <v>275</v>
-      </c>
-      <c r="C7">
-        <v>266</v>
-      </c>
-      <c r="D7" s="25" t="s">
-        <v>833</v>
-      </c>
-      <c r="E7" t="s">
-        <v>116</v>
-      </c>
-      <c r="F7" t="s">
-        <v>846</v>
-      </c>
-      <c r="G7" s="25" t="s">
-        <v>18</v>
-      </c>
-      <c r="H7" s="25" t="s">
-        <v>159</v>
-      </c>
-      <c r="I7" t="s">
-        <v>226</v>
-      </c>
-      <c r="J7" t="s">
-        <v>116</v>
-      </c>
-      <c r="L7" t="s">
-        <v>146</v>
-      </c>
-      <c r="M7" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>13</v>
-      </c>
-      <c r="B8" t="s">
-        <v>275</v>
-      </c>
-      <c r="C8">
-        <v>267</v>
-      </c>
-      <c r="D8" s="25" t="s">
-        <v>834</v>
-      </c>
-      <c r="E8" t="s">
-        <v>116</v>
-      </c>
-      <c r="F8" t="s">
-        <v>847</v>
-      </c>
-      <c r="G8" s="25" t="s">
-        <v>18</v>
-      </c>
-      <c r="H8" s="25" t="s">
-        <v>392</v>
-      </c>
-      <c r="I8" t="s">
-        <v>226</v>
-      </c>
-      <c r="J8" t="s">
-        <v>823</v>
-      </c>
-      <c r="L8" t="s">
-        <v>146</v>
-      </c>
-      <c r="M8" s="18" t="s">
-        <v>826</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>13</v>
-      </c>
-      <c r="B9" t="s">
-        <v>275</v>
-      </c>
-      <c r="C9">
-        <v>268</v>
-      </c>
-      <c r="D9" s="25" t="s">
-        <v>835</v>
-      </c>
-      <c r="E9" t="s">
-        <v>116</v>
-      </c>
-      <c r="F9" t="s">
-        <v>848</v>
-      </c>
-      <c r="G9" s="25" t="s">
-        <v>18</v>
-      </c>
-      <c r="H9" s="25" t="s">
-        <v>159</v>
-      </c>
-      <c r="I9" t="s">
-        <v>226</v>
-      </c>
-      <c r="J9" t="s">
-        <v>823</v>
-      </c>
-      <c r="L9" t="s">
-        <v>146</v>
-      </c>
-      <c r="M9" s="18" t="s">
-        <v>826</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
-        <v>13</v>
-      </c>
-      <c r="B10" t="s">
-        <v>275</v>
-      </c>
-      <c r="C10">
-        <v>269</v>
-      </c>
-      <c r="D10" s="25" t="s">
-        <v>836</v>
-      </c>
-      <c r="E10" t="s">
-        <v>116</v>
-      </c>
-      <c r="F10" t="s">
-        <v>839</v>
-      </c>
-      <c r="G10" s="25" t="s">
-        <v>18</v>
-      </c>
-      <c r="H10" s="25" t="s">
-        <v>219</v>
-      </c>
-      <c r="I10" t="s">
-        <v>226</v>
-      </c>
-      <c r="L10" t="s">
-        <v>146</v>
-      </c>
-      <c r="M10" s="18" t="s">
-        <v>838</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
-        <v>13</v>
-      </c>
-      <c r="B11" t="s">
-        <v>275</v>
-      </c>
-      <c r="C11">
-        <v>270</v>
-      </c>
-      <c r="D11" s="25" t="s">
-        <v>837</v>
-      </c>
-      <c r="E11" t="s">
-        <v>116</v>
-      </c>
-      <c r="F11" t="s">
-        <v>840</v>
-      </c>
-      <c r="G11" s="25" t="s">
-        <v>30</v>
-      </c>
-      <c r="H11" s="25" t="s">
-        <v>219</v>
-      </c>
-      <c r="I11" t="s">
-        <v>31</v>
-      </c>
-      <c r="L11" t="s">
-        <v>146</v>
-      </c>
-      <c r="M11" s="18" t="s">
-        <v>827</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF337E51-0D9D-46A6-9DB2-8DF5F9FC1667}">
-  <dimension ref="A1:M37"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="4" max="4" width="43.6328125" customWidth="1"/>
-    <col min="5" max="5" width="15.90625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="58.453125" customWidth="1"/>
-    <col min="7" max="7" width="9.81640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.90625" customWidth="1"/>
-    <col min="9" max="9" width="16.6328125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.1796875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.26953125" customWidth="1"/>
-    <col min="12" max="12" width="13.1796875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="49.90625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="23" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>523</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B2" t="s">
-        <v>275</v>
-      </c>
-      <c r="C2">
-        <v>271</v>
-      </c>
-      <c r="D2" s="33" t="s">
-        <v>481</v>
-      </c>
-      <c r="E2" s="33" t="s">
-        <v>266</v>
-      </c>
-      <c r="F2" t="s">
-        <v>913</v>
-      </c>
-      <c r="G2" s="33" t="s">
-        <v>18</v>
-      </c>
-      <c r="H2" s="33" t="s">
-        <v>219</v>
-      </c>
-      <c r="I2" s="33" t="s">
-        <v>20</v>
-      </c>
-      <c r="J2" s="6" t="s">
-        <v>445</v>
-      </c>
-      <c r="L2" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="M2" s="6" t="s">
-        <v>482</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B3" t="s">
-        <v>275</v>
-      </c>
-      <c r="C3">
-        <v>272</v>
-      </c>
-      <c r="D3" s="33" t="s">
-        <v>483</v>
-      </c>
-      <c r="E3" s="33" t="s">
-        <v>266</v>
-      </c>
-      <c r="F3" t="s">
-        <v>916</v>
-      </c>
-      <c r="G3" s="33" t="s">
-        <v>18</v>
-      </c>
-      <c r="H3" s="33" t="s">
-        <v>392</v>
-      </c>
-      <c r="I3" s="33" t="s">
-        <v>20</v>
-      </c>
-      <c r="J3" s="6" t="s">
-        <v>445</v>
-      </c>
-      <c r="L3" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="M3" s="6" t="s">
-        <v>484</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B4" t="s">
-        <v>275</v>
-      </c>
-      <c r="C4">
-        <v>273</v>
-      </c>
-      <c r="D4" s="33" t="s">
-        <v>479</v>
-      </c>
-      <c r="E4" s="33" t="s">
-        <v>266</v>
-      </c>
-      <c r="F4" t="s">
-        <v>918</v>
-      </c>
-      <c r="G4" s="33" t="s">
-        <v>18</v>
-      </c>
-      <c r="H4" s="33" t="s">
-        <v>219</v>
-      </c>
-      <c r="I4" s="33" t="s">
-        <v>20</v>
-      </c>
-      <c r="J4" s="6" t="s">
-        <v>445</v>
-      </c>
-      <c r="L4" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="M4" s="6" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" t="s">
-        <v>275</v>
-      </c>
-      <c r="C5">
-        <v>274</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>849</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="F5" t="s">
-        <v>914</v>
-      </c>
-      <c r="G5" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="H5" s="6" t="s">
-        <v>143</v>
-      </c>
-      <c r="I5" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="J5" s="6" t="s">
-        <v>445</v>
-      </c>
-      <c r="L5" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="M5" s="6" t="s">
-        <v>872</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" t="s">
-        <v>275</v>
-      </c>
-      <c r="C6">
-        <v>275</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>850</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="F6" t="s">
-        <v>917</v>
-      </c>
-      <c r="G6" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="H6" s="6" t="s">
-        <v>143</v>
-      </c>
-      <c r="I6" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="J6" s="6" t="s">
-        <v>445</v>
-      </c>
-      <c r="L6" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="M6" s="6" t="s">
-        <v>873</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>13</v>
-      </c>
-      <c r="B7" t="s">
-        <v>275</v>
-      </c>
-      <c r="C7">
-        <v>276</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>851</v>
-      </c>
-      <c r="E7" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="F7" t="s">
-        <v>919</v>
-      </c>
-      <c r="G7" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="H7" s="6" t="s">
-        <v>219</v>
-      </c>
-      <c r="I7" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="J7" s="6" t="s">
-        <v>445</v>
-      </c>
-      <c r="L7" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="M7" s="6" t="s">
-        <v>874</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>13</v>
-      </c>
-      <c r="B8" t="s">
-        <v>275</v>
-      </c>
-      <c r="C8">
-        <v>277</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>852</v>
-      </c>
-      <c r="E8" s="33" t="s">
-        <v>266</v>
-      </c>
-      <c r="F8" t="s">
-        <v>920</v>
-      </c>
-      <c r="G8" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="H8" s="6" t="s">
-        <v>219</v>
-      </c>
-      <c r="I8" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="J8" s="6" t="s">
-        <v>871</v>
-      </c>
-      <c r="L8" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="M8" s="6" t="s">
-        <v>875</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>13</v>
-      </c>
-      <c r="B9" t="s">
-        <v>275</v>
-      </c>
-      <c r="C9">
-        <v>278</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>853</v>
-      </c>
-      <c r="E9" s="33" t="s">
-        <v>266</v>
-      </c>
-      <c r="F9" t="s">
-        <v>921</v>
-      </c>
-      <c r="G9" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="H9" s="6" t="s">
-        <v>219</v>
-      </c>
-      <c r="I9" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="J9" s="6" t="s">
-        <v>871</v>
-      </c>
-      <c r="L9" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="M9" s="6" t="s">
-        <v>876</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
-        <v>13</v>
-      </c>
-      <c r="B10" t="s">
-        <v>275</v>
-      </c>
-      <c r="C10">
-        <v>279</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>854</v>
-      </c>
-      <c r="E10" s="33" t="s">
-        <v>266</v>
-      </c>
-      <c r="F10" t="s">
-        <v>922</v>
-      </c>
-      <c r="G10" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="H10" s="6" t="s">
-        <v>219</v>
-      </c>
-      <c r="I10" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="J10" s="6" t="s">
-        <v>871</v>
-      </c>
-      <c r="L10" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="M10" s="6" t="s">
-        <v>877</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
-        <v>13</v>
-      </c>
-      <c r="B11" t="s">
-        <v>275</v>
-      </c>
-      <c r="C11">
-        <v>280</v>
-      </c>
-      <c r="D11" s="6" t="s">
-        <v>905</v>
-      </c>
-      <c r="E11" s="33" t="s">
-        <v>266</v>
-      </c>
-      <c r="F11" t="s">
-        <v>923</v>
-      </c>
-      <c r="G11" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="H11" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="I11" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="J11" s="6" t="s">
-        <v>871</v>
-      </c>
-      <c r="L11" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="M11" s="6" t="s">
-        <v>878</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
-        <v>13</v>
-      </c>
-      <c r="B12" t="s">
-        <v>275</v>
-      </c>
-      <c r="C12">
-        <v>281</v>
-      </c>
-      <c r="D12" s="6" t="s">
-        <v>906</v>
-      </c>
-      <c r="E12" s="33" t="s">
-        <v>266</v>
-      </c>
-      <c r="F12" t="s">
-        <v>924</v>
-      </c>
-      <c r="G12" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="H12" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="I12" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="J12" s="6" t="s">
-        <v>871</v>
-      </c>
-      <c r="L12" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="M12" s="6" t="s">
-        <v>879</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
-        <v>13</v>
-      </c>
-      <c r="B13" t="s">
-        <v>275</v>
-      </c>
-      <c r="C13">
-        <v>282</v>
-      </c>
-      <c r="D13" s="6" t="s">
-        <v>907</v>
-      </c>
-      <c r="E13" s="33" t="s">
-        <v>266</v>
-      </c>
-      <c r="F13" t="s">
-        <v>925</v>
-      </c>
-      <c r="G13" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="H13" s="6" t="s">
-        <v>159</v>
-      </c>
-      <c r="I13" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="J13" s="6" t="s">
-        <v>871</v>
-      </c>
-      <c r="L13" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="M13" s="6" t="s">
-        <v>880</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
-        <v>13</v>
-      </c>
-      <c r="B14" t="s">
-        <v>275</v>
-      </c>
-      <c r="C14">
-        <v>283</v>
-      </c>
-      <c r="D14" s="6" t="s">
-        <v>908</v>
-      </c>
-      <c r="E14" s="33" t="s">
-        <v>266</v>
-      </c>
-      <c r="F14" t="s">
-        <v>926</v>
-      </c>
-      <c r="G14" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="H14" s="6" t="s">
-        <v>159</v>
-      </c>
-      <c r="I14" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="J14" s="6" t="s">
-        <v>871</v>
-      </c>
-      <c r="L14" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="M14" s="6" t="s">
-        <v>881</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A15" t="s">
-        <v>13</v>
-      </c>
-      <c r="B15" t="s">
-        <v>275</v>
-      </c>
-      <c r="C15">
-        <v>284</v>
-      </c>
-      <c r="D15" s="6" t="s">
-        <v>909</v>
-      </c>
-      <c r="E15" s="33" t="s">
-        <v>266</v>
-      </c>
-      <c r="F15" t="s">
-        <v>927</v>
-      </c>
-      <c r="G15" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="H15" s="6" t="s">
-        <v>159</v>
-      </c>
-      <c r="I15" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="J15" s="6" t="s">
-        <v>871</v>
-      </c>
-      <c r="L15" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="M15" s="6" t="s">
-        <v>882</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A16" t="s">
-        <v>13</v>
-      </c>
-      <c r="B16" t="s">
-        <v>275</v>
-      </c>
-      <c r="C16">
-        <v>285</v>
-      </c>
-      <c r="D16" s="6" t="s">
-        <v>910</v>
-      </c>
-      <c r="E16" s="33" t="s">
-        <v>266</v>
-      </c>
-      <c r="F16" t="s">
-        <v>928</v>
-      </c>
-      <c r="G16" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="H16" s="6" t="s">
-        <v>159</v>
-      </c>
-      <c r="I16" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="J16" s="6" t="s">
-        <v>871</v>
-      </c>
-      <c r="L16" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="M16" s="6" t="s">
-        <v>883</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A17" t="s">
-        <v>13</v>
-      </c>
-      <c r="B17" t="s">
-        <v>275</v>
-      </c>
-      <c r="C17">
-        <v>286</v>
-      </c>
-      <c r="D17" s="6" t="s">
-        <v>911</v>
-      </c>
-      <c r="E17" s="33" t="s">
-        <v>266</v>
-      </c>
-      <c r="F17" t="s">
-        <v>929</v>
-      </c>
-      <c r="G17" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="H17" s="6" t="s">
-        <v>159</v>
-      </c>
-      <c r="I17" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="J17" s="6" t="s">
-        <v>871</v>
-      </c>
-      <c r="L17" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="M17" s="6" t="s">
-        <v>884</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A18" t="s">
-        <v>13</v>
-      </c>
-      <c r="B18" t="s">
-        <v>275</v>
-      </c>
-      <c r="C18">
-        <v>287</v>
-      </c>
-      <c r="D18" s="33" t="s">
-        <v>477</v>
-      </c>
-      <c r="E18" s="33" t="s">
-        <v>266</v>
-      </c>
-      <c r="F18" t="s">
-        <v>930</v>
-      </c>
-      <c r="G18" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="H18" s="6" t="s">
-        <v>392</v>
-      </c>
-      <c r="I18" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="J18" s="6" t="s">
-        <v>871</v>
-      </c>
-      <c r="L18" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="M18" s="6" t="s">
-        <v>885</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A19" t="s">
-        <v>13</v>
-      </c>
-      <c r="B19" t="s">
-        <v>275</v>
-      </c>
-      <c r="C19">
-        <v>288</v>
-      </c>
-      <c r="D19" s="30" t="s">
-        <v>511</v>
-      </c>
-      <c r="E19" s="33" t="s">
-        <v>266</v>
-      </c>
-      <c r="F19" t="s">
-        <v>931</v>
-      </c>
-      <c r="G19" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="H19" s="6" t="s">
-        <v>143</v>
-      </c>
-      <c r="I19" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="J19" s="6" t="s">
-        <v>871</v>
-      </c>
-      <c r="L19" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="M19" s="6" t="s">
-        <v>886</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A20" t="s">
-        <v>13</v>
-      </c>
-      <c r="B20" t="s">
-        <v>275</v>
-      </c>
-      <c r="C20">
-        <v>289</v>
-      </c>
-      <c r="D20" s="6" t="s">
-        <v>855</v>
-      </c>
-      <c r="E20" s="6" t="s">
-        <v>912</v>
-      </c>
-      <c r="F20" t="s">
-        <v>942</v>
-      </c>
-      <c r="G20" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="H20" s="6" t="s">
-        <v>159</v>
-      </c>
-      <c r="I20" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="J20" s="6" t="s">
-        <v>871</v>
-      </c>
-      <c r="L20" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="M20" s="6" t="s">
-        <v>887</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A21" t="s">
-        <v>13</v>
-      </c>
-      <c r="B21" t="s">
-        <v>275</v>
-      </c>
-      <c r="C21">
-        <v>290</v>
-      </c>
-      <c r="D21" s="17" t="s">
-        <v>856</v>
-      </c>
-      <c r="E21" s="6" t="s">
-        <v>912</v>
-      </c>
-      <c r="F21" t="s">
-        <v>943</v>
-      </c>
-      <c r="G21" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="H21" s="6" t="s">
-        <v>159</v>
-      </c>
-      <c r="I21" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="J21" s="6" t="s">
-        <v>871</v>
-      </c>
-      <c r="L21" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="M21" s="6" t="s">
-        <v>888</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A22" t="s">
-        <v>13</v>
-      </c>
-      <c r="B22" t="s">
-        <v>275</v>
-      </c>
-      <c r="C22">
-        <v>291</v>
-      </c>
-      <c r="D22" s="17" t="s">
-        <v>265</v>
-      </c>
-      <c r="E22" s="6" t="s">
-        <v>912</v>
-      </c>
-      <c r="F22" t="s">
-        <v>944</v>
-      </c>
-      <c r="G22" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="H22" s="6" t="s">
-        <v>159</v>
-      </c>
-      <c r="I22" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="J22" s="6" t="s">
-        <v>871</v>
-      </c>
-      <c r="L22" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="M22" s="6" t="s">
-        <v>889</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A23" t="s">
-        <v>13</v>
-      </c>
-      <c r="B23" t="s">
-        <v>275</v>
-      </c>
-      <c r="C23">
-        <v>292</v>
-      </c>
-      <c r="D23" s="17" t="s">
-        <v>857</v>
-      </c>
-      <c r="E23" s="6" t="s">
-        <v>912</v>
-      </c>
-      <c r="F23" t="s">
-        <v>945</v>
-      </c>
-      <c r="G23" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="H23" s="6" t="s">
-        <v>159</v>
-      </c>
-      <c r="I23" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="J23" s="6" t="s">
-        <v>871</v>
-      </c>
-      <c r="L23" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="M23" s="6" t="s">
-        <v>890</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A24" t="s">
-        <v>13</v>
-      </c>
-      <c r="B24" t="s">
-        <v>275</v>
-      </c>
-      <c r="C24">
-        <v>293</v>
-      </c>
-      <c r="D24" s="6" t="s">
-        <v>858</v>
-      </c>
-      <c r="E24" s="6" t="s">
-        <v>912</v>
-      </c>
-      <c r="F24" t="s">
-        <v>946</v>
-      </c>
-      <c r="G24" s="6" t="s">
-        <v>564</v>
-      </c>
-      <c r="H24" s="6" t="s">
-        <v>143</v>
-      </c>
-      <c r="I24" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="J24" s="6" t="s">
-        <v>871</v>
-      </c>
-      <c r="L24" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="M24" s="6" t="s">
-        <v>891</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A25" t="s">
-        <v>13</v>
-      </c>
-      <c r="B25" t="s">
-        <v>275</v>
-      </c>
-      <c r="C25">
-        <v>294</v>
-      </c>
-      <c r="D25" s="6" t="s">
-        <v>859</v>
-      </c>
-      <c r="E25" s="6" t="s">
-        <v>912</v>
-      </c>
-      <c r="F25" t="s">
-        <v>947</v>
-      </c>
-      <c r="G25" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="H25" s="6" t="s">
-        <v>159</v>
-      </c>
-      <c r="I25" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="J25" s="6" t="s">
-        <v>871</v>
-      </c>
-      <c r="L25" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="M25" s="6" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A26" t="s">
-        <v>13</v>
-      </c>
-      <c r="B26" t="s">
-        <v>275</v>
-      </c>
-      <c r="C26">
-        <v>295</v>
-      </c>
-      <c r="D26" s="6" t="s">
-        <v>860</v>
-      </c>
-      <c r="E26" s="6" t="s">
-        <v>912</v>
-      </c>
-      <c r="F26" t="s">
-        <v>948</v>
-      </c>
-      <c r="G26" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="H26" s="6" t="s">
-        <v>159</v>
-      </c>
-      <c r="I26" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="J26" s="6" t="s">
-        <v>871</v>
-      </c>
-      <c r="L26" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="M26" s="6" t="s">
-        <v>893</v>
-      </c>
-    </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A27" t="s">
-        <v>13</v>
-      </c>
-      <c r="B27" t="s">
-        <v>275</v>
-      </c>
-      <c r="C27">
-        <v>296</v>
-      </c>
-      <c r="D27" s="17" t="s">
-        <v>269</v>
-      </c>
-      <c r="E27" s="33" t="s">
-        <v>266</v>
-      </c>
-      <c r="F27" t="s">
-        <v>932</v>
-      </c>
-      <c r="G27" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="H27" s="6" t="s">
-        <v>219</v>
-      </c>
-      <c r="I27" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="J27" s="6" t="s">
-        <v>871</v>
-      </c>
-      <c r="L27" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="M27" s="6" t="s">
-        <v>894</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A28" t="s">
-        <v>13</v>
-      </c>
-      <c r="B28" t="s">
-        <v>275</v>
-      </c>
-      <c r="C28">
-        <v>297</v>
-      </c>
-      <c r="D28" s="6" t="s">
-        <v>861</v>
-      </c>
-      <c r="E28" s="33" t="s">
-        <v>266</v>
-      </c>
-      <c r="F28" t="s">
-        <v>933</v>
-      </c>
-      <c r="G28" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="H28" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="I28" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="J28" s="6" t="s">
-        <v>871</v>
-      </c>
-      <c r="L28" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="M28" s="6" t="s">
-        <v>895</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A29" t="s">
-        <v>13</v>
-      </c>
-      <c r="B29" t="s">
-        <v>275</v>
-      </c>
-      <c r="C29">
-        <v>298</v>
-      </c>
-      <c r="D29" s="6" t="s">
-        <v>862</v>
-      </c>
-      <c r="E29" s="33" t="s">
-        <v>266</v>
-      </c>
-      <c r="F29" t="s">
-        <v>934</v>
-      </c>
-      <c r="G29" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="H29" s="6" t="s">
-        <v>219</v>
-      </c>
-      <c r="I29" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="J29" s="6" t="s">
-        <v>871</v>
-      </c>
-      <c r="L29" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="M29" s="6" t="s">
-        <v>896</v>
-      </c>
-    </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A30" t="s">
-        <v>13</v>
-      </c>
-      <c r="B30" t="s">
-        <v>275</v>
-      </c>
-      <c r="C30">
-        <v>299</v>
-      </c>
-      <c r="D30" s="6" t="s">
-        <v>863</v>
-      </c>
-      <c r="E30" s="33" t="s">
-        <v>266</v>
-      </c>
-      <c r="F30" t="s">
-        <v>935</v>
-      </c>
-      <c r="G30" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="H30" s="6" t="s">
-        <v>219</v>
-      </c>
-      <c r="I30" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="J30" s="6" t="s">
-        <v>871</v>
-      </c>
-      <c r="L30" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="M30" s="6" t="s">
-        <v>897</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A31" t="s">
-        <v>13</v>
-      </c>
-      <c r="B31" t="s">
-        <v>275</v>
-      </c>
-      <c r="C31">
-        <v>300</v>
-      </c>
-      <c r="D31" s="17" t="s">
-        <v>864</v>
-      </c>
-      <c r="E31" s="33" t="s">
-        <v>266</v>
-      </c>
-      <c r="F31" t="s">
-        <v>936</v>
-      </c>
-      <c r="G31" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="H31" s="17" t="s">
-        <v>159</v>
-      </c>
-      <c r="I31" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="J31" s="6" t="s">
-        <v>871</v>
-      </c>
-      <c r="L31" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="M31" s="17" t="s">
-        <v>898</v>
-      </c>
-    </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A32" t="s">
-        <v>13</v>
-      </c>
-      <c r="B32" t="s">
-        <v>275</v>
-      </c>
-      <c r="C32">
-        <v>301</v>
-      </c>
-      <c r="D32" s="6" t="s">
-        <v>865</v>
-      </c>
-      <c r="E32" s="33" t="s">
-        <v>266</v>
-      </c>
-      <c r="F32" t="s">
-        <v>938</v>
-      </c>
-      <c r="G32" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="H32" s="17" t="s">
-        <v>159</v>
-      </c>
-      <c r="I32" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="J32" s="6" t="s">
-        <v>871</v>
-      </c>
-      <c r="L32" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="M32" s="6" t="s">
-        <v>899</v>
-      </c>
-    </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A33" t="s">
-        <v>13</v>
-      </c>
-      <c r="B33" t="s">
-        <v>275</v>
-      </c>
-      <c r="C33">
-        <v>302</v>
-      </c>
-      <c r="D33" s="6" t="s">
-        <v>866</v>
-      </c>
-      <c r="E33" s="33" t="s">
-        <v>266</v>
-      </c>
-      <c r="F33" t="s">
-        <v>939</v>
-      </c>
-      <c r="G33" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="H33" s="17" t="s">
-        <v>159</v>
-      </c>
-      <c r="I33" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="J33" s="6" t="s">
-        <v>871</v>
-      </c>
-      <c r="L33" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="M33" s="6" t="s">
-        <v>900</v>
-      </c>
-    </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A34" t="s">
-        <v>13</v>
-      </c>
-      <c r="B34" t="s">
-        <v>275</v>
-      </c>
-      <c r="C34">
-        <v>303</v>
-      </c>
-      <c r="D34" s="6" t="s">
-        <v>867</v>
-      </c>
-      <c r="E34" s="33" t="s">
-        <v>266</v>
-      </c>
-      <c r="F34" t="s">
-        <v>915</v>
-      </c>
-      <c r="G34" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="H34" s="17" t="s">
-        <v>159</v>
-      </c>
-      <c r="I34" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="J34" s="6" t="s">
-        <v>871</v>
-      </c>
-      <c r="L34" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="M34" s="6" t="s">
-        <v>901</v>
-      </c>
-    </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A35" t="s">
-        <v>13</v>
-      </c>
-      <c r="B35" t="s">
-        <v>275</v>
-      </c>
-      <c r="C35">
-        <v>304</v>
-      </c>
-      <c r="D35" s="6" t="s">
-        <v>868</v>
-      </c>
-      <c r="E35" s="33" t="s">
-        <v>266</v>
-      </c>
-      <c r="F35" t="s">
-        <v>940</v>
-      </c>
-      <c r="G35" s="6" t="s">
-        <v>564</v>
-      </c>
-      <c r="H35" s="6" t="s">
-        <v>143</v>
-      </c>
-      <c r="I35" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="J35" s="6" t="s">
-        <v>871</v>
-      </c>
-      <c r="L35" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="M35" s="6" t="s">
-        <v>902</v>
-      </c>
-    </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A36" t="s">
-        <v>13</v>
-      </c>
-      <c r="B36" t="s">
-        <v>275</v>
-      </c>
-      <c r="C36">
-        <v>305</v>
-      </c>
-      <c r="D36" s="6" t="s">
-        <v>869</v>
-      </c>
-      <c r="E36" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="F36" t="s">
-        <v>937</v>
-      </c>
-      <c r="G36" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="H36" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="I36" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="J36" s="6" t="s">
-        <v>445</v>
-      </c>
-      <c r="L36" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="M36" s="6" t="s">
-        <v>903</v>
-      </c>
-    </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A37" t="s">
-        <v>13</v>
-      </c>
-      <c r="B37" t="s">
-        <v>275</v>
-      </c>
-      <c r="C37">
-        <v>306</v>
-      </c>
-      <c r="D37" s="6" t="s">
-        <v>870</v>
-      </c>
-      <c r="E37" s="33" t="s">
-        <v>266</v>
-      </c>
-      <c r="F37" t="s">
-        <v>941</v>
-      </c>
-      <c r="G37" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="H37" s="6" t="s">
-        <v>159</v>
-      </c>
-      <c r="I37" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="J37" s="6" t="s">
-        <v>871</v>
-      </c>
-      <c r="L37" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="M37" s="6" t="s">
-        <v>904</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7A22D2F-6AFE-4D3D-A8D1-BBD797E61616}">
-  <dimension ref="A1:M24"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="4" max="4" width="37.90625" customWidth="1"/>
-    <col min="5" max="5" width="15.90625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="43.26953125" customWidth="1"/>
-    <col min="7" max="7" width="9.81640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.90625" customWidth="1"/>
-    <col min="9" max="9" width="16.6328125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.1796875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.26953125" customWidth="1"/>
-    <col min="12" max="12" width="13.1796875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="49.90625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="23" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>523</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="C2">
-        <v>307</v>
-      </c>
-      <c r="D2" s="34" t="s">
-        <v>949</v>
-      </c>
-      <c r="E2" s="36" t="s">
-        <v>996</v>
-      </c>
-      <c r="F2" t="s">
-        <v>997</v>
-      </c>
-      <c r="G2" s="36" t="s">
-        <v>18</v>
-      </c>
-      <c r="H2" s="37" t="s">
-        <v>215</v>
-      </c>
-      <c r="I2" s="36" t="s">
-        <v>20</v>
-      </c>
-      <c r="M2" s="34" t="s">
-        <v>973</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="C3">
-        <v>308</v>
-      </c>
-      <c r="D3" s="35" t="s">
-        <v>950</v>
-      </c>
-      <c r="E3" s="38" t="s">
-        <v>996</v>
-      </c>
-      <c r="F3" t="s">
-        <v>998</v>
-      </c>
-      <c r="G3" s="38" t="s">
-        <v>18</v>
-      </c>
-      <c r="H3" s="39" t="s">
-        <v>143</v>
-      </c>
-      <c r="I3" s="38" t="s">
-        <v>20</v>
-      </c>
-      <c r="M3" s="35" t="s">
-        <v>974</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="C4">
-        <v>309</v>
-      </c>
-      <c r="D4" s="34" t="s">
-        <v>951</v>
-      </c>
-      <c r="E4" s="36" t="s">
-        <v>996</v>
-      </c>
-      <c r="F4" t="s">
-        <v>999</v>
-      </c>
-      <c r="G4" s="36" t="s">
-        <v>18</v>
-      </c>
-      <c r="H4" s="37" t="s">
-        <v>215</v>
-      </c>
-      <c r="I4" s="36" t="s">
-        <v>20</v>
-      </c>
-      <c r="M4" s="34" t="s">
-        <v>975</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="C5">
-        <v>310</v>
-      </c>
-      <c r="D5" s="35" t="s">
-        <v>952</v>
-      </c>
-      <c r="E5" s="38" t="s">
-        <v>996</v>
-      </c>
-      <c r="F5" t="s">
-        <v>1000</v>
-      </c>
-      <c r="G5" s="38" t="s">
-        <v>18</v>
-      </c>
-      <c r="H5" s="39" t="s">
-        <v>215</v>
-      </c>
-      <c r="I5" s="38" t="s">
-        <v>20</v>
-      </c>
-      <c r="M5" s="35" t="s">
-        <v>976</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="C6">
-        <v>311</v>
-      </c>
-      <c r="D6" s="34" t="s">
-        <v>953</v>
-      </c>
-      <c r="E6" s="36" t="s">
-        <v>996</v>
-      </c>
-      <c r="F6" t="s">
-        <v>1001</v>
-      </c>
-      <c r="G6" s="36" t="s">
-        <v>18</v>
-      </c>
-      <c r="H6" s="37" t="s">
-        <v>219</v>
-      </c>
-      <c r="I6" s="36" t="s">
-        <v>20</v>
-      </c>
-      <c r="M6" s="34" t="s">
-        <v>977</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="C7">
-        <v>312</v>
-      </c>
-      <c r="D7" s="35" t="s">
-        <v>954</v>
-      </c>
-      <c r="E7" s="38" t="s">
-        <v>996</v>
-      </c>
-      <c r="F7" t="s">
-        <v>1002</v>
-      </c>
-      <c r="G7" s="38" t="s">
-        <v>18</v>
-      </c>
-      <c r="H7" s="39" t="s">
-        <v>219</v>
-      </c>
-      <c r="I7" s="38" t="s">
-        <v>20</v>
-      </c>
-      <c r="M7" s="35" t="s">
-        <v>978</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="C8">
-        <v>313</v>
-      </c>
-      <c r="D8" s="34" t="s">
-        <v>955</v>
-      </c>
-      <c r="E8" s="36" t="s">
-        <v>996</v>
-      </c>
-      <c r="F8" t="s">
-        <v>1003</v>
-      </c>
-      <c r="G8" s="36" t="s">
-        <v>18</v>
-      </c>
-      <c r="H8" s="37" t="s">
-        <v>219</v>
-      </c>
-      <c r="I8" s="36" t="s">
-        <v>20</v>
-      </c>
-      <c r="M8" s="34" t="s">
-        <v>979</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="C9">
-        <v>314</v>
-      </c>
-      <c r="D9" s="35" t="s">
-        <v>956</v>
-      </c>
-      <c r="E9" s="38" t="s">
-        <v>996</v>
-      </c>
-      <c r="F9" t="s">
-        <v>1004</v>
-      </c>
-      <c r="G9" s="38" t="s">
-        <v>18</v>
-      </c>
-      <c r="H9" s="39" t="s">
-        <v>316</v>
-      </c>
-      <c r="I9" s="38" t="s">
-        <v>20</v>
-      </c>
-      <c r="M9" s="35" t="s">
-        <v>980</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="C10">
-        <v>315</v>
-      </c>
-      <c r="D10" s="34" t="s">
-        <v>957</v>
-      </c>
-      <c r="E10" s="36" t="s">
-        <v>996</v>
-      </c>
-      <c r="F10" t="s">
-        <v>1005</v>
-      </c>
-      <c r="G10" s="36" t="s">
-        <v>18</v>
-      </c>
-      <c r="H10" s="37" t="s">
-        <v>143</v>
-      </c>
-      <c r="I10" s="36" t="s">
-        <v>20</v>
-      </c>
-      <c r="M10" s="34" t="s">
-        <v>981</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="C11">
-        <v>316</v>
-      </c>
-      <c r="D11" s="35" t="s">
-        <v>958</v>
-      </c>
-      <c r="E11" s="38" t="s">
-        <v>996</v>
-      </c>
-      <c r="F11" t="s">
-        <v>1006</v>
-      </c>
-      <c r="G11" s="38" t="s">
-        <v>18</v>
-      </c>
-      <c r="H11" s="39" t="s">
-        <v>215</v>
-      </c>
-      <c r="I11" s="38" t="s">
-        <v>20</v>
-      </c>
-      <c r="M11" s="35" t="s">
-        <v>982</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="C12">
-        <v>317</v>
-      </c>
-      <c r="D12" s="34" t="s">
-        <v>959</v>
-      </c>
-      <c r="E12" s="36" t="s">
-        <v>996</v>
-      </c>
-      <c r="F12" t="s">
-        <v>1007</v>
-      </c>
-      <c r="G12" s="36" t="s">
-        <v>18</v>
-      </c>
-      <c r="H12" s="37" t="s">
-        <v>215</v>
-      </c>
-      <c r="I12" s="36" t="s">
-        <v>20</v>
-      </c>
-      <c r="M12" s="34" t="s">
-        <v>983</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="C13">
-        <v>318</v>
-      </c>
-      <c r="D13" s="35" t="s">
-        <v>960</v>
-      </c>
-      <c r="E13" s="38" t="s">
-        <v>996</v>
-      </c>
-      <c r="F13" t="s">
-        <v>1008</v>
-      </c>
-      <c r="G13" s="38" t="s">
-        <v>18</v>
-      </c>
-      <c r="H13" s="39" t="s">
-        <v>215</v>
-      </c>
-      <c r="I13" s="38" t="s">
-        <v>20</v>
-      </c>
-      <c r="M13" s="35" t="s">
-        <v>984</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="C14">
-        <v>319</v>
-      </c>
-      <c r="D14" s="34" t="s">
-        <v>961</v>
-      </c>
-      <c r="E14" s="36" t="s">
-        <v>996</v>
-      </c>
-      <c r="F14" t="s">
-        <v>1009</v>
-      </c>
-      <c r="G14" s="36" t="s">
-        <v>30</v>
-      </c>
-      <c r="H14" s="37" t="s">
-        <v>215</v>
-      </c>
-      <c r="I14" s="36" t="s">
-        <v>144</v>
-      </c>
-      <c r="M14" s="34" t="s">
-        <v>985</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="C15">
-        <v>320</v>
-      </c>
-      <c r="D15" s="35" t="s">
-        <v>288</v>
-      </c>
-      <c r="E15" s="38" t="s">
-        <v>996</v>
-      </c>
-      <c r="F15" t="s">
-        <v>1010</v>
-      </c>
-      <c r="G15" s="38" t="s">
-        <v>564</v>
-      </c>
-      <c r="H15" s="39" t="s">
-        <v>971</v>
-      </c>
-      <c r="I15" s="38" t="s">
-        <v>20</v>
-      </c>
-      <c r="M15" s="35" t="s">
-        <v>986</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="C16">
-        <v>321</v>
-      </c>
-      <c r="D16" s="34" t="s">
-        <v>962</v>
-      </c>
-      <c r="E16" s="36" t="s">
-        <v>996</v>
-      </c>
-      <c r="F16" t="s">
-        <v>1011</v>
-      </c>
-      <c r="G16" s="36" t="s">
-        <v>18</v>
-      </c>
-      <c r="H16" s="37" t="s">
-        <v>215</v>
-      </c>
-      <c r="I16" s="36" t="s">
-        <v>20</v>
-      </c>
-      <c r="M16" s="34" t="s">
-        <v>987</v>
-      </c>
-    </row>
-    <row r="17" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="C17">
-        <v>322</v>
-      </c>
-      <c r="D17" s="35" t="s">
-        <v>963</v>
-      </c>
-      <c r="E17" s="38" t="s">
-        <v>996</v>
-      </c>
-      <c r="F17" t="s">
-        <v>1012</v>
-      </c>
-      <c r="G17" s="38" t="s">
-        <v>30</v>
-      </c>
-      <c r="H17" s="39" t="s">
-        <v>215</v>
-      </c>
-      <c r="I17" s="38" t="s">
-        <v>144</v>
-      </c>
-      <c r="M17" s="35" t="s">
-        <v>988</v>
-      </c>
-    </row>
-    <row r="18" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="C18">
-        <v>323</v>
-      </c>
-      <c r="D18" s="34" t="s">
-        <v>964</v>
-      </c>
-      <c r="E18" s="36" t="s">
-        <v>996</v>
-      </c>
-      <c r="F18" t="s">
-        <v>1013</v>
-      </c>
-      <c r="G18" s="38" t="s">
-        <v>30</v>
-      </c>
-      <c r="H18" s="37" t="s">
-        <v>972</v>
-      </c>
-      <c r="I18" s="36" t="s">
-        <v>144</v>
-      </c>
-      <c r="M18" s="34" t="s">
-        <v>989</v>
-      </c>
-    </row>
-    <row r="19" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="C19">
-        <v>324</v>
-      </c>
-      <c r="D19" s="35" t="s">
-        <v>965</v>
-      </c>
-      <c r="E19" s="38" t="s">
-        <v>996</v>
-      </c>
-      <c r="F19" t="s">
-        <v>1014</v>
-      </c>
-      <c r="G19" s="38" t="s">
-        <v>30</v>
-      </c>
-      <c r="H19" s="39" t="s">
-        <v>150</v>
-      </c>
-      <c r="I19" s="38" t="s">
-        <v>144</v>
-      </c>
-      <c r="M19" s="35" t="s">
-        <v>990</v>
-      </c>
-    </row>
-    <row r="20" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="C20">
-        <v>325</v>
-      </c>
-      <c r="D20" s="34" t="s">
-        <v>966</v>
-      </c>
-      <c r="E20" s="36" t="s">
-        <v>996</v>
-      </c>
-      <c r="F20" t="s">
-        <v>1015</v>
-      </c>
-      <c r="G20" s="38" t="s">
-        <v>30</v>
-      </c>
-      <c r="H20" s="37" t="s">
-        <v>215</v>
-      </c>
-      <c r="I20" s="36" t="s">
-        <v>144</v>
-      </c>
-      <c r="M20" s="34" t="s">
-        <v>991</v>
-      </c>
-    </row>
-    <row r="21" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="C21">
-        <v>326</v>
-      </c>
-      <c r="D21" s="35" t="s">
-        <v>967</v>
-      </c>
-      <c r="E21" s="38" t="s">
-        <v>996</v>
-      </c>
-      <c r="F21" t="s">
-        <v>1016</v>
-      </c>
-      <c r="G21" s="38" t="s">
-        <v>30</v>
-      </c>
-      <c r="H21" s="39" t="s">
-        <v>316</v>
-      </c>
-      <c r="I21" s="38" t="s">
-        <v>144</v>
-      </c>
-      <c r="M21" s="35" t="s">
-        <v>992</v>
-      </c>
-    </row>
-    <row r="22" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="C22">
-        <v>327</v>
-      </c>
-      <c r="D22" s="34" t="s">
-        <v>968</v>
-      </c>
-      <c r="E22" s="36" t="s">
-        <v>996</v>
-      </c>
-      <c r="F22" t="s">
-        <v>1017</v>
-      </c>
-      <c r="G22" s="38" t="s">
-        <v>30</v>
-      </c>
-      <c r="H22" s="37" t="s">
-        <v>316</v>
-      </c>
-      <c r="I22" s="36" t="s">
-        <v>144</v>
-      </c>
-      <c r="M22" s="34" t="s">
-        <v>993</v>
-      </c>
-    </row>
-    <row r="23" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="C23">
-        <v>328</v>
-      </c>
-      <c r="D23" s="35" t="s">
-        <v>969</v>
-      </c>
-      <c r="E23" s="38" t="s">
-        <v>996</v>
-      </c>
-      <c r="F23" t="s">
-        <v>1018</v>
-      </c>
-      <c r="G23" s="38" t="s">
-        <v>30</v>
-      </c>
-      <c r="H23" s="39" t="s">
-        <v>316</v>
-      </c>
-      <c r="I23" s="38" t="s">
-        <v>144</v>
-      </c>
-      <c r="M23" s="35" t="s">
-        <v>994</v>
-      </c>
-    </row>
-    <row r="24" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="C24">
-        <v>329</v>
-      </c>
-      <c r="D24" s="34" t="s">
-        <v>970</v>
-      </c>
-      <c r="E24" s="36" t="s">
-        <v>996</v>
-      </c>
-      <c r="F24" t="s">
-        <v>1019</v>
-      </c>
-      <c r="G24" s="38" t="s">
-        <v>30</v>
-      </c>
-      <c r="H24" s="37" t="s">
-        <v>143</v>
-      </c>
-      <c r="I24" s="36" t="s">
-        <v>144</v>
-      </c>
-      <c r="M24" s="34" t="s">
-        <v>995</v>
-      </c>
-    </row>
-  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/docs/CDOP_SCHEMA.xlsx
+++ b/docs/CDOP_SCHEMA.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rockmtnins-my.sharepoint.com/personal/sebastian_weeks_rmi_org/Documents/Documents/CDOP Resources/UseCase_Category CSVs_JSONs/Master Version/Round 2 Pods for Testing/Fast Track Pods/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rockmtnins-my.sharepoint.com/personal/sebastian_weeks_rmi_org/Documents/Documents/CDOP Resources/UseCase_Category CSVs_JSONs/Master Version/8_25_26/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="471" documentId="8_{E4888AF0-8469-49B9-BF1F-D7429471A122}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{08F8C38D-0960-4BDB-AD51-6369C48E9E43}"/>
+  <xr:revisionPtr revIDLastSave="118" documentId="8_{E4888AF0-8469-49B9-BF1F-D7429471A122}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{51AF62E9-238E-47E0-BF18-8C0C7E464784}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="12" activeTab="14" xr2:uid="{743398AF-A4FE-47C4-9368-972E95242EBF}"/>
+    <workbookView xWindow="-28215" yWindow="375" windowWidth="27555" windowHeight="15045" activeTab="11" xr2:uid="{743398AF-A4FE-47C4-9368-972E95242EBF}"/>
   </bookViews>
   <sheets>
     <sheet name="Full List" sheetId="5" r:id="rId1"/>
@@ -25,9 +25,6 @@
     <sheet name="Durability_Permanence" sheetId="10" r:id="rId10"/>
     <sheet name="Project Finance" sheetId="11" r:id="rId11"/>
     <sheet name="Labels_Certifications" sheetId="12" r:id="rId12"/>
-    <sheet name="Registry_Metadata" sheetId="13" r:id="rId13"/>
-    <sheet name="Validation_Metadata" sheetId="14" r:id="rId14"/>
-    <sheet name="Verification_Metadata" sheetId="15" r:id="rId15"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Full List'!$A$1:$M$174</definedName>
@@ -53,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7098" uniqueCount="1021">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6394" uniqueCount="824">
   <si>
     <t>schema</t>
   </si>
@@ -2566,605 +2563,14 @@
     <t>project.project_level[].project_level_compliance_potential_eligibility</t>
   </si>
   <si>
-    <t>crediting program</t>
-  </si>
-  <si>
-    <t>Describes the current registry, that contains the information about the project, and units</t>
-  </si>
-  <si>
-    <t>Describes the first registry, where the project was registered</t>
-  </si>
-  <si>
-    <t>Describes the Crediting Program that the proejct is following for the implementationunits</t>
-  </si>
-  <si>
-    <t>Date of the last update</t>
-  </si>
-  <si>
-    <t>registry_identifier</t>
-  </si>
-  <si>
-    <t>registry_name</t>
-  </si>
-  <si>
-    <t>registry_link</t>
-  </si>
-  <si>
-    <t>original_registry_identifier</t>
-  </si>
-  <si>
-    <t>original_registry_name</t>
-  </si>
-  <si>
-    <t>original_registry_link</t>
-  </si>
-  <si>
-    <t>program_identifier</t>
-  </si>
-  <si>
-    <t>program_name</t>
-  </si>
-  <si>
-    <t>creation_date</t>
-  </si>
-  <si>
-    <t>update_date</t>
-  </si>
-  <si>
-    <t>Date that the project was first registered</t>
-  </si>
-  <si>
-    <t>registry.creation_date</t>
-  </si>
-  <si>
-    <t>registry.update_date</t>
-  </si>
-  <si>
-    <t>registry.identification[].registry_identifier</t>
-  </si>
-  <si>
-    <t>registry.identification[].registry_name</t>
-  </si>
-  <si>
-    <t>registry.identification[].registry_link</t>
-  </si>
-  <si>
-    <t>registry.original[].original_registry_identifier</t>
-  </si>
-  <si>
-    <t>registry.original[].original_registry_name</t>
-  </si>
-  <si>
-    <t>registry.original[].original_registry_link</t>
-  </si>
-  <si>
-    <t>registry.program[].program_identifier</t>
-  </si>
-  <si>
-    <t>registry.program[].program_name</t>
-  </si>
-  <si>
-    <t>current_validation_stage</t>
-  </si>
-  <si>
-    <t>current_validation_stage_status</t>
-  </si>
-  <si>
-    <t>date_previous_validation</t>
-  </si>
-  <si>
-    <t>date_validation_expiration</t>
-  </si>
-  <si>
-    <t>date_validation_planned</t>
-  </si>
-  <si>
-    <t>date_validation_requested</t>
-  </si>
-  <si>
-    <t>validation_body_accreditation</t>
-  </si>
-  <si>
-    <t>validation_body_id</t>
-  </si>
-  <si>
-    <t>validator_name</t>
-  </si>
-  <si>
-    <t>validation_body_sectoral_scopes</t>
-  </si>
-  <si>
-    <t>validation_body_selection</t>
-  </si>
-  <si>
-    <t>validation_body_team_members_and_roles</t>
-  </si>
-  <si>
-    <t>validation_is_planned</t>
-  </si>
-  <si>
-    <t>validation_period_end_date</t>
-  </si>
-  <si>
-    <t>validation_period_start_date</t>
-  </si>
-  <si>
-    <t>validation_report_link</t>
-  </si>
-  <si>
-    <t>validation_report_summary</t>
-  </si>
-  <si>
-    <t>validation_stage_description</t>
-  </si>
-  <si>
-    <t>validation_stage_document_link</t>
-  </si>
-  <si>
-    <t>validation_stages</t>
-  </si>
-  <si>
-    <t>validation_status</t>
-  </si>
-  <si>
-    <t>validation_report_version</t>
-  </si>
-  <si>
-    <t>Validation and Verification Body (VVB)/ Certification Bodies/ Third Party Auditors</t>
-  </si>
-  <si>
-    <t>Name of the current validation step</t>
-  </si>
-  <si>
-    <t>Status of the current validation step</t>
-  </si>
-  <si>
-    <t>Date of the previous validation event</t>
-  </si>
-  <si>
-    <t>Date validation expires</t>
-  </si>
-  <si>
-    <t>Planned date of the validation event</t>
-  </si>
-  <si>
-    <t>Date validation was requested</t>
-  </si>
-  <si>
-    <t>LCA has been completed</t>
-  </si>
-  <si>
-    <t>LCA is used to quantify emissions</t>
-  </si>
-  <si>
-    <t>Link to LCA report</t>
-  </si>
-  <si>
-    <t>Link to LCA repository</t>
-  </si>
-  <si>
-    <t>LCA results</t>
-  </si>
-  <si>
-    <t>Link to LCA system boundary figure</t>
-  </si>
-  <si>
-    <t>Overview description of LCA system boundary</t>
-  </si>
-  <si>
-    <t>Identification number of the validation event.</t>
-  </si>
-  <si>
-    <t>Type of validation being carried out</t>
-  </si>
-  <si>
-    <t>List any accreditations of the validation body</t>
-  </si>
-  <si>
-    <t>Identification number of the validation body</t>
-  </si>
-  <si>
-    <t>Name of the validation body</t>
-  </si>
-  <si>
-    <t>Name(s) of the validator(s)</t>
-  </si>
-  <si>
-    <t>List the sectoral scopes the validation body is accredited to validate</t>
-  </si>
-  <si>
-    <t>Describe how the validation body was selected</t>
-  </si>
-  <si>
-    <t>List the names of any other validation body team members and their roles (FIRST NAME - LAST NAME, ROLE)</t>
-  </si>
-  <si>
-    <t>Date of validation event</t>
-  </si>
-  <si>
-    <t>Indicate whether the valiation event is planned.</t>
-  </si>
-  <si>
-    <t>End date of the validation event. Estimate if needed.</t>
-  </si>
-  <si>
-    <t>Start date of the validation event</t>
-  </si>
-  <si>
-    <t>Link (URL) to the project's validation report (if applicable).</t>
-  </si>
-  <si>
-    <t>Enter the validation report's summary</t>
-  </si>
-  <si>
-    <t>Describe the stages of the validation event.</t>
-  </si>
-  <si>
-    <t>Link (URL) to the document that contains the description and details of the validation event stages</t>
-  </si>
-  <si>
-    <t>Select all validation event stages</t>
-  </si>
-  <si>
-    <t>Indicate whether the project has been validated.</t>
-  </si>
-  <si>
-    <t>Which version of the validation report is the current version</t>
-  </si>
-  <si>
-    <t>lca_completed</t>
-  </si>
-  <si>
-    <t>lca_emissions_quantification</t>
-  </si>
-  <si>
-    <t>lca_link</t>
-  </si>
-  <si>
-    <t>lca_repository</t>
-  </si>
-  <si>
-    <t>lca_results</t>
-  </si>
-  <si>
-    <t>lca_system_boundary_figure</t>
-  </si>
-  <si>
-    <t>lca_system_boundary_overview</t>
-  </si>
-  <si>
-    <t>validation _id</t>
-  </si>
-  <si>
-    <t>validation_body</t>
-  </si>
-  <si>
-    <t>validation.crediting_period[].current_crediting_period_end_date</t>
-  </si>
-  <si>
-    <t>project.validation_stage[].current_validation_stage</t>
-  </si>
-  <si>
-    <t>validation.stage[].validation_stage_document_link</t>
-  </si>
-  <si>
-    <t>validation.crediting_period[].current_crediting_period_number</t>
-  </si>
-  <si>
-    <t>project.validation_stage[].current_validation_stage_status</t>
-  </si>
-  <si>
-    <t>validation.crediting_period[].current_crediting_period_start_date</t>
-  </si>
-  <si>
-    <t>project.date[].date_previous_validation</t>
-  </si>
-  <si>
-    <t>validation.date[].date_validation_expiration</t>
-  </si>
-  <si>
-    <t>validation.date[].date_validation_planned</t>
-  </si>
-  <si>
-    <t>validation.date[].date_validation_requested</t>
-  </si>
-  <si>
-    <t>validation.lca[].lca_completed</t>
-  </si>
-  <si>
-    <t>validation.lca[].lca_emissions_quantification</t>
-  </si>
-  <si>
-    <t>validation.lca[].lca_link</t>
-  </si>
-  <si>
-    <t>validation.lca[].lca_repository</t>
-  </si>
-  <si>
-    <t>validation.lca[].lca_results</t>
-  </si>
-  <si>
-    <t>validation.lca[].lca_system_boundary_figure</t>
-  </si>
-  <si>
-    <t>validation.lca[].lca_system_boundary_overview</t>
-  </si>
-  <si>
-    <t>validation.validation_event[].validation _id</t>
-  </si>
-  <si>
-    <t>validation.validation_event[].validation_type</t>
-  </si>
-  <si>
-    <t>validation.validation_event[].validation_date</t>
-  </si>
-  <si>
-    <t>validation.validation_event[].validation_is_planned</t>
-  </si>
-  <si>
-    <t>validation.validation_event[].validation_period_end_date</t>
-  </si>
-  <si>
-    <t>validation.validation_event[].validation_period_start_date</t>
-  </si>
-  <si>
-    <t>validation.report[].validation_report_link</t>
-  </si>
-  <si>
-    <t>project.validation_status</t>
-  </si>
-  <si>
-    <t>validation.report[].validation_report_summary</t>
-  </si>
-  <si>
-    <t>validation.stage[].validation_stage_description</t>
-  </si>
-  <si>
-    <t>validation.stage[].validation_stages</t>
-  </si>
-  <si>
-    <t>validation.report[].validation_report_version</t>
-  </si>
-  <si>
-    <t>validation_body.details[].validation_body_accreditation</t>
-  </si>
-  <si>
-    <t>validation_body.details[].validation_body_id</t>
-  </si>
-  <si>
-    <t>validation_body.details[].validation_body_name</t>
-  </si>
-  <si>
-    <t>validation_body.details[].validator_name</t>
-  </si>
-  <si>
-    <t>validation_body.details[].validation_body_sectoral_scopes</t>
-  </si>
-  <si>
-    <t>validation_body.details[].validation_body_selection</t>
-  </si>
-  <si>
-    <t>validation_body.details[].validation_body_team_members_and_roles</t>
-  </si>
-  <si>
-    <t>verification_id</t>
-  </si>
-  <si>
-    <t>verification_claim_type</t>
-  </si>
-  <si>
-    <t>verification_project_id</t>
-  </si>
-  <si>
-    <t>verification_description</t>
-  </si>
-  <si>
-    <t>verification_reporting_period_start</t>
-  </si>
-  <si>
-    <t>verification_reporting_period_end</t>
-  </si>
-  <si>
-    <t>verification_date</t>
-  </si>
-  <si>
-    <t>verified_quantity</t>
-  </si>
-  <si>
-    <t>verification_quantity_uom</t>
-  </si>
-  <si>
-    <t>verification_body_name</t>
-  </si>
-  <si>
-    <t>verification_body_id</t>
-  </si>
-  <si>
-    <t>verification_applied_standard</t>
-  </si>
-  <si>
-    <t>verification_applied_methodology_protocol</t>
-  </si>
-  <si>
-    <t>verification_credential_issuer_id</t>
-  </si>
-  <si>
-    <t>verification_cryptographic_proof_type</t>
-  </si>
-  <si>
-    <t>verification_digital_signature_payload</t>
-  </si>
-  <si>
-    <t>verification_leakage_risk_mitigation</t>
-  </si>
-  <si>
-    <t>verification_leakage_risk_mitigation_strategy</t>
-  </si>
-  <si>
-    <t>verification_leakage_deduction_quantity</t>
-  </si>
-  <si>
-    <t>verification_uncertainty_deduction_margin</t>
-  </si>
-  <si>
-    <t>verification_buffer_pool_deduction_quantity</t>
-  </si>
-  <si>
-    <t>verification_audit_checkpoint_status</t>
-  </si>
-  <si>
-    <t>URI</t>
-  </si>
-  <si>
-    <t>Object/String</t>
-  </si>
-  <si>
-    <t>A globally unique identifier for the specific verification event or claim.</t>
-  </si>
-  <si>
-    <t>The classification of the claim being verified (e.g., CARBON_REMOVAL, EMISSION_REDUCTION, BIODIVERSITY).</t>
-  </si>
-  <si>
-    <t>The unique ID of the underlying project registered on the host registry.</t>
-  </si>
-  <si>
-    <t>A concise, human-readable summary of the verification scope and findings.</t>
-  </si>
-  <si>
-    <t>The start date of the monitoring/reporting period being verified.</t>
-  </si>
-  <si>
-    <t>The end date of the monitoring/reporting period being verified.</t>
-  </si>
-  <si>
-    <t>The official date the verification process was completed and signed off.</t>
-  </si>
-  <si>
-    <t>The final, audited, and verified net volume for this specific reporting period.</t>
-  </si>
-  <si>
-    <t>The Unit of Measure for the verified quantity (e.g., tCO2e, m3_biogas).</t>
-  </si>
-  <si>
-    <t>The official name of the third-party auditing entity/VVB.</t>
-  </si>
-  <si>
-    <t>The decentralized identifier (DID) or registry ID of the verification body.</t>
-  </si>
-  <si>
-    <t>The overarching registry framework (e.g., Verra_VCS_v4.5, Gold_Standard).</t>
-  </si>
-  <si>
-    <t>The specific methodology version applied (e.g., VM0047_v1.0, CAR_Soil_v1.1).</t>
-  </si>
-  <si>
-    <t>The direct, secure hyperlink to the official public verification report PDF.</t>
-  </si>
-  <si>
-    <t>The decentralized identifier (DID) of the entity issuing the digital verification token.</t>
-  </si>
-  <si>
-    <t>The security protocol used (e.g., Ed25519Signature2020, JSON-LD).</t>
-  </si>
-  <si>
-    <t>The actual cryptographic signature, payload hash, or verifiable presentation metadata.</t>
-  </si>
-  <si>
-    <t>Indicates if leakage risk is accounted for on this verification event</t>
-  </si>
-  <si>
-    <t>links to or summarizes the mitigation strategy for this verification event</t>
-  </si>
-  <si>
-    <t>Volume deducted for this specific reporting period to account for leakage.</t>
-  </si>
-  <si>
-    <t>Percentage or absolute deduction applied for this specific reporting period for uncertainty.</t>
-  </si>
-  <si>
-    <t>Volume deducted for this specific reporting period and contributed to the buffer pool.</t>
-  </si>
-  <si>
-    <t>Summary result of the checklist (e.g., PASS, PASS_WITH_RESERVATIONS, FAIL).</t>
-  </si>
-  <si>
-    <t>verification</t>
-  </si>
-  <si>
-    <t>verification.identification[].verification_id</t>
-  </si>
-  <si>
-    <t>verification.identification[].verification_claim_type</t>
-  </si>
-  <si>
-    <t>verification.identification[].verification_project_id</t>
-  </si>
-  <si>
-    <t>verification.identification[].verification_description</t>
-  </si>
-  <si>
-    <t>verification.reporting[].verification_reporting_period_start</t>
-  </si>
-  <si>
-    <t>verification.reporting[].verification_reporting_period_end</t>
-  </si>
-  <si>
-    <t>verification.reporting[].verification_date</t>
-  </si>
-  <si>
-    <t>verification.quantity[].verified_quantity</t>
-  </si>
-  <si>
-    <t>verification.quantity[].verification_quantity_uom</t>
-  </si>
-  <si>
-    <t>verification.body[].verification_body_name</t>
-  </si>
-  <si>
-    <t>verification.body[].verification_body_id</t>
-  </si>
-  <si>
-    <t>verification.standard[].verification_applied_standard</t>
-  </si>
-  <si>
-    <t>verification.standard[].verification_applied_methodology_protocol</t>
-  </si>
-  <si>
-    <t>verification.verification_report_url</t>
-  </si>
-  <si>
-    <t>verification.verification_credential_issuer_id</t>
-  </si>
-  <si>
-    <t>verification.verification_cryptographic_proof_type</t>
-  </si>
-  <si>
-    <t>verification.verification_digital_signature_payload</t>
-  </si>
-  <si>
-    <t>verification.leakage[].verification_leakage_risk_mitigation</t>
-  </si>
-  <si>
-    <t>verification.leakage[].verification_leakage_risk_mitigation_strategy</t>
-  </si>
-  <si>
-    <t>verification.leakage[].verification_leakage_deduction_quantity</t>
-  </si>
-  <si>
-    <t>verification.verification_uncertainty_deduction_margin</t>
-  </si>
-  <si>
-    <t>verification.verification_buffer_pool_deduction_quantity</t>
-  </si>
-  <si>
-    <t>verification.verification_audit_checkpoint_status</t>
+    <t>crediting_program.carbon_standard_level_accreditation</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3259,15 +2665,8 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF434343"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="10">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3307,18 +2706,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6F8F9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3370,7 +2757,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -3432,35 +2819,6 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -16595,7 +15953,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:13" ht="16" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -16605,14 +15963,14 @@
       <c r="C2">
         <v>242</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="32" t="s">
         <v>763</v>
       </c>
       <c r="E2" s="6" t="s">
         <v>141</v>
       </c>
       <c r="F2" t="s">
-        <v>804</v>
+        <v>823</v>
       </c>
       <c r="G2" t="s">
         <v>30</v>
@@ -16636,7 +15994,7 @@
         <v>785</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:13" ht="16" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -16646,7 +16004,7 @@
       <c r="C3">
         <v>243</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="32" t="s">
         <v>764</v>
       </c>
       <c r="E3" s="6" t="s">
@@ -16677,7 +16035,7 @@
         <v>786</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:13" ht="16" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>13</v>
       </c>
@@ -16687,7 +16045,7 @@
       <c r="C4">
         <v>244</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="32" t="s">
         <v>765</v>
       </c>
       <c r="E4" s="6" t="s">
@@ -16718,7 +16076,7 @@
         <v>787</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:13" ht="16" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -16728,7 +16086,7 @@
       <c r="C5">
         <v>245</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="32" t="s">
         <v>766</v>
       </c>
       <c r="E5" s="6" t="s">
@@ -16759,7 +16117,7 @@
         <v>788</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:13" ht="16" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
         <v>13</v>
       </c>
@@ -16769,7 +16127,7 @@
       <c r="C6">
         <v>246</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D6" s="32" t="s">
         <v>767</v>
       </c>
       <c r="E6" s="6" t="s">
@@ -16800,7 +16158,7 @@
         <v>789</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:13" ht="16" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -16810,7 +16168,7 @@
       <c r="C7">
         <v>247</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="D7" s="32" t="s">
         <v>768</v>
       </c>
       <c r="E7" s="6" t="s">
@@ -16841,7 +16199,7 @@
         <v>790</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:13" ht="16" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
         <v>13</v>
       </c>
@@ -16851,7 +16209,7 @@
       <c r="C8">
         <v>248</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="D8" s="32" t="s">
         <v>769</v>
       </c>
       <c r="E8" s="6" t="s">
@@ -16882,7 +16240,7 @@
         <v>791</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:13" ht="16" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
         <v>13</v>
       </c>
@@ -16892,7 +16250,7 @@
       <c r="C9">
         <v>249</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="D9" s="32" t="s">
         <v>770</v>
       </c>
       <c r="E9" s="6" t="s">
@@ -16923,7 +16281,7 @@
         <v>792</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:13" ht="16" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
         <v>13</v>
       </c>
@@ -16933,7 +16291,7 @@
       <c r="C10">
         <v>250</v>
       </c>
-      <c r="D10" s="6" t="s">
+      <c r="D10" s="32" t="s">
         <v>771</v>
       </c>
       <c r="E10" s="6" t="s">
@@ -16964,7 +16322,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:13" ht="16" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
         <v>13</v>
       </c>
@@ -16974,7 +16332,7 @@
       <c r="C11">
         <v>251</v>
       </c>
-      <c r="D11" s="6" t="s">
+      <c r="D11" s="32" t="s">
         <v>772</v>
       </c>
       <c r="E11" s="6" t="s">
@@ -17005,7 +16363,7 @@
         <v>794</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:13" ht="16" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
         <v>13</v>
       </c>
@@ -17015,7 +16373,7 @@
       <c r="C12">
         <v>252</v>
       </c>
-      <c r="D12" s="6" t="s">
+      <c r="D12" s="32" t="s">
         <v>773</v>
       </c>
       <c r="E12" s="6" t="s">
@@ -17046,7 +16404,7 @@
         <v>795</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:13" ht="16" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
         <v>13</v>
       </c>
@@ -17056,7 +16414,7 @@
       <c r="C13">
         <v>253</v>
       </c>
-      <c r="D13" s="6" t="s">
+      <c r="D13" s="32" t="s">
         <v>774</v>
       </c>
       <c r="E13" s="6" t="s">
@@ -17087,7 +16445,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:13" ht="16" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
         <v>13</v>
       </c>
@@ -17097,7 +16455,7 @@
       <c r="C14">
         <v>254</v>
       </c>
-      <c r="D14" s="6" t="s">
+      <c r="D14" s="32" t="s">
         <v>775</v>
       </c>
       <c r="E14" s="6" t="s">
@@ -17128,7 +16486,7 @@
         <v>797</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:13" ht="16" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
         <v>13</v>
       </c>
@@ -17138,7 +16496,7 @@
       <c r="C15">
         <v>255</v>
       </c>
-      <c r="D15" s="6" t="s">
+      <c r="D15" s="32" t="s">
         <v>776</v>
       </c>
       <c r="E15" s="6" t="s">
@@ -17169,7 +16527,7 @@
         <v>798</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:13" ht="16" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
         <v>13</v>
       </c>
@@ -17179,7 +16537,7 @@
       <c r="C16">
         <v>256</v>
       </c>
-      <c r="D16" s="6" t="s">
+      <c r="D16" s="32" t="s">
         <v>777</v>
       </c>
       <c r="E16" s="6" t="s">
@@ -17210,7 +16568,7 @@
         <v>799</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:13" ht="16" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
         <v>13</v>
       </c>
@@ -17220,7 +16578,7 @@
       <c r="C17">
         <v>257</v>
       </c>
-      <c r="D17" s="6" t="s">
+      <c r="D17" s="32" t="s">
         <v>778</v>
       </c>
       <c r="E17" s="6" t="s">
@@ -17261,7 +16619,7 @@
       <c r="C18">
         <v>258</v>
       </c>
-      <c r="D18" s="6" t="s">
+      <c r="D18" s="32" t="s">
         <v>779</v>
       </c>
       <c r="E18" s="6" t="s">
@@ -17292,7 +16650,7 @@
         <v>801</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:13" ht="16" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
         <v>13</v>
       </c>
@@ -17302,7 +16660,7 @@
       <c r="C19">
         <v>259</v>
       </c>
-      <c r="D19" s="6" t="s">
+      <c r="D19" s="32" t="s">
         <v>780</v>
       </c>
       <c r="E19" s="6" t="s">
@@ -17333,7 +16691,7 @@
         <v>802</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:13" ht="16" x14ac:dyDescent="0.4">
       <c r="A20" t="s">
         <v>13</v>
       </c>
@@ -17343,7 +16701,7 @@
       <c r="C20">
         <v>260</v>
       </c>
-      <c r="D20" s="6" t="s">
+      <c r="D20" s="32" t="s">
         <v>781</v>
       </c>
       <c r="E20" s="6" t="s">
@@ -17376,2536 +16734,6 @@
     </row>
   </sheetData>
   <phoneticPr fontId="12" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5DD793A8-CD91-4786-8377-89E3BC40F96B}">
-  <dimension ref="A1:M11"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="2" max="2" width="8.54296875" customWidth="1"/>
-    <col min="4" max="4" width="30.6328125" customWidth="1"/>
-    <col min="5" max="5" width="15.90625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="52.81640625" customWidth="1"/>
-    <col min="7" max="7" width="9.81640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12" customWidth="1"/>
-    <col min="9" max="9" width="16.6328125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.1796875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.90625" customWidth="1"/>
-    <col min="12" max="12" width="13.1796875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="35.08984375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="23" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>523</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B2" t="s">
-        <v>275</v>
-      </c>
-      <c r="C2">
-        <v>261</v>
-      </c>
-      <c r="D2" s="25" t="s">
-        <v>828</v>
-      </c>
-      <c r="E2" t="s">
-        <v>116</v>
-      </c>
-      <c r="F2" t="s">
-        <v>841</v>
-      </c>
-      <c r="G2" s="25" t="s">
-        <v>18</v>
-      </c>
-      <c r="H2" s="25" t="s">
-        <v>392</v>
-      </c>
-      <c r="I2" t="s">
-        <v>226</v>
-      </c>
-      <c r="J2" t="s">
-        <v>116</v>
-      </c>
-      <c r="L2" t="s">
-        <v>146</v>
-      </c>
-      <c r="M2" s="18" t="s">
-        <v>824</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B3" t="s">
-        <v>275</v>
-      </c>
-      <c r="C3">
-        <v>262</v>
-      </c>
-      <c r="D3" s="25" t="s">
-        <v>829</v>
-      </c>
-      <c r="E3" t="s">
-        <v>116</v>
-      </c>
-      <c r="F3" t="s">
-        <v>842</v>
-      </c>
-      <c r="G3" s="25" t="s">
-        <v>18</v>
-      </c>
-      <c r="H3" s="25" t="s">
-        <v>159</v>
-      </c>
-      <c r="I3" t="s">
-        <v>226</v>
-      </c>
-      <c r="J3" t="s">
-        <v>116</v>
-      </c>
-      <c r="L3" t="s">
-        <v>146</v>
-      </c>
-      <c r="M3" s="18" t="s">
-        <v>824</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B4" t="s">
-        <v>275</v>
-      </c>
-      <c r="C4">
-        <v>263</v>
-      </c>
-      <c r="D4" s="25" t="s">
-        <v>830</v>
-      </c>
-      <c r="E4" t="s">
-        <v>116</v>
-      </c>
-      <c r="F4" t="s">
-        <v>843</v>
-      </c>
-      <c r="G4" s="25" t="s">
-        <v>18</v>
-      </c>
-      <c r="H4" s="25" t="s">
-        <v>159</v>
-      </c>
-      <c r="I4" t="s">
-        <v>226</v>
-      </c>
-      <c r="J4" t="s">
-        <v>116</v>
-      </c>
-      <c r="L4" t="s">
-        <v>146</v>
-      </c>
-      <c r="M4" s="18" t="s">
-        <v>824</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" t="s">
-        <v>275</v>
-      </c>
-      <c r="C5">
-        <v>264</v>
-      </c>
-      <c r="D5" s="25" t="s">
-        <v>831</v>
-      </c>
-      <c r="E5" t="s">
-        <v>116</v>
-      </c>
-      <c r="F5" t="s">
-        <v>844</v>
-      </c>
-      <c r="G5" s="25" t="s">
-        <v>18</v>
-      </c>
-      <c r="H5" s="25" t="s">
-        <v>392</v>
-      </c>
-      <c r="I5" t="s">
-        <v>226</v>
-      </c>
-      <c r="J5" t="s">
-        <v>116</v>
-      </c>
-      <c r="L5" t="s">
-        <v>146</v>
-      </c>
-      <c r="M5" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" t="s">
-        <v>275</v>
-      </c>
-      <c r="C6">
-        <v>265</v>
-      </c>
-      <c r="D6" s="25" t="s">
-        <v>832</v>
-      </c>
-      <c r="E6" t="s">
-        <v>116</v>
-      </c>
-      <c r="F6" t="s">
-        <v>845</v>
-      </c>
-      <c r="G6" s="25" t="s">
-        <v>18</v>
-      </c>
-      <c r="H6" s="25" t="s">
-        <v>159</v>
-      </c>
-      <c r="I6" t="s">
-        <v>226</v>
-      </c>
-      <c r="J6" t="s">
-        <v>116</v>
-      </c>
-      <c r="L6" t="s">
-        <v>146</v>
-      </c>
-      <c r="M6" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>13</v>
-      </c>
-      <c r="B7" t="s">
-        <v>275</v>
-      </c>
-      <c r="C7">
-        <v>266</v>
-      </c>
-      <c r="D7" s="25" t="s">
-        <v>833</v>
-      </c>
-      <c r="E7" t="s">
-        <v>116</v>
-      </c>
-      <c r="F7" t="s">
-        <v>846</v>
-      </c>
-      <c r="G7" s="25" t="s">
-        <v>18</v>
-      </c>
-      <c r="H7" s="25" t="s">
-        <v>159</v>
-      </c>
-      <c r="I7" t="s">
-        <v>226</v>
-      </c>
-      <c r="J7" t="s">
-        <v>116</v>
-      </c>
-      <c r="L7" t="s">
-        <v>146</v>
-      </c>
-      <c r="M7" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>13</v>
-      </c>
-      <c r="B8" t="s">
-        <v>275</v>
-      </c>
-      <c r="C8">
-        <v>267</v>
-      </c>
-      <c r="D8" s="25" t="s">
-        <v>834</v>
-      </c>
-      <c r="E8" t="s">
-        <v>116</v>
-      </c>
-      <c r="F8" t="s">
-        <v>847</v>
-      </c>
-      <c r="G8" s="25" t="s">
-        <v>18</v>
-      </c>
-      <c r="H8" s="25" t="s">
-        <v>392</v>
-      </c>
-      <c r="I8" t="s">
-        <v>226</v>
-      </c>
-      <c r="J8" t="s">
-        <v>823</v>
-      </c>
-      <c r="L8" t="s">
-        <v>146</v>
-      </c>
-      <c r="M8" s="18" t="s">
-        <v>826</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>13</v>
-      </c>
-      <c r="B9" t="s">
-        <v>275</v>
-      </c>
-      <c r="C9">
-        <v>268</v>
-      </c>
-      <c r="D9" s="25" t="s">
-        <v>835</v>
-      </c>
-      <c r="E9" t="s">
-        <v>116</v>
-      </c>
-      <c r="F9" t="s">
-        <v>848</v>
-      </c>
-      <c r="G9" s="25" t="s">
-        <v>18</v>
-      </c>
-      <c r="H9" s="25" t="s">
-        <v>159</v>
-      </c>
-      <c r="I9" t="s">
-        <v>226</v>
-      </c>
-      <c r="J9" t="s">
-        <v>823</v>
-      </c>
-      <c r="L9" t="s">
-        <v>146</v>
-      </c>
-      <c r="M9" s="18" t="s">
-        <v>826</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
-        <v>13</v>
-      </c>
-      <c r="B10" t="s">
-        <v>275</v>
-      </c>
-      <c r="C10">
-        <v>269</v>
-      </c>
-      <c r="D10" s="25" t="s">
-        <v>836</v>
-      </c>
-      <c r="E10" t="s">
-        <v>116</v>
-      </c>
-      <c r="F10" t="s">
-        <v>839</v>
-      </c>
-      <c r="G10" s="25" t="s">
-        <v>18</v>
-      </c>
-      <c r="H10" s="25" t="s">
-        <v>219</v>
-      </c>
-      <c r="I10" t="s">
-        <v>226</v>
-      </c>
-      <c r="L10" t="s">
-        <v>146</v>
-      </c>
-      <c r="M10" s="18" t="s">
-        <v>838</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
-        <v>13</v>
-      </c>
-      <c r="B11" t="s">
-        <v>275</v>
-      </c>
-      <c r="C11">
-        <v>270</v>
-      </c>
-      <c r="D11" s="25" t="s">
-        <v>837</v>
-      </c>
-      <c r="E11" t="s">
-        <v>116</v>
-      </c>
-      <c r="F11" t="s">
-        <v>840</v>
-      </c>
-      <c r="G11" s="25" t="s">
-        <v>30</v>
-      </c>
-      <c r="H11" s="25" t="s">
-        <v>219</v>
-      </c>
-      <c r="I11" t="s">
-        <v>31</v>
-      </c>
-      <c r="L11" t="s">
-        <v>146</v>
-      </c>
-      <c r="M11" s="18" t="s">
-        <v>827</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF337E51-0D9D-46A6-9DB2-8DF5F9FC1667}">
-  <dimension ref="A1:M37"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="4" max="4" width="43.6328125" customWidth="1"/>
-    <col min="5" max="5" width="15.90625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="58.453125" customWidth="1"/>
-    <col min="7" max="7" width="9.81640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.90625" customWidth="1"/>
-    <col min="9" max="9" width="16.6328125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.1796875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.26953125" customWidth="1"/>
-    <col min="12" max="12" width="13.1796875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="49.90625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="23" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>523</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B2" t="s">
-        <v>275</v>
-      </c>
-      <c r="C2">
-        <v>271</v>
-      </c>
-      <c r="D2" s="33" t="s">
-        <v>481</v>
-      </c>
-      <c r="E2" s="33" t="s">
-        <v>266</v>
-      </c>
-      <c r="F2" t="s">
-        <v>914</v>
-      </c>
-      <c r="G2" s="33" t="s">
-        <v>18</v>
-      </c>
-      <c r="H2" s="33" t="s">
-        <v>219</v>
-      </c>
-      <c r="I2" s="33" t="s">
-        <v>20</v>
-      </c>
-      <c r="J2" s="6" t="s">
-        <v>445</v>
-      </c>
-      <c r="L2" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="M2" s="6" t="s">
-        <v>482</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B3" t="s">
-        <v>275</v>
-      </c>
-      <c r="C3">
-        <v>272</v>
-      </c>
-      <c r="D3" s="33" t="s">
-        <v>483</v>
-      </c>
-      <c r="E3" s="33" t="s">
-        <v>266</v>
-      </c>
-      <c r="F3" t="s">
-        <v>917</v>
-      </c>
-      <c r="G3" s="33" t="s">
-        <v>18</v>
-      </c>
-      <c r="H3" s="33" t="s">
-        <v>392</v>
-      </c>
-      <c r="I3" s="33" t="s">
-        <v>20</v>
-      </c>
-      <c r="J3" s="6" t="s">
-        <v>445</v>
-      </c>
-      <c r="L3" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="M3" s="6" t="s">
-        <v>484</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B4" t="s">
-        <v>275</v>
-      </c>
-      <c r="C4">
-        <v>273</v>
-      </c>
-      <c r="D4" s="33" t="s">
-        <v>479</v>
-      </c>
-      <c r="E4" s="33" t="s">
-        <v>266</v>
-      </c>
-      <c r="F4" t="s">
-        <v>919</v>
-      </c>
-      <c r="G4" s="33" t="s">
-        <v>18</v>
-      </c>
-      <c r="H4" s="33" t="s">
-        <v>219</v>
-      </c>
-      <c r="I4" s="33" t="s">
-        <v>20</v>
-      </c>
-      <c r="J4" s="6" t="s">
-        <v>445</v>
-      </c>
-      <c r="L4" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="M4" s="6" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" t="s">
-        <v>275</v>
-      </c>
-      <c r="C5">
-        <v>274</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>849</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="F5" t="s">
-        <v>915</v>
-      </c>
-      <c r="G5" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="H5" s="6" t="s">
-        <v>143</v>
-      </c>
-      <c r="I5" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="J5" s="6" t="s">
-        <v>445</v>
-      </c>
-      <c r="L5" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="M5" s="6" t="s">
-        <v>872</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" t="s">
-        <v>275</v>
-      </c>
-      <c r="C6">
-        <v>275</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>850</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="F6" t="s">
-        <v>918</v>
-      </c>
-      <c r="G6" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="H6" s="6" t="s">
-        <v>143</v>
-      </c>
-      <c r="I6" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="J6" s="6" t="s">
-        <v>445</v>
-      </c>
-      <c r="L6" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="M6" s="6" t="s">
-        <v>873</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>13</v>
-      </c>
-      <c r="B7" t="s">
-        <v>275</v>
-      </c>
-      <c r="C7">
-        <v>276</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>851</v>
-      </c>
-      <c r="E7" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="F7" t="s">
-        <v>920</v>
-      </c>
-      <c r="G7" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="H7" s="6" t="s">
-        <v>219</v>
-      </c>
-      <c r="I7" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="J7" s="6" t="s">
-        <v>445</v>
-      </c>
-      <c r="L7" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="M7" s="6" t="s">
-        <v>874</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>13</v>
-      </c>
-      <c r="B8" t="s">
-        <v>275</v>
-      </c>
-      <c r="C8">
-        <v>277</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>852</v>
-      </c>
-      <c r="E8" s="33" t="s">
-        <v>266</v>
-      </c>
-      <c r="F8" t="s">
-        <v>921</v>
-      </c>
-      <c r="G8" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="H8" s="6" t="s">
-        <v>219</v>
-      </c>
-      <c r="I8" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="J8" s="6" t="s">
-        <v>871</v>
-      </c>
-      <c r="L8" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="M8" s="6" t="s">
-        <v>875</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>13</v>
-      </c>
-      <c r="B9" t="s">
-        <v>275</v>
-      </c>
-      <c r="C9">
-        <v>278</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>853</v>
-      </c>
-      <c r="E9" s="33" t="s">
-        <v>266</v>
-      </c>
-      <c r="F9" t="s">
-        <v>922</v>
-      </c>
-      <c r="G9" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="H9" s="6" t="s">
-        <v>219</v>
-      </c>
-      <c r="I9" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="J9" s="6" t="s">
-        <v>871</v>
-      </c>
-      <c r="L9" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="M9" s="6" t="s">
-        <v>876</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
-        <v>13</v>
-      </c>
-      <c r="B10" t="s">
-        <v>275</v>
-      </c>
-      <c r="C10">
-        <v>279</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>854</v>
-      </c>
-      <c r="E10" s="33" t="s">
-        <v>266</v>
-      </c>
-      <c r="F10" t="s">
-        <v>923</v>
-      </c>
-      <c r="G10" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="H10" s="6" t="s">
-        <v>219</v>
-      </c>
-      <c r="I10" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="J10" s="6" t="s">
-        <v>871</v>
-      </c>
-      <c r="L10" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="M10" s="6" t="s">
-        <v>877</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
-        <v>13</v>
-      </c>
-      <c r="B11" t="s">
-        <v>275</v>
-      </c>
-      <c r="C11">
-        <v>280</v>
-      </c>
-      <c r="D11" s="6" t="s">
-        <v>905</v>
-      </c>
-      <c r="E11" s="33" t="s">
-        <v>266</v>
-      </c>
-      <c r="F11" t="s">
-        <v>924</v>
-      </c>
-      <c r="G11" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="H11" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="I11" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="J11" s="6" t="s">
-        <v>871</v>
-      </c>
-      <c r="L11" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="M11" s="6" t="s">
-        <v>878</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
-        <v>13</v>
-      </c>
-      <c r="B12" t="s">
-        <v>275</v>
-      </c>
-      <c r="C12">
-        <v>281</v>
-      </c>
-      <c r="D12" s="6" t="s">
-        <v>906</v>
-      </c>
-      <c r="E12" s="33" t="s">
-        <v>266</v>
-      </c>
-      <c r="F12" t="s">
-        <v>925</v>
-      </c>
-      <c r="G12" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="H12" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="I12" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="J12" s="6" t="s">
-        <v>871</v>
-      </c>
-      <c r="L12" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="M12" s="6" t="s">
-        <v>879</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
-        <v>13</v>
-      </c>
-      <c r="B13" t="s">
-        <v>275</v>
-      </c>
-      <c r="C13">
-        <v>282</v>
-      </c>
-      <c r="D13" s="6" t="s">
-        <v>907</v>
-      </c>
-      <c r="E13" s="33" t="s">
-        <v>266</v>
-      </c>
-      <c r="F13" t="s">
-        <v>926</v>
-      </c>
-      <c r="G13" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="H13" s="6" t="s">
-        <v>159</v>
-      </c>
-      <c r="I13" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="J13" s="6" t="s">
-        <v>871</v>
-      </c>
-      <c r="L13" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="M13" s="6" t="s">
-        <v>880</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
-        <v>13</v>
-      </c>
-      <c r="B14" t="s">
-        <v>275</v>
-      </c>
-      <c r="C14">
-        <v>283</v>
-      </c>
-      <c r="D14" s="6" t="s">
-        <v>908</v>
-      </c>
-      <c r="E14" s="33" t="s">
-        <v>266</v>
-      </c>
-      <c r="F14" t="s">
-        <v>927</v>
-      </c>
-      <c r="G14" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="H14" s="6" t="s">
-        <v>159</v>
-      </c>
-      <c r="I14" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="J14" s="6" t="s">
-        <v>871</v>
-      </c>
-      <c r="L14" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="M14" s="6" t="s">
-        <v>881</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A15" t="s">
-        <v>13</v>
-      </c>
-      <c r="B15" t="s">
-        <v>275</v>
-      </c>
-      <c r="C15">
-        <v>284</v>
-      </c>
-      <c r="D15" s="6" t="s">
-        <v>909</v>
-      </c>
-      <c r="E15" s="33" t="s">
-        <v>266</v>
-      </c>
-      <c r="F15" t="s">
-        <v>928</v>
-      </c>
-      <c r="G15" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="H15" s="6" t="s">
-        <v>159</v>
-      </c>
-      <c r="I15" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="J15" s="6" t="s">
-        <v>871</v>
-      </c>
-      <c r="L15" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="M15" s="6" t="s">
-        <v>882</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A16" t="s">
-        <v>13</v>
-      </c>
-      <c r="B16" t="s">
-        <v>275</v>
-      </c>
-      <c r="C16">
-        <v>285</v>
-      </c>
-      <c r="D16" s="6" t="s">
-        <v>910</v>
-      </c>
-      <c r="E16" s="33" t="s">
-        <v>266</v>
-      </c>
-      <c r="F16" t="s">
-        <v>929</v>
-      </c>
-      <c r="G16" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="H16" s="6" t="s">
-        <v>159</v>
-      </c>
-      <c r="I16" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="J16" s="6" t="s">
-        <v>871</v>
-      </c>
-      <c r="L16" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="M16" s="6" t="s">
-        <v>883</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A17" t="s">
-        <v>13</v>
-      </c>
-      <c r="B17" t="s">
-        <v>275</v>
-      </c>
-      <c r="C17">
-        <v>286</v>
-      </c>
-      <c r="D17" s="6" t="s">
-        <v>911</v>
-      </c>
-      <c r="E17" s="33" t="s">
-        <v>266</v>
-      </c>
-      <c r="F17" t="s">
-        <v>930</v>
-      </c>
-      <c r="G17" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="H17" s="6" t="s">
-        <v>159</v>
-      </c>
-      <c r="I17" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="J17" s="6" t="s">
-        <v>871</v>
-      </c>
-      <c r="L17" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="M17" s="6" t="s">
-        <v>884</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A18" t="s">
-        <v>13</v>
-      </c>
-      <c r="B18" t="s">
-        <v>275</v>
-      </c>
-      <c r="C18">
-        <v>287</v>
-      </c>
-      <c r="D18" s="33" t="s">
-        <v>912</v>
-      </c>
-      <c r="E18" s="33" t="s">
-        <v>266</v>
-      </c>
-      <c r="F18" t="s">
-        <v>931</v>
-      </c>
-      <c r="G18" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="H18" s="6" t="s">
-        <v>392</v>
-      </c>
-      <c r="I18" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="J18" s="6" t="s">
-        <v>871</v>
-      </c>
-      <c r="L18" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="M18" s="6" t="s">
-        <v>885</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A19" t="s">
-        <v>13</v>
-      </c>
-      <c r="B19" t="s">
-        <v>275</v>
-      </c>
-      <c r="C19">
-        <v>288</v>
-      </c>
-      <c r="D19" s="30" t="s">
-        <v>511</v>
-      </c>
-      <c r="E19" s="33" t="s">
-        <v>266</v>
-      </c>
-      <c r="F19" t="s">
-        <v>932</v>
-      </c>
-      <c r="G19" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="H19" s="6" t="s">
-        <v>143</v>
-      </c>
-      <c r="I19" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="J19" s="6" t="s">
-        <v>871</v>
-      </c>
-      <c r="L19" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="M19" s="6" t="s">
-        <v>886</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A20" t="s">
-        <v>13</v>
-      </c>
-      <c r="B20" t="s">
-        <v>275</v>
-      </c>
-      <c r="C20">
-        <v>289</v>
-      </c>
-      <c r="D20" s="6" t="s">
-        <v>855</v>
-      </c>
-      <c r="E20" s="6" t="s">
-        <v>913</v>
-      </c>
-      <c r="F20" t="s">
-        <v>943</v>
-      </c>
-      <c r="G20" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="H20" s="6" t="s">
-        <v>159</v>
-      </c>
-      <c r="I20" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="J20" s="6" t="s">
-        <v>871</v>
-      </c>
-      <c r="L20" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="M20" s="6" t="s">
-        <v>887</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A21" t="s">
-        <v>13</v>
-      </c>
-      <c r="B21" t="s">
-        <v>275</v>
-      </c>
-      <c r="C21">
-        <v>290</v>
-      </c>
-      <c r="D21" s="17" t="s">
-        <v>856</v>
-      </c>
-      <c r="E21" s="6" t="s">
-        <v>913</v>
-      </c>
-      <c r="F21" t="s">
-        <v>944</v>
-      </c>
-      <c r="G21" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="H21" s="6" t="s">
-        <v>159</v>
-      </c>
-      <c r="I21" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="J21" s="6" t="s">
-        <v>871</v>
-      </c>
-      <c r="L21" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="M21" s="6" t="s">
-        <v>888</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A22" t="s">
-        <v>13</v>
-      </c>
-      <c r="B22" t="s">
-        <v>275</v>
-      </c>
-      <c r="C22">
-        <v>291</v>
-      </c>
-      <c r="D22" s="17" t="s">
-        <v>265</v>
-      </c>
-      <c r="E22" s="6" t="s">
-        <v>913</v>
-      </c>
-      <c r="F22" t="s">
-        <v>945</v>
-      </c>
-      <c r="G22" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="H22" s="6" t="s">
-        <v>159</v>
-      </c>
-      <c r="I22" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="J22" s="6" t="s">
-        <v>871</v>
-      </c>
-      <c r="L22" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="M22" s="6" t="s">
-        <v>889</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A23" t="s">
-        <v>13</v>
-      </c>
-      <c r="B23" t="s">
-        <v>275</v>
-      </c>
-      <c r="C23">
-        <v>292</v>
-      </c>
-      <c r="D23" s="17" t="s">
-        <v>857</v>
-      </c>
-      <c r="E23" s="6" t="s">
-        <v>913</v>
-      </c>
-      <c r="F23" t="s">
-        <v>946</v>
-      </c>
-      <c r="G23" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="H23" s="6" t="s">
-        <v>159</v>
-      </c>
-      <c r="I23" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="J23" s="6" t="s">
-        <v>871</v>
-      </c>
-      <c r="L23" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="M23" s="6" t="s">
-        <v>890</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A24" t="s">
-        <v>13</v>
-      </c>
-      <c r="B24" t="s">
-        <v>275</v>
-      </c>
-      <c r="C24">
-        <v>293</v>
-      </c>
-      <c r="D24" s="6" t="s">
-        <v>858</v>
-      </c>
-      <c r="E24" s="6" t="s">
-        <v>913</v>
-      </c>
-      <c r="F24" t="s">
-        <v>947</v>
-      </c>
-      <c r="G24" s="6" t="s">
-        <v>564</v>
-      </c>
-      <c r="H24" s="6" t="s">
-        <v>143</v>
-      </c>
-      <c r="I24" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="J24" s="6" t="s">
-        <v>871</v>
-      </c>
-      <c r="L24" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="M24" s="6" t="s">
-        <v>891</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A25" t="s">
-        <v>13</v>
-      </c>
-      <c r="B25" t="s">
-        <v>275</v>
-      </c>
-      <c r="C25">
-        <v>294</v>
-      </c>
-      <c r="D25" s="6" t="s">
-        <v>859</v>
-      </c>
-      <c r="E25" s="6" t="s">
-        <v>913</v>
-      </c>
-      <c r="F25" t="s">
-        <v>948</v>
-      </c>
-      <c r="G25" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="H25" s="6" t="s">
-        <v>159</v>
-      </c>
-      <c r="I25" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="J25" s="6" t="s">
-        <v>871</v>
-      </c>
-      <c r="L25" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="M25" s="6" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A26" t="s">
-        <v>13</v>
-      </c>
-      <c r="B26" t="s">
-        <v>275</v>
-      </c>
-      <c r="C26">
-        <v>295</v>
-      </c>
-      <c r="D26" s="6" t="s">
-        <v>860</v>
-      </c>
-      <c r="E26" s="6" t="s">
-        <v>913</v>
-      </c>
-      <c r="F26" t="s">
-        <v>949</v>
-      </c>
-      <c r="G26" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="H26" s="6" t="s">
-        <v>159</v>
-      </c>
-      <c r="I26" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="J26" s="6" t="s">
-        <v>871</v>
-      </c>
-      <c r="L26" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="M26" s="6" t="s">
-        <v>893</v>
-      </c>
-    </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A27" t="s">
-        <v>13</v>
-      </c>
-      <c r="B27" t="s">
-        <v>275</v>
-      </c>
-      <c r="C27">
-        <v>296</v>
-      </c>
-      <c r="D27" s="17" t="s">
-        <v>269</v>
-      </c>
-      <c r="E27" s="33" t="s">
-        <v>266</v>
-      </c>
-      <c r="F27" t="s">
-        <v>933</v>
-      </c>
-      <c r="G27" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="H27" s="6" t="s">
-        <v>219</v>
-      </c>
-      <c r="I27" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="J27" s="6" t="s">
-        <v>871</v>
-      </c>
-      <c r="L27" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="M27" s="6" t="s">
-        <v>894</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A28" t="s">
-        <v>13</v>
-      </c>
-      <c r="B28" t="s">
-        <v>275</v>
-      </c>
-      <c r="C28">
-        <v>297</v>
-      </c>
-      <c r="D28" s="6" t="s">
-        <v>861</v>
-      </c>
-      <c r="E28" s="33" t="s">
-        <v>266</v>
-      </c>
-      <c r="F28" t="s">
-        <v>934</v>
-      </c>
-      <c r="G28" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="H28" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="I28" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="J28" s="6" t="s">
-        <v>871</v>
-      </c>
-      <c r="L28" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="M28" s="6" t="s">
-        <v>895</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A29" t="s">
-        <v>13</v>
-      </c>
-      <c r="B29" t="s">
-        <v>275</v>
-      </c>
-      <c r="C29">
-        <v>298</v>
-      </c>
-      <c r="D29" s="6" t="s">
-        <v>862</v>
-      </c>
-      <c r="E29" s="33" t="s">
-        <v>266</v>
-      </c>
-      <c r="F29" t="s">
-        <v>935</v>
-      </c>
-      <c r="G29" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="H29" s="6" t="s">
-        <v>219</v>
-      </c>
-      <c r="I29" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="J29" s="6" t="s">
-        <v>871</v>
-      </c>
-      <c r="L29" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="M29" s="6" t="s">
-        <v>896</v>
-      </c>
-    </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A30" t="s">
-        <v>13</v>
-      </c>
-      <c r="B30" t="s">
-        <v>275</v>
-      </c>
-      <c r="C30">
-        <v>299</v>
-      </c>
-      <c r="D30" s="6" t="s">
-        <v>863</v>
-      </c>
-      <c r="E30" s="33" t="s">
-        <v>266</v>
-      </c>
-      <c r="F30" t="s">
-        <v>936</v>
-      </c>
-      <c r="G30" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="H30" s="6" t="s">
-        <v>219</v>
-      </c>
-      <c r="I30" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="J30" s="6" t="s">
-        <v>871</v>
-      </c>
-      <c r="L30" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="M30" s="6" t="s">
-        <v>897</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A31" t="s">
-        <v>13</v>
-      </c>
-      <c r="B31" t="s">
-        <v>275</v>
-      </c>
-      <c r="C31">
-        <v>300</v>
-      </c>
-      <c r="D31" s="17" t="s">
-        <v>864</v>
-      </c>
-      <c r="E31" s="33" t="s">
-        <v>266</v>
-      </c>
-      <c r="F31" t="s">
-        <v>937</v>
-      </c>
-      <c r="G31" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="H31" s="17" t="s">
-        <v>159</v>
-      </c>
-      <c r="I31" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="J31" s="6" t="s">
-        <v>871</v>
-      </c>
-      <c r="L31" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="M31" s="17" t="s">
-        <v>898</v>
-      </c>
-    </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A32" t="s">
-        <v>13</v>
-      </c>
-      <c r="B32" t="s">
-        <v>275</v>
-      </c>
-      <c r="C32">
-        <v>301</v>
-      </c>
-      <c r="D32" s="6" t="s">
-        <v>865</v>
-      </c>
-      <c r="E32" s="33" t="s">
-        <v>266</v>
-      </c>
-      <c r="F32" t="s">
-        <v>939</v>
-      </c>
-      <c r="G32" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="H32" s="17" t="s">
-        <v>159</v>
-      </c>
-      <c r="I32" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="J32" s="6" t="s">
-        <v>871</v>
-      </c>
-      <c r="L32" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="M32" s="6" t="s">
-        <v>899</v>
-      </c>
-    </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A33" t="s">
-        <v>13</v>
-      </c>
-      <c r="B33" t="s">
-        <v>275</v>
-      </c>
-      <c r="C33">
-        <v>302</v>
-      </c>
-      <c r="D33" s="6" t="s">
-        <v>866</v>
-      </c>
-      <c r="E33" s="33" t="s">
-        <v>266</v>
-      </c>
-      <c r="F33" t="s">
-        <v>940</v>
-      </c>
-      <c r="G33" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="H33" s="17" t="s">
-        <v>159</v>
-      </c>
-      <c r="I33" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="J33" s="6" t="s">
-        <v>871</v>
-      </c>
-      <c r="L33" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="M33" s="6" t="s">
-        <v>900</v>
-      </c>
-    </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A34" t="s">
-        <v>13</v>
-      </c>
-      <c r="B34" t="s">
-        <v>275</v>
-      </c>
-      <c r="C34">
-        <v>303</v>
-      </c>
-      <c r="D34" s="6" t="s">
-        <v>867</v>
-      </c>
-      <c r="E34" s="33" t="s">
-        <v>266</v>
-      </c>
-      <c r="F34" t="s">
-        <v>916</v>
-      </c>
-      <c r="G34" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="H34" s="17" t="s">
-        <v>159</v>
-      </c>
-      <c r="I34" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="J34" s="6" t="s">
-        <v>871</v>
-      </c>
-      <c r="L34" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="M34" s="6" t="s">
-        <v>901</v>
-      </c>
-    </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A35" t="s">
-        <v>13</v>
-      </c>
-      <c r="B35" t="s">
-        <v>275</v>
-      </c>
-      <c r="C35">
-        <v>304</v>
-      </c>
-      <c r="D35" s="6" t="s">
-        <v>868</v>
-      </c>
-      <c r="E35" s="33" t="s">
-        <v>266</v>
-      </c>
-      <c r="F35" t="s">
-        <v>941</v>
-      </c>
-      <c r="G35" s="6" t="s">
-        <v>564</v>
-      </c>
-      <c r="H35" s="6" t="s">
-        <v>143</v>
-      </c>
-      <c r="I35" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="J35" s="6" t="s">
-        <v>871</v>
-      </c>
-      <c r="L35" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="M35" s="6" t="s">
-        <v>902</v>
-      </c>
-    </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A36" t="s">
-        <v>13</v>
-      </c>
-      <c r="B36" t="s">
-        <v>275</v>
-      </c>
-      <c r="C36">
-        <v>305</v>
-      </c>
-      <c r="D36" s="6" t="s">
-        <v>869</v>
-      </c>
-      <c r="E36" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="F36" t="s">
-        <v>938</v>
-      </c>
-      <c r="G36" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="H36" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="I36" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="J36" s="6" t="s">
-        <v>445</v>
-      </c>
-      <c r="L36" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="M36" s="6" t="s">
-        <v>903</v>
-      </c>
-    </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A37" t="s">
-        <v>13</v>
-      </c>
-      <c r="B37" t="s">
-        <v>275</v>
-      </c>
-      <c r="C37">
-        <v>306</v>
-      </c>
-      <c r="D37" s="6" t="s">
-        <v>870</v>
-      </c>
-      <c r="E37" s="33" t="s">
-        <v>266</v>
-      </c>
-      <c r="F37" t="s">
-        <v>942</v>
-      </c>
-      <c r="G37" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="H37" s="6" t="s">
-        <v>159</v>
-      </c>
-      <c r="I37" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="J37" s="6" t="s">
-        <v>871</v>
-      </c>
-      <c r="L37" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="M37" s="6" t="s">
-        <v>904</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7A22D2F-6AFE-4D3D-A8D1-BBD797E61616}">
-  <dimension ref="A1:M24"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="4" max="4" width="37.90625" customWidth="1"/>
-    <col min="5" max="5" width="15.90625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="43.26953125" customWidth="1"/>
-    <col min="7" max="7" width="9.81640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.90625" customWidth="1"/>
-    <col min="9" max="9" width="16.6328125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.1796875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.26953125" customWidth="1"/>
-    <col min="12" max="12" width="13.1796875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="49.90625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="23" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>523</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="C2" s="36">
-        <v>307</v>
-      </c>
-      <c r="D2" s="37" t="s">
-        <v>950</v>
-      </c>
-      <c r="E2" s="38" t="s">
-        <v>997</v>
-      </c>
-      <c r="F2" s="36" t="s">
-        <v>998</v>
-      </c>
-      <c r="G2" s="38" t="s">
-        <v>18</v>
-      </c>
-      <c r="H2" s="39" t="s">
-        <v>215</v>
-      </c>
-      <c r="I2" s="38" t="s">
-        <v>20</v>
-      </c>
-      <c r="M2" s="34" t="s">
-        <v>974</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="C3" s="36">
-        <v>308</v>
-      </c>
-      <c r="D3" s="40" t="s">
-        <v>951</v>
-      </c>
-      <c r="E3" s="41" t="s">
-        <v>997</v>
-      </c>
-      <c r="F3" s="36" t="s">
-        <v>999</v>
-      </c>
-      <c r="G3" s="41" t="s">
-        <v>18</v>
-      </c>
-      <c r="H3" s="42" t="s">
-        <v>143</v>
-      </c>
-      <c r="I3" s="41" t="s">
-        <v>20</v>
-      </c>
-      <c r="M3" s="35" t="s">
-        <v>975</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="C4" s="36">
-        <v>309</v>
-      </c>
-      <c r="D4" s="37" t="s">
-        <v>952</v>
-      </c>
-      <c r="E4" s="38" t="s">
-        <v>997</v>
-      </c>
-      <c r="F4" s="36" t="s">
-        <v>1000</v>
-      </c>
-      <c r="G4" s="38" t="s">
-        <v>18</v>
-      </c>
-      <c r="H4" s="39" t="s">
-        <v>215</v>
-      </c>
-      <c r="I4" s="38" t="s">
-        <v>20</v>
-      </c>
-      <c r="M4" s="34" t="s">
-        <v>976</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="C5" s="36">
-        <v>310</v>
-      </c>
-      <c r="D5" s="40" t="s">
-        <v>953</v>
-      </c>
-      <c r="E5" s="41" t="s">
-        <v>997</v>
-      </c>
-      <c r="F5" s="36" t="s">
-        <v>1001</v>
-      </c>
-      <c r="G5" s="41" t="s">
-        <v>18</v>
-      </c>
-      <c r="H5" s="42" t="s">
-        <v>215</v>
-      </c>
-      <c r="I5" s="41" t="s">
-        <v>20</v>
-      </c>
-      <c r="M5" s="35" t="s">
-        <v>977</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="C6" s="36">
-        <v>311</v>
-      </c>
-      <c r="D6" s="37" t="s">
-        <v>954</v>
-      </c>
-      <c r="E6" s="38" t="s">
-        <v>997</v>
-      </c>
-      <c r="F6" s="43" t="s">
-        <v>1002</v>
-      </c>
-      <c r="G6" s="38" t="s">
-        <v>18</v>
-      </c>
-      <c r="H6" s="39" t="s">
-        <v>219</v>
-      </c>
-      <c r="I6" s="38" t="s">
-        <v>20</v>
-      </c>
-      <c r="M6" s="34" t="s">
-        <v>978</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="C7" s="36">
-        <v>312</v>
-      </c>
-      <c r="D7" s="40" t="s">
-        <v>955</v>
-      </c>
-      <c r="E7" s="41" t="s">
-        <v>997</v>
-      </c>
-      <c r="F7" s="43" t="s">
-        <v>1003</v>
-      </c>
-      <c r="G7" s="41" t="s">
-        <v>18</v>
-      </c>
-      <c r="H7" s="42" t="s">
-        <v>219</v>
-      </c>
-      <c r="I7" s="41" t="s">
-        <v>20</v>
-      </c>
-      <c r="M7" s="35" t="s">
-        <v>979</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="C8" s="36">
-        <v>313</v>
-      </c>
-      <c r="D8" s="37" t="s">
-        <v>956</v>
-      </c>
-      <c r="E8" s="38" t="s">
-        <v>997</v>
-      </c>
-      <c r="F8" s="43" t="s">
-        <v>1004</v>
-      </c>
-      <c r="G8" s="38" t="s">
-        <v>18</v>
-      </c>
-      <c r="H8" s="39" t="s">
-        <v>219</v>
-      </c>
-      <c r="I8" s="38" t="s">
-        <v>20</v>
-      </c>
-      <c r="M8" s="34" t="s">
-        <v>980</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="C9" s="36">
-        <v>314</v>
-      </c>
-      <c r="D9" s="40" t="s">
-        <v>957</v>
-      </c>
-      <c r="E9" s="41" t="s">
-        <v>997</v>
-      </c>
-      <c r="F9" s="43" t="s">
-        <v>1005</v>
-      </c>
-      <c r="G9" s="41" t="s">
-        <v>18</v>
-      </c>
-      <c r="H9" s="42" t="s">
-        <v>316</v>
-      </c>
-      <c r="I9" s="41" t="s">
-        <v>20</v>
-      </c>
-      <c r="M9" s="35" t="s">
-        <v>981</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="C10" s="36">
-        <v>315</v>
-      </c>
-      <c r="D10" s="37" t="s">
-        <v>958</v>
-      </c>
-      <c r="E10" s="38" t="s">
-        <v>997</v>
-      </c>
-      <c r="F10" s="43" t="s">
-        <v>1006</v>
-      </c>
-      <c r="G10" s="38" t="s">
-        <v>18</v>
-      </c>
-      <c r="H10" s="39" t="s">
-        <v>143</v>
-      </c>
-      <c r="I10" s="38" t="s">
-        <v>20</v>
-      </c>
-      <c r="M10" s="34" t="s">
-        <v>982</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="C11" s="36">
-        <v>316</v>
-      </c>
-      <c r="D11" s="40" t="s">
-        <v>959</v>
-      </c>
-      <c r="E11" s="41" t="s">
-        <v>997</v>
-      </c>
-      <c r="F11" s="43" t="s">
-        <v>1007</v>
-      </c>
-      <c r="G11" s="41" t="s">
-        <v>18</v>
-      </c>
-      <c r="H11" s="42" t="s">
-        <v>215</v>
-      </c>
-      <c r="I11" s="41" t="s">
-        <v>20</v>
-      </c>
-      <c r="M11" s="35" t="s">
-        <v>983</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="C12" s="36">
-        <v>317</v>
-      </c>
-      <c r="D12" s="37" t="s">
-        <v>960</v>
-      </c>
-      <c r="E12" s="38" t="s">
-        <v>997</v>
-      </c>
-      <c r="F12" s="43" t="s">
-        <v>1008</v>
-      </c>
-      <c r="G12" s="38" t="s">
-        <v>18</v>
-      </c>
-      <c r="H12" s="39" t="s">
-        <v>215</v>
-      </c>
-      <c r="I12" s="38" t="s">
-        <v>20</v>
-      </c>
-      <c r="M12" s="34" t="s">
-        <v>984</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="C13" s="36">
-        <v>318</v>
-      </c>
-      <c r="D13" s="40" t="s">
-        <v>961</v>
-      </c>
-      <c r="E13" s="41" t="s">
-        <v>997</v>
-      </c>
-      <c r="F13" s="43" t="s">
-        <v>1009</v>
-      </c>
-      <c r="G13" s="41" t="s">
-        <v>18</v>
-      </c>
-      <c r="H13" s="42" t="s">
-        <v>215</v>
-      </c>
-      <c r="I13" s="41" t="s">
-        <v>20</v>
-      </c>
-      <c r="M13" s="35" t="s">
-        <v>985</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="C14" s="36">
-        <v>319</v>
-      </c>
-      <c r="D14" s="37" t="s">
-        <v>962</v>
-      </c>
-      <c r="E14" s="38" t="s">
-        <v>997</v>
-      </c>
-      <c r="F14" s="43" t="s">
-        <v>1010</v>
-      </c>
-      <c r="G14" s="38" t="s">
-        <v>30</v>
-      </c>
-      <c r="H14" s="39" t="s">
-        <v>215</v>
-      </c>
-      <c r="I14" s="38" t="s">
-        <v>144</v>
-      </c>
-      <c r="M14" s="34" t="s">
-        <v>986</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="C15" s="36">
-        <v>320</v>
-      </c>
-      <c r="D15" s="40" t="s">
-        <v>288</v>
-      </c>
-      <c r="E15" s="41" t="s">
-        <v>997</v>
-      </c>
-      <c r="F15" s="43" t="s">
-        <v>1011</v>
-      </c>
-      <c r="G15" s="41" t="s">
-        <v>564</v>
-      </c>
-      <c r="H15" s="42" t="s">
-        <v>972</v>
-      </c>
-      <c r="I15" s="41" t="s">
-        <v>20</v>
-      </c>
-      <c r="M15" s="35" t="s">
-        <v>987</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="C16" s="36">
-        <v>321</v>
-      </c>
-      <c r="D16" s="37" t="s">
-        <v>963</v>
-      </c>
-      <c r="E16" s="38" t="s">
-        <v>997</v>
-      </c>
-      <c r="F16" s="43" t="s">
-        <v>1012</v>
-      </c>
-      <c r="G16" s="38" t="s">
-        <v>18</v>
-      </c>
-      <c r="H16" s="39" t="s">
-        <v>215</v>
-      </c>
-      <c r="I16" s="38" t="s">
-        <v>20</v>
-      </c>
-      <c r="M16" s="34" t="s">
-        <v>988</v>
-      </c>
-    </row>
-    <row r="17" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="C17" s="36">
-        <v>322</v>
-      </c>
-      <c r="D17" s="40" t="s">
-        <v>964</v>
-      </c>
-      <c r="E17" s="41" t="s">
-        <v>997</v>
-      </c>
-      <c r="F17" s="43" t="s">
-        <v>1013</v>
-      </c>
-      <c r="G17" s="41" t="s">
-        <v>30</v>
-      </c>
-      <c r="H17" s="42" t="s">
-        <v>215</v>
-      </c>
-      <c r="I17" s="41" t="s">
-        <v>144</v>
-      </c>
-      <c r="M17" s="35" t="s">
-        <v>989</v>
-      </c>
-    </row>
-    <row r="18" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="C18" s="36">
-        <v>323</v>
-      </c>
-      <c r="D18" s="37" t="s">
-        <v>965</v>
-      </c>
-      <c r="E18" s="38" t="s">
-        <v>997</v>
-      </c>
-      <c r="F18" s="43" t="s">
-        <v>1014</v>
-      </c>
-      <c r="G18" s="41" t="s">
-        <v>30</v>
-      </c>
-      <c r="H18" s="39" t="s">
-        <v>973</v>
-      </c>
-      <c r="I18" s="38" t="s">
-        <v>144</v>
-      </c>
-      <c r="M18" s="34" t="s">
-        <v>990</v>
-      </c>
-    </row>
-    <row r="19" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="C19" s="36">
-        <v>324</v>
-      </c>
-      <c r="D19" s="40" t="s">
-        <v>966</v>
-      </c>
-      <c r="E19" s="41" t="s">
-        <v>997</v>
-      </c>
-      <c r="F19" s="43" t="s">
-        <v>1015</v>
-      </c>
-      <c r="G19" s="41" t="s">
-        <v>30</v>
-      </c>
-      <c r="H19" s="42" t="s">
-        <v>150</v>
-      </c>
-      <c r="I19" s="41" t="s">
-        <v>144</v>
-      </c>
-      <c r="M19" s="35" t="s">
-        <v>991</v>
-      </c>
-    </row>
-    <row r="20" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="C20" s="36">
-        <v>325</v>
-      </c>
-      <c r="D20" s="37" t="s">
-        <v>967</v>
-      </c>
-      <c r="E20" s="38" t="s">
-        <v>997</v>
-      </c>
-      <c r="F20" s="43" t="s">
-        <v>1016</v>
-      </c>
-      <c r="G20" s="41" t="s">
-        <v>30</v>
-      </c>
-      <c r="H20" s="39" t="s">
-        <v>215</v>
-      </c>
-      <c r="I20" s="38" t="s">
-        <v>144</v>
-      </c>
-      <c r="M20" s="34" t="s">
-        <v>992</v>
-      </c>
-    </row>
-    <row r="21" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="C21" s="36">
-        <v>326</v>
-      </c>
-      <c r="D21" s="40" t="s">
-        <v>968</v>
-      </c>
-      <c r="E21" s="41" t="s">
-        <v>997</v>
-      </c>
-      <c r="F21" s="43" t="s">
-        <v>1017</v>
-      </c>
-      <c r="G21" s="41" t="s">
-        <v>30</v>
-      </c>
-      <c r="H21" s="42" t="s">
-        <v>316</v>
-      </c>
-      <c r="I21" s="41" t="s">
-        <v>144</v>
-      </c>
-      <c r="M21" s="35" t="s">
-        <v>993</v>
-      </c>
-    </row>
-    <row r="22" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="C22" s="36">
-        <v>327</v>
-      </c>
-      <c r="D22" s="37" t="s">
-        <v>969</v>
-      </c>
-      <c r="E22" s="38" t="s">
-        <v>997</v>
-      </c>
-      <c r="F22" s="43" t="s">
-        <v>1018</v>
-      </c>
-      <c r="G22" s="41" t="s">
-        <v>30</v>
-      </c>
-      <c r="H22" s="39" t="s">
-        <v>316</v>
-      </c>
-      <c r="I22" s="38" t="s">
-        <v>144</v>
-      </c>
-      <c r="M22" s="34" t="s">
-        <v>994</v>
-      </c>
-    </row>
-    <row r="23" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="C23" s="36">
-        <v>328</v>
-      </c>
-      <c r="D23" s="40" t="s">
-        <v>970</v>
-      </c>
-      <c r="E23" s="41" t="s">
-        <v>997</v>
-      </c>
-      <c r="F23" s="43" t="s">
-        <v>1019</v>
-      </c>
-      <c r="G23" s="41" t="s">
-        <v>30</v>
-      </c>
-      <c r="H23" s="42" t="s">
-        <v>316</v>
-      </c>
-      <c r="I23" s="41" t="s">
-        <v>144</v>
-      </c>
-      <c r="M23" s="35" t="s">
-        <v>995</v>
-      </c>
-    </row>
-    <row r="24" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="C24" s="36">
-        <v>329</v>
-      </c>
-      <c r="D24" s="37" t="s">
-        <v>971</v>
-      </c>
-      <c r="E24" s="38" t="s">
-        <v>997</v>
-      </c>
-      <c r="F24" s="43" t="s">
-        <v>1020</v>
-      </c>
-      <c r="G24" s="41" t="s">
-        <v>30</v>
-      </c>
-      <c r="H24" s="39" t="s">
-        <v>143</v>
-      </c>
-      <c r="I24" s="38" t="s">
-        <v>144</v>
-      </c>
-      <c r="M24" s="34" t="s">
-        <v>996</v>
-      </c>
-    </row>
-  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/docs/CDOP_SCHEMA.xlsx
+++ b/docs/CDOP_SCHEMA.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rockmtnins-my.sharepoint.com/personal/sebastian_weeks_rmi_org/Documents/Documents/CDOP Resources/UseCase_Category CSVs_JSONs/Master Version/8_25_26/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rockmtnins-my.sharepoint.com/personal/sebastian_weeks_rmi_org/Documents/Documents/CDOP Resources/UseCase_Category CSVs_JSONs/Master Version/Round 2 Pods for Testing/Fast Track Pods/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="118" documentId="8_{E4888AF0-8469-49B9-BF1F-D7429471A122}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{51AF62E9-238E-47E0-BF18-8C0C7E464784}"/>
+  <xr:revisionPtr revIDLastSave="472" documentId="8_{E4888AF0-8469-49B9-BF1F-D7429471A122}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{805E69B9-42B6-4388-969F-9DB549C29CA3}"/>
   <bookViews>
-    <workbookView xWindow="-28215" yWindow="375" windowWidth="27555" windowHeight="15045" activeTab="11" xr2:uid="{743398AF-A4FE-47C4-9368-972E95242EBF}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="3" xr2:uid="{743398AF-A4FE-47C4-9368-972E95242EBF}"/>
   </bookViews>
   <sheets>
     <sheet name="Full List" sheetId="5" r:id="rId1"/>
@@ -25,6 +25,9 @@
     <sheet name="Durability_Permanence" sheetId="10" r:id="rId10"/>
     <sheet name="Project Finance" sheetId="11" r:id="rId11"/>
     <sheet name="Labels_Certifications" sheetId="12" r:id="rId12"/>
+    <sheet name="Registry_Metadata" sheetId="13" r:id="rId13"/>
+    <sheet name="Validation_Metadata" sheetId="14" r:id="rId14"/>
+    <sheet name="Verification_Metadata" sheetId="15" r:id="rId15"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Full List'!$A$1:$M$174</definedName>
@@ -50,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6394" uniqueCount="824">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7098" uniqueCount="1020">
   <si>
     <t>schema</t>
   </si>
@@ -2563,14 +2566,602 @@
     <t>project.project_level[].project_level_compliance_potential_eligibility</t>
   </si>
   <si>
-    <t>crediting_program.carbon_standard_level_accreditation</t>
+    <t>crediting program</t>
+  </si>
+  <si>
+    <t>Describes the current registry, that contains the information about the project, and units</t>
+  </si>
+  <si>
+    <t>Describes the first registry, where the project was registered</t>
+  </si>
+  <si>
+    <t>Describes the Crediting Program that the proejct is following for the implementationunits</t>
+  </si>
+  <si>
+    <t>Date of the last update</t>
+  </si>
+  <si>
+    <t>registry_identifier</t>
+  </si>
+  <si>
+    <t>registry_name</t>
+  </si>
+  <si>
+    <t>registry_link</t>
+  </si>
+  <si>
+    <t>original_registry_identifier</t>
+  </si>
+  <si>
+    <t>original_registry_name</t>
+  </si>
+  <si>
+    <t>original_registry_link</t>
+  </si>
+  <si>
+    <t>program_identifier</t>
+  </si>
+  <si>
+    <t>program_name</t>
+  </si>
+  <si>
+    <t>creation_date</t>
+  </si>
+  <si>
+    <t>update_date</t>
+  </si>
+  <si>
+    <t>Date that the project was first registered</t>
+  </si>
+  <si>
+    <t>registry.creation_date</t>
+  </si>
+  <si>
+    <t>registry.update_date</t>
+  </si>
+  <si>
+    <t>registry.identification[].registry_identifier</t>
+  </si>
+  <si>
+    <t>registry.identification[].registry_name</t>
+  </si>
+  <si>
+    <t>registry.identification[].registry_link</t>
+  </si>
+  <si>
+    <t>registry.original[].original_registry_identifier</t>
+  </si>
+  <si>
+    <t>registry.original[].original_registry_name</t>
+  </si>
+  <si>
+    <t>registry.original[].original_registry_link</t>
+  </si>
+  <si>
+    <t>registry.program[].program_identifier</t>
+  </si>
+  <si>
+    <t>registry.program[].program_name</t>
+  </si>
+  <si>
+    <t>current_validation_stage</t>
+  </si>
+  <si>
+    <t>current_validation_stage_status</t>
+  </si>
+  <si>
+    <t>date_previous_validation</t>
+  </si>
+  <si>
+    <t>date_validation_expiration</t>
+  </si>
+  <si>
+    <t>date_validation_planned</t>
+  </si>
+  <si>
+    <t>date_validation_requested</t>
+  </si>
+  <si>
+    <t>validation_body_accreditation</t>
+  </si>
+  <si>
+    <t>validation_body_id</t>
+  </si>
+  <si>
+    <t>validator_name</t>
+  </si>
+  <si>
+    <t>validation_body_sectoral_scopes</t>
+  </si>
+  <si>
+    <t>validation_body_selection</t>
+  </si>
+  <si>
+    <t>validation_body_team_members_and_roles</t>
+  </si>
+  <si>
+    <t>validation_is_planned</t>
+  </si>
+  <si>
+    <t>validation_period_end_date</t>
+  </si>
+  <si>
+    <t>validation_period_start_date</t>
+  </si>
+  <si>
+    <t>validation_report_link</t>
+  </si>
+  <si>
+    <t>validation_report_summary</t>
+  </si>
+  <si>
+    <t>validation_stage_description</t>
+  </si>
+  <si>
+    <t>validation_stage_document_link</t>
+  </si>
+  <si>
+    <t>validation_stages</t>
+  </si>
+  <si>
+    <t>validation_status</t>
+  </si>
+  <si>
+    <t>validation_report_version</t>
+  </si>
+  <si>
+    <t>Validation and Verification Body (VVB)/ Certification Bodies/ Third Party Auditors</t>
+  </si>
+  <si>
+    <t>Name of the current validation step</t>
+  </si>
+  <si>
+    <t>Status of the current validation step</t>
+  </si>
+  <si>
+    <t>Date of the previous validation event</t>
+  </si>
+  <si>
+    <t>Date validation expires</t>
+  </si>
+  <si>
+    <t>Planned date of the validation event</t>
+  </si>
+  <si>
+    <t>Date validation was requested</t>
+  </si>
+  <si>
+    <t>LCA has been completed</t>
+  </si>
+  <si>
+    <t>LCA is used to quantify emissions</t>
+  </si>
+  <si>
+    <t>Link to LCA report</t>
+  </si>
+  <si>
+    <t>Link to LCA repository</t>
+  </si>
+  <si>
+    <t>LCA results</t>
+  </si>
+  <si>
+    <t>Link to LCA system boundary figure</t>
+  </si>
+  <si>
+    <t>Overview description of LCA system boundary</t>
+  </si>
+  <si>
+    <t>Identification number of the validation event.</t>
+  </si>
+  <si>
+    <t>Type of validation being carried out</t>
+  </si>
+  <si>
+    <t>List any accreditations of the validation body</t>
+  </si>
+  <si>
+    <t>Identification number of the validation body</t>
+  </si>
+  <si>
+    <t>Name of the validation body</t>
+  </si>
+  <si>
+    <t>Name(s) of the validator(s)</t>
+  </si>
+  <si>
+    <t>List the sectoral scopes the validation body is accredited to validate</t>
+  </si>
+  <si>
+    <t>Describe how the validation body was selected</t>
+  </si>
+  <si>
+    <t>List the names of any other validation body team members and their roles (FIRST NAME - LAST NAME, ROLE)</t>
+  </si>
+  <si>
+    <t>Date of validation event</t>
+  </si>
+  <si>
+    <t>Indicate whether the valiation event is planned.</t>
+  </si>
+  <si>
+    <t>End date of the validation event. Estimate if needed.</t>
+  </si>
+  <si>
+    <t>Start date of the validation event</t>
+  </si>
+  <si>
+    <t>Link (URL) to the project's validation report (if applicable).</t>
+  </si>
+  <si>
+    <t>Enter the validation report's summary</t>
+  </si>
+  <si>
+    <t>Describe the stages of the validation event.</t>
+  </si>
+  <si>
+    <t>Link (URL) to the document that contains the description and details of the validation event stages</t>
+  </si>
+  <si>
+    <t>Select all validation event stages</t>
+  </si>
+  <si>
+    <t>Indicate whether the project has been validated.</t>
+  </si>
+  <si>
+    <t>Which version of the validation report is the current version</t>
+  </si>
+  <si>
+    <t>lca_completed</t>
+  </si>
+  <si>
+    <t>lca_emissions_quantification</t>
+  </si>
+  <si>
+    <t>lca_link</t>
+  </si>
+  <si>
+    <t>lca_repository</t>
+  </si>
+  <si>
+    <t>lca_results</t>
+  </si>
+  <si>
+    <t>lca_system_boundary_figure</t>
+  </si>
+  <si>
+    <t>lca_system_boundary_overview</t>
+  </si>
+  <si>
+    <t>validation_body</t>
+  </si>
+  <si>
+    <t>validation.crediting_period[].current_crediting_period_end_date</t>
+  </si>
+  <si>
+    <t>project.validation_stage[].current_validation_stage</t>
+  </si>
+  <si>
+    <t>validation.stage[].validation_stage_document_link</t>
+  </si>
+  <si>
+    <t>validation.crediting_period[].current_crediting_period_number</t>
+  </si>
+  <si>
+    <t>project.validation_stage[].current_validation_stage_status</t>
+  </si>
+  <si>
+    <t>validation.crediting_period[].current_crediting_period_start_date</t>
+  </si>
+  <si>
+    <t>project.date[].date_previous_validation</t>
+  </si>
+  <si>
+    <t>validation.date[].date_validation_expiration</t>
+  </si>
+  <si>
+    <t>validation.date[].date_validation_planned</t>
+  </si>
+  <si>
+    <t>validation.date[].date_validation_requested</t>
+  </si>
+  <si>
+    <t>validation.lca[].lca_completed</t>
+  </si>
+  <si>
+    <t>validation.lca[].lca_emissions_quantification</t>
+  </si>
+  <si>
+    <t>validation.lca[].lca_link</t>
+  </si>
+  <si>
+    <t>validation.lca[].lca_repository</t>
+  </si>
+  <si>
+    <t>validation.lca[].lca_results</t>
+  </si>
+  <si>
+    <t>validation.lca[].lca_system_boundary_figure</t>
+  </si>
+  <si>
+    <t>validation.lca[].lca_system_boundary_overview</t>
+  </si>
+  <si>
+    <t>validation.validation_event[].validation _id</t>
+  </si>
+  <si>
+    <t>validation.validation_event[].validation_type</t>
+  </si>
+  <si>
+    <t>validation.validation_event[].validation_date</t>
+  </si>
+  <si>
+    <t>validation.validation_event[].validation_is_planned</t>
+  </si>
+  <si>
+    <t>validation.validation_event[].validation_period_end_date</t>
+  </si>
+  <si>
+    <t>validation.validation_event[].validation_period_start_date</t>
+  </si>
+  <si>
+    <t>validation.report[].validation_report_link</t>
+  </si>
+  <si>
+    <t>project.validation_status</t>
+  </si>
+  <si>
+    <t>validation.report[].validation_report_summary</t>
+  </si>
+  <si>
+    <t>validation.stage[].validation_stage_description</t>
+  </si>
+  <si>
+    <t>validation.stage[].validation_stages</t>
+  </si>
+  <si>
+    <t>validation.report[].validation_report_version</t>
+  </si>
+  <si>
+    <t>validation_body.details[].validation_body_accreditation</t>
+  </si>
+  <si>
+    <t>validation_body.details[].validation_body_id</t>
+  </si>
+  <si>
+    <t>validation_body.details[].validation_body_name</t>
+  </si>
+  <si>
+    <t>validation_body.details[].validator_name</t>
+  </si>
+  <si>
+    <t>validation_body.details[].validation_body_sectoral_scopes</t>
+  </si>
+  <si>
+    <t>validation_body.details[].validation_body_selection</t>
+  </si>
+  <si>
+    <t>validation_body.details[].validation_body_team_members_and_roles</t>
+  </si>
+  <si>
+    <t>verification_id</t>
+  </si>
+  <si>
+    <t>verification_claim_type</t>
+  </si>
+  <si>
+    <t>verification_project_id</t>
+  </si>
+  <si>
+    <t>verification_description</t>
+  </si>
+  <si>
+    <t>verification_reporting_period_start</t>
+  </si>
+  <si>
+    <t>verification_reporting_period_end</t>
+  </si>
+  <si>
+    <t>verification_date</t>
+  </si>
+  <si>
+    <t>verified_quantity</t>
+  </si>
+  <si>
+    <t>verification_quantity_uom</t>
+  </si>
+  <si>
+    <t>verification_body_name</t>
+  </si>
+  <si>
+    <t>verification_body_id</t>
+  </si>
+  <si>
+    <t>verification_applied_standard</t>
+  </si>
+  <si>
+    <t>verification_applied_methodology_protocol</t>
+  </si>
+  <si>
+    <t>verification_credential_issuer_id</t>
+  </si>
+  <si>
+    <t>verification_cryptographic_proof_type</t>
+  </si>
+  <si>
+    <t>verification_digital_signature_payload</t>
+  </si>
+  <si>
+    <t>verification_leakage_risk_mitigation</t>
+  </si>
+  <si>
+    <t>verification_leakage_risk_mitigation_strategy</t>
+  </si>
+  <si>
+    <t>verification_leakage_deduction_quantity</t>
+  </si>
+  <si>
+    <t>verification_uncertainty_deduction_margin</t>
+  </si>
+  <si>
+    <t>verification_buffer_pool_deduction_quantity</t>
+  </si>
+  <si>
+    <t>verification_audit_checkpoint_status</t>
+  </si>
+  <si>
+    <t>URI</t>
+  </si>
+  <si>
+    <t>Object/String</t>
+  </si>
+  <si>
+    <t>A globally unique identifier for the specific verification event or claim.</t>
+  </si>
+  <si>
+    <t>The classification of the claim being verified (e.g., CARBON_REMOVAL, EMISSION_REDUCTION, BIODIVERSITY).</t>
+  </si>
+  <si>
+    <t>The unique ID of the underlying project registered on the host registry.</t>
+  </si>
+  <si>
+    <t>A concise, human-readable summary of the verification scope and findings.</t>
+  </si>
+  <si>
+    <t>The start date of the monitoring/reporting period being verified.</t>
+  </si>
+  <si>
+    <t>The end date of the monitoring/reporting period being verified.</t>
+  </si>
+  <si>
+    <t>The official date the verification process was completed and signed off.</t>
+  </si>
+  <si>
+    <t>The final, audited, and verified net volume for this specific reporting period.</t>
+  </si>
+  <si>
+    <t>The Unit of Measure for the verified quantity (e.g., tCO2e, m3_biogas).</t>
+  </si>
+  <si>
+    <t>The official name of the third-party auditing entity/VVB.</t>
+  </si>
+  <si>
+    <t>The decentralized identifier (DID) or registry ID of the verification body.</t>
+  </si>
+  <si>
+    <t>The overarching registry framework (e.g., Verra_VCS_v4.5, Gold_Standard).</t>
+  </si>
+  <si>
+    <t>The specific methodology version applied (e.g., VM0047_v1.0, CAR_Soil_v1.1).</t>
+  </si>
+  <si>
+    <t>The direct, secure hyperlink to the official public verification report PDF.</t>
+  </si>
+  <si>
+    <t>The decentralized identifier (DID) of the entity issuing the digital verification token.</t>
+  </si>
+  <si>
+    <t>The security protocol used (e.g., Ed25519Signature2020, JSON-LD).</t>
+  </si>
+  <si>
+    <t>The actual cryptographic signature, payload hash, or verifiable presentation metadata.</t>
+  </si>
+  <si>
+    <t>Indicates if leakage risk is accounted for on this verification event</t>
+  </si>
+  <si>
+    <t>links to or summarizes the mitigation strategy for this verification event</t>
+  </si>
+  <si>
+    <t>Volume deducted for this specific reporting period to account for leakage.</t>
+  </si>
+  <si>
+    <t>Percentage or absolute deduction applied for this specific reporting period for uncertainty.</t>
+  </si>
+  <si>
+    <t>Volume deducted for this specific reporting period and contributed to the buffer pool.</t>
+  </si>
+  <si>
+    <t>Summary result of the checklist (e.g., PASS, PASS_WITH_RESERVATIONS, FAIL).</t>
+  </si>
+  <si>
+    <t>verification</t>
+  </si>
+  <si>
+    <t>verification.identification[].verification_id</t>
+  </si>
+  <si>
+    <t>verification.identification[].verification_claim_type</t>
+  </si>
+  <si>
+    <t>verification.identification[].verification_project_id</t>
+  </si>
+  <si>
+    <t>verification.identification[].verification_description</t>
+  </si>
+  <si>
+    <t>verification.reporting[].verification_reporting_period_start</t>
+  </si>
+  <si>
+    <t>verification.reporting[].verification_reporting_period_end</t>
+  </si>
+  <si>
+    <t>verification.reporting[].verification_date</t>
+  </si>
+  <si>
+    <t>verification.quantity[].verified_quantity</t>
+  </si>
+  <si>
+    <t>verification.quantity[].verification_quantity_uom</t>
+  </si>
+  <si>
+    <t>verification.body[].verification_body_name</t>
+  </si>
+  <si>
+    <t>verification.body[].verification_body_id</t>
+  </si>
+  <si>
+    <t>verification.standard[].verification_applied_standard</t>
+  </si>
+  <si>
+    <t>verification.standard[].verification_applied_methodology_protocol</t>
+  </si>
+  <si>
+    <t>verification.verification_report_url</t>
+  </si>
+  <si>
+    <t>verification.verification_credential_issuer_id</t>
+  </si>
+  <si>
+    <t>verification.verification_cryptographic_proof_type</t>
+  </si>
+  <si>
+    <t>verification.verification_digital_signature_payload</t>
+  </si>
+  <si>
+    <t>verification.leakage[].verification_leakage_risk_mitigation</t>
+  </si>
+  <si>
+    <t>verification.leakage[].verification_leakage_risk_mitigation_strategy</t>
+  </si>
+  <si>
+    <t>verification.leakage[].verification_leakage_deduction_quantity</t>
+  </si>
+  <si>
+    <t>verification.verification_uncertainty_deduction_margin</t>
+  </si>
+  <si>
+    <t>verification.verification_buffer_pool_deduction_quantity</t>
+  </si>
+  <si>
+    <t>verification.verification_audit_checkpoint_status</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2665,8 +3256,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF434343"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2706,6 +3304,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6F8F9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2757,7 +3367,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -2819,6 +3429,27 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -15953,7 +16584,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -15963,14 +16594,14 @@
       <c r="C2">
         <v>242</v>
       </c>
-      <c r="D2" s="32" t="s">
+      <c r="D2" s="6" t="s">
         <v>763</v>
       </c>
       <c r="E2" s="6" t="s">
         <v>141</v>
       </c>
       <c r="F2" t="s">
-        <v>823</v>
+        <v>804</v>
       </c>
       <c r="G2" t="s">
         <v>30</v>
@@ -15994,7 +16625,7 @@
         <v>785</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -16004,7 +16635,7 @@
       <c r="C3">
         <v>243</v>
       </c>
-      <c r="D3" s="32" t="s">
+      <c r="D3" s="6" t="s">
         <v>764</v>
       </c>
       <c r="E3" s="6" t="s">
@@ -16035,7 +16666,7 @@
         <v>786</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>13</v>
       </c>
@@ -16045,7 +16676,7 @@
       <c r="C4">
         <v>244</v>
       </c>
-      <c r="D4" s="32" t="s">
+      <c r="D4" s="6" t="s">
         <v>765</v>
       </c>
       <c r="E4" s="6" t="s">
@@ -16076,7 +16707,7 @@
         <v>787</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -16086,7 +16717,7 @@
       <c r="C5">
         <v>245</v>
       </c>
-      <c r="D5" s="32" t="s">
+      <c r="D5" s="6" t="s">
         <v>766</v>
       </c>
       <c r="E5" s="6" t="s">
@@ -16117,7 +16748,7 @@
         <v>788</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>13</v>
       </c>
@@ -16127,7 +16758,7 @@
       <c r="C6">
         <v>246</v>
       </c>
-      <c r="D6" s="32" t="s">
+      <c r="D6" s="6" t="s">
         <v>767</v>
       </c>
       <c r="E6" s="6" t="s">
@@ -16158,7 +16789,7 @@
         <v>789</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -16168,7 +16799,7 @@
       <c r="C7">
         <v>247</v>
       </c>
-      <c r="D7" s="32" t="s">
+      <c r="D7" s="6" t="s">
         <v>768</v>
       </c>
       <c r="E7" s="6" t="s">
@@ -16199,7 +16830,7 @@
         <v>790</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>13</v>
       </c>
@@ -16209,7 +16840,7 @@
       <c r="C8">
         <v>248</v>
       </c>
-      <c r="D8" s="32" t="s">
+      <c r="D8" s="6" t="s">
         <v>769</v>
       </c>
       <c r="E8" s="6" t="s">
@@ -16240,7 +16871,7 @@
         <v>791</v>
       </c>
     </row>
-    <row r="9" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>13</v>
       </c>
@@ -16250,7 +16881,7 @@
       <c r="C9">
         <v>249</v>
       </c>
-      <c r="D9" s="32" t="s">
+      <c r="D9" s="6" t="s">
         <v>770</v>
       </c>
       <c r="E9" s="6" t="s">
@@ -16281,7 +16912,7 @@
         <v>792</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>13</v>
       </c>
@@ -16291,7 +16922,7 @@
       <c r="C10">
         <v>250</v>
       </c>
-      <c r="D10" s="32" t="s">
+      <c r="D10" s="6" t="s">
         <v>771</v>
       </c>
       <c r="E10" s="6" t="s">
@@ -16322,7 +16953,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>13</v>
       </c>
@@ -16332,7 +16963,7 @@
       <c r="C11">
         <v>251</v>
       </c>
-      <c r="D11" s="32" t="s">
+      <c r="D11" s="6" t="s">
         <v>772</v>
       </c>
       <c r="E11" s="6" t="s">
@@ -16363,7 +16994,7 @@
         <v>794</v>
       </c>
     </row>
-    <row r="12" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>13</v>
       </c>
@@ -16373,7 +17004,7 @@
       <c r="C12">
         <v>252</v>
       </c>
-      <c r="D12" s="32" t="s">
+      <c r="D12" s="6" t="s">
         <v>773</v>
       </c>
       <c r="E12" s="6" t="s">
@@ -16404,7 +17035,7 @@
         <v>795</v>
       </c>
     </row>
-    <row r="13" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>13</v>
       </c>
@@ -16414,7 +17045,7 @@
       <c r="C13">
         <v>253</v>
       </c>
-      <c r="D13" s="32" t="s">
+      <c r="D13" s="6" t="s">
         <v>774</v>
       </c>
       <c r="E13" s="6" t="s">
@@ -16445,7 +17076,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="14" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>13</v>
       </c>
@@ -16455,7 +17086,7 @@
       <c r="C14">
         <v>254</v>
       </c>
-      <c r="D14" s="32" t="s">
+      <c r="D14" s="6" t="s">
         <v>775</v>
       </c>
       <c r="E14" s="6" t="s">
@@ -16486,7 +17117,7 @@
         <v>797</v>
       </c>
     </row>
-    <row r="15" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>13</v>
       </c>
@@ -16496,7 +17127,7 @@
       <c r="C15">
         <v>255</v>
       </c>
-      <c r="D15" s="32" t="s">
+      <c r="D15" s="6" t="s">
         <v>776</v>
       </c>
       <c r="E15" s="6" t="s">
@@ -16527,7 +17158,7 @@
         <v>798</v>
       </c>
     </row>
-    <row r="16" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>13</v>
       </c>
@@ -16537,7 +17168,7 @@
       <c r="C16">
         <v>256</v>
       </c>
-      <c r="D16" s="32" t="s">
+      <c r="D16" s="6" t="s">
         <v>777</v>
       </c>
       <c r="E16" s="6" t="s">
@@ -16568,7 +17199,7 @@
         <v>799</v>
       </c>
     </row>
-    <row r="17" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>13</v>
       </c>
@@ -16578,7 +17209,7 @@
       <c r="C17">
         <v>257</v>
       </c>
-      <c r="D17" s="32" t="s">
+      <c r="D17" s="6" t="s">
         <v>778</v>
       </c>
       <c r="E17" s="6" t="s">
@@ -16619,7 +17250,7 @@
       <c r="C18">
         <v>258</v>
       </c>
-      <c r="D18" s="32" t="s">
+      <c r="D18" s="6" t="s">
         <v>779</v>
       </c>
       <c r="E18" s="6" t="s">
@@ -16650,7 +17281,7 @@
         <v>801</v>
       </c>
     </row>
-    <row r="19" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>13</v>
       </c>
@@ -16660,7 +17291,7 @@
       <c r="C19">
         <v>259</v>
       </c>
-      <c r="D19" s="32" t="s">
+      <c r="D19" s="6" t="s">
         <v>780</v>
       </c>
       <c r="E19" s="6" t="s">
@@ -16691,7 +17322,7 @@
         <v>802</v>
       </c>
     </row>
-    <row r="20" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>13</v>
       </c>
@@ -16701,7 +17332,7 @@
       <c r="C20">
         <v>260</v>
       </c>
-      <c r="D20" s="32" t="s">
+      <c r="D20" s="6" t="s">
         <v>781</v>
       </c>
       <c r="E20" s="6" t="s">
@@ -16734,6 +17365,2536 @@
     </row>
   </sheetData>
   <phoneticPr fontId="12" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5DD793A8-CD91-4786-8377-89E3BC40F96B}">
+  <dimension ref="A1:M11"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="2" width="8.54296875" customWidth="1"/>
+    <col min="4" max="4" width="30.6328125" customWidth="1"/>
+    <col min="5" max="5" width="15.90625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="52.81640625" customWidth="1"/>
+    <col min="7" max="7" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12" customWidth="1"/>
+    <col min="9" max="9" width="16.6328125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.90625" customWidth="1"/>
+    <col min="12" max="12" width="13.1796875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="35.08984375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" t="s">
+        <v>275</v>
+      </c>
+      <c r="C2">
+        <v>261</v>
+      </c>
+      <c r="D2" s="25" t="s">
+        <v>828</v>
+      </c>
+      <c r="E2" t="s">
+        <v>116</v>
+      </c>
+      <c r="F2" t="s">
+        <v>841</v>
+      </c>
+      <c r="G2" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="H2" s="25" t="s">
+        <v>392</v>
+      </c>
+      <c r="I2" t="s">
+        <v>226</v>
+      </c>
+      <c r="J2" t="s">
+        <v>116</v>
+      </c>
+      <c r="L2" t="s">
+        <v>146</v>
+      </c>
+      <c r="M2" s="18" t="s">
+        <v>824</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" t="s">
+        <v>275</v>
+      </c>
+      <c r="C3">
+        <v>262</v>
+      </c>
+      <c r="D3" s="25" t="s">
+        <v>829</v>
+      </c>
+      <c r="E3" t="s">
+        <v>116</v>
+      </c>
+      <c r="F3" t="s">
+        <v>842</v>
+      </c>
+      <c r="G3" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="H3" s="25" t="s">
+        <v>159</v>
+      </c>
+      <c r="I3" t="s">
+        <v>226</v>
+      </c>
+      <c r="J3" t="s">
+        <v>116</v>
+      </c>
+      <c r="L3" t="s">
+        <v>146</v>
+      </c>
+      <c r="M3" s="18" t="s">
+        <v>824</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" t="s">
+        <v>275</v>
+      </c>
+      <c r="C4">
+        <v>263</v>
+      </c>
+      <c r="D4" s="25" t="s">
+        <v>830</v>
+      </c>
+      <c r="E4" t="s">
+        <v>116</v>
+      </c>
+      <c r="F4" t="s">
+        <v>843</v>
+      </c>
+      <c r="G4" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="H4" s="25" t="s">
+        <v>159</v>
+      </c>
+      <c r="I4" t="s">
+        <v>226</v>
+      </c>
+      <c r="J4" t="s">
+        <v>116</v>
+      </c>
+      <c r="L4" t="s">
+        <v>146</v>
+      </c>
+      <c r="M4" s="18" t="s">
+        <v>824</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" t="s">
+        <v>275</v>
+      </c>
+      <c r="C5">
+        <v>264</v>
+      </c>
+      <c r="D5" s="25" t="s">
+        <v>831</v>
+      </c>
+      <c r="E5" t="s">
+        <v>116</v>
+      </c>
+      <c r="F5" t="s">
+        <v>844</v>
+      </c>
+      <c r="G5" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="H5" s="25" t="s">
+        <v>392</v>
+      </c>
+      <c r="I5" t="s">
+        <v>226</v>
+      </c>
+      <c r="J5" t="s">
+        <v>116</v>
+      </c>
+      <c r="L5" t="s">
+        <v>146</v>
+      </c>
+      <c r="M5" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" t="s">
+        <v>275</v>
+      </c>
+      <c r="C6">
+        <v>265</v>
+      </c>
+      <c r="D6" s="25" t="s">
+        <v>832</v>
+      </c>
+      <c r="E6" t="s">
+        <v>116</v>
+      </c>
+      <c r="F6" t="s">
+        <v>845</v>
+      </c>
+      <c r="G6" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="H6" s="25" t="s">
+        <v>159</v>
+      </c>
+      <c r="I6" t="s">
+        <v>226</v>
+      </c>
+      <c r="J6" t="s">
+        <v>116</v>
+      </c>
+      <c r="L6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M6" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" t="s">
+        <v>275</v>
+      </c>
+      <c r="C7">
+        <v>266</v>
+      </c>
+      <c r="D7" s="25" t="s">
+        <v>833</v>
+      </c>
+      <c r="E7" t="s">
+        <v>116</v>
+      </c>
+      <c r="F7" t="s">
+        <v>846</v>
+      </c>
+      <c r="G7" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="H7" s="25" t="s">
+        <v>159</v>
+      </c>
+      <c r="I7" t="s">
+        <v>226</v>
+      </c>
+      <c r="J7" t="s">
+        <v>116</v>
+      </c>
+      <c r="L7" t="s">
+        <v>146</v>
+      </c>
+      <c r="M7" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" t="s">
+        <v>275</v>
+      </c>
+      <c r="C8">
+        <v>267</v>
+      </c>
+      <c r="D8" s="25" t="s">
+        <v>834</v>
+      </c>
+      <c r="E8" t="s">
+        <v>116</v>
+      </c>
+      <c r="F8" t="s">
+        <v>847</v>
+      </c>
+      <c r="G8" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="H8" s="25" t="s">
+        <v>392</v>
+      </c>
+      <c r="I8" t="s">
+        <v>226</v>
+      </c>
+      <c r="J8" t="s">
+        <v>823</v>
+      </c>
+      <c r="L8" t="s">
+        <v>146</v>
+      </c>
+      <c r="M8" s="18" t="s">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" t="s">
+        <v>275</v>
+      </c>
+      <c r="C9">
+        <v>268</v>
+      </c>
+      <c r="D9" s="25" t="s">
+        <v>835</v>
+      </c>
+      <c r="E9" t="s">
+        <v>116</v>
+      </c>
+      <c r="F9" t="s">
+        <v>848</v>
+      </c>
+      <c r="G9" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="H9" s="25" t="s">
+        <v>159</v>
+      </c>
+      <c r="I9" t="s">
+        <v>226</v>
+      </c>
+      <c r="J9" t="s">
+        <v>823</v>
+      </c>
+      <c r="L9" t="s">
+        <v>146</v>
+      </c>
+      <c r="M9" s="18" t="s">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" t="s">
+        <v>275</v>
+      </c>
+      <c r="C10">
+        <v>269</v>
+      </c>
+      <c r="D10" s="25" t="s">
+        <v>836</v>
+      </c>
+      <c r="E10" t="s">
+        <v>116</v>
+      </c>
+      <c r="F10" t="s">
+        <v>839</v>
+      </c>
+      <c r="G10" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="H10" s="25" t="s">
+        <v>219</v>
+      </c>
+      <c r="I10" t="s">
+        <v>226</v>
+      </c>
+      <c r="L10" t="s">
+        <v>146</v>
+      </c>
+      <c r="M10" s="18" t="s">
+        <v>838</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>13</v>
+      </c>
+      <c r="B11" t="s">
+        <v>275</v>
+      </c>
+      <c r="C11">
+        <v>270</v>
+      </c>
+      <c r="D11" s="25" t="s">
+        <v>837</v>
+      </c>
+      <c r="E11" t="s">
+        <v>116</v>
+      </c>
+      <c r="F11" t="s">
+        <v>840</v>
+      </c>
+      <c r="G11" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="H11" s="25" t="s">
+        <v>219</v>
+      </c>
+      <c r="I11" t="s">
+        <v>31</v>
+      </c>
+      <c r="L11" t="s">
+        <v>146</v>
+      </c>
+      <c r="M11" s="18" t="s">
+        <v>827</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF337E51-0D9D-46A6-9DB2-8DF5F9FC1667}">
+  <dimension ref="A1:M37"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="4" max="4" width="43.6328125" customWidth="1"/>
+    <col min="5" max="5" width="15.90625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="58.453125" customWidth="1"/>
+    <col min="7" max="7" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.90625" customWidth="1"/>
+    <col min="9" max="9" width="16.6328125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.26953125" customWidth="1"/>
+    <col min="12" max="12" width="13.1796875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="49.90625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" t="s">
+        <v>275</v>
+      </c>
+      <c r="C2">
+        <v>271</v>
+      </c>
+      <c r="D2" s="33" t="s">
+        <v>481</v>
+      </c>
+      <c r="E2" s="33" t="s">
+        <v>266</v>
+      </c>
+      <c r="F2" t="s">
+        <v>913</v>
+      </c>
+      <c r="G2" s="33" t="s">
+        <v>18</v>
+      </c>
+      <c r="H2" s="33" t="s">
+        <v>219</v>
+      </c>
+      <c r="I2" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="J2" s="6" t="s">
+        <v>445</v>
+      </c>
+      <c r="L2" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M2" s="6" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" t="s">
+        <v>275</v>
+      </c>
+      <c r="C3">
+        <v>272</v>
+      </c>
+      <c r="D3" s="33" t="s">
+        <v>483</v>
+      </c>
+      <c r="E3" s="33" t="s">
+        <v>266</v>
+      </c>
+      <c r="F3" t="s">
+        <v>916</v>
+      </c>
+      <c r="G3" s="33" t="s">
+        <v>18</v>
+      </c>
+      <c r="H3" s="33" t="s">
+        <v>392</v>
+      </c>
+      <c r="I3" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="J3" s="6" t="s">
+        <v>445</v>
+      </c>
+      <c r="L3" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M3" s="6" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" t="s">
+        <v>275</v>
+      </c>
+      <c r="C4">
+        <v>273</v>
+      </c>
+      <c r="D4" s="33" t="s">
+        <v>479</v>
+      </c>
+      <c r="E4" s="33" t="s">
+        <v>266</v>
+      </c>
+      <c r="F4" t="s">
+        <v>918</v>
+      </c>
+      <c r="G4" s="33" t="s">
+        <v>18</v>
+      </c>
+      <c r="H4" s="33" t="s">
+        <v>219</v>
+      </c>
+      <c r="I4" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="J4" s="6" t="s">
+        <v>445</v>
+      </c>
+      <c r="L4" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M4" s="6" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" t="s">
+        <v>275</v>
+      </c>
+      <c r="C5">
+        <v>274</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>849</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F5" t="s">
+        <v>914</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H5" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="I5" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="J5" s="6" t="s">
+        <v>445</v>
+      </c>
+      <c r="L5" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M5" s="6" t="s">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" t="s">
+        <v>275</v>
+      </c>
+      <c r="C6">
+        <v>275</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>850</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F6" t="s">
+        <v>917</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H6" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="I6" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="J6" s="6" t="s">
+        <v>445</v>
+      </c>
+      <c r="L6" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M6" s="6" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" t="s">
+        <v>275</v>
+      </c>
+      <c r="C7">
+        <v>276</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>851</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F7" t="s">
+        <v>919</v>
+      </c>
+      <c r="G7" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="H7" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="I7" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="J7" s="6" t="s">
+        <v>445</v>
+      </c>
+      <c r="L7" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M7" s="6" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" t="s">
+        <v>275</v>
+      </c>
+      <c r="C8">
+        <v>277</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>852</v>
+      </c>
+      <c r="E8" s="33" t="s">
+        <v>266</v>
+      </c>
+      <c r="F8" t="s">
+        <v>920</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H8" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="I8" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="J8" s="6" t="s">
+        <v>871</v>
+      </c>
+      <c r="L8" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M8" s="6" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" t="s">
+        <v>275</v>
+      </c>
+      <c r="C9">
+        <v>278</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>853</v>
+      </c>
+      <c r="E9" s="33" t="s">
+        <v>266</v>
+      </c>
+      <c r="F9" t="s">
+        <v>921</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H9" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="I9" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="J9" s="6" t="s">
+        <v>871</v>
+      </c>
+      <c r="L9" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M9" s="6" t="s">
+        <v>876</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" t="s">
+        <v>275</v>
+      </c>
+      <c r="C10">
+        <v>279</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>854</v>
+      </c>
+      <c r="E10" s="33" t="s">
+        <v>266</v>
+      </c>
+      <c r="F10" t="s">
+        <v>922</v>
+      </c>
+      <c r="G10" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H10" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="I10" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="J10" s="6" t="s">
+        <v>871</v>
+      </c>
+      <c r="L10" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M10" s="6" t="s">
+        <v>877</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>13</v>
+      </c>
+      <c r="B11" t="s">
+        <v>275</v>
+      </c>
+      <c r="C11">
+        <v>280</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>905</v>
+      </c>
+      <c r="E11" s="33" t="s">
+        <v>266</v>
+      </c>
+      <c r="F11" t="s">
+        <v>923</v>
+      </c>
+      <c r="G11" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="H11" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="I11" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="J11" s="6" t="s">
+        <v>871</v>
+      </c>
+      <c r="L11" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M11" s="6" t="s">
+        <v>878</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12" t="s">
+        <v>275</v>
+      </c>
+      <c r="C12">
+        <v>281</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>906</v>
+      </c>
+      <c r="E12" s="33" t="s">
+        <v>266</v>
+      </c>
+      <c r="F12" t="s">
+        <v>924</v>
+      </c>
+      <c r="G12" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="H12" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="I12" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="J12" s="6" t="s">
+        <v>871</v>
+      </c>
+      <c r="L12" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M12" s="6" t="s">
+        <v>879</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13" t="s">
+        <v>275</v>
+      </c>
+      <c r="C13">
+        <v>282</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>907</v>
+      </c>
+      <c r="E13" s="33" t="s">
+        <v>266</v>
+      </c>
+      <c r="F13" t="s">
+        <v>925</v>
+      </c>
+      <c r="G13" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="H13" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="I13" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="J13" s="6" t="s">
+        <v>871</v>
+      </c>
+      <c r="L13" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M13" s="6" t="s">
+        <v>880</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>275</v>
+      </c>
+      <c r="C14">
+        <v>283</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>908</v>
+      </c>
+      <c r="E14" s="33" t="s">
+        <v>266</v>
+      </c>
+      <c r="F14" t="s">
+        <v>926</v>
+      </c>
+      <c r="G14" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="H14" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="I14" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="J14" s="6" t="s">
+        <v>871</v>
+      </c>
+      <c r="L14" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M14" s="6" t="s">
+        <v>881</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>13</v>
+      </c>
+      <c r="B15" t="s">
+        <v>275</v>
+      </c>
+      <c r="C15">
+        <v>284</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>909</v>
+      </c>
+      <c r="E15" s="33" t="s">
+        <v>266</v>
+      </c>
+      <c r="F15" t="s">
+        <v>927</v>
+      </c>
+      <c r="G15" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="H15" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="I15" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="J15" s="6" t="s">
+        <v>871</v>
+      </c>
+      <c r="L15" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M15" s="6" t="s">
+        <v>882</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>13</v>
+      </c>
+      <c r="B16" t="s">
+        <v>275</v>
+      </c>
+      <c r="C16">
+        <v>285</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>910</v>
+      </c>
+      <c r="E16" s="33" t="s">
+        <v>266</v>
+      </c>
+      <c r="F16" t="s">
+        <v>928</v>
+      </c>
+      <c r="G16" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="H16" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="I16" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="J16" s="6" t="s">
+        <v>871</v>
+      </c>
+      <c r="L16" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M16" s="6" t="s">
+        <v>883</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>13</v>
+      </c>
+      <c r="B17" t="s">
+        <v>275</v>
+      </c>
+      <c r="C17">
+        <v>286</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>911</v>
+      </c>
+      <c r="E17" s="33" t="s">
+        <v>266</v>
+      </c>
+      <c r="F17" t="s">
+        <v>929</v>
+      </c>
+      <c r="G17" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="H17" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="I17" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="J17" s="6" t="s">
+        <v>871</v>
+      </c>
+      <c r="L17" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M17" s="6" t="s">
+        <v>884</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>13</v>
+      </c>
+      <c r="B18" t="s">
+        <v>275</v>
+      </c>
+      <c r="C18">
+        <v>287</v>
+      </c>
+      <c r="D18" s="33" t="s">
+        <v>477</v>
+      </c>
+      <c r="E18" s="33" t="s">
+        <v>266</v>
+      </c>
+      <c r="F18" t="s">
+        <v>930</v>
+      </c>
+      <c r="G18" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H18" s="6" t="s">
+        <v>392</v>
+      </c>
+      <c r="I18" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="J18" s="6" t="s">
+        <v>871</v>
+      </c>
+      <c r="L18" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M18" s="6" t="s">
+        <v>885</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>13</v>
+      </c>
+      <c r="B19" t="s">
+        <v>275</v>
+      </c>
+      <c r="C19">
+        <v>288</v>
+      </c>
+      <c r="D19" s="30" t="s">
+        <v>511</v>
+      </c>
+      <c r="E19" s="33" t="s">
+        <v>266</v>
+      </c>
+      <c r="F19" t="s">
+        <v>931</v>
+      </c>
+      <c r="G19" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H19" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="I19" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="J19" s="6" t="s">
+        <v>871</v>
+      </c>
+      <c r="L19" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M19" s="6" t="s">
+        <v>886</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>13</v>
+      </c>
+      <c r="B20" t="s">
+        <v>275</v>
+      </c>
+      <c r="C20">
+        <v>289</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>855</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>912</v>
+      </c>
+      <c r="F20" t="s">
+        <v>942</v>
+      </c>
+      <c r="G20" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="H20" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="I20" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="J20" s="6" t="s">
+        <v>871</v>
+      </c>
+      <c r="L20" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M20" s="6" t="s">
+        <v>887</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>13</v>
+      </c>
+      <c r="B21" t="s">
+        <v>275</v>
+      </c>
+      <c r="C21">
+        <v>290</v>
+      </c>
+      <c r="D21" s="17" t="s">
+        <v>856</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>912</v>
+      </c>
+      <c r="F21" t="s">
+        <v>943</v>
+      </c>
+      <c r="G21" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H21" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="I21" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="J21" s="6" t="s">
+        <v>871</v>
+      </c>
+      <c r="L21" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M21" s="6" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>13</v>
+      </c>
+      <c r="B22" t="s">
+        <v>275</v>
+      </c>
+      <c r="C22">
+        <v>291</v>
+      </c>
+      <c r="D22" s="17" t="s">
+        <v>265</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>912</v>
+      </c>
+      <c r="F22" t="s">
+        <v>944</v>
+      </c>
+      <c r="G22" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H22" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="I22" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="J22" s="6" t="s">
+        <v>871</v>
+      </c>
+      <c r="L22" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M22" s="6" t="s">
+        <v>889</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>13</v>
+      </c>
+      <c r="B23" t="s">
+        <v>275</v>
+      </c>
+      <c r="C23">
+        <v>292</v>
+      </c>
+      <c r="D23" s="17" t="s">
+        <v>857</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>912</v>
+      </c>
+      <c r="F23" t="s">
+        <v>945</v>
+      </c>
+      <c r="G23" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H23" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="I23" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="J23" s="6" t="s">
+        <v>871</v>
+      </c>
+      <c r="L23" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M23" s="6" t="s">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>13</v>
+      </c>
+      <c r="B24" t="s">
+        <v>275</v>
+      </c>
+      <c r="C24">
+        <v>293</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>858</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>912</v>
+      </c>
+      <c r="F24" t="s">
+        <v>946</v>
+      </c>
+      <c r="G24" s="6" t="s">
+        <v>564</v>
+      </c>
+      <c r="H24" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="I24" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="J24" s="6" t="s">
+        <v>871</v>
+      </c>
+      <c r="L24" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M24" s="6" t="s">
+        <v>891</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>13</v>
+      </c>
+      <c r="B25" t="s">
+        <v>275</v>
+      </c>
+      <c r="C25">
+        <v>294</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>859</v>
+      </c>
+      <c r="E25" s="6" t="s">
+        <v>912</v>
+      </c>
+      <c r="F25" t="s">
+        <v>947</v>
+      </c>
+      <c r="G25" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H25" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="I25" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="J25" s="6" t="s">
+        <v>871</v>
+      </c>
+      <c r="L25" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M25" s="6" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>13</v>
+      </c>
+      <c r="B26" t="s">
+        <v>275</v>
+      </c>
+      <c r="C26">
+        <v>295</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>860</v>
+      </c>
+      <c r="E26" s="6" t="s">
+        <v>912</v>
+      </c>
+      <c r="F26" t="s">
+        <v>948</v>
+      </c>
+      <c r="G26" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H26" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="I26" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="J26" s="6" t="s">
+        <v>871</v>
+      </c>
+      <c r="L26" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M26" s="6" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>13</v>
+      </c>
+      <c r="B27" t="s">
+        <v>275</v>
+      </c>
+      <c r="C27">
+        <v>296</v>
+      </c>
+      <c r="D27" s="17" t="s">
+        <v>269</v>
+      </c>
+      <c r="E27" s="33" t="s">
+        <v>266</v>
+      </c>
+      <c r="F27" t="s">
+        <v>932</v>
+      </c>
+      <c r="G27" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H27" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="I27" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="J27" s="6" t="s">
+        <v>871</v>
+      </c>
+      <c r="L27" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M27" s="6" t="s">
+        <v>894</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
+        <v>13</v>
+      </c>
+      <c r="B28" t="s">
+        <v>275</v>
+      </c>
+      <c r="C28">
+        <v>297</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>861</v>
+      </c>
+      <c r="E28" s="33" t="s">
+        <v>266</v>
+      </c>
+      <c r="F28" t="s">
+        <v>933</v>
+      </c>
+      <c r="G28" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H28" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="I28" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="J28" s="6" t="s">
+        <v>871</v>
+      </c>
+      <c r="L28" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M28" s="6" t="s">
+        <v>895</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
+        <v>13</v>
+      </c>
+      <c r="B29" t="s">
+        <v>275</v>
+      </c>
+      <c r="C29">
+        <v>298</v>
+      </c>
+      <c r="D29" s="6" t="s">
+        <v>862</v>
+      </c>
+      <c r="E29" s="33" t="s">
+        <v>266</v>
+      </c>
+      <c r="F29" t="s">
+        <v>934</v>
+      </c>
+      <c r="G29" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H29" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="I29" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="J29" s="6" t="s">
+        <v>871</v>
+      </c>
+      <c r="L29" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M29" s="6" t="s">
+        <v>896</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
+        <v>13</v>
+      </c>
+      <c r="B30" t="s">
+        <v>275</v>
+      </c>
+      <c r="C30">
+        <v>299</v>
+      </c>
+      <c r="D30" s="6" t="s">
+        <v>863</v>
+      </c>
+      <c r="E30" s="33" t="s">
+        <v>266</v>
+      </c>
+      <c r="F30" t="s">
+        <v>935</v>
+      </c>
+      <c r="G30" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H30" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="I30" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="J30" s="6" t="s">
+        <v>871</v>
+      </c>
+      <c r="L30" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M30" s="6" t="s">
+        <v>897</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>13</v>
+      </c>
+      <c r="B31" t="s">
+        <v>275</v>
+      </c>
+      <c r="C31">
+        <v>300</v>
+      </c>
+      <c r="D31" s="17" t="s">
+        <v>864</v>
+      </c>
+      <c r="E31" s="33" t="s">
+        <v>266</v>
+      </c>
+      <c r="F31" t="s">
+        <v>936</v>
+      </c>
+      <c r="G31" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="H31" s="17" t="s">
+        <v>159</v>
+      </c>
+      <c r="I31" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="J31" s="6" t="s">
+        <v>871</v>
+      </c>
+      <c r="L31" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M31" s="17" t="s">
+        <v>898</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
+        <v>13</v>
+      </c>
+      <c r="B32" t="s">
+        <v>275</v>
+      </c>
+      <c r="C32">
+        <v>301</v>
+      </c>
+      <c r="D32" s="6" t="s">
+        <v>865</v>
+      </c>
+      <c r="E32" s="33" t="s">
+        <v>266</v>
+      </c>
+      <c r="F32" t="s">
+        <v>938</v>
+      </c>
+      <c r="G32" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="H32" s="17" t="s">
+        <v>159</v>
+      </c>
+      <c r="I32" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="J32" s="6" t="s">
+        <v>871</v>
+      </c>
+      <c r="L32" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M32" s="6" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>13</v>
+      </c>
+      <c r="B33" t="s">
+        <v>275</v>
+      </c>
+      <c r="C33">
+        <v>302</v>
+      </c>
+      <c r="D33" s="6" t="s">
+        <v>866</v>
+      </c>
+      <c r="E33" s="33" t="s">
+        <v>266</v>
+      </c>
+      <c r="F33" t="s">
+        <v>939</v>
+      </c>
+      <c r="G33" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="H33" s="17" t="s">
+        <v>159</v>
+      </c>
+      <c r="I33" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="J33" s="6" t="s">
+        <v>871</v>
+      </c>
+      <c r="L33" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M33" s="6" t="s">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
+        <v>13</v>
+      </c>
+      <c r="B34" t="s">
+        <v>275</v>
+      </c>
+      <c r="C34">
+        <v>303</v>
+      </c>
+      <c r="D34" s="6" t="s">
+        <v>867</v>
+      </c>
+      <c r="E34" s="33" t="s">
+        <v>266</v>
+      </c>
+      <c r="F34" t="s">
+        <v>915</v>
+      </c>
+      <c r="G34" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="H34" s="17" t="s">
+        <v>159</v>
+      </c>
+      <c r="I34" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="J34" s="6" t="s">
+        <v>871</v>
+      </c>
+      <c r="L34" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M34" s="6" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
+        <v>13</v>
+      </c>
+      <c r="B35" t="s">
+        <v>275</v>
+      </c>
+      <c r="C35">
+        <v>304</v>
+      </c>
+      <c r="D35" s="6" t="s">
+        <v>868</v>
+      </c>
+      <c r="E35" s="33" t="s">
+        <v>266</v>
+      </c>
+      <c r="F35" t="s">
+        <v>940</v>
+      </c>
+      <c r="G35" s="6" t="s">
+        <v>564</v>
+      </c>
+      <c r="H35" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="I35" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="J35" s="6" t="s">
+        <v>871</v>
+      </c>
+      <c r="L35" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M35" s="6" t="s">
+        <v>902</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
+        <v>13</v>
+      </c>
+      <c r="B36" t="s">
+        <v>275</v>
+      </c>
+      <c r="C36">
+        <v>305</v>
+      </c>
+      <c r="D36" s="6" t="s">
+        <v>869</v>
+      </c>
+      <c r="E36" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F36" t="s">
+        <v>937</v>
+      </c>
+      <c r="G36" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H36" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="I36" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="J36" s="6" t="s">
+        <v>445</v>
+      </c>
+      <c r="L36" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M36" s="6" t="s">
+        <v>903</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A37" t="s">
+        <v>13</v>
+      </c>
+      <c r="B37" t="s">
+        <v>275</v>
+      </c>
+      <c r="C37">
+        <v>306</v>
+      </c>
+      <c r="D37" s="6" t="s">
+        <v>870</v>
+      </c>
+      <c r="E37" s="33" t="s">
+        <v>266</v>
+      </c>
+      <c r="F37" t="s">
+        <v>941</v>
+      </c>
+      <c r="G37" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="H37" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="I37" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="J37" s="6" t="s">
+        <v>871</v>
+      </c>
+      <c r="L37" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M37" s="6" t="s">
+        <v>904</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7A22D2F-6AFE-4D3D-A8D1-BBD797E61616}">
+  <dimension ref="A1:M24"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="4" max="4" width="37.90625" customWidth="1"/>
+    <col min="5" max="5" width="15.90625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="43.26953125" customWidth="1"/>
+    <col min="7" max="7" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.90625" customWidth="1"/>
+    <col min="9" max="9" width="16.6328125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.26953125" customWidth="1"/>
+    <col min="12" max="12" width="13.1796875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="49.90625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="C2">
+        <v>307</v>
+      </c>
+      <c r="D2" s="34" t="s">
+        <v>949</v>
+      </c>
+      <c r="E2" s="36" t="s">
+        <v>996</v>
+      </c>
+      <c r="F2" t="s">
+        <v>997</v>
+      </c>
+      <c r="G2" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="H2" s="37" t="s">
+        <v>215</v>
+      </c>
+      <c r="I2" s="36" t="s">
+        <v>20</v>
+      </c>
+      <c r="M2" s="34" t="s">
+        <v>973</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="C3">
+        <v>308</v>
+      </c>
+      <c r="D3" s="35" t="s">
+        <v>950</v>
+      </c>
+      <c r="E3" s="38" t="s">
+        <v>996</v>
+      </c>
+      <c r="F3" t="s">
+        <v>998</v>
+      </c>
+      <c r="G3" s="38" t="s">
+        <v>18</v>
+      </c>
+      <c r="H3" s="39" t="s">
+        <v>143</v>
+      </c>
+      <c r="I3" s="38" t="s">
+        <v>20</v>
+      </c>
+      <c r="M3" s="35" t="s">
+        <v>974</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="C4">
+        <v>309</v>
+      </c>
+      <c r="D4" s="34" t="s">
+        <v>951</v>
+      </c>
+      <c r="E4" s="36" t="s">
+        <v>996</v>
+      </c>
+      <c r="F4" t="s">
+        <v>999</v>
+      </c>
+      <c r="G4" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="H4" s="37" t="s">
+        <v>215</v>
+      </c>
+      <c r="I4" s="36" t="s">
+        <v>20</v>
+      </c>
+      <c r="M4" s="34" t="s">
+        <v>975</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="C5">
+        <v>310</v>
+      </c>
+      <c r="D5" s="35" t="s">
+        <v>952</v>
+      </c>
+      <c r="E5" s="38" t="s">
+        <v>996</v>
+      </c>
+      <c r="F5" t="s">
+        <v>1000</v>
+      </c>
+      <c r="G5" s="38" t="s">
+        <v>18</v>
+      </c>
+      <c r="H5" s="39" t="s">
+        <v>215</v>
+      </c>
+      <c r="I5" s="38" t="s">
+        <v>20</v>
+      </c>
+      <c r="M5" s="35" t="s">
+        <v>976</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="C6">
+        <v>311</v>
+      </c>
+      <c r="D6" s="34" t="s">
+        <v>953</v>
+      </c>
+      <c r="E6" s="36" t="s">
+        <v>996</v>
+      </c>
+      <c r="F6" t="s">
+        <v>1001</v>
+      </c>
+      <c r="G6" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="H6" s="37" t="s">
+        <v>219</v>
+      </c>
+      <c r="I6" s="36" t="s">
+        <v>20</v>
+      </c>
+      <c r="M6" s="34" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="C7">
+        <v>312</v>
+      </c>
+      <c r="D7" s="35" t="s">
+        <v>954</v>
+      </c>
+      <c r="E7" s="38" t="s">
+        <v>996</v>
+      </c>
+      <c r="F7" t="s">
+        <v>1002</v>
+      </c>
+      <c r="G7" s="38" t="s">
+        <v>18</v>
+      </c>
+      <c r="H7" s="39" t="s">
+        <v>219</v>
+      </c>
+      <c r="I7" s="38" t="s">
+        <v>20</v>
+      </c>
+      <c r="M7" s="35" t="s">
+        <v>978</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="C8">
+        <v>313</v>
+      </c>
+      <c r="D8" s="34" t="s">
+        <v>955</v>
+      </c>
+      <c r="E8" s="36" t="s">
+        <v>996</v>
+      </c>
+      <c r="F8" t="s">
+        <v>1003</v>
+      </c>
+      <c r="G8" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="H8" s="37" t="s">
+        <v>219</v>
+      </c>
+      <c r="I8" s="36" t="s">
+        <v>20</v>
+      </c>
+      <c r="M8" s="34" t="s">
+        <v>979</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="C9">
+        <v>314</v>
+      </c>
+      <c r="D9" s="35" t="s">
+        <v>956</v>
+      </c>
+      <c r="E9" s="38" t="s">
+        <v>996</v>
+      </c>
+      <c r="F9" t="s">
+        <v>1004</v>
+      </c>
+      <c r="G9" s="38" t="s">
+        <v>18</v>
+      </c>
+      <c r="H9" s="39" t="s">
+        <v>316</v>
+      </c>
+      <c r="I9" s="38" t="s">
+        <v>20</v>
+      </c>
+      <c r="M9" s="35" t="s">
+        <v>980</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="C10">
+        <v>315</v>
+      </c>
+      <c r="D10" s="34" t="s">
+        <v>957</v>
+      </c>
+      <c r="E10" s="36" t="s">
+        <v>996</v>
+      </c>
+      <c r="F10" t="s">
+        <v>1005</v>
+      </c>
+      <c r="G10" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="H10" s="37" t="s">
+        <v>143</v>
+      </c>
+      <c r="I10" s="36" t="s">
+        <v>20</v>
+      </c>
+      <c r="M10" s="34" t="s">
+        <v>981</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="C11">
+        <v>316</v>
+      </c>
+      <c r="D11" s="35" t="s">
+        <v>958</v>
+      </c>
+      <c r="E11" s="38" t="s">
+        <v>996</v>
+      </c>
+      <c r="F11" t="s">
+        <v>1006</v>
+      </c>
+      <c r="G11" s="38" t="s">
+        <v>18</v>
+      </c>
+      <c r="H11" s="39" t="s">
+        <v>215</v>
+      </c>
+      <c r="I11" s="38" t="s">
+        <v>20</v>
+      </c>
+      <c r="M11" s="35" t="s">
+        <v>982</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="C12">
+        <v>317</v>
+      </c>
+      <c r="D12" s="34" t="s">
+        <v>959</v>
+      </c>
+      <c r="E12" s="36" t="s">
+        <v>996</v>
+      </c>
+      <c r="F12" t="s">
+        <v>1007</v>
+      </c>
+      <c r="G12" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="H12" s="37" t="s">
+        <v>215</v>
+      </c>
+      <c r="I12" s="36" t="s">
+        <v>20</v>
+      </c>
+      <c r="M12" s="34" t="s">
+        <v>983</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="C13">
+        <v>318</v>
+      </c>
+      <c r="D13" s="35" t="s">
+        <v>960</v>
+      </c>
+      <c r="E13" s="38" t="s">
+        <v>996</v>
+      </c>
+      <c r="F13" t="s">
+        <v>1008</v>
+      </c>
+      <c r="G13" s="38" t="s">
+        <v>18</v>
+      </c>
+      <c r="H13" s="39" t="s">
+        <v>215</v>
+      </c>
+      <c r="I13" s="38" t="s">
+        <v>20</v>
+      </c>
+      <c r="M13" s="35" t="s">
+        <v>984</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="C14">
+        <v>319</v>
+      </c>
+      <c r="D14" s="34" t="s">
+        <v>961</v>
+      </c>
+      <c r="E14" s="36" t="s">
+        <v>996</v>
+      </c>
+      <c r="F14" t="s">
+        <v>1009</v>
+      </c>
+      <c r="G14" s="36" t="s">
+        <v>30</v>
+      </c>
+      <c r="H14" s="37" t="s">
+        <v>215</v>
+      </c>
+      <c r="I14" s="36" t="s">
+        <v>144</v>
+      </c>
+      <c r="M14" s="34" t="s">
+        <v>985</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="C15">
+        <v>320</v>
+      </c>
+      <c r="D15" s="35" t="s">
+        <v>288</v>
+      </c>
+      <c r="E15" s="38" t="s">
+        <v>996</v>
+      </c>
+      <c r="F15" t="s">
+        <v>1010</v>
+      </c>
+      <c r="G15" s="38" t="s">
+        <v>564</v>
+      </c>
+      <c r="H15" s="39" t="s">
+        <v>971</v>
+      </c>
+      <c r="I15" s="38" t="s">
+        <v>20</v>
+      </c>
+      <c r="M15" s="35" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="C16">
+        <v>321</v>
+      </c>
+      <c r="D16" s="34" t="s">
+        <v>962</v>
+      </c>
+      <c r="E16" s="36" t="s">
+        <v>996</v>
+      </c>
+      <c r="F16" t="s">
+        <v>1011</v>
+      </c>
+      <c r="G16" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="H16" s="37" t="s">
+        <v>215</v>
+      </c>
+      <c r="I16" s="36" t="s">
+        <v>20</v>
+      </c>
+      <c r="M16" s="34" t="s">
+        <v>987</v>
+      </c>
+    </row>
+    <row r="17" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="C17">
+        <v>322</v>
+      </c>
+      <c r="D17" s="35" t="s">
+        <v>963</v>
+      </c>
+      <c r="E17" s="38" t="s">
+        <v>996</v>
+      </c>
+      <c r="F17" t="s">
+        <v>1012</v>
+      </c>
+      <c r="G17" s="38" t="s">
+        <v>30</v>
+      </c>
+      <c r="H17" s="39" t="s">
+        <v>215</v>
+      </c>
+      <c r="I17" s="38" t="s">
+        <v>144</v>
+      </c>
+      <c r="M17" s="35" t="s">
+        <v>988</v>
+      </c>
+    </row>
+    <row r="18" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="C18">
+        <v>323</v>
+      </c>
+      <c r="D18" s="34" t="s">
+        <v>964</v>
+      </c>
+      <c r="E18" s="36" t="s">
+        <v>996</v>
+      </c>
+      <c r="F18" t="s">
+        <v>1013</v>
+      </c>
+      <c r="G18" s="38" t="s">
+        <v>30</v>
+      </c>
+      <c r="H18" s="37" t="s">
+        <v>972</v>
+      </c>
+      <c r="I18" s="36" t="s">
+        <v>144</v>
+      </c>
+      <c r="M18" s="34" t="s">
+        <v>989</v>
+      </c>
+    </row>
+    <row r="19" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="C19">
+        <v>324</v>
+      </c>
+      <c r="D19" s="35" t="s">
+        <v>965</v>
+      </c>
+      <c r="E19" s="38" t="s">
+        <v>996</v>
+      </c>
+      <c r="F19" t="s">
+        <v>1014</v>
+      </c>
+      <c r="G19" s="38" t="s">
+        <v>30</v>
+      </c>
+      <c r="H19" s="39" t="s">
+        <v>150</v>
+      </c>
+      <c r="I19" s="38" t="s">
+        <v>144</v>
+      </c>
+      <c r="M19" s="35" t="s">
+        <v>990</v>
+      </c>
+    </row>
+    <row r="20" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="C20">
+        <v>325</v>
+      </c>
+      <c r="D20" s="34" t="s">
+        <v>966</v>
+      </c>
+      <c r="E20" s="36" t="s">
+        <v>996</v>
+      </c>
+      <c r="F20" t="s">
+        <v>1015</v>
+      </c>
+      <c r="G20" s="38" t="s">
+        <v>30</v>
+      </c>
+      <c r="H20" s="37" t="s">
+        <v>215</v>
+      </c>
+      <c r="I20" s="36" t="s">
+        <v>144</v>
+      </c>
+      <c r="M20" s="34" t="s">
+        <v>991</v>
+      </c>
+    </row>
+    <row r="21" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="C21">
+        <v>326</v>
+      </c>
+      <c r="D21" s="35" t="s">
+        <v>967</v>
+      </c>
+      <c r="E21" s="38" t="s">
+        <v>996</v>
+      </c>
+      <c r="F21" t="s">
+        <v>1016</v>
+      </c>
+      <c r="G21" s="38" t="s">
+        <v>30</v>
+      </c>
+      <c r="H21" s="39" t="s">
+        <v>316</v>
+      </c>
+      <c r="I21" s="38" t="s">
+        <v>144</v>
+      </c>
+      <c r="M21" s="35" t="s">
+        <v>992</v>
+      </c>
+    </row>
+    <row r="22" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="C22">
+        <v>327</v>
+      </c>
+      <c r="D22" s="34" t="s">
+        <v>968</v>
+      </c>
+      <c r="E22" s="36" t="s">
+        <v>996</v>
+      </c>
+      <c r="F22" t="s">
+        <v>1017</v>
+      </c>
+      <c r="G22" s="38" t="s">
+        <v>30</v>
+      </c>
+      <c r="H22" s="37" t="s">
+        <v>316</v>
+      </c>
+      <c r="I22" s="36" t="s">
+        <v>144</v>
+      </c>
+      <c r="M22" s="34" t="s">
+        <v>993</v>
+      </c>
+    </row>
+    <row r="23" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="C23">
+        <v>328</v>
+      </c>
+      <c r="D23" s="35" t="s">
+        <v>969</v>
+      </c>
+      <c r="E23" s="38" t="s">
+        <v>996</v>
+      </c>
+      <c r="F23" t="s">
+        <v>1018</v>
+      </c>
+      <c r="G23" s="38" t="s">
+        <v>30</v>
+      </c>
+      <c r="H23" s="39" t="s">
+        <v>316</v>
+      </c>
+      <c r="I23" s="38" t="s">
+        <v>144</v>
+      </c>
+      <c r="M23" s="35" t="s">
+        <v>994</v>
+      </c>
+    </row>
+    <row r="24" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="C24">
+        <v>329</v>
+      </c>
+      <c r="D24" s="34" t="s">
+        <v>970</v>
+      </c>
+      <c r="E24" s="36" t="s">
+        <v>996</v>
+      </c>
+      <c r="F24" t="s">
+        <v>1019</v>
+      </c>
+      <c r="G24" s="38" t="s">
+        <v>30</v>
+      </c>
+      <c r="H24" s="37" t="s">
+        <v>143</v>
+      </c>
+      <c r="I24" s="36" t="s">
+        <v>144</v>
+      </c>
+      <c r="M24" s="34" t="s">
+        <v>995</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/docs/CDOP_SCHEMA.xlsx
+++ b/docs/CDOP_SCHEMA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rockmtnins-my.sharepoint.com/personal/sebastian_weeks_rmi_org/Documents/Documents/CDOP Resources/UseCase_Category CSVs_JSONs/Master Version/Round 2 Pods for Testing/Fast Track Pods/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="472" documentId="8_{E4888AF0-8469-49B9-BF1F-D7429471A122}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{805E69B9-42B6-4388-969F-9DB549C29CA3}"/>
+  <xr:revisionPtr revIDLastSave="473" documentId="8_{E4888AF0-8469-49B9-BF1F-D7429471A122}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{39F6345D-2B03-42F2-B361-04542480C060}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="3" xr2:uid="{743398AF-A4FE-47C4-9368-972E95242EBF}"/>
+    <workbookView xWindow="-180" yWindow="760" windowWidth="19380" windowHeight="10570" firstSheet="12" activeTab="13" xr2:uid="{743398AF-A4FE-47C4-9368-972E95242EBF}"/>
   </bookViews>
   <sheets>
     <sheet name="Full List" sheetId="5" r:id="rId1"/>
@@ -2887,9 +2887,6 @@
     <t>validation.lca[].lca_system_boundary_overview</t>
   </si>
   <si>
-    <t>validation.validation_event[].validation _id</t>
-  </si>
-  <si>
     <t>validation.validation_event[].validation_type</t>
   </si>
   <si>
@@ -3155,6 +3152,9 @@
   </si>
   <si>
     <t>verification.verification_audit_checkpoint_status</t>
+  </si>
+  <si>
+    <t>validation.validation_event[].validation_id</t>
   </si>
 </sst>
 </file>
@@ -18490,7 +18490,7 @@
         <v>266</v>
       </c>
       <c r="F18" t="s">
-        <v>930</v>
+        <v>1019</v>
       </c>
       <c r="G18" s="6" t="s">
         <v>18</v>
@@ -18528,7 +18528,7 @@
         <v>266</v>
       </c>
       <c r="F19" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="G19" s="6" t="s">
         <v>18</v>
@@ -18566,7 +18566,7 @@
         <v>912</v>
       </c>
       <c r="F20" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="G20" s="17" t="s">
         <v>30</v>
@@ -18604,7 +18604,7 @@
         <v>912</v>
       </c>
       <c r="F21" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="G21" s="6" t="s">
         <v>18</v>
@@ -18642,7 +18642,7 @@
         <v>912</v>
       </c>
       <c r="F22" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="G22" s="6" t="s">
         <v>18</v>
@@ -18680,7 +18680,7 @@
         <v>912</v>
       </c>
       <c r="F23" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="G23" s="6" t="s">
         <v>18</v>
@@ -18718,7 +18718,7 @@
         <v>912</v>
       </c>
       <c r="F24" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="G24" s="6" t="s">
         <v>564</v>
@@ -18756,7 +18756,7 @@
         <v>912</v>
       </c>
       <c r="F25" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="G25" s="6" t="s">
         <v>18</v>
@@ -18794,7 +18794,7 @@
         <v>912</v>
       </c>
       <c r="F26" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="G26" s="6" t="s">
         <v>18</v>
@@ -18832,7 +18832,7 @@
         <v>266</v>
       </c>
       <c r="F27" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="G27" s="6" t="s">
         <v>18</v>
@@ -18870,7 +18870,7 @@
         <v>266</v>
       </c>
       <c r="F28" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="G28" s="6" t="s">
         <v>18</v>
@@ -18908,7 +18908,7 @@
         <v>266</v>
       </c>
       <c r="F29" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="G29" s="6" t="s">
         <v>18</v>
@@ -18946,7 +18946,7 @@
         <v>266</v>
       </c>
       <c r="F30" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="G30" s="6" t="s">
         <v>18</v>
@@ -18984,7 +18984,7 @@
         <v>266</v>
       </c>
       <c r="F31" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="G31" s="17" t="s">
         <v>30</v>
@@ -19022,7 +19022,7 @@
         <v>266</v>
       </c>
       <c r="F32" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="G32" s="17" t="s">
         <v>30</v>
@@ -19060,7 +19060,7 @@
         <v>266</v>
       </c>
       <c r="F33" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="G33" s="17" t="s">
         <v>30</v>
@@ -19136,7 +19136,7 @@
         <v>266</v>
       </c>
       <c r="F35" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="G35" s="6" t="s">
         <v>564</v>
@@ -19174,7 +19174,7 @@
         <v>16</v>
       </c>
       <c r="F36" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="G36" s="6" t="s">
         <v>18</v>
@@ -19212,7 +19212,7 @@
         <v>266</v>
       </c>
       <c r="F37" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="G37" s="17" t="s">
         <v>30</v>
@@ -19301,13 +19301,13 @@
         <v>307</v>
       </c>
       <c r="D2" s="34" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="E2" s="36" t="s">
+        <v>995</v>
+      </c>
+      <c r="F2" t="s">
         <v>996</v>
-      </c>
-      <c r="F2" t="s">
-        <v>997</v>
       </c>
       <c r="G2" s="36" t="s">
         <v>18</v>
@@ -19319,7 +19319,7 @@
         <v>20</v>
       </c>
       <c r="M2" s="34" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.35">
@@ -19327,13 +19327,13 @@
         <v>308</v>
       </c>
       <c r="D3" s="35" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="E3" s="38" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="F3" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="G3" s="38" t="s">
         <v>18</v>
@@ -19345,7 +19345,7 @@
         <v>20</v>
       </c>
       <c r="M3" s="35" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.35">
@@ -19353,13 +19353,13 @@
         <v>309</v>
       </c>
       <c r="D4" s="34" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="E4" s="36" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="F4" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="G4" s="36" t="s">
         <v>18</v>
@@ -19371,7 +19371,7 @@
         <v>20</v>
       </c>
       <c r="M4" s="34" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.35">
@@ -19379,13 +19379,13 @@
         <v>310</v>
       </c>
       <c r="D5" s="35" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="E5" s="38" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="F5" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="G5" s="38" t="s">
         <v>18</v>
@@ -19397,7 +19397,7 @@
         <v>20</v>
       </c>
       <c r="M5" s="35" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.35">
@@ -19405,13 +19405,13 @@
         <v>311</v>
       </c>
       <c r="D6" s="34" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="E6" s="36" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="F6" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="G6" s="36" t="s">
         <v>18</v>
@@ -19423,7 +19423,7 @@
         <v>20</v>
       </c>
       <c r="M6" s="34" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.35">
@@ -19431,13 +19431,13 @@
         <v>312</v>
       </c>
       <c r="D7" s="35" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="E7" s="38" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="F7" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="G7" s="38" t="s">
         <v>18</v>
@@ -19449,7 +19449,7 @@
         <v>20</v>
       </c>
       <c r="M7" s="35" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.35">
@@ -19457,13 +19457,13 @@
         <v>313</v>
       </c>
       <c r="D8" s="34" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="E8" s="36" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="F8" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="G8" s="36" t="s">
         <v>18</v>
@@ -19475,7 +19475,7 @@
         <v>20</v>
       </c>
       <c r="M8" s="34" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.35">
@@ -19483,13 +19483,13 @@
         <v>314</v>
       </c>
       <c r="D9" s="35" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="E9" s="38" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="F9" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="G9" s="38" t="s">
         <v>18</v>
@@ -19501,7 +19501,7 @@
         <v>20</v>
       </c>
       <c r="M9" s="35" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.35">
@@ -19509,13 +19509,13 @@
         <v>315</v>
       </c>
       <c r="D10" s="34" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="E10" s="36" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="F10" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="G10" s="36" t="s">
         <v>18</v>
@@ -19527,7 +19527,7 @@
         <v>20</v>
       </c>
       <c r="M10" s="34" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.35">
@@ -19535,13 +19535,13 @@
         <v>316</v>
       </c>
       <c r="D11" s="35" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="E11" s="38" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="F11" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="G11" s="38" t="s">
         <v>18</v>
@@ -19553,7 +19553,7 @@
         <v>20</v>
       </c>
       <c r="M11" s="35" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.35">
@@ -19561,13 +19561,13 @@
         <v>317</v>
       </c>
       <c r="D12" s="34" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E12" s="36" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="F12" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="G12" s="36" t="s">
         <v>18</v>
@@ -19579,7 +19579,7 @@
         <v>20</v>
       </c>
       <c r="M12" s="34" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.35">
@@ -19587,13 +19587,13 @@
         <v>318</v>
       </c>
       <c r="D13" s="35" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="E13" s="38" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="F13" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="G13" s="38" t="s">
         <v>18</v>
@@ -19605,7 +19605,7 @@
         <v>20</v>
       </c>
       <c r="M13" s="35" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.35">
@@ -19613,13 +19613,13 @@
         <v>319</v>
       </c>
       <c r="D14" s="34" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="E14" s="36" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="F14" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="G14" s="36" t="s">
         <v>30</v>
@@ -19631,7 +19631,7 @@
         <v>144</v>
       </c>
       <c r="M14" s="34" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.35">
@@ -19642,22 +19642,22 @@
         <v>288</v>
       </c>
       <c r="E15" s="38" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="F15" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="G15" s="38" t="s">
         <v>564</v>
       </c>
       <c r="H15" s="39" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="I15" s="38" t="s">
         <v>20</v>
       </c>
       <c r="M15" s="35" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.35">
@@ -19665,13 +19665,13 @@
         <v>321</v>
       </c>
       <c r="D16" s="34" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="E16" s="36" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="F16" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="G16" s="36" t="s">
         <v>18</v>
@@ -19683,7 +19683,7 @@
         <v>20</v>
       </c>
       <c r="M16" s="34" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
     </row>
     <row r="17" spans="3:13" x14ac:dyDescent="0.35">
@@ -19691,13 +19691,13 @@
         <v>322</v>
       </c>
       <c r="D17" s="35" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="E17" s="38" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="F17" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="G17" s="38" t="s">
         <v>30</v>
@@ -19709,7 +19709,7 @@
         <v>144</v>
       </c>
       <c r="M17" s="35" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
     </row>
     <row r="18" spans="3:13" x14ac:dyDescent="0.35">
@@ -19717,25 +19717,25 @@
         <v>323</v>
       </c>
       <c r="D18" s="34" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="E18" s="36" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="F18" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="G18" s="38" t="s">
         <v>30</v>
       </c>
       <c r="H18" s="37" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="I18" s="36" t="s">
         <v>144</v>
       </c>
       <c r="M18" s="34" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
     </row>
     <row r="19" spans="3:13" x14ac:dyDescent="0.35">
@@ -19743,13 +19743,13 @@
         <v>324</v>
       </c>
       <c r="D19" s="35" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E19" s="38" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="F19" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="G19" s="38" t="s">
         <v>30</v>
@@ -19761,7 +19761,7 @@
         <v>144</v>
       </c>
       <c r="M19" s="35" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
     </row>
     <row r="20" spans="3:13" x14ac:dyDescent="0.35">
@@ -19769,13 +19769,13 @@
         <v>325</v>
       </c>
       <c r="D20" s="34" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="E20" s="36" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="F20" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="G20" s="38" t="s">
         <v>30</v>
@@ -19787,7 +19787,7 @@
         <v>144</v>
       </c>
       <c r="M20" s="34" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
     </row>
     <row r="21" spans="3:13" x14ac:dyDescent="0.35">
@@ -19795,13 +19795,13 @@
         <v>326</v>
       </c>
       <c r="D21" s="35" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="E21" s="38" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="F21" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="G21" s="38" t="s">
         <v>30</v>
@@ -19813,7 +19813,7 @@
         <v>144</v>
       </c>
       <c r="M21" s="35" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
     </row>
     <row r="22" spans="3:13" x14ac:dyDescent="0.35">
@@ -19821,13 +19821,13 @@
         <v>327</v>
       </c>
       <c r="D22" s="34" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="E22" s="36" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="F22" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="G22" s="38" t="s">
         <v>30</v>
@@ -19839,7 +19839,7 @@
         <v>144</v>
       </c>
       <c r="M22" s="34" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
     </row>
     <row r="23" spans="3:13" x14ac:dyDescent="0.35">
@@ -19847,13 +19847,13 @@
         <v>328</v>
       </c>
       <c r="D23" s="35" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="E23" s="38" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="F23" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="G23" s="38" t="s">
         <v>30</v>
@@ -19865,7 +19865,7 @@
         <v>144</v>
       </c>
       <c r="M23" s="35" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
     </row>
     <row r="24" spans="3:13" x14ac:dyDescent="0.35">
@@ -19873,13 +19873,13 @@
         <v>329</v>
       </c>
       <c r="D24" s="34" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="E24" s="36" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="F24" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="G24" s="38" t="s">
         <v>30</v>
@@ -19891,7 +19891,7 @@
         <v>144</v>
       </c>
       <c r="M24" s="34" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
     </row>
   </sheetData>
